--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1716</v>
+        <v>1707</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>85</v>
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>767</v>
+        <v>757</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>14</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>42</v>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>15</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>6</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C14" s="8" t="inlineStr"/>
     </row>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>11</v>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>13</v>
@@ -852,7 +852,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1379</v>
+        <v>1375</v>
       </c>
     </row>
   </sheetData>
@@ -26350,7 +26350,7 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>5 / 1.9 / 0/14</t>
+          <t>3 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -26681,7 +26681,7 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.1 / 0/14</t>
+          <t>3 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -27126,7 +27126,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.2 / 0/14</t>
+          <t>1 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -28085,7 +28085,7 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.9 / 0/14</t>
+          <t>1 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
@@ -28095,7 +28095,7 @@
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.1 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -28757,7 +28757,7 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.6 / 0/14</t>
+          <t>2 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
@@ -28809,7 +28809,7 @@
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
@@ -28967,7 +28967,7 @@
       <c r="B72" s="13" t="inlineStr"/>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
@@ -29075,7 +29075,7 @@
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29113,7 +29113,7 @@
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="I75" s="14" t="inlineStr">
@@ -29250,7 +29250,7 @@
       <c r="D79" s="14" t="inlineStr"/>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>9 / 5.6 / 5/14</t>
+          <t>11 / 5.7 / 5/14</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$198</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$312</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$307</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1649</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>270</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1800</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1707</v>
+        <v>1701</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1112</v>
+        <v>1098</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>969</v>
+        <v>927</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>709</v>
+        <v>728</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>14</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>616</v>
+        <v>634</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -749,36 +749,36 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>548</v>
+        <v>613</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Insurance &amp; Superannuation</t>
+          <t>Banking &amp; Financial Services</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Banking &amp; Financial Services</t>
+          <t>Insurance &amp; Superannuation</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>6</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C14" s="8" t="inlineStr"/>
     </row>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>11</v>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>13</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1375</v>
+        <v>1390</v>
       </c>
     </row>
   </sheetData>
@@ -8310,7 +8310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O312"/>
+  <dimension ref="A1:O307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>1</v>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>0</v>
@@ -9005,7 +9005,7 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>1</v>
@@ -9016,7 +9016,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>0</v>
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>1</v>
@@ -9071,7 +9071,7 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0</v>
@@ -9161,27 +9161,27 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Chelmsford</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>/nottingham/jobs</t>
+          <t>/chelmsford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0</v>
@@ -9190,16 +9190,16 @@
         <v>0</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>0</v>
@@ -9216,12 +9216,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chelmsford</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
@@ -9232,11 +9232,11 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>/chelmsford/service-administrator-jobs</t>
+          <t>/edinburgh/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0</v>
@@ -9245,10 +9245,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>0</v>
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -9287,11 +9287,11 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>/edinburgh/service-administrator-jobs</t>
+          <t>/nottingham/jobs</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0</v>
@@ -9309,7 +9309,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>0</v>
@@ -9335,7 +9335,7 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>1</v>
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
@@ -10261,12 +10261,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>/cambridge/service-administrator-jobs</t>
+          <t>/cardiff/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
@@ -10316,12 +10316,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -10332,11 +10332,11 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>/cardiff/service-administrator-jobs</t>
+          <t>/chester/jobs</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H37" s="5" t="n">
         <v>0</v>
@@ -10348,7 +10348,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="5" t="n">
         <v>0</v>
@@ -10371,12 +10371,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
@@ -10387,11 +10387,11 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>/chester/jobs</t>
+          <t>/leicester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>0</v>
@@ -10426,12 +10426,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -10442,11 +10442,11 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>/leicester/service-administrator-jobs</t>
+          <t>/norwich/jobs</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H39" s="5" t="n">
         <v>0</v>
@@ -10455,7 +10455,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" s="5" t="n">
         <v>0</v>
@@ -10481,12 +10481,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>York</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
@@ -10497,11 +10497,11 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>/norwich/jobs</t>
+          <t>/york/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0</v>
@@ -10510,7 +10510,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -10536,27 +10536,27 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>/york/service-administrator-jobs</t>
+          <t>/altrincham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H41" s="5" t="n">
         <v>0</v>
@@ -10591,12 +10591,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>/altrincham/service-administrator-jobs</t>
+          <t>/bournemouth/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Aylesbury</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>/aylesbury/service-administrator-jobs</t>
+          <t>/bradford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G43" s="5" t="n">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Brighton &amp; Hove</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>/bournemouth/service-administrator-jobs</t>
+          <t>/brighton-hove/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Bradford</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>/bradford/service-administrator-jobs</t>
+          <t>/cambridge/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove</t>
+          <t>Chester Le Street</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>/brighton-hove/service-administrator-jobs</t>
+          <t>/chester-le-street/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chester Le Street</t>
+          <t>Hemel Hempstead</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
@@ -10882,23 +10882,23 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>/chester-le-street/service-administrator-jobs</t>
+          <t>/hemel-hempstead/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="5" t="n">
         <v>0</v>
@@ -10921,12 +10921,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Gloucester</t>
+          <t>Macclesfield</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
@@ -10937,7 +10937,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>/gloucester/service-administrator-jobs</t>
+          <t>/macclesfield/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Hemel Hempstead</t>
+          <t>Northallerton</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
@@ -10992,23 +10992,23 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>/hemel-hempstead/service-administrator-jobs</t>
+          <t>/northallerton/jobs</t>
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="5" t="n">
         <v>0</v>
@@ -11031,12 +11031,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Macclesfield</t>
+          <t>Peterborough</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>/macclesfield/service-administrator-jobs</t>
+          <t>/peterborough/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
@@ -11086,12 +11086,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Northallerton</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
@@ -11102,17 +11102,17 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>/northallerton/jobs</t>
+          <t>/plymouth/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="5" t="n">
         <v>0</v>
@@ -11141,12 +11141,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Peterborough</t>
+          <t>Stoke-on-trent</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>/peterborough/service-administrator-jobs</t>
+          <t>/stoke-on-trent/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
@@ -11196,12 +11196,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
@@ -11212,17 +11212,17 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>/plymouth/service-administrator-jobs</t>
+          <t>/sunderland/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H53" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" s="5" t="n">
         <v>0</v>
@@ -11251,12 +11251,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Stoke-on-trent</t>
+          <t>Warwick</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
@@ -11267,11 +11267,11 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>/stoke-on-trent/service-administrator-jobs</t>
+          <t>/warwick/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0</v>
@@ -11289,7 +11289,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>0</v>
@@ -11306,12 +11306,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Worcester</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>/sunderland/service-administrator-jobs</t>
+          <t>/worcester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
@@ -11361,23 +11361,23 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Warwick</t>
+          <t>Aylesbury</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>/warwick/service-administrator-jobs</t>
+          <t>/aylesbury/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
@@ -11399,7 +11399,7 @@
         <v>0</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" s="3" t="n">
         <v>0</v>
@@ -11416,27 +11416,27 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Worcester</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>/worcester/service-administrator-jobs</t>
+          <t>/barnsley/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57" s="5" t="n">
         <v>0</v>
@@ -11471,12 +11471,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>/barnsley/service-administrator-jobs</t>
+          <t>/durham/jobs</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Gloucester</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>/durham/jobs</t>
+          <t>/gloucester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
@@ -14881,29 +14881,29 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" s="3" t="n">
         <v>0</v>
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Amersham</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -14948,13 +14948,13 @@
       </c>
       <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H125" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J125" s="5" t="n">
         <v>0</v>
@@ -14983,12 +14983,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Amersham</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -15034,12 +15034,12 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Atherstone</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -15050,7 +15050,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H127" s="5" t="n">
         <v>0</v>
@@ -15068,7 +15068,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N127" s="5" t="n">
         <v>0</v>
@@ -15085,12 +15085,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Atherstone</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H128" s="3" t="n">
         <v>0</v>
@@ -15119,7 +15119,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N128" s="3" t="n">
         <v>0</v>
@@ -15136,12 +15136,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Beaminster</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15187,12 +15187,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Beaminster</t>
+          <t>Berwick-upon-tweed</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -15203,13 +15203,13 @@
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H130" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="J130" s="3" t="n">
         <v>0</v>
@@ -15238,12 +15238,12 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Berwick-upon-tweed</t>
+          <t>Bicester</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15254,13 +15254,13 @@
       </c>
       <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H131" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J131" s="5" t="n">
         <v>0</v>
@@ -15289,12 +15289,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Bicester</t>
+          <t>Bracknell</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
@@ -15340,12 +15340,12 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Bracknell</t>
+          <t>Bridgwater</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15391,12 +15391,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Bridgwater</t>
+          <t>Brinsworth</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -15442,12 +15442,12 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Brinsworth</t>
+          <t>Bromsgrove</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15493,12 +15493,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Bromsgrove</t>
+          <t>Canterbury</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>Chatham</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -15595,12 +15595,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Chatham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -15646,12 +15646,12 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Coalville</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15697,12 +15697,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Coalville</t>
+          <t>Cottingham</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
@@ -15748,12 +15748,12 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Cottingham</t>
+          <t>Cramlington</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15764,13 +15764,13 @@
       </c>
       <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H141" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J141" s="5" t="n">
         <v>0</v>
@@ -15799,12 +15799,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Cramlington</t>
+          <t>Crawley</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -15815,13 +15815,13 @@
       </c>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H142" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J142" s="3" t="n">
         <v>0</v>
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Crawley</t>
+          <t>Crewe</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15901,12 +15901,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Crewe</t>
+          <t>Darlington</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -15917,7 +15917,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H144" s="3" t="n">
         <v>0</v>
@@ -15938,7 +15938,7 @@
         <v>0</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O144" s="3" t="n">
         <v>0</v>
@@ -15952,12 +15952,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Darlington</t>
+          <t>Dewsbury</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15968,7 +15968,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H145" s="5" t="n">
         <v>0</v>
@@ -15989,7 +15989,7 @@
         <v>0</v>
       </c>
       <c r="N145" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O145" s="5" t="n">
         <v>0</v>
@@ -16003,12 +16003,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Dewsbury</t>
+          <t>Didcot</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -16054,12 +16054,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Didcot</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -16105,12 +16105,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>East Grinstead</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -16121,10 +16121,10 @@
       </c>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148" s="3" t="n">
         <v>0</v>
@@ -16156,12 +16156,12 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>East Grinstead</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -16207,7 +16207,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Fareham</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -16226,7 +16226,7 @@
         <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>0</v>
@@ -16244,7 +16244,7 @@
         <v>0</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O150" s="3" t="n">
         <v>0</v>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Fareham</t>
+          <t>Farnborough</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -16277,7 +16277,7 @@
         <v>1</v>
       </c>
       <c r="H151" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151" s="5" t="n">
         <v>0</v>
@@ -16295,7 +16295,7 @@
         <v>0</v>
       </c>
       <c r="N151" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O151" s="5" t="n">
         <v>0</v>
@@ -16309,12 +16309,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Farnborough</t>
+          <t>Godalming</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -16328,10 +16328,10 @@
         <v>1</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J152" s="3" t="n">
         <v>0</v>
@@ -16360,12 +16360,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Godalming</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -16376,13 +16376,13 @@
       </c>
       <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H153" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" s="5" t="n">
         <v>0</v>
@@ -16411,12 +16411,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Haywards Heath</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -16427,10 +16427,10 @@
       </c>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>0</v>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Haywards Heath</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -16478,10 +16478,10 @@
       </c>
       <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H155" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I155" s="5" t="n">
         <v>0</v>
@@ -16513,12 +16513,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H156" s="3" t="n">
         <v>0</v>
@@ -16538,7 +16538,7 @@
         <v>0</v>
       </c>
       <c r="J156" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K156" s="3" t="n">
         <v>0</v>
@@ -16564,12 +16564,12 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Huntingdon</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -16615,12 +16615,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Keynsham</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H158" s="3" t="n">
         <v>0</v>
@@ -16640,7 +16640,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" s="3" t="n">
         <v>0</v>
@@ -16666,12 +16666,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Knowle</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -16717,12 +16717,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Keynsham</t>
+          <t>Knutsford</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Knowle</t>
+          <t>Maldon</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -16784,16 +16784,16 @@
       </c>
       <c r="F161" s="4" t="inlineStr"/>
       <c r="G161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H161" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J161" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="K161" s="5" t="n">
         <v>0</v>
@@ -16819,12 +16819,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Knutsford</t>
+          <t>Melksham</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
@@ -16870,12 +16870,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Maldon</t>
+          <t>Newton Abbot</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -16886,16 +16886,16 @@
       </c>
       <c r="F163" s="4" t="inlineStr"/>
       <c r="G163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K163" s="5" t="n">
         <v>0</v>
@@ -16921,12 +16921,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Melksham</t>
+          <t>Newtownards</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
@@ -16937,22 +16937,22 @@
       </c>
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H164" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I164" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J164" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K164" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L164" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="M164" s="3" t="n">
         <v>0</v>
@@ -16972,12 +16972,12 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Newton Abbot</t>
+          <t>Ramsgate</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -16988,13 +16988,13 @@
       </c>
       <c r="F165" s="4" t="inlineStr"/>
       <c r="G165" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H165" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J165" s="5" t="n">
         <v>0</v>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Newtownards</t>
+          <t>Redditch</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H166" s="3" t="n">
         <v>0</v>
@@ -17054,7 +17054,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M166" s="3" t="n">
         <v>0</v>
@@ -17074,12 +17074,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Ramsgate</t>
+          <t>Rickmansworth</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -17125,12 +17125,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Redditch</t>
+          <t>Ringwood</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -17141,10 +17141,10 @@
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I168" s="3" t="n">
         <v>0</v>
@@ -17176,12 +17176,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Rickmansworth</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -17227,12 +17227,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Ringwood</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
@@ -17246,7 +17246,7 @@
         <v>1</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I170" s="3" t="n">
         <v>0</v>
@@ -17261,7 +17261,7 @@
         <v>0</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N170" s="3" t="n">
         <v>0</v>
@@ -17278,12 +17278,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Rochester</t>
+          <t>Stafford</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -17329,12 +17329,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -17380,12 +17380,12 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Stockport</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -17396,7 +17396,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr"/>
       <c r="G173" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H173" s="5" t="n">
         <v>0</v>
@@ -17414,7 +17414,7 @@
         <v>0</v>
       </c>
       <c r="M173" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N173" s="5" t="n">
         <v>0</v>
@@ -17431,12 +17431,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>Stonehouse</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -17447,7 +17447,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H174" s="3" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="K174" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L174" s="3" t="n">
         <v>0</v>
@@ -17482,12 +17482,12 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swindon</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -17498,10 +17498,10 @@
       </c>
       <c r="F175" s="4" t="inlineStr"/>
       <c r="G175" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H175" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I175" s="5" t="n">
         <v>0</v>
@@ -17533,12 +17533,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Stockport</t>
+          <t>Thame</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Stonehouse</t>
+          <t>Truro</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -17600,7 +17600,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr"/>
       <c r="G177" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H177" s="5" t="n">
         <v>0</v>
@@ -17612,7 +17612,7 @@
         <v>0</v>
       </c>
       <c r="K177" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L177" s="5" t="n">
         <v>0</v>
@@ -17635,12 +17635,12 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Swindon</t>
+          <t>Ventnor</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
@@ -17651,10 +17651,10 @@
       </c>
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>0</v>
@@ -17686,12 +17686,12 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Thame</t>
+          <t>Ware</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D179" s="5" t="n">
@@ -17702,13 +17702,13 @@
       </c>
       <c r="F179" s="4" t="inlineStr"/>
       <c r="G179" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H179" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J179" s="5" t="n">
         <v>0</v>
@@ -17737,12 +17737,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Truro</t>
+          <t>Welwyn Garden City</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -17753,7 +17753,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H180" s="3" t="n">
         <v>0</v>
@@ -17765,7 +17765,7 @@
         <v>0</v>
       </c>
       <c r="K180" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L180" s="3" t="n">
         <v>0</v>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Ventnor</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -17804,10 +17804,10 @@
       </c>
       <c r="F181" s="4" t="inlineStr"/>
       <c r="G181" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H181" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I181" s="5" t="n">
         <v>0</v>
@@ -17825,7 +17825,7 @@
         <v>0</v>
       </c>
       <c r="N181" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O181" s="5" t="n">
         <v>0</v>
@@ -17839,12 +17839,12 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Ware</t>
+          <t>Wokingham</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -17855,13 +17855,13 @@
       </c>
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H182" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J182" s="3" t="n">
         <v>0</v>
@@ -17890,12 +17890,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Welwyn Garden City</t>
+          <t>Woodbridge</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -17906,7 +17906,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr"/>
       <c r="G183" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H183" s="5" t="n">
         <v>0</v>
@@ -17918,7 +17918,7 @@
         <v>0</v>
       </c>
       <c r="K183" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L183" s="5" t="n">
         <v>0</v>
@@ -17941,12 +17941,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
@@ -17957,7 +17957,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H184" s="3" t="n">
         <v>0</v>
@@ -17978,7 +17978,7 @@
         <v>0</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O184" s="3" t="n">
         <v>0</v>
@@ -17992,23 +17992,23 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Wokingham</t>
+          <t>Alresford</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E185" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F185" s="4" t="inlineStr"/>
       <c r="G185" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H185" s="5" t="n">
         <v>0</v>
@@ -18043,23 +18043,23 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Woodbridge</t>
+          <t>Ashington</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E186" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H186" s="3" t="n">
         <v>0</v>
@@ -18094,12 +18094,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Aylesford</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
@@ -18145,12 +18145,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Alresford</t>
+          <t>Ballyclare</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
@@ -18196,12 +18196,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Ashington</t>
+          <t>Ballymena</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
@@ -18247,12 +18247,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Aylesford</t>
+          <t>Banbury</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -18298,12 +18298,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Ballyclare</t>
+          <t>Banstead</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
@@ -18349,12 +18349,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Ballymena</t>
+          <t>Bexhill-on-sea</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -18400,12 +18400,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Banbury</t>
+          <t>Billericay</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
@@ -18451,12 +18451,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Banstead</t>
+          <t>Bingley</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -18502,12 +18502,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Bexhill-on-sea</t>
+          <t>Bishop's Stortford</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
@@ -18553,12 +18553,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Billericay</t>
+          <t>Bognor Regis</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -18604,12 +18604,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Bingley</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -18655,12 +18655,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Bishop's Stortford</t>
+          <t>Buckingham</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H198" s="3" t="n">
         <v>0</v>
@@ -18692,7 +18692,7 @@
         <v>0</v>
       </c>
       <c r="N198" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O198" s="3" t="n">
         <v>0</v>
@@ -18706,12 +18706,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Bognor Regis</t>
+          <t>Burford</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -18722,10 +18722,10 @@
       </c>
       <c r="F199" s="4" t="inlineStr"/>
       <c r="G199" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H199" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I199" s="5" t="n">
         <v>0</v>
@@ -18757,12 +18757,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Bury St Edmunds</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -18808,12 +18808,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Buckingham</t>
+          <t>Caerphilly</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr"/>
       <c r="G201" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H201" s="5" t="n">
         <v>0</v>
@@ -18845,7 +18845,7 @@
         <v>0</v>
       </c>
       <c r="N201" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O201" s="5" t="n">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Burford</t>
+          <t>Camberley</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -18875,10 +18875,10 @@
       </c>
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I202" s="3" t="n">
         <v>0</v>
@@ -18910,12 +18910,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Bury St Edmunds</t>
+          <t>Carrickfergus</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Caerphilly</t>
+          <t>Chelmsley Wood</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -19012,12 +19012,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Camberley</t>
+          <t>Cheltenham</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -19063,12 +19063,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Carrickfergus</t>
+          <t>Chesham</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -19114,12 +19114,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Chelmsley Wood</t>
+          <t>Chichester</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -19165,12 +19165,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Cheltenham</t>
+          <t>Chippenham</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -19216,12 +19216,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Chesham</t>
+          <t>Cleethorpes</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -19267,12 +19267,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Chichester</t>
+          <t>Cobham</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -19283,10 +19283,10 @@
       </c>
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>0</v>
@@ -19318,12 +19318,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Chippenham</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr"/>
       <c r="G211" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H211" s="5" t="n">
         <v>0</v>
@@ -19343,7 +19343,7 @@
         <v>0</v>
       </c>
       <c r="J211" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K211" s="5" t="n">
         <v>0</v>
@@ -19369,12 +19369,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Cleethorpes</t>
+          <t>Colden Common</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -19385,7 +19385,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
         <v>0</v>
@@ -19406,7 +19406,7 @@
         <v>0</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O212" s="3" t="n">
         <v>0</v>
@@ -19420,12 +19420,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Cobham</t>
+          <t>Congleton</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
@@ -19436,10 +19436,10 @@
       </c>
       <c r="F213" s="4" t="inlineStr"/>
       <c r="G213" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H213" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I213" s="5" t="n">
         <v>0</v>
@@ -19471,12 +19471,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>Devizes</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr"/>
       <c r="G214" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H214" s="3" t="n">
         <v>0</v>
@@ -19496,7 +19496,7 @@
         <v>0</v>
       </c>
       <c r="J214" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K214" s="3" t="n">
         <v>0</v>
@@ -19522,12 +19522,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Colden Common</t>
+          <t>Dorchester</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
@@ -19538,7 +19538,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr"/>
       <c r="G215" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H215" s="5" t="n">
         <v>0</v>
@@ -19559,7 +19559,7 @@
         <v>0</v>
       </c>
       <c r="N215" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O215" s="5" t="n">
         <v>0</v>
@@ -19573,12 +19573,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Congleton</t>
+          <t>Dorking</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -19624,12 +19624,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Devizes</t>
+          <t>Dursley</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Dorchester</t>
+          <t>Eastbourne</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
@@ -19691,10 +19691,10 @@
       </c>
       <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I218" s="3" t="n">
         <v>0</v>
@@ -19726,12 +19726,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Dorking</t>
+          <t>Ellesmere Port</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Dursley</t>
+          <t>Ely</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
@@ -19828,12 +19828,12 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Eastbourne</t>
+          <t>Epsom</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
@@ -19847,7 +19847,7 @@
         <v>0</v>
       </c>
       <c r="H221" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I221" s="5" t="n">
         <v>0</v>
@@ -19856,7 +19856,7 @@
         <v>0</v>
       </c>
       <c r="K221" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L221" s="5" t="n">
         <v>0</v>
@@ -19879,12 +19879,12 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Ellesmere Port</t>
+          <t>Esher</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
@@ -19895,13 +19895,13 @@
       </c>
       <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J222" s="3" t="n">
         <v>0</v>
@@ -19930,12 +19930,12 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Ely</t>
+          <t>Felixstowe</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
@@ -19981,7 +19981,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Epsom</t>
+          <t>Fetcham</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -20009,7 +20009,7 @@
         <v>0</v>
       </c>
       <c r="K224" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L224" s="3" t="n">
         <v>0</v>
@@ -20018,7 +20018,7 @@
         <v>0</v>
       </c>
       <c r="N224" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O224" s="3" t="n">
         <v>0</v>
@@ -20032,12 +20032,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Esher</t>
+          <t>Freshwater</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D225" s="5" t="n">
@@ -20051,10 +20051,10 @@
         <v>0</v>
       </c>
       <c r="H225" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J225" s="5" t="n">
         <v>0</v>
@@ -20083,12 +20083,12 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Felixstowe</t>
+          <t>Gainsborough</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Fetcham</t>
+          <t>Godstone</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
@@ -20150,7 +20150,7 @@
       </c>
       <c r="F227" s="4" t="inlineStr"/>
       <c r="G227" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H227" s="5" t="n">
         <v>0</v>
@@ -20171,7 +20171,7 @@
         <v>0</v>
       </c>
       <c r="N227" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O227" s="5" t="n">
         <v>0</v>
@@ -20185,12 +20185,12 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Freshwater</t>
+          <t>Goole</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
@@ -20201,10 +20201,10 @@
       </c>
       <c r="F228" s="2" t="inlineStr"/>
       <c r="G228" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I228" s="3" t="n">
         <v>0</v>
@@ -20236,12 +20236,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Gainsborough</t>
+          <t>Grange-over-sands</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
@@ -20252,10 +20252,10 @@
       </c>
       <c r="F229" s="4" t="inlineStr"/>
       <c r="G229" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H229" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I229" s="5" t="n">
         <v>0</v>
@@ -20287,12 +20287,12 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Godstone</t>
+          <t>Grantham</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
@@ -20338,12 +20338,12 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Goole</t>
+          <t>Gravesend</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
@@ -20354,10 +20354,10 @@
       </c>
       <c r="F231" s="4" t="inlineStr"/>
       <c r="G231" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H231" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I231" s="5" t="n">
         <v>0</v>
@@ -20389,12 +20389,12 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Grange-over-sands</t>
+          <t>Hailsham</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
@@ -20408,10 +20408,10 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J232" s="3" t="n">
         <v>0</v>
@@ -20440,12 +20440,12 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Grantham</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D233" s="5" t="n">
@@ -20456,10 +20456,10 @@
       </c>
       <c r="F233" s="4" t="inlineStr"/>
       <c r="G233" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H233" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I233" s="5" t="n">
         <v>0</v>
@@ -20491,12 +20491,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Gravesend</t>
+          <t>Harrogate</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
@@ -20507,10 +20507,10 @@
       </c>
       <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I234" s="3" t="n">
         <v>0</v>
@@ -20542,12 +20542,12 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Hailsham</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
@@ -20558,13 +20558,13 @@
       </c>
       <c r="F235" s="4" t="inlineStr"/>
       <c r="G235" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H235" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J235" s="5" t="n">
         <v>0</v>
@@ -20593,12 +20593,12 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
@@ -20644,12 +20644,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Harrogate</t>
+          <t>Hebburn</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="F237" s="4" t="inlineStr"/>
       <c r="G237" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H237" s="5" t="n">
         <v>0</v>
@@ -20681,7 +20681,7 @@
         <v>0</v>
       </c>
       <c r="N237" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O237" s="5" t="n">
         <v>0</v>
@@ -20695,12 +20695,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>Henley-on-thames</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
@@ -20746,12 +20746,12 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Hertford</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
@@ -20762,10 +20762,10 @@
       </c>
       <c r="F239" s="4" t="inlineStr"/>
       <c r="G239" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H239" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I239" s="5" t="n">
         <v>0</v>
@@ -20797,12 +20797,12 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Hebburn</t>
+          <t>Huntingdon</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr"/>
       <c r="G240" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H240" s="3" t="n">
         <v>0</v>
@@ -20834,7 +20834,7 @@
         <v>0</v>
       </c>
       <c r="N240" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O240" s="3" t="n">
         <v>0</v>
@@ -20848,12 +20848,12 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Henley-on-thames</t>
+          <t>Ilminster</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D241" s="5" t="n">
@@ -20899,12 +20899,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Hertford</t>
+          <t>Jarrow</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
@@ -20950,12 +20950,12 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Ilminster</t>
+          <t>Kendal</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
@@ -20966,10 +20966,10 @@
       </c>
       <c r="F243" s="4" t="inlineStr"/>
       <c r="G243" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H243" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I243" s="5" t="n">
         <v>0</v>
@@ -21001,12 +21001,12 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Jarrow</t>
+          <t>Kirriemuir</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
@@ -21052,12 +21052,12 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Kendal</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
@@ -21068,10 +21068,10 @@
       </c>
       <c r="F245" s="4" t="inlineStr"/>
       <c r="G245" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H245" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I245" s="5" t="n">
         <v>0</v>
@@ -21103,12 +21103,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Kirriemuir</t>
+          <t>Leighton Buzzard</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Lichfield</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
@@ -21170,7 +21170,7 @@
       </c>
       <c r="F247" s="4" t="inlineStr"/>
       <c r="G247" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H247" s="5" t="n">
         <v>0</v>
@@ -21191,7 +21191,7 @@
         <v>0</v>
       </c>
       <c r="N247" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O247" s="5" t="n">
         <v>0</v>
@@ -21205,12 +21205,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Leatherhead</t>
+          <t>Liskeard</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
@@ -21256,12 +21256,12 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Leighton Buzzard</t>
+          <t>Littlehampton</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
@@ -21307,12 +21307,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Lichfield</t>
+          <t>Loughborough</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
@@ -21323,7 +21323,7 @@
       </c>
       <c r="F250" s="2" t="inlineStr"/>
       <c r="G250" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H250" s="3" t="n">
         <v>0</v>
@@ -21344,7 +21344,7 @@
         <v>0</v>
       </c>
       <c r="N250" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O250" s="3" t="n">
         <v>0</v>
@@ -21358,12 +21358,12 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Liskeard</t>
+          <t>Marlborough</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
@@ -21409,12 +21409,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Littlehampton</t>
+          <t>Marlow</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
@@ -21460,12 +21460,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Loughborough</t>
+          <t>Mirfield</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
@@ -21511,12 +21511,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Luton</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
@@ -21527,13 +21527,13 @@
       </c>
       <c r="F254" s="2" t="inlineStr"/>
       <c r="G254" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I254" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J254" s="3" t="n">
         <v>0</v>
@@ -21562,12 +21562,12 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Lutterworth</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
@@ -21613,12 +21613,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Marlborough</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
@@ -21664,12 +21664,12 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Marlow</t>
+          <t>Newbury</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
@@ -21680,7 +21680,7 @@
       </c>
       <c r="F257" s="4" t="inlineStr"/>
       <c r="G257" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H257" s="5" t="n">
         <v>0</v>
@@ -21692,7 +21692,7 @@
         <v>0</v>
       </c>
       <c r="K257" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L257" s="5" t="n">
         <v>0</v>
@@ -21715,12 +21715,12 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Mirfield</t>
+          <t>Newmarket</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
@@ -21766,12 +21766,12 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>North Shields</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
@@ -21782,13 +21782,13 @@
       </c>
       <c r="F259" s="4" t="inlineStr"/>
       <c r="G259" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H259" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I259" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J259" s="5" t="n">
         <v>0</v>
@@ -21817,12 +21817,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Otley</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
@@ -21868,12 +21868,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
@@ -21884,13 +21884,13 @@
       </c>
       <c r="F261" s="4" t="inlineStr"/>
       <c r="G261" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H261" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I261" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J261" s="5" t="n">
         <v>0</v>
@@ -21919,12 +21919,12 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Newbury</t>
+          <t>Pickering</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D262" s="3" t="n">
@@ -21935,7 +21935,7 @@
       </c>
       <c r="F262" s="2" t="inlineStr"/>
       <c r="G262" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H262" s="3" t="n">
         <v>0</v>
@@ -21947,7 +21947,7 @@
         <v>0</v>
       </c>
       <c r="K262" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L262" s="3" t="n">
         <v>0</v>
@@ -21970,12 +21970,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Newmarket</t>
+          <t>Pontypridd</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
@@ -22021,12 +22021,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>North Shields</t>
+          <t>Portishead</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D264" s="3" t="n">
@@ -22072,12 +22072,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Otley</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
@@ -22123,12 +22123,12 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Redruth</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
@@ -22139,13 +22139,13 @@
       </c>
       <c r="F266" s="2" t="inlineStr"/>
       <c r="G266" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H266" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I266" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J266" s="3" t="n">
         <v>0</v>
@@ -22174,7 +22174,7 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Pickering</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
@@ -22225,12 +22225,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Pontypridd</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D268" s="3" t="n">
@@ -22241,7 +22241,7 @@
       </c>
       <c r="F268" s="2" t="inlineStr"/>
       <c r="G268" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H268" s="3" t="n">
         <v>0</v>
@@ -22253,7 +22253,7 @@
         <v>0</v>
       </c>
       <c r="K268" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L268" s="3" t="n">
         <v>0</v>
@@ -22276,12 +22276,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Portishead</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D269" s="5" t="n">
@@ -22327,12 +22327,12 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Rugby</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D270" s="3" t="n">
@@ -22378,12 +22378,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Redruth</t>
+          <t>Runcorn</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D271" s="5" t="n">
@@ -22429,12 +22429,12 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Ryton</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D272" s="3" t="n">
@@ -22480,12 +22480,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
@@ -22496,7 +22496,7 @@
       </c>
       <c r="F273" s="4" t="inlineStr"/>
       <c r="G273" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H273" s="5" t="n">
         <v>0</v>
@@ -22508,7 +22508,7 @@
         <v>0</v>
       </c>
       <c r="K273" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L273" s="5" t="n">
         <v>0</v>
@@ -22531,12 +22531,12 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Rugby</t>
+          <t>Seaham</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D274" s="3" t="n">
@@ -22582,12 +22582,12 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Runcorn</t>
+          <t>Shepperton</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
@@ -22633,12 +22633,12 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Ryton</t>
+          <t>Shipley</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D276" s="3" t="n">
@@ -22684,12 +22684,12 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Shirley</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
@@ -22735,12 +22735,12 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Seaham</t>
+          <t>Snodland</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D278" s="3" t="n">
@@ -22751,13 +22751,13 @@
       </c>
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H278" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I278" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J278" s="3" t="n">
         <v>0</v>
@@ -22786,12 +22786,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Shepperton</t>
+          <t>Southam</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D279" s="5" t="n">
@@ -22837,12 +22837,12 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Shipley</t>
+          <t>Southend-on-sea</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D280" s="3" t="n">
@@ -22888,12 +22888,12 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Spennymoor</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D281" s="5" t="n">
@@ -22939,12 +22939,12 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Snodland</t>
+          <t>St. Austell</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D282" s="3" t="n">
@@ -22955,13 +22955,13 @@
       </c>
       <c r="F282" s="2" t="inlineStr"/>
       <c r="G282" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H282" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I282" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J282" s="3" t="n">
         <v>0</v>
@@ -22990,12 +22990,12 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Southam</t>
+          <t>St. Ives</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D283" s="5" t="n">
@@ -23041,12 +23041,12 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Southend-on-sea</t>
+          <t>St. Neots</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D284" s="3" t="n">
@@ -23092,12 +23092,12 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Spennymoor</t>
+          <t>Staines</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D285" s="5" t="n">
@@ -23143,12 +23143,12 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>St. Austell</t>
+          <t>Street</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D286" s="3" t="n">
@@ -23194,12 +23194,12 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>St. Ives</t>
+          <t>Stroud</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D287" s="5" t="n">
@@ -23245,12 +23245,12 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>St. Neots</t>
+          <t>Taunton</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D288" s="3" t="n">
@@ -23296,12 +23296,12 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Staines</t>
+          <t>Tipton</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D289" s="5" t="n">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D290" s="3" t="n">
@@ -23363,13 +23363,13 @@
       </c>
       <c r="F290" s="2" t="inlineStr"/>
       <c r="G290" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H290" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I290" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J290" s="3" t="n">
         <v>0</v>
@@ -23398,12 +23398,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Stroud</t>
+          <t>Torquay</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D291" s="5" t="n">
@@ -23449,12 +23449,12 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Taunton</t>
+          <t>Trowbridge</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D292" s="3" t="n">
@@ -23500,12 +23500,12 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Tipton</t>
+          <t>Ulverston</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
@@ -23516,10 +23516,10 @@
       </c>
       <c r="F293" s="4" t="inlineStr"/>
       <c r="G293" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H293" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I293" s="5" t="n">
         <v>0</v>
@@ -23551,12 +23551,12 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D294" s="3" t="n">
@@ -23567,13 +23567,13 @@
       </c>
       <c r="F294" s="2" t="inlineStr"/>
       <c r="G294" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H294" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I294" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J294" s="3" t="n">
         <v>0</v>
@@ -23602,12 +23602,12 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Waltham Cross</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D295" s="5" t="n">
@@ -23653,12 +23653,12 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Trowbridge</t>
+          <t>Walton-on-thames</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D296" s="3" t="n">
@@ -23704,12 +23704,12 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Ulverston</t>
+          <t>Waterlooville</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D297" s="5" t="n">
@@ -23720,10 +23720,10 @@
       </c>
       <c r="F297" s="4" t="inlineStr"/>
       <c r="G297" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H297" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I297" s="5" t="n">
         <v>0</v>
@@ -23755,12 +23755,12 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Wellingborough</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D298" s="3" t="n">
@@ -23806,12 +23806,12 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Waltham Cross</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D299" s="5" t="n">
@@ -23857,12 +23857,12 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D300" s="3" t="n">
@@ -23908,12 +23908,12 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Waterlooville</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D301" s="5" t="n">
@@ -23959,12 +23959,12 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Wednesbury</t>
+          <t>Whitstable</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D302" s="3" t="n">
@@ -23975,13 +23975,13 @@
       </c>
       <c r="F302" s="2" t="inlineStr"/>
       <c r="G302" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H302" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I302" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J302" s="3" t="n">
         <v>0</v>
@@ -24010,12 +24010,12 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Wellingborough</t>
+          <t>Wilmslow</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D303" s="5" t="n">
@@ -24061,12 +24061,12 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D304" s="3" t="n">
@@ -24112,12 +24112,12 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Witney</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D305" s="5" t="n">
@@ -24163,12 +24163,12 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Worksop</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D306" s="3" t="n">
@@ -24214,12 +24214,12 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Whitstable</t>
+          <t>Wymondham</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D307" s="5" t="n">
@@ -24230,13 +24230,13 @@
       </c>
       <c r="F307" s="4" t="inlineStr"/>
       <c r="G307" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H307" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J307" s="5" t="n">
         <v>0</v>
@@ -24257,263 +24257,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B308" s="2" t="inlineStr">
-        <is>
-          <t>Wilmslow</t>
-        </is>
-      </c>
-      <c r="C308" s="2" t="inlineStr">
-        <is>
-          <t>Cheshire - East</t>
-        </is>
-      </c>
-      <c r="D308" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F308" s="2" t="inlineStr"/>
-      <c r="G308" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O308" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B309" s="4" t="inlineStr">
-        <is>
-          <t>Windsor</t>
-        </is>
-      </c>
-      <c r="C309" s="4" t="inlineStr">
-        <is>
-          <t>Berkshire</t>
-        </is>
-      </c>
-      <c r="D309" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E309" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F309" s="4" t="inlineStr"/>
-      <c r="G309" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H309" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I309" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J309" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K309" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L309" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M309" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N309" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O309" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B310" s="2" t="inlineStr">
-        <is>
-          <t>Witney</t>
-        </is>
-      </c>
-      <c r="C310" s="2" t="inlineStr">
-        <is>
-          <t>Oxfordshire</t>
-        </is>
-      </c>
-      <c r="D310" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E310" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F310" s="2" t="inlineStr"/>
-      <c r="G310" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H310" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I310" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J310" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K310" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L310" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M310" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N310" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O310" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B311" s="4" t="inlineStr">
-        <is>
-          <t>Worksop</t>
-        </is>
-      </c>
-      <c r="C311" s="4" t="inlineStr">
-        <is>
-          <t>Nottinghamshire</t>
-        </is>
-      </c>
-      <c r="D311" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E311" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F311" s="4" t="inlineStr"/>
-      <c r="G311" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H311" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I311" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J311" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K311" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L311" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M311" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N311" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O311" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B312" s="2" t="inlineStr">
-        <is>
-          <t>Wymondham</t>
-        </is>
-      </c>
-      <c r="C312" s="2" t="inlineStr">
-        <is>
-          <t>Norfolk</t>
-        </is>
-      </c>
-      <c r="D312" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E312" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F312" s="2" t="inlineStr"/>
-      <c r="G312" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H312" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I312" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J312" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K312" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L312" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M312" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N312" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O312" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O312"/>
+  <autoFilter ref="A1:O307"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24592,7 +24337,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
@@ -24632,7 +24377,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="3" t="n">
@@ -24657,7 +24402,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
@@ -24678,7 +24423,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
@@ -24835,7 +24580,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="5" t="n">
@@ -24900,7 +24645,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
@@ -24999,7 +24744,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>11</v>
@@ -25058,7 +24803,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>3</v>
@@ -25156,7 +24901,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
@@ -25190,7 +24935,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>21</v>
@@ -25221,7 +24966,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
@@ -25439,7 +25184,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr"/>
@@ -25658,7 +25403,7 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
@@ -25713,7 +25458,7 @@
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>1</v>
@@ -25855,7 +25600,7 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>
@@ -25876,7 +25621,7 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="inlineStr"/>
@@ -26123,7 +25868,7 @@
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.2 / 0/14</t>
+          <t>5 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
@@ -26133,12 +25878,12 @@
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
@@ -26156,19 +25901,19 @@
       <c r="B3" s="14" t="inlineStr"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr"/>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr"/>
@@ -26193,19 +25938,19 @@
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>7 / 4.2 / 5/14</t>
+          <t>7 / 4.7 / 6/14</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.9 / 0/14</t>
+          <t>4 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.4 / 0/14</t>
+          <t>2 / 3.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26223,23 +25968,23 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/14</t>
+          <t>3 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>2 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr"/>
@@ -26263,23 +26008,23 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>3 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/14</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26297,17 +26042,17 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.3 / 0/14</t>
+          <t>4 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -26322,7 +26067,7 @@
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.3 / 0/14</t>
+          <t>2 / 2.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26340,7 +26085,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 1/14</t>
+          <t>1 / 0.9 / 1/14</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -26350,7 +26095,7 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/14</t>
+          <t>4 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
@@ -26379,18 +26124,18 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/14</t>
+          <t>3 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -26413,7 +26158,7 @@
       <c r="B10" s="13" t="inlineStr"/>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -26455,7 +26200,7 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>2 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -26502,7 +26247,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
@@ -26518,17 +26263,17 @@
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
@@ -26598,12 +26343,12 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.4 / 0/14</t>
+          <t>4 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.5 / 0/14</t>
+          <t>4 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
@@ -26618,12 +26363,12 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26636,29 +26381,29 @@
       <c r="B15" s="14" t="inlineStr"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/14</t>
+          <t>2 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr"/>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>2 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>3 / 4.6 / 5/14</t>
+          <t>3 / 4.8 / 5/14</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>2 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 2.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26676,17 +26421,17 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.4 / 0/14</t>
+          <t>2 / 3.5 / 0/14</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.1 / 0/14</t>
+          <t>5 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -26696,7 +26441,7 @@
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
@@ -26719,7 +26464,7 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.8 / 1/14</t>
+          <t>3 / 3.9 / 1/14</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
@@ -26727,7 +26472,7 @@
       <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.8 / 4/14</t>
+          <t>6 / 3.1 / 5/14</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
@@ -26750,7 +26495,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>1 / 3.5 / 3/14</t>
+          <t>2 / 3.6 / 3/14</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -26762,12 +26507,12 @@
       <c r="G18" s="13" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/14</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 0/14</t>
+          <t>3 / 3.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26786,7 +26531,7 @@
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>15 / 7.5 / 8/14</t>
+          <t>16 / 8.5 / 9/14</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr"/>
@@ -26794,7 +26539,7 @@
       <c r="H19" s="14" t="inlineStr"/>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>0 / 1.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26806,7 +26551,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 0/14</t>
+          <t>4 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -26831,7 +26576,7 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
@@ -26864,7 +26609,7 @@
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>2 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr"/>
@@ -26898,32 +26643,32 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
+          <t>1 / 0.6 / 0/14</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>3 / 1.4 / 0/14</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>3 / 1.1 / 0/14</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/14</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.6 / 0/14</t>
-        </is>
-      </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26938,22 +26683,22 @@
       <c r="D23" s="14" t="inlineStr"/>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/14</t>
+          <t>3 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>6 / 7.4 / 13/14</t>
+          <t>6 / 7.5 / 14/14</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>5 / 2.2 / 0/14</t>
+          <t>5 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>7 / 5.3 / 5/14</t>
+          <t>7 / 5.6 / 6/14</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr"/>
@@ -27020,23 +26765,23 @@
       <c r="D25" s="14" t="inlineStr"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>2 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/14</t>
+          <t>3 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/14</t>
+          <t>1 / 2.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27051,18 +26796,18 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>13 / 7.9 / 8/14</t>
+          <t>12 / 8.7 / 9/14</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.4 / 0/14</t>
+          <t>3 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
@@ -27094,12 +26839,12 @@
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -27173,7 +26918,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.9 / 0/14</t>
+          <t>3 / 3.0 / 0/14</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -27245,7 +26990,7 @@
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>2 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -27277,7 +27022,7 @@
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
@@ -27315,7 +27060,7 @@
       <c r="B32" s="13" t="inlineStr"/>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -27325,27 +27070,27 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.7 / 0/14</t>
+          <t>5 / 3.0 / 0/14</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.3 / 0/14</t>
+          <t>2 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27368,7 +27113,7 @@
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>2 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
@@ -27383,12 +27128,12 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27421,12 +27166,12 @@
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.3 / 4/14</t>
+          <t>6 / 3.7 / 5/14</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr"/>
@@ -27437,12 +27182,12 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>2 / 0.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27454,7 +27199,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -27469,7 +27214,7 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -27501,7 +27246,7 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>3 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -27511,7 +27256,7 @@
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
@@ -27521,12 +27266,12 @@
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
@@ -27558,22 +27303,22 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>2 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
@@ -27601,13 +27346,13 @@
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.7 / 3/14</t>
+          <t>7 / 3.1 / 4/14</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -27617,7 +27362,7 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.1 / 0/14</t>
+          <t>3 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
@@ -27637,14 +27382,14 @@
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.0 / 0/14</t>
+          <t>4 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr"/>
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.2 / 0/14</t>
+          <t>4 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
@@ -27674,7 +27419,7 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
@@ -27706,7 +27451,7 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -27716,7 +27461,7 @@
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
@@ -27731,7 +27476,7 @@
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/14</t>
+          <t>2 / 1.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27743,12 +27488,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.0 / 0/14</t>
+          <t>2 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
@@ -27778,7 +27523,7 @@
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27796,7 +27541,7 @@
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>4 / 6.2 / 7/14</t>
+          <t>4 / 6.4 / 7/14</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -27806,17 +27551,17 @@
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.7 / 0/14</t>
+          <t>2 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.2 / 0/14</t>
+          <t>5 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.0 / 0/14</t>
+          <t>5 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
@@ -27834,17 +27579,17 @@
       <c r="B45" s="14" t="inlineStr"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/14</t>
+          <t>2 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>15 / 12.0 / 10/14</t>
+          <t>15 / 13.0 / 11/14</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr"/>
@@ -27864,7 +27609,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>21 / 19.1 / 11/14</t>
+          <t>22 / 20.5 / 12/14</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -27874,7 +27619,7 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.4 / 0/14</t>
+          <t>2 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -27884,12 +27629,12 @@
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/14</t>
+          <t>3 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.5 / 0/14</t>
+          <t>4 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -27899,7 +27644,7 @@
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27912,17 +27657,17 @@
       <c r="B47" s="14" t="inlineStr"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.7 / 0/14</t>
+          <t>3 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>8 / 3.6 / 4/14</t>
+          <t>7 / 4.0 / 5/14</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
@@ -27932,13 +27677,13 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr"/>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27952,12 +27697,12 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.8 / 0/14</t>
+          <t>3 / 4.0 / 0/14</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/14</t>
+          <t>3 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr"/>
@@ -27968,7 +27713,7 @@
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
@@ -28032,7 +27777,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.2 / 0/14</t>
+          <t>5 / 3.5 / 0/14</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -28062,7 +27807,7 @@
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="I50" s="13" t="inlineStr">
@@ -28085,17 +27830,17 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.8 / 0/14</t>
+          <t>1 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/14</t>
+          <t>1 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>2 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -28105,7 +27850,7 @@
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
@@ -28147,7 +27892,7 @@
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -28169,17 +27914,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
+          <t>3 / 1.4 / 0/14</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
           <t>1 / 1.3 / 0/14</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="D53" s="14" t="inlineStr">
-        <is>
-          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -28227,12 +27972,12 @@
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
@@ -28274,7 +28019,7 @@
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
@@ -28313,7 +28058,7 @@
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
@@ -28323,7 +28068,7 @@
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -28333,7 +28078,7 @@
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 1/14</t>
+          <t>1 / 1.5 / 1/14</t>
         </is>
       </c>
     </row>
@@ -28370,7 +28115,7 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="H57" s="14" t="inlineStr">
@@ -28445,12 +28190,12 @@
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>2 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/14</t>
+          <t>3 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr">
@@ -28466,7 +28211,7 @@
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28479,7 +28224,7 @@
       <c r="B60" s="13" t="inlineStr"/>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
@@ -28489,17 +28234,17 @@
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.3 / 0/14</t>
+          <t>4 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -28527,7 +28272,7 @@
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
@@ -28537,7 +28282,7 @@
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.5 / 3/14</t>
+          <t>6 / 3.9 / 4/14</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -28547,7 +28292,7 @@
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr"/>
@@ -28566,23 +28311,23 @@
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.6 / 0/14</t>
+          <t>2 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/14</t>
+          <t>3 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/14</t>
+          <t>2 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
@@ -28602,18 +28347,18 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>11 / 7.4 / 8/14</t>
+          <t>11 / 8.1 / 9/14</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>6 / 4.7 / 5/14</t>
+          <t>6 / 4.9 / 6/14</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.7 / 0/14</t>
+          <t>5 / 3.9 / 0/14</t>
         </is>
       </c>
       <c r="I63" s="14" t="inlineStr"/>
@@ -28629,23 +28374,23 @@
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.6 / 0/14</t>
+          <t>5 / 3.9 / 0/14</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>5 / 4.3 / 3/14</t>
+          <t>5 / 4.5 / 3/14</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.1 / 0/14</t>
+          <t>5 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.6 / 0/14</t>
+          <t>1 / 2.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28757,17 +28502,17 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.7 / 0/14</t>
+          <t>2 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>3 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -28794,7 +28539,7 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -28809,12 +28554,12 @@
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
@@ -28841,7 +28586,7 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.7 / 0/14</t>
+          <t>1 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
@@ -28889,12 +28634,12 @@
       <c r="B70" s="13" t="inlineStr"/>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/14</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -28919,7 +28664,7 @@
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28932,7 +28677,7 @@
       <c r="B71" s="14" t="inlineStr"/>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
@@ -28942,19 +28687,19 @@
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>10 / 4.8 / 5/14</t>
+          <t>10 / 5.4 / 6/14</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.9 / 0/14</t>
+          <t>4 / 3.0 / 0/14</t>
         </is>
       </c>
       <c r="H71" s="14" t="inlineStr"/>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.9 / 0/14</t>
+          <t>1 / 2.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28967,17 +28712,17 @@
       <c r="B72" s="13" t="inlineStr"/>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.6 / 0/14</t>
+          <t>3 / 3.9 / 0/14</t>
         </is>
       </c>
       <c r="F72" s="13" t="inlineStr">
@@ -29010,33 +28755,33 @@
       <c r="B73" s="14" t="inlineStr"/>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.8 / 7/14</t>
+          <t>2 / 3.9 / 7/14</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>5 / 4.9 / 5/14</t>
+          <t>5 / 5.2 / 5/14</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.0 / 0/14</t>
+          <t>4 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr"/>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29050,27 +28795,27 @@
       <c r="C74" s="13" t="inlineStr"/>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/14</t>
+          <t>2 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 0/14</t>
+          <t>4 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.4 / 0/14</t>
+          <t>4 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.1 / 0/14</t>
+          <t>3 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I74" s="13" t="inlineStr">
@@ -29093,17 +28838,17 @@
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.6 / 0/14</t>
+          <t>4 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/14</t>
+          <t>0 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
@@ -29113,12 +28858,12 @@
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29141,12 +28886,12 @@
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
@@ -29156,12 +28901,12 @@
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>2 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/14</t>
+          <t>1 / 2.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29179,19 +28924,19 @@
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.4 / 0/14</t>
+          <t>2 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>9 / 3.2 / 4/14</t>
+          <t>9 / 3.9 / 5/14</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr"/>
       <c r="G77" s="14" t="inlineStr"/>
       <c r="H77" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.9 / 3/14</t>
+          <t>6 / 3.3 / 4/14</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
@@ -29210,32 +28955,32 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.3 / 0/14</t>
+          <t>2 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.5 / 0/14</t>
+          <t>4 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>5 / 5.2 / 6/14</t>
+          <t>5 / 5.6 / 6/14</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.2 / 0/14</t>
+          <t>3 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>3 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29250,19 +28995,19 @@
       <c r="D79" s="14" t="inlineStr"/>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>11 / 5.7 / 5/14</t>
+          <t>11 / 6.3 / 6/14</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>9 / 13.6 / 13/14</t>
+          <t>8 / 14.1 / 14/14</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>
       <c r="H79" s="14" t="inlineStr"/>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.5 / 0/14</t>
+          <t>2 / 2.4 / 0/14</t>
         </is>
       </c>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$198</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$307</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$308</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1630</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1379</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="4">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1781</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="6">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8">
@@ -674,7 +674,7 @@
         <v>1009</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="5">
@@ -852,7 +852,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1390</v>
+        <v>1392</v>
       </c>
     </row>
   </sheetData>
@@ -867,7 +867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -941,7 +941,7 @@
       <c r="D2" s="11" t="inlineStr"/>
       <c r="E2" s="11" t="inlineStr"/>
       <c r="F2" s="12" t="n">
-        <v>1820</v>
+        <v>1811</v>
       </c>
       <c r="G2" s="11" t="inlineStr"/>
       <c r="H2" s="11" t="inlineStr">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="F3" s="12" t="n">
-        <v>1628</v>
+        <v>1621</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>1628</v>
+        <v>1621</v>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="F4" s="12" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G4" s="11" t="inlineStr"/>
       <c r="H4" s="11" t="inlineStr">
@@ -1594,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>1</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>1</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -4630,19 +4630,19 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/customer-service-jobs</t>
+          <t>/job-search/london/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4663,24 +4663,24 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>/job-search/london/hr-recruitment-jobs</t>
+          <t>/job-search/manchester-salford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F103" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -4701,24 +4701,24 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Finance &amp; Accounts</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/service-administrator-jobs</t>
+          <t>/job-search/london/finance-accounts-jobs</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4739,24 +4739,24 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>/job-search/london/finance-accounts-jobs</t>
+          <t>/job-search/oxfordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F105" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4787,14 +4787,14 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>/job-search/oxfordshire/service-administrator-jobs</t>
+          <t>/job-search/bristol-bath/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/service-administrator-jobs</t>
+          <t>/job-search/essex/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F107" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -4853,24 +4853,24 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>/job-search/essex/service-administrator-jobs</t>
+          <t>/job-search/hampshire/customer-service-jobs</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4891,24 +4891,24 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>/job-search/hampshire/customer-service-jobs</t>
+          <t>/job-search/cambridgeshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cambridgeshire/service-administrator-jobs</t>
+          <t>/job-search/gloucestershire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -4967,17 +4967,17 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>/job-search/gloucestershire/service-administrator-jobs</t>
+          <t>/job-search/london/support-worker</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
@@ -5005,24 +5005,24 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/support-worker</t>
+          <t>/job-search/dorset/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5043,24 +5043,24 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>/job-search/dorset/service-administrator-jobs</t>
+          <t>/job-search/staffordshire/customer-service-jobs</t>
         </is>
       </c>
       <c r="F113" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -5081,24 +5081,24 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>/job-search/staffordshire/customer-service-jobs</t>
+          <t>/job-search/devon/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5119,24 +5119,24 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>/job-search/devon/service-administrator-jobs</t>
+          <t>/job-search/surrey/customer-service-jobs</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -5157,24 +5157,24 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>/job-search/surrey/customer-service-jobs</t>
+          <t>/job-search/wiltshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -5205,14 +5205,14 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>/job-search/wiltshire/service-administrator-jobs</t>
+          <t>/job-search/northamptonshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F117" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5243,14 +5243,14 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>/job-search/northamptonshire/service-administrator-jobs</t>
+          <t>/job-search/berkshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -5281,14 +5281,14 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/service-administrator-jobs</t>
+          <t>/job-search/nottinghamshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F119" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -5319,14 +5319,14 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>/job-search/nottinghamshire/service-administrator-jobs</t>
+          <t>/job-search/buckinghamshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -5357,14 +5357,14 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>/job-search/buckinghamshire/service-administrator-jobs</t>
+          <t>/job-search/hertfordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F121" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -5385,24 +5385,24 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>/job-search/surrey/support-worker</t>
+          <t>/job-search/staffordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -5433,14 +5433,14 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/service-administrator-jobs</t>
+          <t>/job-search/norfolk/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F123" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -5471,14 +5471,14 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>/job-search/staffordshire/service-administrator-jobs</t>
+          <t>/job-search/birmingham-solihull/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5499,24 +5499,24 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>/job-search/norfolk/service-administrator-jobs</t>
+          <t>/job-search/west-yorkshire/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F125" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -5547,14 +5547,14 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>/job-search/birmingham-solihull/service-administrator-jobs</t>
+          <t>/job-search/greater-manchester-south/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5575,24 +5575,24 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>/job-search/west-yorkshire/hr-recruitment-jobs</t>
+          <t>/job-search/wiltshire/support-worker</t>
         </is>
       </c>
       <c r="F127" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -5623,14 +5623,14 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>/job-search/greater-manchester-south/service-administrator-jobs</t>
+          <t>/job-search/somerset/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F128" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5651,24 +5651,24 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>/job-search/wiltshire/support-worker</t>
+          <t>/job-search/london/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F129" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
@@ -5689,24 +5689,24 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>/job-search/somerset/service-administrator-jobs</t>
+          <t>/job-search/manchester-salford/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5727,17 +5727,17 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>/job-search/london/customer-sales-jobs</t>
+          <t>/job-search/leicestershire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F131" s="5" t="n">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/customer-sales-jobs</t>
+          <t>/job-search/warrington-halton/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -5813,14 +5813,14 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>/job-search/leicestershire/service-administrator-jobs</t>
+          <t>/job-search/cornwall/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F133" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5851,14 +5851,14 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>/job-search/warrington-halton/service-administrator-jobs</t>
+          <t>/job-search/suffolk/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F134" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -5889,14 +5889,14 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>/job-search/cornwall/service-administrator-jobs</t>
+          <t>/job-search/derbyshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F135" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -5927,14 +5927,14 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>/job-search/suffolk/service-administrator-jobs</t>
+          <t>/job-search/cheshire-east/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F136" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -5965,14 +5965,14 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>/job-search/derbyshire/service-administrator-jobs</t>
+          <t>/job-search/lincolnshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F137" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -6003,14 +6003,14 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-east/service-administrator-jobs</t>
+          <t>/job-search/merseyside-liverpool/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -6041,14 +6041,14 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>/job-search/lincolnshire/service-administrator-jobs</t>
+          <t>/job-search/shropshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F139" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -6079,14 +6079,14 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>/job-search/merseyside-liverpool/service-administrator-jobs</t>
+          <t>/job-search/wigan-bolton/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -6117,14 +6117,14 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>/job-search/shropshire/service-administrator-jobs</t>
+          <t>/job-search/black-country/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F141" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -6145,24 +6145,24 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Legal Assistant &amp; Paralegal</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>/job-search/wigan-bolton/service-administrator-jobs</t>
+          <t>/job-search/london/paralegal-jobs</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6183,24 +6183,24 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Legal Assistant &amp; Paralegal</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>/job-search/black-country/service-administrator-jobs</t>
+          <t>/job-search/suffolk/paralegal-jobs</t>
         </is>
       </c>
       <c r="F143" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -6231,14 +6231,14 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/paralegal-jobs</t>
+          <t>/job-search/essex/paralegal-jobs</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -6269,14 +6269,14 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>/job-search/suffolk/paralegal-jobs</t>
+          <t>/job-search/norfolk/paralegal-jobs</t>
         </is>
       </c>
       <c r="F145" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -6297,24 +6297,24 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Legal Assistant &amp; Paralegal</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>/job-search/essex/paralegal-jobs</t>
+          <t>/job-search/london/marketing-jobs</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6335,24 +6335,24 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Legal Assistant &amp; Paralegal</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>/job-search/norfolk/paralegal-jobs</t>
+          <t>/job-search/surrey/marketing-jobs</t>
         </is>
       </c>
       <c r="F147" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -6383,14 +6383,14 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/marketing-jobs</t>
+          <t>/job-search/manchester-salford/marketing-jobs</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -6421,14 +6421,14 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>/job-search/surrey/marketing-jobs</t>
+          <t>/job-search/birmingham-solihull/marketing-jobs</t>
         </is>
       </c>
       <c r="F149" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -6449,24 +6449,24 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/marketing-jobs</t>
+          <t>/job-search/berkshire/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F150" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6487,24 +6487,24 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>/job-search/birmingham-solihull/marketing-jobs</t>
+          <t>/job-search/manchester-salford/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F151" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6535,14 +6535,14 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/hr-recruitment-jobs</t>
+          <t>/job-search/nottinghamshire/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -6573,14 +6573,14 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/hr-recruitment-jobs</t>
+          <t>/job-search/birmingham-solihull/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F153" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6611,14 +6611,14 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>/job-search/nottinghamshire/hr-recruitment-jobs</t>
+          <t>/job-search/sussex/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F154" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6639,24 +6639,24 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>/job-search/birmingham-solihull/hr-recruitment-jobs</t>
+          <t>/job-search/cheshire-west/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F155" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -6677,24 +6677,24 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>/job-search/sussex/hr-recruitment-jobs</t>
+          <t>/job-search/edinburgh-lothians/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -6725,14 +6725,14 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-west/service-administrator-jobs</t>
+          <t>/job-search/worcestershire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F157" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -6753,24 +6753,24 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>/job-search/edinburgh-lothians/service-administrator-jobs</t>
+          <t>/job-search/berkshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6791,24 +6791,24 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>/job-search/worcestershire/service-administrator-jobs</t>
+          <t>/job-search/kent/support-worker</t>
         </is>
       </c>
       <c r="F159" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -6829,24 +6829,24 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>North East</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/marketing-jobs</t>
+          <t>/job-search/north-east/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F160" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -6877,14 +6877,14 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>/job-search/kent/support-worker</t>
+          <t>/job-search/oxfordshire/support-worker</t>
         </is>
       </c>
       <c r="F161" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -6905,24 +6905,24 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>North East</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Finance &amp; Accounts</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>/job-search/north-east/customer-sales-jobs</t>
+          <t>/job-search/northern-ireland-east/finance-accounts-jobs</t>
         </is>
       </c>
       <c r="F162" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -6943,24 +6943,24 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>/job-search/oxfordshire/support-worker</t>
+          <t>/job-search/bedfordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F163" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -6981,24 +6981,24 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>/job-search/northern-ireland-east/finance-accounts-jobs</t>
+          <t>/job-search/bristol-bath/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F164" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7019,24 +7019,24 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>/job-search/bedfordshire/service-administrator-jobs</t>
+          <t>/job-search/buckinghamshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F165" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -7057,17 +7057,17 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/customer-sales-jobs</t>
+          <t>/job-search/cardiff-vale/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F166" s="3" t="n">
@@ -7095,24 +7095,24 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>/job-search/buckinghamshire/marketing-jobs</t>
+          <t>/job-search/berkshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F167" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -7133,24 +7133,24 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cardiff-vale/service-administrator-jobs</t>
+          <t>/job-search/hertfordshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F168" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -7181,14 +7181,14 @@
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/customer-sales-jobs</t>
+          <t>/job-search/kent/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F169" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -7219,14 +7219,14 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/customer-sales-jobs</t>
+          <t>/job-search/glasgow/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F170" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -7257,14 +7257,14 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>/job-search/kent/customer-sales-jobs</t>
+          <t>/job-search/surrey/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F171" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -7295,14 +7295,14 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>/job-search/glasgow/customer-sales-jobs</t>
+          <t>/job-search/sussex/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F172" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7323,24 +7323,24 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>/job-search/surrey/customer-sales-jobs</t>
+          <t>/job-search/bristol-bath/marketing-jobs</t>
         </is>
       </c>
       <c r="F173" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
@@ -7361,24 +7361,24 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>/job-search/sussex/customer-sales-jobs</t>
+          <t>/job-search/gloucestershire/marketing-jobs</t>
         </is>
       </c>
       <c r="F174" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -7409,14 +7409,14 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/marketing-jobs</t>
+          <t>/job-search/hertfordshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F175" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -7447,14 +7447,14 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>/job-search/gloucestershire/marketing-jobs</t>
+          <t>/job-search/kent/marketing-jobs</t>
         </is>
       </c>
       <c r="F176" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -7485,14 +7485,14 @@
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/marketing-jobs</t>
+          <t>/job-search/oxfordshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F177" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -7513,24 +7513,24 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>/job-search/kent/marketing-jobs</t>
+          <t>/job-search/north-scotland/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F178" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7551,24 +7551,24 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>/job-search/oxfordshire/marketing-jobs</t>
+          <t>/job-search/tayside/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F179" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>/job-search/north-scotland/service-administrator-jobs</t>
+          <t>/job-search/south-wales-valleys/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F180" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7627,24 +7627,24 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>/job-search/tayside/service-administrator-jobs</t>
+          <t>/job-search/cambridgeshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F181" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -7665,24 +7665,24 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>/job-search/south-wales-valleys/service-administrator-jobs</t>
+          <t>/job-search/cheshire-west/marketing-jobs</t>
         </is>
       </c>
       <c r="F182" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -7713,14 +7713,14 @@
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>/job-search/cambridgeshire/marketing-jobs</t>
+          <t>/job-search/essex/marketing-jobs</t>
         </is>
       </c>
       <c r="F183" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -7751,14 +7751,14 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-west/marketing-jobs</t>
+          <t>/job-search/merseyside-liverpool/marketing-jobs</t>
         </is>
       </c>
       <c r="F184" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>North East</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -7789,14 +7789,14 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>/job-search/essex/marketing-jobs</t>
+          <t>/job-search/north-east/marketing-jobs</t>
         </is>
       </c>
       <c r="F185" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -7817,24 +7817,24 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>/job-search/merseyside-liverpool/marketing-jobs</t>
+          <t>/job-search/buckinghamshire/customer-service-jobs</t>
         </is>
       </c>
       <c r="F186" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -7860,19 +7860,19 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>/job-search/north-east/marketing-jobs</t>
+          <t>/job-search/north-east/customer-service-jobs</t>
         </is>
       </c>
       <c r="F187" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G187" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -7893,24 +7893,24 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>/job-search/buckinghamshire/customer-service-jobs</t>
+          <t>/job-search/devon/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F188" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -7931,24 +7931,24 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>North East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>/job-search/north-east/customer-service-jobs</t>
+          <t>/job-search/hampshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F189" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -7979,14 +7979,14 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>/job-search/devon/customer-sales-jobs</t>
+          <t>/job-search/north-scotland/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F190" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8007,24 +8007,24 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>/job-search/hampshire/customer-sales-jobs</t>
+          <t>/job-search/greater-manchester-south/marketing-jobs</t>
         </is>
       </c>
       <c r="F191" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G191" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -8045,24 +8045,24 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>/job-search/north-scotland/customer-sales-jobs</t>
+          <t>/job-search/northern-ireland-east/marketing-jobs</t>
         </is>
       </c>
       <c r="F192" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -8093,14 +8093,14 @@
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>/job-search/greater-manchester-south/marketing-jobs</t>
+          <t>/job-search/north-yorkshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F193" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G193" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -8121,24 +8121,24 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance &amp; Accounts</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>/job-search/northern-ireland-east/marketing-jobs</t>
+          <t>/job-search/manchester-salford/finance-accounts-jobs</t>
         </is>
       </c>
       <c r="F194" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8159,24 +8159,24 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>/job-search/north-yorkshire/marketing-jobs</t>
+          <t>/job-search/northern-ireland-east/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F195" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G195" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
@@ -8197,24 +8197,24 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/finance-accounts-jobs</t>
+          <t>/job-search/coventry-warwickshire/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F196" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8222,84 +8222,8 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="4" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>Regional/category</t>
-        </is>
-      </c>
-      <c r="C197" s="4" t="inlineStr">
-        <is>
-          <t>Northern Ireland - East</t>
-        </is>
-      </c>
-      <c r="D197" s="4" t="inlineStr">
-        <is>
-          <t>HR &amp; Recruitment</t>
-        </is>
-      </c>
-      <c r="E197" s="4" t="inlineStr">
-        <is>
-          <t>/job-search/northern-ireland-east/hr-recruitment-jobs</t>
-        </is>
-      </c>
-      <c r="F197" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G197" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H197" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>Regional/category</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t>HR &amp; Recruitment</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>/job-search/coventry-warwickshire/hr-recruitment-jobs</t>
-        </is>
-      </c>
-      <c r="F198" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G198" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H198" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H198"/>
+  <autoFilter ref="A1:H196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8310,7 +8234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O307"/>
+  <dimension ref="A1:O308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8517,16 +8441,16 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Sittingbourne</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -8536,7 +8460,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0</v>
@@ -8568,16 +8492,16 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Forfar</t>
+          <t>Sittingbourne</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -8587,7 +8511,7 @@
         <v>4</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>0</v>
@@ -8730,7 +8654,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>1</v>
@@ -8741,7 +8665,7 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0</v>
@@ -8785,7 +8709,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>1</v>
@@ -8796,7 +8720,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>0</v>
@@ -8808,7 +8732,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L9" s="5" t="n">
         <v>4</v>
@@ -8895,7 +8819,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>1</v>
@@ -8912,7 +8836,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>0</v>
@@ -8950,7 +8874,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>1</v>
@@ -8961,7 +8885,7 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>1</v>
@@ -9005,7 +8929,7 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>1</v>
@@ -9016,7 +8940,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>0</v>
@@ -9051,27 +8975,27 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>/liverpool/service-administrator-jobs</t>
+          <t>/glasgow/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0</v>
@@ -9083,7 +9007,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>0</v>
@@ -9106,27 +9030,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>/glasgow/service-administrator-jobs</t>
+          <t>/liverpool/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0</v>
@@ -9138,7 +9062,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" s="5" t="n">
         <v>0</v>
@@ -9161,12 +9085,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Chelmsford</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -9177,11 +9101,11 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>/chelmsford/service-administrator-jobs</t>
+          <t>/nottingham/jobs</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0</v>
@@ -9190,16 +9114,16 @@
         <v>0</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>0</v>
@@ -9225,7 +9149,7 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>1</v>
@@ -9236,7 +9160,7 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0</v>
@@ -9271,33 +9195,33 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Exeter</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>/nottingham/jobs</t>
+          <t>/exeter/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>0</v>
@@ -9309,7 +9233,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>0</v>
@@ -9326,33 +9250,33 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Exeter</t>
+          <t>Basingstoke</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>/exeter/service-administrator-jobs</t>
+          <t>/basingstoke/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>0</v>
@@ -9367,7 +9291,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="5" t="n">
         <v>0</v>
@@ -9381,12 +9305,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Basingstoke</t>
+          <t>Chelmsford</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -9397,23 +9321,23 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>/basingstoke/service-administrator-jobs</t>
+          <t>/chelmsford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>0</v>
@@ -9422,7 +9346,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>0</v>
@@ -9656,31 +9580,31 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>/oxford/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="I25" s="5" t="n">
         <v>0</v>
       </c>
@@ -9688,7 +9612,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="5" t="n">
         <v>0</v>
@@ -9711,30 +9635,30 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Farnham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>/farnham/service-administrator-jobs</t>
+          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0</v>
@@ -9766,12 +9690,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Farnham</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -9782,17 +9706,17 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>/gateshead/jobs</t>
+          <t>/farnham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" s="5" t="n">
         <v>0</v>
@@ -9807,7 +9731,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" s="5" t="n">
         <v>0</v>
@@ -9821,30 +9745,30 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Bolton</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>/oxford/service-administrator-jobs</t>
+          <t>/bolton/jobs</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0</v>
@@ -9853,7 +9777,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
@@ -9876,27 +9800,27 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Bolton</t>
+          <t>Doncaster</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>/bolton/jobs</t>
+          <t>/doncaster/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>0</v>
@@ -9931,12 +9855,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
@@ -9947,11 +9871,11 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/doncaster/service-administrator-jobs</t>
+          <t>/gateshead/jobs</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0</v>
@@ -9972,7 +9896,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>0</v>
@@ -9986,12 +9910,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Newtownabbey</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
@@ -10002,11 +9926,11 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>/newtownabbey/service-administrator-jobs</t>
+          <t>/leicester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>0</v>
@@ -10024,7 +9948,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="5" t="n">
         <v>0</v>
@@ -10041,12 +9965,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Northampton</t>
+          <t>Newtownabbey</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
@@ -10057,11 +9981,11 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>/northampton/service-administrator-jobs</t>
+          <t>/newtownabbey/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0</v>
@@ -10079,7 +10003,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>0</v>
@@ -10096,12 +10020,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Northampton</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -10112,7 +10036,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>/portsmouth/service-administrator-jobs</t>
+          <t>/northampton/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
@@ -10151,12 +10075,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
@@ -10167,7 +10091,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>/reading/jobs</t>
+          <t>/portsmouth/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
@@ -10206,27 +10130,27 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>/bedford/service-administrator-jobs</t>
+          <t>/reading/jobs</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H35" s="5" t="n">
         <v>0</v>
@@ -10261,12 +10185,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
@@ -10277,7 +10201,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>/cardiff/service-administrator-jobs</t>
+          <t>/bedford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
@@ -10371,12 +10295,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
@@ -10387,11 +10311,11 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>/leicester/service-administrator-jobs</t>
+          <t>/norwich/jobs</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0</v>
@@ -10400,7 +10324,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0</v>
@@ -10426,12 +10350,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>Warrington</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -10442,11 +10366,11 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>/norwich/jobs</t>
+          <t>/warrington/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H39" s="5" t="n">
         <v>0</v>
@@ -10455,7 +10379,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" s="5" t="n">
         <v>0</v>
@@ -10811,12 +10735,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Chester Le Street</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
@@ -10827,7 +10751,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>/chester-le-street/service-administrator-jobs</t>
+          <t>/cardiff/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
@@ -10866,12 +10790,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Hemel Hempstead</t>
+          <t>Chester Le Street</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
@@ -10882,23 +10806,23 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>/hemel-hempstead/service-administrator-jobs</t>
+          <t>/chester-le-street/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="5" t="n">
         <v>0</v>
@@ -11526,12 +11450,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Gloucester</t>
+          <t>Hemel Hempstead</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
@@ -11542,11 +11466,11 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>/gloucester/service-administrator-jobs</t>
+          <t>/hemel-hempstead/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" s="5" t="n">
         <v>0</v>
@@ -11558,7 +11482,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="5" t="n">
         <v>0</v>
@@ -11911,12 +11835,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Maidstone</t>
+          <t>Gloucester</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
@@ -11927,17 +11851,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>/maidstone/service-administrator-jobs</t>
+          <t>/gloucester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" s="3" t="n">
         <v>0</v>
@@ -11966,12 +11890,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Warrington</t>
+          <t>Maidstone</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
@@ -11982,17 +11906,17 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>/warrington/service-administrator-jobs</t>
+          <t>/maidstone/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" s="5" t="n">
         <v>0</v>
@@ -12280,7 +12204,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Isleworth</t>
+          <t>Uxbridge</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -12296,7 +12220,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H73" s="5" t="n">
         <v>0</v>
@@ -12305,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" s="5" t="n">
         <v>0</v>
@@ -12331,7 +12255,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Uxbridge</t>
+          <t>Isleworth</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -12340,7 +12264,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>0</v>
@@ -12356,7 +12280,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" s="3" t="n">
         <v>0</v>
@@ -13819,7 +13743,7 @@
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E103" s="5" t="n">
         <v>0</v>
@@ -13838,7 +13762,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L103" s="5" t="n">
         <v>0</v>
@@ -13912,29 +13836,29 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Hove</t>
+          <t>Lisburn</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E105" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F105" s="4" t="inlineStr"/>
       <c r="G105" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H105" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" s="5" t="n">
         <v>0</v>
@@ -13943,10 +13867,10 @@
         <v>0</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N105" s="5" t="n">
         <v>0</v>
@@ -13963,12 +13887,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Inverness</t>
+          <t>Cramlington</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
@@ -13979,13 +13903,13 @@
       </c>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="H106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>0</v>
@@ -14014,12 +13938,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Lisburn</t>
+          <t>Hove</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -14030,13 +13954,13 @@
       </c>
       <c r="F107" s="4" t="inlineStr"/>
       <c r="G107" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H107" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" s="5" t="n">
         <v>0</v>
@@ -14045,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N107" s="5" t="n">
         <v>0</v>
@@ -14065,12 +13989,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Northwich</t>
+          <t>Maidenhead</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
@@ -14081,7 +14005,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H108" s="3" t="n">
         <v>0</v>
@@ -14093,7 +14017,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L108" s="3" t="n">
         <v>0</v>
@@ -14116,12 +14040,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Northwich</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -14132,7 +14056,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H109" s="5" t="n">
         <v>0</v>
@@ -14144,7 +14068,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L109" s="5" t="n">
         <v>0</v>
@@ -14167,16 +14091,16 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -14195,7 +14119,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L110" s="3" t="n">
         <v>0</v>
@@ -14218,12 +14142,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Brighouse</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -14269,12 +14193,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Burgess Hill</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
@@ -14285,7 +14209,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -14297,7 +14221,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -14320,12 +14244,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Cirencester</t>
+          <t>Brighouse</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14371,12 +14295,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Fleet</t>
+          <t>Burgess Hill</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
@@ -14387,13 +14311,13 @@
       </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H114" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J114" s="3" t="n">
         <v>0</v>
@@ -14422,12 +14346,12 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Gerrards Cross</t>
+          <t>Cirencester</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14438,7 +14362,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H115" s="5" t="n">
         <v>0</v>
@@ -14450,7 +14374,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L115" s="5" t="n">
         <v>0</v>
@@ -14473,12 +14397,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Gosport</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
@@ -14489,10 +14413,10 @@
       </c>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>0</v>
@@ -14524,12 +14448,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14540,19 +14464,19 @@
       </c>
       <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J117" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="5" t="n">
         <v>0</v>
@@ -14575,12 +14499,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Knaresborough</t>
+          <t>Gerrards Cross</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -14626,12 +14550,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Lowestoft</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -14642,7 +14566,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H119" s="5" t="n">
         <v>0</v>
@@ -14654,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="K119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="5" t="n">
         <v>0</v>
@@ -14677,12 +14601,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Maidenhead</t>
+          <t>Inverness</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
@@ -14693,19 +14617,19 @@
       </c>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L120" s="3" t="n">
         <v>0</v>
@@ -14728,12 +14652,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Newry</t>
+          <t>Knaresborough</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -14744,7 +14668,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H121" s="5" t="n">
         <v>0</v>
@@ -14756,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L121" s="5" t="n">
         <v>0</v>
@@ -14779,12 +14703,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Tunbridge Wells</t>
+          <t>Knutsford</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
@@ -14795,13 +14719,13 @@
       </c>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J122" s="3" t="n">
         <v>0</v>
@@ -14830,12 +14754,12 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Lowestoft</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -14846,13 +14770,13 @@
       </c>
       <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H123" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J123" s="5" t="n">
         <v>0</v>
@@ -14881,29 +14805,29 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Newry</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
         <v>0</v>
@@ -14932,23 +14856,23 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Amersham</t>
+          <t>Truro</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E125" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H125" s="5" t="n">
         <v>0</v>
@@ -14983,29 +14907,29 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Tunbridge Wells</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E126" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H126" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="J126" s="3" t="n">
         <v>0</v>
@@ -15034,16 +14958,16 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Atherstone</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E127" s="5" t="n">
         <v>0</v>
@@ -15056,7 +14980,7 @@
         <v>0</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J127" s="5" t="n">
         <v>0</v>
@@ -15068,7 +14992,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N127" s="5" t="n">
         <v>0</v>
@@ -15085,12 +15009,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Amersham</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -15136,12 +15060,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Beaminster</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15187,12 +15111,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Berwick-upon-tweed</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -15203,13 +15127,13 @@
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H130" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J130" s="3" t="n">
         <v>0</v>
@@ -15238,12 +15162,12 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Bicester</t>
+          <t>Atherstone</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15254,7 +15178,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H131" s="5" t="n">
         <v>0</v>
@@ -15272,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N131" s="5" t="n">
         <v>0</v>
@@ -15289,12 +15213,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Bracknell</t>
+          <t>Ballyclare</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
@@ -15340,12 +15264,12 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Bridgwater</t>
+          <t>Beaminster</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15391,12 +15315,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Brinsworth</t>
+          <t>Berwick-upon-tweed</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -15407,13 +15331,13 @@
       </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H134" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -15442,12 +15366,12 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Bromsgrove</t>
+          <t>Bicester</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15493,12 +15417,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>Bridgwater</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
@@ -15544,12 +15468,12 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Chatham</t>
+          <t>Brinsworth</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -15595,12 +15519,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bromsgrove</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -15646,12 +15570,12 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Coalville</t>
+          <t>Canterbury</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15697,12 +15621,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Cottingham</t>
+          <t>Chatham</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
@@ -15748,12 +15672,12 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Cramlington</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15764,13 +15688,13 @@
       </c>
       <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H141" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141" s="5" t="n">
         <v>0</v>
@@ -15799,12 +15723,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Crawley</t>
+          <t>Coalville</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -15850,12 +15774,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Crewe</t>
+          <t>Cottingham</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15901,12 +15825,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Darlington</t>
+          <t>Crawley</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -15917,7 +15841,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H144" s="3" t="n">
         <v>0</v>
@@ -15938,7 +15862,7 @@
         <v>0</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O144" s="3" t="n">
         <v>0</v>
@@ -15952,12 +15876,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Dewsbury</t>
+          <t>Crewe</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -16003,12 +15927,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Didcot</t>
+          <t>Darlington</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -16019,7 +15943,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H146" s="3" t="n">
         <v>0</v>
@@ -16040,7 +15964,7 @@
         <v>0</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O146" s="3" t="n">
         <v>0</v>
@@ -16054,12 +15978,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Dewsbury</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -16105,12 +16029,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>East Grinstead</t>
+          <t>Didcot</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -16121,10 +16045,10 @@
       </c>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I148" s="3" t="n">
         <v>0</v>
@@ -16156,12 +16080,12 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>East Grinstead</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -16207,7 +16131,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Fareham</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -16226,7 +16150,7 @@
         <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>0</v>
@@ -16244,7 +16168,7 @@
         <v>0</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O150" s="3" t="n">
         <v>0</v>
@@ -16258,7 +16182,7 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Farnborough</t>
+          <t>Fareham</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -16277,7 +16201,7 @@
         <v>1</v>
       </c>
       <c r="H151" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I151" s="5" t="n">
         <v>0</v>
@@ -16295,7 +16219,7 @@
         <v>0</v>
       </c>
       <c r="N151" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O151" s="5" t="n">
         <v>0</v>
@@ -16309,12 +16233,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Godalming</t>
+          <t>Farnborough</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -16328,10 +16252,10 @@
         <v>1</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J152" s="3" t="n">
         <v>0</v>
@@ -16360,12 +16284,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Godalming</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -16376,13 +16300,13 @@
       </c>
       <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H153" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" s="5" t="n">
         <v>0</v>
@@ -16411,12 +16335,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Haywards Heath</t>
+          <t>Gosport</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -16462,12 +16386,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -16513,12 +16437,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Haywards Heath</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -16532,13 +16456,13 @@
         <v>1</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I156" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J156" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K156" s="3" t="n">
         <v>0</v>
@@ -16564,12 +16488,12 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -16615,12 +16539,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Keynsham</t>
+          <t>Huntingdon</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
@@ -16666,12 +16590,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Knowle</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -16682,7 +16606,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr"/>
       <c r="G159" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H159" s="5" t="n">
         <v>0</v>
@@ -16691,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K159" s="5" t="n">
         <v>0</v>
@@ -16717,12 +16641,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Knutsford</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -16768,12 +16692,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Maldon</t>
+          <t>Keynsham</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -16784,7 +16708,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr"/>
       <c r="G161" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H161" s="5" t="n">
         <v>0</v>
@@ -16793,7 +16717,7 @@
         <v>0</v>
       </c>
       <c r="J161" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K161" s="5" t="n">
         <v>0</v>
@@ -16819,12 +16743,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Melksham</t>
+          <t>Knowle</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
@@ -16870,12 +16794,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Newton Abbot</t>
+          <t>Leighton Buzzard</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -16886,13 +16810,13 @@
       </c>
       <c r="F163" s="4" t="inlineStr"/>
       <c r="G163" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H163" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J163" s="5" t="n">
         <v>0</v>
@@ -16921,12 +16845,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Newtownards</t>
+          <t>Maldon</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
@@ -16946,13 +16870,13 @@
         <v>0</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K164" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L164" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M164" s="3" t="n">
         <v>0</v>
@@ -16972,12 +16896,12 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Ramsgate</t>
+          <t>Melksham</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -17023,12 +16947,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Redditch</t>
+          <t>Newton Abbot</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -17039,13 +16963,13 @@
       </c>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H166" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J166" s="3" t="n">
         <v>0</v>
@@ -17074,12 +16998,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Rickmansworth</t>
+          <t>Newtownards</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -17090,22 +17014,22 @@
       </c>
       <c r="F167" s="4" t="inlineStr"/>
       <c r="G167" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H167" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I167" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J167" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="M167" s="5" t="n">
         <v>0</v>
@@ -17125,12 +17049,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Ringwood</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -17141,10 +17065,10 @@
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I168" s="3" t="n">
         <v>0</v>
@@ -17176,12 +17100,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Ramsgate</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -17227,12 +17151,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Redditch</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
@@ -17243,7 +17167,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H170" s="3" t="n">
         <v>0</v>
@@ -17261,7 +17185,7 @@
         <v>0</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N170" s="3" t="n">
         <v>0</v>
@@ -17278,12 +17202,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>Rickmansworth</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -17329,12 +17253,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ringwood</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -17345,10 +17269,10 @@
       </c>
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>0</v>
@@ -17380,12 +17304,12 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Stockport</t>
+          <t>Runcorn</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -17431,12 +17355,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Stonehouse</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -17459,13 +17383,13 @@
         <v>0</v>
       </c>
       <c r="K174" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L174" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M174" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N174" s="3" t="n">
         <v>0</v>
@@ -17482,12 +17406,12 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Swindon</t>
+          <t>Stafford</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -17498,10 +17422,10 @@
       </c>
       <c r="F175" s="4" t="inlineStr"/>
       <c r="G175" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H175" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I175" s="5" t="n">
         <v>0</v>
@@ -17533,12 +17457,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Thame</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -17584,12 +17508,12 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Truro</t>
+          <t>Stockport</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -17635,12 +17559,12 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Ventnor</t>
+          <t>Stonehouse</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
@@ -17651,10 +17575,10 @@
       </c>
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>0</v>
@@ -17663,7 +17587,7 @@
         <v>0</v>
       </c>
       <c r="K178" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L178" s="3" t="n">
         <v>0</v>
@@ -17686,12 +17610,12 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Ware</t>
+          <t>Swindon</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D179" s="5" t="n">
@@ -17705,10 +17629,10 @@
         <v>1</v>
       </c>
       <c r="H179" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J179" s="5" t="n">
         <v>0</v>
@@ -17737,12 +17661,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Welwyn Garden City</t>
+          <t>Thame</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -17753,7 +17677,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H180" s="3" t="n">
         <v>0</v>
@@ -17765,7 +17689,7 @@
         <v>0</v>
       </c>
       <c r="K180" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L180" s="3" t="n">
         <v>0</v>
@@ -17788,12 +17712,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Torquay</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
@@ -17804,7 +17728,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr"/>
       <c r="G181" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H181" s="5" t="n">
         <v>0</v>
@@ -17825,7 +17749,7 @@
         <v>0</v>
       </c>
       <c r="N181" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O181" s="5" t="n">
         <v>0</v>
@@ -17839,12 +17763,12 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Wokingham</t>
+          <t>Ventnor</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -17855,10 +17779,10 @@
       </c>
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H182" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="I182" s="3" t="n">
         <v>0</v>
@@ -17890,12 +17814,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Woodbridge</t>
+          <t>Ware</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -17906,13 +17830,13 @@
       </c>
       <c r="F183" s="4" t="inlineStr"/>
       <c r="G183" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H183" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J183" s="5" t="n">
         <v>0</v>
@@ -17941,12 +17865,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Waterlooville</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
@@ -17957,13 +17881,13 @@
       </c>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H184" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J184" s="3" t="n">
         <v>0</v>
@@ -17992,16 +17916,16 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Alresford</t>
+          <t>Welwyn Garden City</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" s="5" t="n">
         <v>0</v>
@@ -18020,7 +17944,7 @@
         <v>0</v>
       </c>
       <c r="K185" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L185" s="5" t="n">
         <v>0</v>
@@ -18043,16 +17967,16 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Ashington</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E186" s="3" t="n">
         <v>0</v>
@@ -18080,7 +18004,7 @@
         <v>0</v>
       </c>
       <c r="N186" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O186" s="3" t="n">
         <v>0</v>
@@ -18094,23 +18018,23 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Aylesford</t>
+          <t>Wokingham</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E187" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F187" s="4" t="inlineStr"/>
       <c r="G187" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H187" s="5" t="n">
         <v>0</v>
@@ -18145,23 +18069,23 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Ballyclare</t>
+          <t>Woodbridge</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E188" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H188" s="3" t="n">
         <v>0</v>
@@ -18196,23 +18120,23 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Ballymena</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E189" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F189" s="4" t="inlineStr"/>
       <c r="G189" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H189" s="5" t="n">
         <v>0</v>
@@ -18247,12 +18171,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Banbury</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -18298,12 +18222,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Banstead</t>
+          <t>Alresford</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
@@ -18349,12 +18273,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Bexhill-on-sea</t>
+          <t>Ashington</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -18400,12 +18324,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Billericay</t>
+          <t>Aylesford</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
@@ -18451,12 +18375,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Bingley</t>
+          <t>Ballymena</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -18502,12 +18426,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Bishop's Stortford</t>
+          <t>Banbury</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
@@ -18553,12 +18477,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Bognor Regis</t>
+          <t>Banstead</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -18604,12 +18528,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Bexhill-on-sea</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -18655,12 +18579,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Buckingham</t>
+          <t>Billericay</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -18671,7 +18595,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H198" s="3" t="n">
         <v>0</v>
@@ -18692,7 +18616,7 @@
         <v>0</v>
       </c>
       <c r="N198" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O198" s="3" t="n">
         <v>0</v>
@@ -18706,12 +18630,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Burford</t>
+          <t>Bingley</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -18722,10 +18646,10 @@
       </c>
       <c r="F199" s="4" t="inlineStr"/>
       <c r="G199" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H199" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I199" s="5" t="n">
         <v>0</v>
@@ -18757,12 +18681,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Bury St Edmunds</t>
+          <t>Bishop's Stortford</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -18808,12 +18732,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Caerphilly</t>
+          <t>Bognor Regis</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -18859,12 +18783,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Camberley</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -18910,12 +18834,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Carrickfergus</t>
+          <t>Bracknell</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -18961,12 +18885,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Chelmsley Wood</t>
+          <t>Buckingham</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -18977,7 +18901,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H204" s="3" t="n">
         <v>0</v>
@@ -18998,7 +18922,7 @@
         <v>0</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O204" s="3" t="n">
         <v>0</v>
@@ -19012,12 +18936,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Cheltenham</t>
+          <t>Bury St Edmunds</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -19063,12 +18987,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Chesham</t>
+          <t>Caerphilly</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -19114,12 +19038,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Chichester</t>
+          <t>Camberley</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -19165,12 +19089,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Chippenham</t>
+          <t>Carrickfergus</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -19216,12 +19140,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Cleethorpes</t>
+          <t>Chelmsley Wood</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -19267,12 +19191,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Cobham</t>
+          <t>Cheltenham</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -19283,10 +19207,10 @@
       </c>
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>0</v>
@@ -19318,12 +19242,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>Chichester</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -19334,7 +19258,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr"/>
       <c r="G211" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H211" s="5" t="n">
         <v>0</v>
@@ -19343,7 +19267,7 @@
         <v>0</v>
       </c>
       <c r="J211" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K211" s="5" t="n">
         <v>0</v>
@@ -19369,12 +19293,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Colden Common</t>
+          <t>Chippenham</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -19385,7 +19309,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H212" s="3" t="n">
         <v>0</v>
@@ -19406,7 +19330,7 @@
         <v>0</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O212" s="3" t="n">
         <v>0</v>
@@ -19420,12 +19344,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Congleton</t>
+          <t>Cleethorpes</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
@@ -19471,12 +19395,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Devizes</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -19487,7 +19411,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr"/>
       <c r="G214" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H214" s="3" t="n">
         <v>0</v>
@@ -19496,7 +19420,7 @@
         <v>0</v>
       </c>
       <c r="J214" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K214" s="3" t="n">
         <v>0</v>
@@ -19522,12 +19446,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Dorchester</t>
+          <t>Colden Common</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
@@ -19538,7 +19462,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr"/>
       <c r="G215" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H215" s="5" t="n">
         <v>0</v>
@@ -19559,7 +19483,7 @@
         <v>0</v>
       </c>
       <c r="N215" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O215" s="5" t="n">
         <v>0</v>
@@ -19573,12 +19497,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Dorking</t>
+          <t>Congleton</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -19624,12 +19548,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Dursley</t>
+          <t>Devizes</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
@@ -19675,12 +19599,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Eastbourne</t>
+          <t>Dorchester</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
@@ -19691,10 +19615,10 @@
       </c>
       <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I218" s="3" t="n">
         <v>0</v>
@@ -19726,12 +19650,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Ellesmere Port</t>
+          <t>Dorking</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
@@ -19777,12 +19701,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Ely</t>
+          <t>Dursley</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
@@ -19828,12 +19752,12 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Epsom</t>
+          <t>Eastbourne</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
@@ -19847,7 +19771,7 @@
         <v>0</v>
       </c>
       <c r="H221" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I221" s="5" t="n">
         <v>0</v>
@@ -19856,7 +19780,7 @@
         <v>0</v>
       </c>
       <c r="K221" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L221" s="5" t="n">
         <v>0</v>
@@ -19879,12 +19803,12 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Esher</t>
+          <t>Ellesmere Port</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
@@ -19895,13 +19819,13 @@
       </c>
       <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H222" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J222" s="3" t="n">
         <v>0</v>
@@ -19930,12 +19854,12 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Felixstowe</t>
+          <t>Epsom</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
@@ -19946,7 +19870,7 @@
       </c>
       <c r="F223" s="4" t="inlineStr"/>
       <c r="G223" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H223" s="5" t="n">
         <v>0</v>
@@ -19958,7 +19882,7 @@
         <v>0</v>
       </c>
       <c r="K223" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L223" s="5" t="n">
         <v>0</v>
@@ -19981,7 +19905,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Fetcham</t>
+          <t>Esher</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -20003,7 +19927,7 @@
         <v>0</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J224" s="3" t="n">
         <v>0</v>
@@ -20018,7 +19942,7 @@
         <v>0</v>
       </c>
       <c r="N224" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O224" s="3" t="n">
         <v>0</v>
@@ -20032,12 +19956,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Freshwater</t>
+          <t>Felixstowe</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D225" s="5" t="n">
@@ -20048,10 +19972,10 @@
       </c>
       <c r="F225" s="4" t="inlineStr"/>
       <c r="G225" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H225" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I225" s="5" t="n">
         <v>0</v>
@@ -20083,12 +20007,12 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Gainsborough</t>
+          <t>Fetcham</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
@@ -20099,7 +20023,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
         <v>0</v>
@@ -20120,7 +20044,7 @@
         <v>0</v>
       </c>
       <c r="N226" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O226" s="3" t="n">
         <v>0</v>
@@ -20134,12 +20058,12 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Godstone</t>
+          <t>Freshwater</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D227" s="5" t="n">
@@ -20150,10 +20074,10 @@
       </c>
       <c r="F227" s="4" t="inlineStr"/>
       <c r="G227" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H227" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I227" s="5" t="n">
         <v>0</v>
@@ -20185,12 +20109,12 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Goole</t>
+          <t>Frodsham</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
@@ -20236,12 +20160,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Grange-over-sands</t>
+          <t>Gainsborough</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
@@ -20252,10 +20176,10 @@
       </c>
       <c r="F229" s="4" t="inlineStr"/>
       <c r="G229" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H229" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I229" s="5" t="n">
         <v>0</v>
@@ -20287,12 +20211,12 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Grantham</t>
+          <t>Godstone</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
@@ -20338,12 +20262,12 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Gravesend</t>
+          <t>Goole</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
@@ -20354,10 +20278,10 @@
       </c>
       <c r="F231" s="4" t="inlineStr"/>
       <c r="G231" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H231" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I231" s="5" t="n">
         <v>0</v>
@@ -20389,12 +20313,12 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Hailsham</t>
+          <t>Grange-over-sands</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
@@ -20408,10 +20332,10 @@
         <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J232" s="3" t="n">
         <v>0</v>
@@ -20440,12 +20364,12 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Grantham</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D233" s="5" t="n">
@@ -20456,10 +20380,10 @@
       </c>
       <c r="F233" s="4" t="inlineStr"/>
       <c r="G233" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H233" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I233" s="5" t="n">
         <v>0</v>
@@ -20491,12 +20415,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Harrogate</t>
+          <t>Gravesend</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
@@ -20507,10 +20431,10 @@
       </c>
       <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I234" s="3" t="n">
         <v>0</v>
@@ -20542,12 +20466,12 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>Hailsham</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
@@ -20558,13 +20482,13 @@
       </c>
       <c r="F235" s="4" t="inlineStr"/>
       <c r="G235" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H235" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J235" s="5" t="n">
         <v>0</v>
@@ -20593,12 +20517,12 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
@@ -20644,12 +20568,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Hebburn</t>
+          <t>Harrogate</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
@@ -20660,7 +20584,7 @@
       </c>
       <c r="F237" s="4" t="inlineStr"/>
       <c r="G237" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H237" s="5" t="n">
         <v>0</v>
@@ -20681,7 +20605,7 @@
         <v>0</v>
       </c>
       <c r="N237" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O237" s="5" t="n">
         <v>0</v>
@@ -20695,12 +20619,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Henley-on-thames</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
@@ -20746,12 +20670,12 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Hertford</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
@@ -20762,10 +20686,10 @@
       </c>
       <c r="F239" s="4" t="inlineStr"/>
       <c r="G239" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H239" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I239" s="5" t="n">
         <v>0</v>
@@ -20797,12 +20721,12 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Huntingdon</t>
+          <t>Hebburn</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
@@ -20813,7 +20737,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr"/>
       <c r="G240" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H240" s="3" t="n">
         <v>0</v>
@@ -20834,7 +20758,7 @@
         <v>0</v>
       </c>
       <c r="N240" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O240" s="3" t="n">
         <v>0</v>
@@ -20848,12 +20772,12 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Ilminster</t>
+          <t>Henley-on-thames</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D241" s="5" t="n">
@@ -20899,12 +20823,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Jarrow</t>
+          <t>Hertford</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
@@ -20950,12 +20874,12 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Kendal</t>
+          <t>Ilminster</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
@@ -20966,10 +20890,10 @@
       </c>
       <c r="F243" s="4" t="inlineStr"/>
       <c r="G243" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H243" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I243" s="5" t="n">
         <v>0</v>
@@ -21001,12 +20925,12 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Kirriemuir</t>
+          <t>Kendal</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
@@ -21017,10 +20941,10 @@
       </c>
       <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I244" s="3" t="n">
         <v>0</v>
@@ -21052,12 +20976,12 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Kirriemuir</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
@@ -21103,12 +21027,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Leighton Buzzard</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
@@ -21154,12 +21078,12 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Lichfield</t>
+          <t>Leigh</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
@@ -21170,7 +21094,7 @@
       </c>
       <c r="F247" s="4" t="inlineStr"/>
       <c r="G247" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H247" s="5" t="n">
         <v>0</v>
@@ -21191,7 +21115,7 @@
         <v>0</v>
       </c>
       <c r="N247" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O247" s="5" t="n">
         <v>0</v>
@@ -21205,12 +21129,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Liskeard</t>
+          <t>Lichfield</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
@@ -21221,7 +21145,7 @@
       </c>
       <c r="F248" s="2" t="inlineStr"/>
       <c r="G248" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H248" s="3" t="n">
         <v>0</v>
@@ -21242,7 +21166,7 @@
         <v>0</v>
       </c>
       <c r="N248" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O248" s="3" t="n">
         <v>0</v>
@@ -21256,12 +21180,12 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Littlehampton</t>
+          <t>Liskeard</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
@@ -21307,12 +21231,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Loughborough</t>
+          <t>Littlehampton</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
@@ -21358,12 +21282,12 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Marlborough</t>
+          <t>Loughborough</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
@@ -21409,12 +21333,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Marlow</t>
+          <t>Marlborough</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
@@ -21460,12 +21384,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Mirfield</t>
+          <t>Marlow</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
@@ -21511,12 +21435,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Mirfield</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
@@ -21527,13 +21451,13 @@
       </c>
       <c r="F254" s="2" t="inlineStr"/>
       <c r="G254" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H254" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I254" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J254" s="3" t="n">
         <v>0</v>
@@ -21562,12 +21486,12 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
@@ -21578,13 +21502,13 @@
       </c>
       <c r="F255" s="4" t="inlineStr"/>
       <c r="G255" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H255" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I255" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J255" s="5" t="n">
         <v>0</v>
@@ -21613,12 +21537,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
@@ -21664,12 +21588,12 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Newbury</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
@@ -21680,7 +21604,7 @@
       </c>
       <c r="F257" s="4" t="inlineStr"/>
       <c r="G257" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H257" s="5" t="n">
         <v>0</v>
@@ -21692,7 +21616,7 @@
         <v>0</v>
       </c>
       <c r="K257" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L257" s="5" t="n">
         <v>0</v>
@@ -21715,12 +21639,12 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Newmarket</t>
+          <t>Newbury</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
@@ -21731,7 +21655,7 @@
       </c>
       <c r="F258" s="2" t="inlineStr"/>
       <c r="G258" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H258" s="3" t="n">
         <v>0</v>
@@ -21743,7 +21667,7 @@
         <v>0</v>
       </c>
       <c r="K258" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L258" s="3" t="n">
         <v>0</v>
@@ -21766,12 +21690,12 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>North Shields</t>
+          <t>Newmarket</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
@@ -21817,12 +21741,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Otley</t>
+          <t>Newport-on-tay</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
@@ -21868,12 +21792,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>North Shields</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
@@ -21884,13 +21808,13 @@
       </c>
       <c r="F261" s="4" t="inlineStr"/>
       <c r="G261" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H261" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I261" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J261" s="5" t="n">
         <v>0</v>
@@ -21919,12 +21843,12 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Pickering</t>
+          <t>Otley</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D262" s="3" t="n">
@@ -21970,12 +21894,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Pontypridd</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
@@ -21986,13 +21910,13 @@
       </c>
       <c r="F263" s="4" t="inlineStr"/>
       <c r="G263" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H263" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I263" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J263" s="5" t="n">
         <v>0</v>
@@ -22021,12 +21945,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Portishead</t>
+          <t>Pickering</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D264" s="3" t="n">
@@ -22072,12 +21996,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Pontefract</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
@@ -22123,12 +22047,12 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Redruth</t>
+          <t>Portishead</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
@@ -22174,12 +22098,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
@@ -22225,12 +22149,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Redruth</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D268" s="3" t="n">
@@ -22241,7 +22165,7 @@
       </c>
       <c r="F268" s="2" t="inlineStr"/>
       <c r="G268" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H268" s="3" t="n">
         <v>0</v>
@@ -22253,7 +22177,7 @@
         <v>0</v>
       </c>
       <c r="K268" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L268" s="3" t="n">
         <v>0</v>
@@ -22276,12 +22200,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Rochester</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D269" s="5" t="n">
@@ -22327,12 +22251,12 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Rugby</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D270" s="3" t="n">
@@ -22343,7 +22267,7 @@
       </c>
       <c r="F270" s="2" t="inlineStr"/>
       <c r="G270" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H270" s="3" t="n">
         <v>0</v>
@@ -22355,7 +22279,7 @@
         <v>0</v>
       </c>
       <c r="K270" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L270" s="3" t="n">
         <v>0</v>
@@ -22378,12 +22302,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Runcorn</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D271" s="5" t="n">
@@ -22429,12 +22353,12 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Ryton</t>
+          <t>Romsey</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D272" s="3" t="n">
@@ -22480,12 +22404,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Rugby</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
@@ -22531,12 +22455,12 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Seaham</t>
+          <t>Ryton</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D274" s="3" t="n">
@@ -22582,12 +22506,12 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Shepperton</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
@@ -22633,12 +22557,12 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Shipley</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D276" s="3" t="n">
@@ -22684,12 +22608,12 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Seaham</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
@@ -22735,12 +22659,12 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Snodland</t>
+          <t>Shepperton</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D278" s="3" t="n">
@@ -22751,13 +22675,13 @@
       </c>
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H278" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I278" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J278" s="3" t="n">
         <v>0</v>
@@ -22786,12 +22710,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Southam</t>
+          <t>Shipley</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D279" s="5" t="n">
@@ -22837,12 +22761,12 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Southend-on-sea</t>
+          <t>Shirley</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D280" s="3" t="n">
@@ -22888,12 +22812,12 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Spennymoor</t>
+          <t>Snodland</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D281" s="5" t="n">
@@ -22904,13 +22828,13 @@
       </c>
       <c r="F281" s="4" t="inlineStr"/>
       <c r="G281" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H281" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J281" s="5" t="n">
         <v>0</v>
@@ -22939,12 +22863,12 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>St. Austell</t>
+          <t>Southam</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D282" s="3" t="n">
@@ -22990,12 +22914,12 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>St. Ives</t>
+          <t>Southend-on-sea</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D283" s="5" t="n">
@@ -23041,12 +22965,12 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>St. Neots</t>
+          <t>Spennymoor</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D284" s="3" t="n">
@@ -23092,12 +23016,12 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Staines</t>
+          <t>St. Austell</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D285" s="5" t="n">
@@ -23143,12 +23067,12 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>St. Ives</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D286" s="3" t="n">
@@ -23194,12 +23118,12 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Stroud</t>
+          <t>St. Neots</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D287" s="5" t="n">
@@ -23245,12 +23169,12 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Taunton</t>
+          <t>Staines</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D288" s="3" t="n">
@@ -23296,12 +23220,12 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Tipton</t>
+          <t>Street</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D289" s="5" t="n">
@@ -23347,12 +23271,12 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Stroud</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D290" s="3" t="n">
@@ -23363,13 +23287,13 @@
       </c>
       <c r="F290" s="2" t="inlineStr"/>
       <c r="G290" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H290" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I290" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J290" s="3" t="n">
         <v>0</v>
@@ -23398,12 +23322,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Taunton</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D291" s="5" t="n">
@@ -23449,12 +23373,12 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Trowbridge</t>
+          <t>Tipton</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D292" s="3" t="n">
@@ -23500,12 +23424,12 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Ulverston</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
@@ -23519,10 +23443,10 @@
         <v>0</v>
       </c>
       <c r="H293" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I293" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J293" s="5" t="n">
         <v>0</v>
@@ -23551,12 +23475,12 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Trowbridge</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D294" s="3" t="n">
@@ -23602,12 +23526,12 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Waltham Cross</t>
+          <t>Ulverston</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D295" s="5" t="n">
@@ -23618,10 +23542,10 @@
       </c>
       <c r="F295" s="4" t="inlineStr"/>
       <c r="G295" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H295" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I295" s="5" t="n">
         <v>0</v>
@@ -23653,12 +23577,12 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D296" s="3" t="n">
@@ -23704,12 +23628,12 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Waterlooville</t>
+          <t>Waltham Cross</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D297" s="5" t="n">
@@ -23755,12 +23679,12 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Wellingborough</t>
+          <t>Walton-on-thames</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D298" s="3" t="n">
@@ -23806,12 +23730,12 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Wellingborough</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D299" s="5" t="n">
@@ -23857,12 +23781,12 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D300" s="3" t="n">
@@ -23908,12 +23832,12 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D301" s="5" t="n">
@@ -23959,12 +23883,12 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Whitstable</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D302" s="3" t="n">
@@ -23975,13 +23899,13 @@
       </c>
       <c r="F302" s="2" t="inlineStr"/>
       <c r="G302" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H302" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I302" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J302" s="3" t="n">
         <v>0</v>
@@ -24010,12 +23934,12 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Wilmslow</t>
+          <t>Whitstable</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D303" s="5" t="n">
@@ -24026,13 +23950,13 @@
       </c>
       <c r="F303" s="4" t="inlineStr"/>
       <c r="G303" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H303" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I303" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J303" s="5" t="n">
         <v>0</v>
@@ -24061,12 +23985,12 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Wilmslow</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D304" s="3" t="n">
@@ -24112,12 +24036,12 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Witney</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D305" s="5" t="n">
@@ -24163,12 +24087,12 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Worksop</t>
+          <t>Witney</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D306" s="3" t="n">
@@ -24214,12 +24138,12 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Wymondham</t>
+          <t>Worksop</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D307" s="5" t="n">
@@ -24257,8 +24181,59 @@
         <v>0</v>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>Wymondham</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>Norfolk</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E308" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F308" s="2" t="inlineStr"/>
+      <c r="G308" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H308" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K308" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L308" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M308" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N308" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O308" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O307"/>
+  <autoFilter ref="A1:O308"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24362,7 +24337,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="5" t="n">
@@ -24377,11 +24352,11 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
@@ -24402,7 +24377,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
@@ -24442,7 +24417,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr"/>
@@ -24459,7 +24434,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
@@ -24480,13 +24455,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr"/>
@@ -24499,7 +24474,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
@@ -24563,7 +24538,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
@@ -24580,7 +24555,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="5" t="n">
@@ -24620,7 +24595,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
@@ -24645,7 +24620,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
@@ -24708,13 +24683,13 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr"/>
@@ -24727,7 +24702,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr"/>
@@ -24750,7 +24725,7 @@
         <v>11</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr"/>
@@ -24786,11 +24761,11 @@
       </c>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
@@ -24803,10 +24778,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>7</v>
@@ -24901,7 +24876,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
@@ -24918,7 +24893,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
       <c r="D33" s="4" t="inlineStr"/>
@@ -24938,25 +24913,27 @@
         <v>180</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -24966,13 +24943,13 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr"/>
@@ -25049,7 +25026,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -25080,11 +25057,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
       <c r="D41" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr"/>
@@ -25146,13 +25123,13 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G45" s="5" t="n">
         <v>16</v>
@@ -25184,7 +25161,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr"/>
@@ -25203,10 +25180,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
@@ -25254,7 +25231,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
       <c r="D51" s="4" t="inlineStr"/>
@@ -25301,7 +25278,7 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr"/>
@@ -25333,7 +25310,7 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="3" t="n">
@@ -25382,7 +25359,7 @@
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
       <c r="D59" s="4" t="inlineStr"/>
@@ -25420,7 +25397,7 @@
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
       <c r="D61" s="4" t="inlineStr"/>
@@ -25460,15 +25437,17 @@
       <c r="B63" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="C63" s="5" t="n">
-        <v>1</v>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
       </c>
       <c r="D63" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr"/>
@@ -25483,7 +25462,7 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>3</v>
@@ -25536,7 +25515,7 @@
         </is>
       </c>
       <c r="B67" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
       <c r="D67" s="4" t="inlineStr"/>
@@ -25583,7 +25562,7 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr"/>
@@ -25600,7 +25579,7 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>
@@ -25657,7 +25636,7 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>2</v>
@@ -25676,7 +25655,7 @@
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
       <c r="D75" s="4" t="inlineStr"/>
@@ -25754,7 +25733,7 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C79" s="5" t="n">
         <v>2</v>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1643</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1789</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="6">
@@ -9580,30 +9580,30 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Farnham</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>/oxford/service-administrator-jobs</t>
+          <t>/farnham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>0</v>
@@ -9612,7 +9612,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L25" s="5" t="n">
         <v>0</v>
@@ -9635,31 +9635,31 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>/oxford/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="I26" s="3" t="n">
         <v>0</v>
       </c>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>0</v>
@@ -9690,30 +9690,30 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Farnham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>/farnham/service-administrator-jobs</t>
+          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>0</v>
@@ -11670,12 +11670,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Wakefield</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>/shrewsbury/service-administrator-jobs</t>
+          <t>/wakefield/jobs</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
@@ -11725,27 +11725,27 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Wakefield</t>
+          <t>Ashford</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>/wakefield/jobs</t>
+          <t>/ashford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0</v>
@@ -11780,12 +11780,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Ashford</t>
+          <t>Gloucester</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>/ashford/service-administrator-jobs</t>
+          <t>/gloucester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Gloucester</t>
+          <t>Maidstone</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
@@ -11851,17 +11851,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>/gloucester/service-administrator-jobs</t>
+          <t>/maidstone/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="3" t="n">
         <v>0</v>
@@ -11890,12 +11890,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Maidstone</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
@@ -11906,17 +11906,17 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>/maidstone/service-administrator-jobs</t>
+          <t>/shrewsbury/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" s="5" t="n">
         <v>0</v>
@@ -15672,12 +15672,12 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Coalville</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15723,12 +15723,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Coalville</t>
+          <t>Cottingham</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -15774,12 +15774,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Cottingham</t>
+          <t>Crawley</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15825,12 +15825,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Crawley</t>
+          <t>Crewe</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -15876,12 +15876,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Crewe</t>
+          <t>Darlington</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H145" s="5" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
         <v>0</v>
       </c>
       <c r="N145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O145" s="5" t="n">
         <v>0</v>
@@ -15927,12 +15927,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Darlington</t>
+          <t>Dewsbury</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -15943,7 +15943,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H146" s="3" t="n">
         <v>0</v>
@@ -15964,7 +15964,7 @@
         <v>0</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O146" s="3" t="n">
         <v>0</v>
@@ -15978,12 +15978,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Dewsbury</t>
+          <t>Didcot</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -16029,12 +16029,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Didcot</t>
+          <t>East Grinstead</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -16045,10 +16045,10 @@
       </c>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148" s="3" t="n">
         <v>0</v>
@@ -16080,12 +16080,12 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>East Grinstead</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Fareham</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -16150,7 +16150,7 @@
         <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>0</v>
@@ -16168,7 +16168,7 @@
         <v>0</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O150" s="3" t="n">
         <v>0</v>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Fareham</t>
+          <t>Farnborough</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -16201,7 +16201,7 @@
         <v>1</v>
       </c>
       <c r="H151" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151" s="5" t="n">
         <v>0</v>
@@ -16219,7 +16219,7 @@
         <v>0</v>
       </c>
       <c r="N151" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O151" s="5" t="n">
         <v>0</v>
@@ -16233,12 +16233,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Farnborough</t>
+          <t>Godalming</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -16252,10 +16252,10 @@
         <v>1</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J152" s="3" t="n">
         <v>0</v>
@@ -16284,12 +16284,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Godalming</t>
+          <t>Gosport</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -16303,10 +16303,10 @@
         <v>1</v>
       </c>
       <c r="H153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" s="5" t="n">
         <v>0</v>
@@ -16335,12 +16335,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Gosport</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -16351,10 +16351,10 @@
       </c>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>0</v>
@@ -16386,12 +16386,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Haywards Heath</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -16402,10 +16402,10 @@
       </c>
       <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H155" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I155" s="5" t="n">
         <v>0</v>
@@ -16437,7 +16437,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Haywards Heath</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -16453,10 +16453,10 @@
       </c>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I156" s="3" t="n">
         <v>0</v>
@@ -16488,12 +16488,12 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Huntingdon</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Huntingdon</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
@@ -16555,7 +16555,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H158" s="3" t="n">
         <v>0</v>
@@ -16564,7 +16564,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K158" s="3" t="n">
         <v>0</v>
@@ -16590,12 +16590,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -16606,7 +16606,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr"/>
       <c r="G159" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H159" s="5" t="n">
         <v>0</v>
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K159" s="5" t="n">
         <v>0</v>
@@ -16641,12 +16641,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Keynsham</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -16692,12 +16692,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Keynsham</t>
+          <t>Knowle</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -16743,12 +16743,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Knowle</t>
+          <t>Leighton Buzzard</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
@@ -16794,12 +16794,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Leighton Buzzard</t>
+          <t>Maldon</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -16810,16 +16810,16 @@
       </c>
       <c r="F163" s="4" t="inlineStr"/>
       <c r="G163" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H163" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J163" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="K163" s="5" t="n">
         <v>0</v>
@@ -16845,12 +16845,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Maldon</t>
+          <t>Melksham</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
@@ -16861,7 +16861,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H164" s="3" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>0</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K164" s="3" t="n">
         <v>0</v>
@@ -16896,12 +16896,12 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Melksham</t>
+          <t>Newton Abbot</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -16912,13 +16912,13 @@
       </c>
       <c r="F165" s="4" t="inlineStr"/>
       <c r="G165" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H165" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J165" s="5" t="n">
         <v>0</v>
@@ -16947,12 +16947,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Newton Abbot</t>
+          <t>Newtownards</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -16963,13 +16963,13 @@
       </c>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J166" s="3" t="n">
         <v>0</v>
@@ -16978,7 +16978,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M166" s="3" t="n">
         <v>0</v>
@@ -16998,12 +16998,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Newtownards</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr"/>
       <c r="G167" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H167" s="5" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M167" s="5" t="n">
         <v>0</v>
@@ -17049,12 +17049,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Perth</t>
+          <t>Ramsgate</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -17100,12 +17100,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Ramsgate</t>
+          <t>Redditch</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -17151,12 +17151,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Redditch</t>
+          <t>Rickmansworth</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
@@ -17202,12 +17202,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Rickmansworth</t>
+          <t>Ringwood</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -17218,10 +17218,10 @@
       </c>
       <c r="F171" s="4" t="inlineStr"/>
       <c r="G171" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H171" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I171" s="5" t="n">
         <v>0</v>
@@ -17253,12 +17253,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Ringwood</t>
+          <t>Runcorn</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -17269,10 +17269,10 @@
       </c>
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>0</v>
@@ -17304,12 +17304,12 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Runcorn</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -17320,7 +17320,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr"/>
       <c r="G173" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H173" s="5" t="n">
         <v>0</v>
@@ -17338,7 +17338,7 @@
         <v>0</v>
       </c>
       <c r="M173" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N173" s="5" t="n">
         <v>0</v>
@@ -17355,12 +17355,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Stafford</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -17371,7 +17371,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H174" s="3" t="n">
         <v>0</v>
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="M174" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N174" s="3" t="n">
         <v>0</v>
@@ -17406,12 +17406,12 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -17457,12 +17457,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Stockport</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Stockport</t>
+          <t>Stonehouse</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -17524,7 +17524,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr"/>
       <c r="G177" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H177" s="5" t="n">
         <v>0</v>
@@ -17536,7 +17536,7 @@
         <v>0</v>
       </c>
       <c r="K177" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L177" s="5" t="n">
         <v>0</v>
@@ -17559,12 +17559,12 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Stonehouse</t>
+          <t>Swindon</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
@@ -17578,7 +17578,7 @@
         <v>1</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I178" s="3" t="n">
         <v>0</v>
@@ -17587,7 +17587,7 @@
         <v>0</v>
       </c>
       <c r="K178" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L178" s="3" t="n">
         <v>0</v>
@@ -17610,12 +17610,12 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Swindon</t>
+          <t>Thame</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D179" s="5" t="n">
@@ -17626,10 +17626,10 @@
       </c>
       <c r="F179" s="4" t="inlineStr"/>
       <c r="G179" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H179" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I179" s="5" t="n">
         <v>0</v>
@@ -17661,12 +17661,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Thame</t>
+          <t>Torquay</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Ventnor</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
@@ -17728,10 +17728,10 @@
       </c>
       <c r="F181" s="4" t="inlineStr"/>
       <c r="G181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H181" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="I181" s="5" t="n">
         <v>0</v>
@@ -17763,12 +17763,12 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Ventnor</t>
+          <t>Ware</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -17779,13 +17779,13 @@
       </c>
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J182" s="3" t="n">
         <v>0</v>
@@ -17814,12 +17814,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Ware</t>
+          <t>Waterlooville</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Waterlooville</t>
+          <t>Welwyn Garden City</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
@@ -17887,13 +17887,13 @@
         <v>0</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J184" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K184" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L184" s="3" t="n">
         <v>0</v>
@@ -17916,12 +17916,12 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Welwyn Garden City</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
@@ -17944,7 +17944,7 @@
         <v>0</v>
       </c>
       <c r="K185" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L185" s="5" t="n">
         <v>0</v>
@@ -17953,7 +17953,7 @@
         <v>0</v>
       </c>
       <c r="N185" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O185" s="5" t="n">
         <v>0</v>
@@ -17967,12 +17967,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Wokingham</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
@@ -17983,7 +17983,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H186" s="3" t="n">
         <v>0</v>
@@ -18004,7 +18004,7 @@
         <v>0</v>
       </c>
       <c r="N186" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O186" s="3" t="n">
         <v>0</v>
@@ -18018,12 +18018,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Wokingham</t>
+          <t>Woodbridge</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
@@ -18069,12 +18069,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Woodbridge</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
@@ -18120,23 +18120,23 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E189" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F189" s="4" t="inlineStr"/>
       <c r="G189" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H189" s="5" t="n">
         <v>0</v>
@@ -18171,12 +18171,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Alresford</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -18222,12 +18222,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Alresford</t>
+          <t>Ashington</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
@@ -18273,12 +18273,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Ashington</t>
+          <t>Aylesford</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Aylesford</t>
+          <t>Ballymena</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
@@ -18375,12 +18375,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Ballymena</t>
+          <t>Banbury</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -18426,12 +18426,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Banbury</t>
+          <t>Banstead</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
@@ -18477,12 +18477,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Banstead</t>
+          <t>Bexhill-on-sea</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -18528,12 +18528,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Bexhill-on-sea</t>
+          <t>Billericay</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -18579,12 +18579,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Billericay</t>
+          <t>Bingley</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -18630,12 +18630,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Bingley</t>
+          <t>Bishop's Stortford</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Bishop's Stortford</t>
+          <t>Bognor Regis</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Bognor Regis</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -18783,12 +18783,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Bracknell</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -18834,12 +18834,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Bracknell</t>
+          <t>Buckingham</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr"/>
       <c r="G203" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H203" s="5" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>0</v>
       </c>
       <c r="N203" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O203" s="5" t="n">
         <v>0</v>
@@ -18885,12 +18885,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Buckingham</t>
+          <t>Bury St Edmunds</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -18901,7 +18901,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H204" s="3" t="n">
         <v>0</v>
@@ -18922,7 +18922,7 @@
         <v>0</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O204" s="3" t="n">
         <v>0</v>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Bury St Edmunds</t>
+          <t>Caerphilly</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -18987,12 +18987,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Caerphilly</t>
+          <t>Camberley</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -19038,12 +19038,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Camberley</t>
+          <t>Carrickfergus</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -19089,12 +19089,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Carrickfergus</t>
+          <t>Chelmsley Wood</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -19140,12 +19140,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Chelmsley Wood</t>
+          <t>Cheltenham</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -19191,12 +19191,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Cheltenham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -24538,7 +24538,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>11</v>
@@ -25026,7 +25026,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>2</v>
@@ -25359,7 +25359,7 @@
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
       <c r="D59" s="4" t="inlineStr"/>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1701</v>
+        <v>1576</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1009</v>
+        <v>996</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>526</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -710,49 +710,49 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>738</v>
+        <v>756</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Real Estate &amp; Property</t>
+          <t>Call Centre / CustomerService</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>14</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Real Estate &amp; Property</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>634</v>
+        <v>709</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Call Centre / CustomerService</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>613</v>
+        <v>652</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>172</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>16</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>6</v>
@@ -797,25 +797,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Executive Positions</t>
+          <t>Consulting &amp; Corporate Strategy</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="C14" s="8" t="inlineStr"/>
+        <v>203</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Consulting &amp; Corporate Strategy</t>
+          <t>Executive Positions</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -825,10 +827,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -838,7 +840,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
@@ -852,7 +854,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>1392</v>
+        <v>1415</v>
       </c>
     </row>
   </sheetData>
@@ -25847,7 +25849,7 @@
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.4 / 0/14</t>
+          <t>6 / 3.5 / 1/14</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
@@ -25917,7 +25919,7 @@
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>7 / 4.7 / 6/14</t>
+          <t>9 / 4.9 / 6/14</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
@@ -25952,7 +25954,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr"/>
@@ -25982,7 +25984,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -25993,7 +25995,7 @@
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -26069,7 +26071,7 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>3 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
@@ -26108,7 +26110,7 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/14</t>
+          <t>2 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr"/>
@@ -26157,7 +26159,7 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -26327,7 +26329,7 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.8 / 0/14</t>
+          <t>3 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
@@ -26337,7 +26339,7 @@
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -26366,7 +26368,7 @@
       <c r="D15" s="14" t="inlineStr"/>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/14</t>
+          <t>3 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
@@ -26555,7 +26557,7 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
@@ -26850,7 +26852,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/14</t>
+          <t>2 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -26885,7 +26887,7 @@
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26907,7 +26909,7 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -27049,7 +27051,7 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.0 / 0/14</t>
+          <t>4 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
@@ -27059,12 +27061,12 @@
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.4 / 0/14</t>
+          <t>3 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="I32" s="13" t="inlineStr">
@@ -27225,7 +27227,7 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.9 / 0/14</t>
+          <t>5 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -27272,7 +27274,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -27307,7 +27309,7 @@
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27331,7 +27333,7 @@
       <c r="E39" s="14" t="inlineStr"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>7 / 3.1 / 4/14</t>
+          <t>5 / 3.0 / 3/14</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -27368,7 +27370,7 @@
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.4 / 0/14</t>
+          <t>3 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
@@ -27408,7 +27410,7 @@
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27520,7 +27522,7 @@
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>4 / 6.4 / 7/14</t>
+          <t>3 / 6.4 / 7/14</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -27535,12 +27537,12 @@
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.5 / 0/14</t>
+          <t>4 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.3 / 0/14</t>
+          <t>4 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
@@ -27588,7 +27590,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>22 / 20.5 / 12/14</t>
+          <t>19 / 20.3 / 12/14</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -27598,7 +27600,7 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.5 / 0/14</t>
+          <t>1 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -27646,7 +27648,7 @@
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>7 / 4.0 / 5/14</t>
+          <t>6 / 3.9 / 5/14</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
@@ -27692,7 +27694,7 @@
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
@@ -27814,7 +27816,7 @@
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/14</t>
+          <t>0 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
@@ -27893,7 +27895,7 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/14</t>
+          <t>9 / 1.9 / 1/14</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -27956,7 +27958,7 @@
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
@@ -28218,7 +28220,7 @@
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.6 / 0/14</t>
+          <t>5 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
@@ -28290,7 +28292,7 @@
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.7 / 0/14</t>
+          <t>3 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
@@ -28326,7 +28328,7 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>11 / 8.1 / 9/14</t>
+          <t>7 / 7.8 / 9/14</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
@@ -28443,7 +28445,7 @@
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
@@ -28481,7 +28483,7 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.9 / 0/14</t>
+          <t>1 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
@@ -28623,7 +28625,7 @@
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.9 / 0/14</t>
+          <t>0 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
@@ -28666,7 +28668,7 @@
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>10 / 5.4 / 6/14</t>
+          <t>12 / 5.6 / 6/14</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
@@ -28754,7 +28756,7 @@
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.3 / 0/14</t>
+          <t>3 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr"/>
@@ -28779,7 +28781,7 @@
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.4 / 0/14</t>
+          <t>2 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
@@ -28822,7 +28824,7 @@
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.9 / 0/14</t>
+          <t>3 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
@@ -28865,7 +28867,7 @@
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
@@ -28979,7 +28981,7 @@
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>8 / 14.1 / 14/14</t>
+          <t>9 / 14.2 / 14/14</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -16,9 +16,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$308</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$307</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1637</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1783</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1576</v>
+        <v>1572</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1105</v>
+        <v>1132</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>520</v>
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>871</v>
+        <v>818</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>12</v>
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>652</v>
+        <v>665</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>16</v>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>35</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>6</v>
@@ -797,27 +797,25 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Consulting &amp; Corporate Strategy</t>
+          <t>Executive Positions</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>11</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="C14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Executive Positions</t>
+          <t>Consulting &amp; Corporate Strategy</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -827,10 +825,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -840,25 +838,36 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Ventes et Commercialisation</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Total Ontap JobG8 jobs published today</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B19" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="C18" s="10" t="n">
-        <v>1415</v>
+      <c r="C19" s="10" t="n">
+        <v>1408</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C18"/>
+  <autoFilter ref="A1:C19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8236,7 +8245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O308"/>
+  <dimension ref="A1:O307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11232,27 +11241,27 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Worcester</t>
+          <t>Aylesbury</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>/worcester/service-administrator-jobs</t>
+          <t>/aylesbury/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H55" s="5" t="n">
         <v>0</v>
@@ -11287,12 +11296,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Aylesbury</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
@@ -11303,7 +11312,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>/aylesbury/service-administrator-jobs</t>
+          <t>/barnsley/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
@@ -11342,12 +11351,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
@@ -11358,7 +11367,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>/barnsley/service-administrator-jobs</t>
+          <t>/durham/jobs</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
@@ -11397,12 +11406,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Huddersfield</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
@@ -11413,7 +11422,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>/durham/jobs</t>
+          <t>/huddersfield/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
@@ -11452,12 +11461,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Hemel Hempstead</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
@@ -11468,11 +11477,11 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>/hemel-hempstead/service-administrator-jobs</t>
+          <t>/rotherham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59" s="5" t="n">
         <v>0</v>
@@ -11484,7 +11493,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="5" t="n">
         <v>0</v>
@@ -11507,12 +11516,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Huddersfield</t>
+          <t>Salford</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
@@ -11523,17 +11532,17 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>/huddersfield/service-administrator-jobs</t>
+          <t>/salford/jobs</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="J60" s="3" t="n">
         <v>0</v>
@@ -11562,12 +11571,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Wakefield</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
@@ -11578,7 +11587,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>/rotherham/service-administrator-jobs</t>
+          <t>/wakefield/jobs</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
@@ -11617,12 +11626,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Salford</t>
+          <t>Worcester</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
@@ -11633,17 +11642,17 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>/salford/jobs</t>
+          <t>/worcester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="n">
         <v>0</v>
@@ -11672,27 +11681,27 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Wakefield</t>
+          <t>Ashford</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>/wakefield/jobs</t>
+          <t>/ashford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H63" s="5" t="n">
         <v>0</v>
@@ -11727,12 +11736,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Ashford</t>
+          <t>Gloucester</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
@@ -11743,7 +11752,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>/ashford/service-administrator-jobs</t>
+          <t>/gloucester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
@@ -11782,12 +11791,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Gloucester</t>
+          <t>Hemel Hempstead</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
@@ -11798,11 +11807,11 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>/gloucester/service-administrator-jobs</t>
+          <t>/hemel-hempstead/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" s="5" t="n">
         <v>0</v>
@@ -11814,7 +11823,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="5" t="n">
         <v>0</v>
@@ -18581,12 +18590,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Bingley</t>
+          <t>Bishop's Stortford</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -18632,12 +18641,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Bishop's Stortford</t>
+          <t>Bognor Regis</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -18683,12 +18692,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Bognor Regis</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -18734,12 +18743,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Bracknell</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -18785,12 +18794,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Bracknell</t>
+          <t>Buckingham</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -18801,7 +18810,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
         <v>0</v>
@@ -18822,7 +18831,7 @@
         <v>0</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O202" s="3" t="n">
         <v>0</v>
@@ -18836,12 +18845,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Buckingham</t>
+          <t>Bury St Edmunds</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -18852,7 +18861,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr"/>
       <c r="G203" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H203" s="5" t="n">
         <v>0</v>
@@ -18873,7 +18882,7 @@
         <v>0</v>
       </c>
       <c r="N203" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O203" s="5" t="n">
         <v>0</v>
@@ -18887,12 +18896,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Bury St Edmunds</t>
+          <t>Caerphilly</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -18938,12 +18947,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Caerphilly</t>
+          <t>Camberley</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -18989,12 +18998,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Camberley</t>
+          <t>Carrickfergus</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -19040,12 +19049,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Carrickfergus</t>
+          <t>Chelmsley Wood</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -19091,12 +19100,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Chelmsley Wood</t>
+          <t>Cheltenham</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -19142,12 +19151,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Cheltenham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -19193,12 +19202,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Chichester</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -19244,12 +19253,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Chichester</t>
+          <t>Chippenham</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -19295,12 +19304,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Chippenham</t>
+          <t>Cleethorpes</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -19346,12 +19355,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Cleethorpes</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
@@ -19362,7 +19371,7 @@
       </c>
       <c r="F213" s="4" t="inlineStr"/>
       <c r="G213" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H213" s="5" t="n">
         <v>0</v>
@@ -19371,7 +19380,7 @@
         <v>0</v>
       </c>
       <c r="J213" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K213" s="5" t="n">
         <v>0</v>
@@ -19397,12 +19406,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>Colden Common</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -19422,7 +19431,7 @@
         <v>0</v>
       </c>
       <c r="J214" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K214" s="3" t="n">
         <v>0</v>
@@ -19434,7 +19443,7 @@
         <v>0</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O214" s="3" t="n">
         <v>0</v>
@@ -19448,12 +19457,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Colden Common</t>
+          <t>Congleton</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
@@ -19464,7 +19473,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr"/>
       <c r="G215" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H215" s="5" t="n">
         <v>0</v>
@@ -19485,7 +19494,7 @@
         <v>0</v>
       </c>
       <c r="N215" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O215" s="5" t="n">
         <v>0</v>
@@ -19499,12 +19508,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Congleton</t>
+          <t>Devizes</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -19550,12 +19559,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Devizes</t>
+          <t>Dorchester</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
@@ -19601,12 +19610,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Dorchester</t>
+          <t>Dorking</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
@@ -19652,12 +19661,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Dorking</t>
+          <t>Dursley</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
@@ -19703,12 +19712,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Dursley</t>
+          <t>Eastbourne</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
@@ -19719,10 +19728,10 @@
       </c>
       <c r="F220" s="2" t="inlineStr"/>
       <c r="G220" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I220" s="3" t="n">
         <v>0</v>
@@ -19754,12 +19763,12 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Eastbourne</t>
+          <t>Ellesmere Port</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
@@ -19770,10 +19779,10 @@
       </c>
       <c r="F221" s="4" t="inlineStr"/>
       <c r="G221" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H221" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I221" s="5" t="n">
         <v>0</v>
@@ -19805,12 +19814,12 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Ellesmere Port</t>
+          <t>Epsom</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
@@ -19821,7 +19830,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H222" s="3" t="n">
         <v>0</v>
@@ -19833,7 +19842,7 @@
         <v>0</v>
       </c>
       <c r="K222" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L222" s="3" t="n">
         <v>0</v>
@@ -19856,7 +19865,7 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Epsom</t>
+          <t>Esher</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
@@ -19878,13 +19887,13 @@
         <v>0</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J223" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K223" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L223" s="5" t="n">
         <v>0</v>
@@ -19907,12 +19916,12 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Esher</t>
+          <t>Felixstowe</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D224" s="3" t="n">
@@ -19923,13 +19932,13 @@
       </c>
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H224" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J224" s="3" t="n">
         <v>0</v>
@@ -19958,12 +19967,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Felixstowe</t>
+          <t>Fetcham</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D225" s="5" t="n">
@@ -19974,7 +19983,7 @@
       </c>
       <c r="F225" s="4" t="inlineStr"/>
       <c r="G225" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H225" s="5" t="n">
         <v>0</v>
@@ -19995,7 +20004,7 @@
         <v>0</v>
       </c>
       <c r="N225" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O225" s="5" t="n">
         <v>0</v>
@@ -20009,12 +20018,12 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Fetcham</t>
+          <t>Freshwater</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
@@ -20028,7 +20037,7 @@
         <v>0</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I226" s="3" t="n">
         <v>0</v>
@@ -20046,7 +20055,7 @@
         <v>0</v>
       </c>
       <c r="N226" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O226" s="3" t="n">
         <v>0</v>
@@ -20060,12 +20069,12 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Freshwater</t>
+          <t>Frodsham</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D227" s="5" t="n">
@@ -20076,10 +20085,10 @@
       </c>
       <c r="F227" s="4" t="inlineStr"/>
       <c r="G227" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H227" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I227" s="5" t="n">
         <v>0</v>
@@ -20111,12 +20120,12 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Frodsham</t>
+          <t>Gainsborough</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
@@ -20162,12 +20171,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Gainsborough</t>
+          <t>Godstone</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
@@ -20213,12 +20222,12 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Godstone</t>
+          <t>Goole</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
@@ -20264,12 +20273,12 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Goole</t>
+          <t>Grange-over-sands</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
@@ -20280,10 +20289,10 @@
       </c>
       <c r="F231" s="4" t="inlineStr"/>
       <c r="G231" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H231" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I231" s="5" t="n">
         <v>0</v>
@@ -20315,12 +20324,12 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Grange-over-sands</t>
+          <t>Grantham</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
@@ -20331,10 +20340,10 @@
       </c>
       <c r="F232" s="2" t="inlineStr"/>
       <c r="G232" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I232" s="3" t="n">
         <v>0</v>
@@ -20366,12 +20375,12 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Grantham</t>
+          <t>Gravesend</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D233" s="5" t="n">
@@ -20382,10 +20391,10 @@
       </c>
       <c r="F233" s="4" t="inlineStr"/>
       <c r="G233" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H233" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I233" s="5" t="n">
         <v>0</v>
@@ -20417,12 +20426,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Gravesend</t>
+          <t>Hailsham</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
@@ -20436,10 +20445,10 @@
         <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J234" s="3" t="n">
         <v>0</v>
@@ -20468,12 +20477,12 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Hailsham</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
@@ -20487,10 +20496,10 @@
         <v>0</v>
       </c>
       <c r="H235" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J235" s="5" t="n">
         <v>0</v>
@@ -20519,12 +20528,12 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Harrogate</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
@@ -20535,10 +20544,10 @@
       </c>
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H236" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I236" s="3" t="n">
         <v>0</v>
@@ -20570,12 +20579,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Harrogate</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
@@ -20621,12 +20630,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
@@ -20637,10 +20646,10 @@
       </c>
       <c r="F238" s="2" t="inlineStr"/>
       <c r="G238" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I238" s="3" t="n">
         <v>0</v>
@@ -20672,12 +20681,12 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Hebburn</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
@@ -20691,7 +20700,7 @@
         <v>0</v>
       </c>
       <c r="H239" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I239" s="5" t="n">
         <v>0</v>
@@ -20709,7 +20718,7 @@
         <v>0</v>
       </c>
       <c r="N239" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O239" s="5" t="n">
         <v>0</v>
@@ -20723,12 +20732,12 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Hebburn</t>
+          <t>Henley-on-thames</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
@@ -20739,7 +20748,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr"/>
       <c r="G240" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H240" s="3" t="n">
         <v>0</v>
@@ -20760,7 +20769,7 @@
         <v>0</v>
       </c>
       <c r="N240" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O240" s="3" t="n">
         <v>0</v>
@@ -20774,12 +20783,12 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Henley-on-thames</t>
+          <t>Hertford</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D241" s="5" t="n">
@@ -20825,12 +20834,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Hertford</t>
+          <t>Ilminster</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
@@ -20876,12 +20885,12 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Ilminster</t>
+          <t>Kendal</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
@@ -20892,10 +20901,10 @@
       </c>
       <c r="F243" s="4" t="inlineStr"/>
       <c r="G243" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H243" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I243" s="5" t="n">
         <v>0</v>
@@ -20927,12 +20936,12 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Kendal</t>
+          <t>Kirriemuir</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
@@ -20943,10 +20952,10 @@
       </c>
       <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I244" s="3" t="n">
         <v>0</v>
@@ -20978,12 +20987,12 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Kirriemuir</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
@@ -21029,12 +21038,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Leigh</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
@@ -21080,12 +21089,12 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Leigh</t>
+          <t>Lichfield</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
@@ -21096,7 +21105,7 @@
       </c>
       <c r="F247" s="4" t="inlineStr"/>
       <c r="G247" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H247" s="5" t="n">
         <v>0</v>
@@ -21117,7 +21126,7 @@
         <v>0</v>
       </c>
       <c r="N247" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O247" s="5" t="n">
         <v>0</v>
@@ -21131,12 +21140,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Lichfield</t>
+          <t>Liskeard</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
@@ -21147,7 +21156,7 @@
       </c>
       <c r="F248" s="2" t="inlineStr"/>
       <c r="G248" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H248" s="3" t="n">
         <v>0</v>
@@ -21168,7 +21177,7 @@
         <v>0</v>
       </c>
       <c r="N248" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O248" s="3" t="n">
         <v>0</v>
@@ -21182,12 +21191,12 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Liskeard</t>
+          <t>Littlehampton</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
@@ -21233,12 +21242,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Littlehampton</t>
+          <t>Loughborough</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
@@ -21284,12 +21293,12 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Loughborough</t>
+          <t>Marlborough</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
@@ -21335,12 +21344,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Marlborough</t>
+          <t>Marlow</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
@@ -21386,12 +21395,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Marlow</t>
+          <t>Mirfield</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
@@ -21437,12 +21446,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Mirfield</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
@@ -21453,13 +21462,13 @@
       </c>
       <c r="F254" s="2" t="inlineStr"/>
       <c r="G254" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H254" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I254" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J254" s="3" t="n">
         <v>0</v>
@@ -21488,12 +21497,12 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
@@ -21504,13 +21513,13 @@
       </c>
       <c r="F255" s="4" t="inlineStr"/>
       <c r="G255" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H255" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I255" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J255" s="5" t="n">
         <v>0</v>
@@ -21539,12 +21548,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
@@ -21590,12 +21599,12 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Newbury</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
@@ -21606,7 +21615,7 @@
       </c>
       <c r="F257" s="4" t="inlineStr"/>
       <c r="G257" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H257" s="5" t="n">
         <v>0</v>
@@ -21618,7 +21627,7 @@
         <v>0</v>
       </c>
       <c r="K257" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L257" s="5" t="n">
         <v>0</v>
@@ -21641,12 +21650,12 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Newbury</t>
+          <t>Newmarket</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
@@ -21657,7 +21666,7 @@
       </c>
       <c r="F258" s="2" t="inlineStr"/>
       <c r="G258" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H258" s="3" t="n">
         <v>0</v>
@@ -21669,7 +21678,7 @@
         <v>0</v>
       </c>
       <c r="K258" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L258" s="3" t="n">
         <v>0</v>
@@ -21692,12 +21701,12 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Newmarket</t>
+          <t>Newport-on-tay</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
@@ -21743,12 +21752,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Newport-on-tay</t>
+          <t>North Shields</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
@@ -21794,12 +21803,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>North Shields</t>
+          <t>Otley</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
@@ -21845,12 +21854,12 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Otley</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D262" s="3" t="n">
@@ -21861,13 +21870,13 @@
       </c>
       <c r="F262" s="2" t="inlineStr"/>
       <c r="G262" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H262" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I262" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J262" s="3" t="n">
         <v>0</v>
@@ -21896,12 +21905,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Pickering</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
@@ -21912,13 +21921,13 @@
       </c>
       <c r="F263" s="4" t="inlineStr"/>
       <c r="G263" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H263" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I263" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J263" s="5" t="n">
         <v>0</v>
@@ -21947,12 +21956,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Pickering</t>
+          <t>Pontefract</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D264" s="3" t="n">
@@ -21998,12 +22007,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Pontefract</t>
+          <t>Portishead</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
@@ -22049,12 +22058,12 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Portishead</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
@@ -22100,12 +22109,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Redruth</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
@@ -22151,12 +22160,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Redruth</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D268" s="3" t="n">
@@ -22202,7 +22211,7 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
@@ -22218,7 +22227,7 @@
       </c>
       <c r="F269" s="4" t="inlineStr"/>
       <c r="G269" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H269" s="5" t="n">
         <v>0</v>
@@ -22230,7 +22239,7 @@
         <v>0</v>
       </c>
       <c r="K269" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L269" s="5" t="n">
         <v>0</v>
@@ -22253,12 +22262,12 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D270" s="3" t="n">
@@ -22269,7 +22278,7 @@
       </c>
       <c r="F270" s="2" t="inlineStr"/>
       <c r="G270" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H270" s="3" t="n">
         <v>0</v>
@@ -22281,7 +22290,7 @@
         <v>0</v>
       </c>
       <c r="K270" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L270" s="3" t="n">
         <v>0</v>
@@ -22304,12 +22313,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Rochester</t>
+          <t>Romsey</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D271" s="5" t="n">
@@ -22355,12 +22364,12 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Romsey</t>
+          <t>Rugby</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D272" s="3" t="n">
@@ -22406,12 +22415,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Rugby</t>
+          <t>Ryton</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
@@ -22457,12 +22466,12 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Ryton</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D274" s="3" t="n">
@@ -22508,12 +22517,12 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
@@ -22559,12 +22568,12 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Seaham</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D276" s="3" t="n">
@@ -22610,12 +22619,12 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Seaham</t>
+          <t>Shepperton</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
@@ -22661,12 +22670,12 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Shepperton</t>
+          <t>Shipley</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D278" s="3" t="n">
@@ -22712,12 +22721,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Shipley</t>
+          <t>Shirley</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D279" s="5" t="n">
@@ -22763,12 +22772,12 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Snodland</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D280" s="3" t="n">
@@ -22779,13 +22788,13 @@
       </c>
       <c r="F280" s="2" t="inlineStr"/>
       <c r="G280" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H280" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I280" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J280" s="3" t="n">
         <v>0</v>
@@ -22814,12 +22823,12 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Snodland</t>
+          <t>Southam</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D281" s="5" t="n">
@@ -22830,13 +22839,13 @@
       </c>
       <c r="F281" s="4" t="inlineStr"/>
       <c r="G281" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H281" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J281" s="5" t="n">
         <v>0</v>
@@ -22865,12 +22874,12 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Southam</t>
+          <t>Southend-on-sea</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D282" s="3" t="n">
@@ -22916,12 +22925,12 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Southend-on-sea</t>
+          <t>Spennymoor</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D283" s="5" t="n">
@@ -22967,12 +22976,12 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Spennymoor</t>
+          <t>St. Austell</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D284" s="3" t="n">
@@ -23018,12 +23027,12 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>St. Austell</t>
+          <t>St. Ives</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D285" s="5" t="n">
@@ -23069,7 +23078,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>St. Ives</t>
+          <t>St. Neots</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -23120,12 +23129,12 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>St. Neots</t>
+          <t>Staines</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D287" s="5" t="n">
@@ -23171,12 +23180,12 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Staines</t>
+          <t>Street</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D288" s="3" t="n">
@@ -23222,12 +23231,12 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Stroud</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D289" s="5" t="n">
@@ -23273,12 +23282,12 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Stroud</t>
+          <t>Taunton</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D290" s="3" t="n">
@@ -23324,12 +23333,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Taunton</t>
+          <t>Tipton</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D291" s="5" t="n">
@@ -23375,12 +23384,12 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Tipton</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D292" s="3" t="n">
@@ -23391,13 +23400,13 @@
       </c>
       <c r="F292" s="2" t="inlineStr"/>
       <c r="G292" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H292" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I292" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J292" s="3" t="n">
         <v>0</v>
@@ -23426,12 +23435,12 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Trowbridge</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
@@ -23442,13 +23451,13 @@
       </c>
       <c r="F293" s="4" t="inlineStr"/>
       <c r="G293" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H293" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I293" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J293" s="5" t="n">
         <v>0</v>
@@ -23477,12 +23486,12 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Trowbridge</t>
+          <t>Ulverston</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D294" s="3" t="n">
@@ -23493,10 +23502,10 @@
       </c>
       <c r="F294" s="2" t="inlineStr"/>
       <c r="G294" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H294" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I294" s="3" t="n">
         <v>0</v>
@@ -23528,12 +23537,12 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Ulverston</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D295" s="5" t="n">
@@ -23544,10 +23553,10 @@
       </c>
       <c r="F295" s="4" t="inlineStr"/>
       <c r="G295" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H295" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I295" s="5" t="n">
         <v>0</v>
@@ -23579,12 +23588,12 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Waltham Cross</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D296" s="3" t="n">
@@ -23630,12 +23639,12 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Waltham Cross</t>
+          <t>Walton-on-thames</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D297" s="5" t="n">
@@ -23681,12 +23690,12 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Wellingborough</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D298" s="3" t="n">
@@ -23732,12 +23741,12 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Wellingborough</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D299" s="5" t="n">
@@ -23783,12 +23792,12 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D300" s="3" t="n">
@@ -23834,12 +23843,12 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D301" s="5" t="n">
@@ -23885,12 +23894,12 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Whitstable</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D302" s="3" t="n">
@@ -23901,13 +23910,13 @@
       </c>
       <c r="F302" s="2" t="inlineStr"/>
       <c r="G302" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H302" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I302" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J302" s="3" t="n">
         <v>0</v>
@@ -23936,12 +23945,12 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Whitstable</t>
+          <t>Wilmslow</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D303" s="5" t="n">
@@ -23952,13 +23961,13 @@
       </c>
       <c r="F303" s="4" t="inlineStr"/>
       <c r="G303" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H303" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I303" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J303" s="5" t="n">
         <v>0</v>
@@ -23987,12 +23996,12 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Wilmslow</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D304" s="3" t="n">
@@ -24038,12 +24047,12 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Witney</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D305" s="5" t="n">
@@ -24089,12 +24098,12 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Witney</t>
+          <t>Worksop</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D306" s="3" t="n">
@@ -24140,12 +24149,12 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Worksop</t>
+          <t>Wymondham</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D307" s="5" t="n">
@@ -24183,59 +24192,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B308" s="2" t="inlineStr">
-        <is>
-          <t>Wymondham</t>
-        </is>
-      </c>
-      <c r="C308" s="2" t="inlineStr">
-        <is>
-          <t>Norfolk</t>
-        </is>
-      </c>
-      <c r="D308" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F308" s="2" t="inlineStr"/>
-      <c r="G308" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N308" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O308" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O308"/>
+  <autoFilter ref="A1:O307"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24759,7 +24717,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="5" t="n">
@@ -24912,7 +24870,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>20</v>
@@ -25028,7 +24986,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -25657,7 +25615,7 @@
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
       <c r="D75" s="4" t="inlineStr"/>
@@ -25735,7 +25693,7 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C79" s="5" t="n">
         <v>2</v>
@@ -25849,12 +25807,12 @@
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>6 / 3.5 / 1/14</t>
+          <t>6 / 3.6 / 2/14</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>2 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
@@ -25882,25 +25840,25 @@
       <c r="B3" s="14" t="inlineStr"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr"/>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr"/>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25919,19 +25877,19 @@
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>9 / 4.9 / 6/14</t>
+          <t>10 / 5.4 / 7/14</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 0/14</t>
+          <t>4 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.5 / 0/14</t>
+          <t>2 / 3.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25954,7 +25912,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr"/>
@@ -25965,7 +25923,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/14</t>
+          <t>2 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr"/>
@@ -25984,7 +25942,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -25995,12 +25953,12 @@
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>3 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -26023,17 +25981,17 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.6 / 0/14</t>
+          <t>5 / 3.7 / 0/14</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -26048,7 +26006,7 @@
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.4 / 0/14</t>
+          <t>2 / 2.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26066,17 +26024,17 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 1/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/14</t>
+          <t>3 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.1 / 0/14</t>
+          <t>5 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
@@ -26116,17 +26074,17 @@
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26139,12 +26097,12 @@
       <c r="B10" s="13" t="inlineStr"/>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -26169,7 +26127,7 @@
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26181,7 +26139,7 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/14</t>
+          <t>2 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -26244,7 +26202,7 @@
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
@@ -26271,7 +26229,7 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
@@ -26329,12 +26287,12 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.7 / 0/14</t>
+          <t>3 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
@@ -26349,7 +26307,7 @@
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26362,18 +26320,18 @@
       <c r="B15" s="14" t="inlineStr"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/14</t>
+          <t>2 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr"/>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/14</t>
+          <t>2 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>3 / 4.8 / 5/14</t>
+          <t>3 / 4.6 / 4/14</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
@@ -26384,7 +26342,7 @@
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26402,32 +26360,32 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.5 / 0/14</t>
+          <t>2 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>5 / 1.4 / 0/14</t>
+          <t>6 / 1.9 / 1/14</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26440,12 +26398,12 @@
       <c r="B17" s="14" t="inlineStr"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.9 / 1/14</t>
+          <t>3 / 3.8 / 1/14</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
@@ -26453,12 +26411,12 @@
       <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.1 / 5/14</t>
+          <t>6 / 3.5 / 6/14</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.1 / 0/14</t>
+          <t>2 / 2.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26471,17 +26429,17 @@
       <c r="B18" s="13" t="inlineStr"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.6 / 3/14</t>
+          <t>1 / 3.4 / 3/14</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr"/>
@@ -26506,13 +26464,13 @@
       <c r="B19" s="14" t="inlineStr"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>2 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>16 / 8.5 / 9/14</t>
+          <t>17 / 9.5 / 10/14</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr"/>
@@ -26520,7 +26478,7 @@
       <c r="H19" s="14" t="inlineStr"/>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/14</t>
+          <t>0 / 1.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26532,12 +26490,12 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.3 / 0/14</t>
+          <t>5 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
@@ -26557,17 +26515,17 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>2 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26585,12 +26543,12 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr"/>
@@ -26601,12 +26559,12 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26629,7 +26587,7 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/14</t>
+          <t>3 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
@@ -26644,12 +26602,12 @@
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26664,22 +26622,22 @@
       <c r="D23" s="14" t="inlineStr"/>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.2 / 0/14</t>
+          <t>3 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>6 / 7.5 / 14/14</t>
+          <t>6 / 7.2 / 14/14</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>5 / 2.6 / 0/14</t>
+          <t>5 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>7 / 5.6 / 6/14</t>
+          <t>7 / 5.8 / 7/14</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr"/>
@@ -26692,12 +26650,12 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
@@ -26740,19 +26698,19 @@
       <c r="B25" s="14" t="inlineStr"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/14</t>
+          <t>2 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/14</t>
+          <t>2 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
@@ -26762,7 +26720,7 @@
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.3 / 0/14</t>
+          <t>1 / 2.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26777,7 +26735,7 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>12 / 8.7 / 9/14</t>
+          <t>11 / 9.3 / 10/14</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
@@ -26788,12 +26746,12 @@
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/14</t>
+          <t>3 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26805,32 +26763,32 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>2 / 2.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/14</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>2 / 2.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
@@ -26852,7 +26810,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/14</t>
+          <t>1 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -26862,7 +26820,7 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -26877,7 +26835,7 @@
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -26899,17 +26857,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.0 / 0/14</t>
+          <t>4 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -26919,12 +26877,12 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.3 / 0/14</t>
+          <t>0 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>2 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
@@ -26956,12 +26914,12 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -26971,7 +26929,7 @@
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/14</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -27046,22 +27004,22 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.9 / 0/14</t>
+          <t>4 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/14</t>
+          <t>3 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -27071,7 +27029,7 @@
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27089,17 +27047,17 @@
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.9 / 0/14</t>
+          <t>0 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/14</t>
+          <t>3 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>3 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -27114,7 +27072,7 @@
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27142,7 +27100,7 @@
       <c r="B35" s="14" t="inlineStr"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -27152,7 +27110,7 @@
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.7 / 5/14</t>
+          <t>7 / 4.1 / 6/14</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr"/>
@@ -27163,12 +27121,12 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/14</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27180,7 +27138,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -27195,7 +27153,7 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -27227,7 +27185,7 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>5 / 1.1 / 0/14</t>
+          <t>5 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -27252,7 +27210,7 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
@@ -27274,7 +27232,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -27284,7 +27242,7 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -27333,17 +27291,17 @@
       <c r="E39" s="14" t="inlineStr"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.0 / 3/14</t>
+          <t>5 / 3.2 / 3/14</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.3 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
@@ -27363,14 +27321,14 @@
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.3 / 0/14</t>
+          <t>4 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr"/>
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/14</t>
+          <t>2 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
@@ -27390,7 +27348,7 @@
       <c r="D41" s="14" t="inlineStr"/>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr">
@@ -27400,7 +27358,7 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
@@ -27410,7 +27368,7 @@
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27422,7 +27380,7 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.1 / 0/14</t>
+          <t>3 / 3.0 / 0/14</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -27432,32 +27390,32 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
+          <t>3 / 1.9 / 0/14</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
           <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
-      <c r="E42" s="13" t="inlineStr">
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.4 / 0/14</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="F42" s="13" t="inlineStr">
-        <is>
-          <t>2 / 1.9 / 0/14</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>1 / 1.4 / 0/14</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27469,12 +27427,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.1 / 0/14</t>
+          <t>2 / 3.0 / 0/14</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
@@ -27517,37 +27475,37 @@
       <c r="B44" s="13" t="inlineStr"/>
       <c r="C44" s="13" t="inlineStr">
         <is>
+          <t>1 / 1.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>4 / 5.9 / 6/14</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
           <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
-        <is>
-          <t>3 / 6.4 / 7/14</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.9 / 0/14</t>
-        </is>
-      </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.8 / 0/14</t>
+          <t>2 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.4 / 0/14</t>
+          <t>4 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.2 / 0/14</t>
+          <t>4 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27560,17 +27518,17 @@
       <c r="B45" s="14" t="inlineStr"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>15 / 13.0 / 11/14</t>
+          <t>15 / 14.0 / 12/14</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr"/>
@@ -27590,7 +27548,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>19 / 20.3 / 12/14</t>
+          <t>19 / 21.4 / 13/14</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -27600,7 +27558,7 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.4 / 0/14</t>
+          <t>1 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -27610,12 +27568,12 @@
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.7 / 0/14</t>
+          <t>3 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.8 / 0/14</t>
+          <t>4 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -27625,7 +27583,7 @@
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>2 / 1.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27638,7 +27596,7 @@
       <c r="B47" s="14" t="inlineStr"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
@@ -27648,23 +27606,23 @@
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.9 / 5/14</t>
+          <t>6 / 4.2 / 6/14</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>1 / 3.0 / 0/14</t>
+          <t>1 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr"/>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27678,28 +27636,28 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>3 / 4.0 / 0/14</t>
+          <t>3 / 3.9 / 0/14</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr"/>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
+          <t>0 / 1.2 / 0/14</t>
+        </is>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
           <t>0 / 1.3 / 0/14</t>
-        </is>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>0 / 1.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27758,7 +27716,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.5 / 0/14</t>
+          <t>5 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -27783,17 +27741,17 @@
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27811,22 +27769,22 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.9 / 0/14</t>
+          <t>1 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.1 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/14</t>
+          <t>2 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>2 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">
@@ -27836,7 +27794,7 @@
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27848,7 +27806,7 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -27883,7 +27841,7 @@
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27895,7 +27853,7 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>9 / 1.9 / 1/14</t>
+          <t>9 / 2.4 / 2/14</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -27905,7 +27863,7 @@
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -27958,7 +27916,7 @@
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
@@ -27973,7 +27931,7 @@
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28039,7 +27997,7 @@
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>2 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
@@ -28059,7 +28017,7 @@
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 1/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28071,32 +28029,32 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
+          <t>1 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="D57" s="14" t="inlineStr">
+      <c r="E57" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="E57" s="14" t="inlineStr">
+      <c r="F57" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="F57" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>2 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="H57" s="14" t="inlineStr">
@@ -28128,7 +28086,7 @@
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -28171,12 +28129,12 @@
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr">
@@ -28205,12 +28163,12 @@
       <c r="B60" s="13" t="inlineStr"/>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.9 / 0/14</t>
+          <t>2 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -28220,12 +28178,12 @@
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.6 / 0/14</t>
+          <t>6 / 3.8 / 1/14</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -28235,7 +28193,7 @@
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28253,27 +28211,27 @@
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.9 / 4/14</t>
+          <t>6 / 4.2 / 5/14</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr"/>
@@ -28298,22 +28256,22 @@
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/14</t>
+          <t>3 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28328,18 +28286,18 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>7 / 7.8 / 9/14</t>
+          <t>7 / 7.9 / 10/14</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>6 / 4.9 / 6/14</t>
+          <t>4 / 4.9 / 6/14</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.9 / 0/14</t>
+          <t>5 / 4.1 / 0/14</t>
         </is>
       </c>
       <c r="I63" s="14" t="inlineStr"/>
@@ -28355,23 +28313,23 @@
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.9 / 0/14</t>
+          <t>5 / 4.0 / 0/14</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>5 / 4.5 / 3/14</t>
+          <t>6 / 4.6 / 4/14</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.3 / 0/14</t>
+          <t>7 / 3.5 / 1/14</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.4 / 0/14</t>
+          <t>1 / 2.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28430,37 +28388,37 @@
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.9 / 0/14</t>
+          <t>2 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
+          <t>1 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="E66" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.1 / 0/14</t>
-        </is>
-      </c>
-      <c r="F66" s="13" t="inlineStr">
+      <c r="G66" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="G66" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
@@ -28483,17 +28441,17 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.8 / 0/14</t>
+          <t>1 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/14</t>
+          <t>3 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -28508,7 +28466,7 @@
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28520,7 +28478,7 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -28530,27 +28488,27 @@
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
+          <t>1 / 0.6 / 0/14</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
           <t>1 / 0.5 / 0/14</t>
-        </is>
-      </c>
-      <c r="G68" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="H68" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="I68" s="13" t="inlineStr">
@@ -28567,7 +28525,7 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.6 / 0/14</t>
+          <t>1 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
@@ -28582,12 +28540,12 @@
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
@@ -28615,7 +28573,7 @@
       <c r="B70" s="13" t="inlineStr"/>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/14</t>
+          <t>2 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
@@ -28625,7 +28583,7 @@
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.9 / 0/14</t>
+          <t>0 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
@@ -28645,7 +28603,7 @@
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.3 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28663,24 +28621,24 @@
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>3 / 6.4 / 7/14</t>
+          <t>3 / 5.9 / 6/14</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>12 / 5.6 / 6/14</t>
+          <t>12 / 6.2 / 7/14</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.0 / 0/14</t>
+          <t>4 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="H71" s="14" t="inlineStr"/>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.8 / 0/14</t>
+          <t>1 / 2.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28698,27 +28656,27 @@
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.4 / 0/14</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>4 / 3.9 / 0/14</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
-      <c r="E72" s="13" t="inlineStr">
-        <is>
-          <t>3 / 3.9 / 0/14</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.6 / 0/14</t>
-        </is>
-      </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>2 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="I72" s="13" t="inlineStr">
@@ -28736,17 +28694,17 @@
       <c r="B73" s="14" t="inlineStr"/>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>2 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.9 / 7/14</t>
+          <t>2 / 3.6 / 6/14</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>3 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
@@ -28762,7 +28720,7 @@
       <c r="H73" s="14" t="inlineStr"/>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28776,27 +28734,27 @@
       <c r="C74" s="13" t="inlineStr"/>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.2 / 0/14</t>
+          <t>2 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.3 / 0/14</t>
+          <t>2 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.6 / 0/14</t>
+          <t>4 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.3 / 0/14</t>
+          <t>3 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>3 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="I74" s="13" t="inlineStr">
@@ -28819,27 +28777,27 @@
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 0/14</t>
+          <t>3 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.1 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
+          <t>1 / 1.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
           <t>1 / 0.9 / 0/14</t>
-        </is>
-      </c>
-      <c r="H75" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="I75" s="14" t="inlineStr">
@@ -28877,17 +28835,17 @@
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/14</t>
+          <t>3 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28905,24 +28863,24 @@
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.6 / 0/14</t>
+          <t>2 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>9 / 3.9 / 5/14</t>
+          <t>9 / 4.5 / 6/14</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr"/>
       <c r="G77" s="14" t="inlineStr"/>
       <c r="H77" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.3 / 4/14</t>
+          <t>6 / 3.6 / 5/14</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28936,7 +28894,7 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.4 / 0/14</t>
+          <t>2 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -28946,22 +28904,22 @@
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>5 / 5.6 / 6/14</t>
+          <t>5 / 5.5 / 5/14</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.9 / 0/14</t>
+          <t>3 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28976,12 +28934,12 @@
       <c r="D79" s="14" t="inlineStr"/>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>11 / 6.3 / 6/14</t>
+          <t>9 / 6.6 / 7/14</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>9 / 14.2 / 14/14</t>
+          <t>10 / 13.8 / 14/14</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1656</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1793</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="6">
@@ -10067,30 +10067,30 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Sheffield</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>/sheffield/service-administrator-jobs</t>
+          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>0</v>
@@ -10122,30 +10122,30 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bolton</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
+          <t>/bolton/jobs</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0</v>
@@ -10177,12 +10177,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Bolton</t>
+          <t>Farnham</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>/bolton/jobs</t>
+          <t>/farnham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
@@ -10232,12 +10232,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Farnham</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
@@ -10248,14 +10248,14 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>/farnham/service-administrator-jobs</t>
+          <t>/oxford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>0</v>
@@ -10264,7 +10264,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>0</v>
@@ -10287,12 +10287,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Sheffield</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -10303,14 +10303,14 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>/oxford/service-administrator-jobs</t>
+          <t>/sheffield/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>0</v>
@@ -10319,7 +10319,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="5" t="n">
         <v>0</v>
@@ -25456,7 +25456,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1572</v>
+        <v>1585</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1132</v>
+        <v>1152</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>95</v>
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>521</v>
+        <v>514</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6">
@@ -697,62 +697,62 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>818</v>
+        <v>804</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>I.T. &amp; Communications</t>
+          <t>Call Centre / CustomerService</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>22</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Call Centre / CustomerService</t>
+          <t>I.T. &amp; Communications</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>734</v>
+        <v>763</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>211</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Real Estate &amp; Property</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>714</v>
+        <v>685</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Real Estate &amp; Property</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>17</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C14" s="8" t="inlineStr"/>
     </row>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>11</v>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
@@ -26377,7 +26377,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.7 / 0/14</t>
+          <t>4 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -26466,7 +26466,7 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
@@ -26656,7 +26656,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
@@ -26677,12 +26677,12 @@
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
@@ -26772,7 +26772,7 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>2 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
@@ -26796,12 +26796,12 @@
       <c r="D15" s="14" t="inlineStr"/>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/14</t>
+          <t>3 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>3 / 4.6 / 4/14</t>
+          <t>2 / 4.5 / 4/14</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
@@ -26881,7 +26881,7 @@
       <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.5 / 6/14</t>
+          <t>5 / 3.4 / 5/14</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
@@ -26934,7 +26934,7 @@
       <c r="B19" s="14" t="inlineStr"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr"/>
@@ -27097,7 +27097,7 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>6 / 7.2 / 14/14</t>
+          <t>7 / 7.3 / 14/14</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
@@ -27300,7 +27300,7 @@
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
@@ -27347,7 +27347,7 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.1 / 0/14</t>
+          <t>1 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
@@ -27374,7 +27374,7 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -27399,12 +27399,12 @@
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
@@ -27469,7 +27469,7 @@
       <c r="B32" s="13" t="inlineStr"/>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -27484,7 +27484,7 @@
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>3 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
@@ -27580,7 +27580,7 @@
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>7 / 4.1 / 6/14</t>
+          <t>9 / 4.3 / 6/14</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr"/>
@@ -27761,7 +27761,7 @@
       <c r="E39" s="14" t="inlineStr"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.2 / 3/14</t>
+          <t>6 / 3.3 / 4/14</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -27838,7 +27838,7 @@
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -27998,7 +27998,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>15 / 14.0 / 12/14</t>
+          <t>16 / 14.1 / 12/14</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr"/>
@@ -28043,7 +28043,7 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.1 / 0/14</t>
+          <t>3 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -28196,7 +28196,7 @@
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
@@ -28604,7 +28604,7 @@
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr">
@@ -28648,7 +28648,7 @@
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>6 / 3.8 / 1/14</t>
+          <t>5 / 3.7 / 0/14</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
@@ -28720,7 +28720,7 @@
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 0/14</t>
+          <t>4 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
@@ -28788,7 +28788,7 @@
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>6 / 4.6 / 4/14</t>
+          <t>8 / 4.7 / 4/14</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
@@ -28863,7 +28863,7 @@
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>5 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
@@ -28916,7 +28916,7 @@
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.3 / 0/14</t>
+          <t>4 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
@@ -28995,7 +28995,7 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.4 / 0/14</t>
+          <t>9 / 3.0 / 1/14</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
@@ -29010,7 +29010,7 @@
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
@@ -29048,7 +29048,7 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -29073,7 +29073,7 @@
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29151,7 +29151,7 @@
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29164,7 +29164,7 @@
       <c r="B73" s="14" t="inlineStr"/>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/14</t>
+          <t>1 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
@@ -29209,7 +29209,7 @@
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.1 / 0/14</t>
+          <t>3 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/14</t>
+          <t>4 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
@@ -29252,12 +29252,12 @@
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.9 / 0/14</t>
+          <t>4 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>1 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
@@ -29300,7 +29300,7 @@
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
@@ -29338,14 +29338,14 @@
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>9 / 4.5 / 6/14</t>
+          <t>8 / 4.4 / 6/14</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr"/>
       <c r="G77" s="14" t="inlineStr"/>
       <c r="H77" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.6 / 5/14</t>
+          <t>5 / 3.5 / 4/14</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
@@ -29404,12 +29404,12 @@
       <c r="D79" s="14" t="inlineStr"/>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>9 / 6.6 / 7/14</t>
+          <t>8 / 6.6 / 7/14</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>10 / 13.8 / 14/14</t>
+          <t>11 / 13.9 / 14/14</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$195</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$317</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$315</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1654</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1791</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1585</v>
+        <v>1626</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1152</v>
+        <v>1138</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>901</v>
+        <v>882</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>220</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>664</v>
+        <v>635</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>398</v>
+        <v>376</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>8</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C14" s="8" t="inlineStr"/>
     </row>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
@@ -863,7 +863,7 @@
         <v>10000</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1410</v>
+        <v>1427</v>
       </c>
     </row>
   </sheetData>
@@ -8207,7 +8207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O317"/>
+  <dimension ref="A1:O315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9352,12 +9352,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -9368,11 +9368,11 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>/birmingham/service-administrator-jobs</t>
+          <t>/glasgow/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
@@ -9384,7 +9384,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>0</v>
@@ -9407,27 +9407,27 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>/glasgow/service-administrator-jobs</t>
+          <t>/birmingham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0</v>
@@ -9439,7 +9439,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" s="5" t="n">
         <v>0</v>
@@ -9737,12 +9737,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chelmsford</t>
+          <t>Exeter</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -9753,23 +9753,23 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>/chelmsford/service-administrator-jobs</t>
+          <t>/exeter/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="5" t="n">
         <v>0</v>
@@ -9792,39 +9792,39 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Exeter</t>
+          <t>Chelmsford</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/exeter/service-administrator-jobs</t>
+          <t>/chelmsford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>0</v>
@@ -10562,27 +10562,27 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>/portsmouth/service-administrator-jobs</t>
+          <t>/chester/jobs</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0</v>
@@ -10594,7 +10594,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>0</v>
@@ -10617,12 +10617,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>/chester/jobs</t>
+          <t>/norwich/jobs</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
@@ -10646,10 +10646,10 @@
         <v>0</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="5" t="n">
         <v>0</v>
@@ -10672,12 +10672,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>Peterborough</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
@@ -10688,11 +10688,11 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>/norwich/jobs</t>
+          <t>/peterborough/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0</v>
@@ -10701,7 +10701,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>0</v>
@@ -10727,12 +10727,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Peterborough</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>/peterborough/service-administrator-jobs</t>
+          <t>/portsmouth/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Bradford</t>
+          <t>Brighton &amp; Hove</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>/bradford/service-administrator-jobs</t>
+          <t>/brighton-hove/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
@@ -11167,12 +11167,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>/brighton-hove/service-administrator-jobs</t>
+          <t>/cambridge/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
@@ -11222,12 +11222,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>/cambridge/service-administrator-jobs</t>
+          <t>/cardiff/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
@@ -11277,12 +11277,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Chester Le Street</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>/cardiff/service-administrator-jobs</t>
+          <t>/chester-le-street/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
@@ -11332,12 +11332,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Chester Le Street</t>
+          <t>Macclesfield</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>/chester-le-street/service-administrator-jobs</t>
+          <t>/macclesfield/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
@@ -11387,12 +11387,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Macclesfield</t>
+          <t>Northallerton</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>/macclesfield/service-administrator-jobs</t>
+          <t>/northallerton/jobs</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
@@ -11442,12 +11442,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Northallerton</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>/northallerton/jobs</t>
+          <t>/reading/jobs</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Worcester</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>/reading/jobs</t>
+          <t>/worcester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
@@ -11552,27 +11552,27 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Worcester</t>
+          <t>Aylesbury</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>/worcester/service-administrator-jobs</t>
+          <t>/aylesbury/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0</v>
@@ -11607,12 +11607,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Aylesbury</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>/aylesbury/service-administrator-jobs</t>
+          <t>/bradford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
@@ -11882,12 +11882,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Wakefield</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>/sunderland/service-administrator-jobs</t>
+          <t>/wakefield/jobs</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
@@ -11937,27 +11937,27 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Wakefield</t>
+          <t>Ashford</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>/wakefield/jobs</t>
+          <t>/ashford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69" s="5" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Ashford</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>/ashford/service-administrator-jobs</t>
+          <t>/barnsley/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Gloucester</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>/barnsley/service-administrator-jobs</t>
+          <t>/gloucester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Gloucester</t>
+          <t>Hemel Hempstead</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
@@ -12118,11 +12118,11 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>/gloucester/service-administrator-jobs</t>
+          <t>/hemel-hempstead/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" s="3" t="n">
         <v>0</v>
@@ -12134,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="3" t="n">
         <v>0</v>
@@ -12157,12 +12157,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Hemel Hempstead</t>
+          <t>Huddersfield</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
@@ -12173,11 +12173,11 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>/hemel-hempstead/service-administrator-jobs</t>
+          <t>/huddersfield/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="5" t="n">
         <v>0</v>
@@ -12189,7 +12189,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="5" t="n">
         <v>0</v>
@@ -12212,12 +12212,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Huddersfield</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>/huddersfield/service-administrator-jobs</t>
+          <t>/sunderland/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
@@ -12267,12 +12267,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Wigston</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>/shrewsbury/service-administrator-jobs</t>
+          <t>/wigston/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G75" s="5" t="n">
@@ -12322,27 +12322,23 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Wigston</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Leicestershire</t>
-        </is>
-      </c>
+          <t>Maidstone</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>/wigston/service-administrator-jobs</t>
+          <t>/maidstone/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" s="3" t="n">
         <v>0</v>
@@ -12377,7 +12373,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Maidstone</t>
+          <t>Poole</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
@@ -12389,7 +12385,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>/maidstone/service-administrator-jobs</t>
+          <t>/poole/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G77" s="5" t="n">
@@ -12428,7 +12424,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Poole</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr"/>
@@ -12440,7 +12436,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>/poole/service-administrator-jobs</t>
+          <t>/scarborough/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
@@ -12479,7 +12475,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -12491,7 +12487,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>/scarborough/service-administrator-jobs</t>
+          <t>/shrewsbury/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G79" s="5" t="n">
@@ -12641,14 +12637,14 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82" s="3" t="n">
         <v>0</v>
@@ -14570,12 +14566,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Hove</t>
+          <t>Maidenhead</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
@@ -14586,19 +14582,19 @@
       </c>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L120" s="3" t="n">
         <v>0</v>
@@ -14621,12 +14617,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Maidenhead</t>
+          <t>Northwich</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -14637,7 +14633,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H121" s="5" t="n">
         <v>0</v>
@@ -14649,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L121" s="5" t="n">
         <v>0</v>
@@ -14672,12 +14668,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Northwich</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
@@ -14688,7 +14684,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H122" s="3" t="n">
         <v>0</v>
@@ -14700,7 +14696,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L122" s="3" t="n">
         <v>0</v>
@@ -14723,23 +14719,23 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E123" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H123" s="5" t="n">
         <v>0</v>
@@ -14751,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L123" s="5" t="n">
         <v>0</v>
@@ -14774,12 +14770,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -14790,7 +14786,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H124" s="3" t="n">
         <v>0</v>
@@ -14802,7 +14798,7 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="3" t="n">
         <v>0</v>
@@ -14825,12 +14821,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Burgess Hill</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -14841,7 +14837,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H125" s="5" t="n">
         <v>0</v>
@@ -14853,7 +14849,7 @@
         <v>0</v>
       </c>
       <c r="K125" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" s="5" t="n">
         <v>0</v>
@@ -14876,12 +14872,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Burgess Hill</t>
+          <t>Cirencester</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -14927,12 +14923,12 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Cirencester</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -14943,13 +14939,13 @@
       </c>
       <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H127" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J127" s="5" t="n">
         <v>0</v>
@@ -14978,12 +14974,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Fleet</t>
+          <t>Gerrards Cross</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -15000,13 +14996,13 @@
         <v>0</v>
       </c>
       <c r="I128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="J128" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="L128" s="3" t="n">
         <v>0</v>
@@ -15029,7 +15025,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Gerrards Cross</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -15045,7 +15041,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H129" s="5" t="n">
         <v>0</v>
@@ -15057,7 +15053,7 @@
         <v>0</v>
       </c>
       <c r="K129" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L129" s="5" t="n">
         <v>0</v>
@@ -15080,12 +15076,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Hove</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -15102,13 +15098,13 @@
         <v>0</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K130" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" s="3" t="n">
         <v>0</v>
@@ -20792,12 +20788,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Harrogate</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
@@ -20843,12 +20839,12 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
@@ -20859,10 +20855,10 @@
       </c>
       <c r="F243" s="4" t="inlineStr"/>
       <c r="G243" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H243" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I243" s="5" t="n">
         <v>0</v>
@@ -20894,12 +20890,12 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Haywards Heath</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
@@ -20910,10 +20906,10 @@
       </c>
       <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I244" s="3" t="n">
         <v>0</v>
@@ -20945,12 +20941,12 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Haywards Heath</t>
+          <t>Hebburn</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
@@ -20961,7 +20957,7 @@
       </c>
       <c r="F245" s="4" t="inlineStr"/>
       <c r="G245" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H245" s="5" t="n">
         <v>0</v>
@@ -20982,7 +20978,7 @@
         <v>0</v>
       </c>
       <c r="N245" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245" s="5" t="n">
         <v>0</v>
@@ -20996,12 +20992,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Hebburn</t>
+          <t>Hertford</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
@@ -21012,7 +21008,7 @@
       </c>
       <c r="F246" s="2" t="inlineStr"/>
       <c r="G246" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H246" s="3" t="n">
         <v>0</v>
@@ -21033,7 +21029,7 @@
         <v>0</v>
       </c>
       <c r="N246" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O246" s="3" t="n">
         <v>0</v>
@@ -21047,12 +21043,12 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Hertford</t>
+          <t>Huntingdon</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
@@ -21098,12 +21094,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Huntingdon</t>
+          <t>Ilminster</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
@@ -21149,12 +21145,12 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Ilminster</t>
+          <t>Kendal</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
@@ -21165,10 +21161,10 @@
       </c>
       <c r="F249" s="4" t="inlineStr"/>
       <c r="G249" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H249" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I249" s="5" t="n">
         <v>0</v>
@@ -21200,12 +21196,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Kendal</t>
+          <t>Kidlington</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
@@ -21216,10 +21212,10 @@
       </c>
       <c r="F250" s="2" t="inlineStr"/>
       <c r="G250" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I250" s="3" t="n">
         <v>0</v>
@@ -21251,12 +21247,12 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Kidlington</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
@@ -21302,12 +21298,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Lichfield</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
@@ -21318,7 +21314,7 @@
       </c>
       <c r="F252" s="2" t="inlineStr"/>
       <c r="G252" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
         <v>0</v>
@@ -21339,7 +21335,7 @@
         <v>0</v>
       </c>
       <c r="N252" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O252" s="3" t="n">
         <v>0</v>
@@ -21353,12 +21349,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Lichfield</t>
+          <t>Liskeard</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
@@ -21369,7 +21365,7 @@
       </c>
       <c r="F253" s="4" t="inlineStr"/>
       <c r="G253" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H253" s="5" t="n">
         <v>0</v>
@@ -21390,7 +21386,7 @@
         <v>0</v>
       </c>
       <c r="N253" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O253" s="5" t="n">
         <v>0</v>
@@ -21404,12 +21400,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Liskeard</t>
+          <t>Littlehampton</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
@@ -21455,12 +21451,12 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Littlehampton</t>
+          <t>Loughborough</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
@@ -21506,12 +21502,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Loughborough</t>
+          <t>Marlborough</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
@@ -21557,12 +21553,12 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Marlborough</t>
+          <t>Marlow</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
@@ -21608,12 +21604,12 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Marlow</t>
+          <t>Mirfield</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
@@ -21659,12 +21655,12 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Mirfield</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
@@ -21675,13 +21671,13 @@
       </c>
       <c r="F259" s="4" t="inlineStr"/>
       <c r="G259" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H259" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I259" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J259" s="5" t="n">
         <v>0</v>
@@ -21710,12 +21706,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
@@ -21726,13 +21722,13 @@
       </c>
       <c r="F260" s="2" t="inlineStr"/>
       <c r="G260" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H260" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I260" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J260" s="3" t="n">
         <v>0</v>
@@ -21761,12 +21757,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
@@ -21812,12 +21808,12 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Newmarket</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D262" s="3" t="n">
@@ -21863,12 +21859,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Newmarket</t>
+          <t>North Shields</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
@@ -21914,12 +21910,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>North Shields</t>
+          <t>Northfleet</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D264" s="3" t="n">
@@ -21930,13 +21926,13 @@
       </c>
       <c r="F264" s="2" t="inlineStr"/>
       <c r="G264" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H264" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J264" s="3" t="n">
         <v>0</v>
@@ -21965,12 +21961,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Northfleet</t>
+          <t>Otley</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
@@ -21981,13 +21977,13 @@
       </c>
       <c r="F265" s="4" t="inlineStr"/>
       <c r="G265" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H265" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I265" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J265" s="5" t="n">
         <v>0</v>
@@ -22016,12 +22012,12 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Otley</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
@@ -22032,13 +22028,13 @@
       </c>
       <c r="F266" s="2" t="inlineStr"/>
       <c r="G266" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H266" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I266" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J266" s="3" t="n">
         <v>0</v>
@@ -22067,12 +22063,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Pickering</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
@@ -22083,13 +22079,13 @@
       </c>
       <c r="F267" s="4" t="inlineStr"/>
       <c r="G267" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H267" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I267" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J267" s="5" t="n">
         <v>0</v>
@@ -22118,12 +22114,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Pickering</t>
+          <t>Pontefract</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D268" s="3" t="n">
@@ -22169,12 +22165,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Pontefract</t>
+          <t>Portishead</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D269" s="5" t="n">
@@ -22220,12 +22216,12 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Portishead</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D270" s="3" t="n">
@@ -22271,12 +22267,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Redruth</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D271" s="5" t="n">
@@ -22322,12 +22318,12 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Redruth</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D272" s="3" t="n">
@@ -22373,7 +22369,7 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
@@ -22389,7 +22385,7 @@
       </c>
       <c r="F273" s="4" t="inlineStr"/>
       <c r="G273" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H273" s="5" t="n">
         <v>0</v>
@@ -22401,7 +22397,7 @@
         <v>0</v>
       </c>
       <c r="K273" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L273" s="5" t="n">
         <v>0</v>
@@ -22424,12 +22420,12 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D274" s="3" t="n">
@@ -22440,7 +22436,7 @@
       </c>
       <c r="F274" s="2" t="inlineStr"/>
       <c r="G274" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H274" s="3" t="n">
         <v>0</v>
@@ -22452,7 +22448,7 @@
         <v>0</v>
       </c>
       <c r="K274" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L274" s="3" t="n">
         <v>0</v>
@@ -22475,12 +22471,12 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Rochester</t>
+          <t>Romsey</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
@@ -22526,12 +22522,12 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Romsey</t>
+          <t>Rugby</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D276" s="3" t="n">
@@ -22577,12 +22573,12 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Rugby</t>
+          <t>Ryton</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
@@ -22628,12 +22624,12 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Ryton</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D278" s="3" t="n">
@@ -22679,12 +22675,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D279" s="5" t="n">
@@ -22730,12 +22726,12 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Seaham</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D280" s="3" t="n">
@@ -22781,12 +22777,12 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Seaham</t>
+          <t>Sevenoaks</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D281" s="5" t="n">
@@ -22832,12 +22828,12 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Sevenoaks</t>
+          <t>Sherborne</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D282" s="3" t="n">
@@ -22883,12 +22879,12 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Shepperton</t>
+          <t>Shipley</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D283" s="5" t="n">
@@ -22934,12 +22930,12 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Sherborne</t>
+          <t>Shirley</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D284" s="3" t="n">
@@ -22985,12 +22981,12 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Shipley</t>
+          <t>Snodland</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D285" s="5" t="n">
@@ -23001,13 +22997,13 @@
       </c>
       <c r="F285" s="4" t="inlineStr"/>
       <c r="G285" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H285" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I285" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J285" s="5" t="n">
         <v>0</v>
@@ -23036,12 +23032,12 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Southam</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D286" s="3" t="n">
@@ -23087,12 +23083,12 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Snodland</t>
+          <t>Southend-on-sea</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D287" s="5" t="n">
@@ -23103,13 +23099,13 @@
       </c>
       <c r="F287" s="4" t="inlineStr"/>
       <c r="G287" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H287" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I287" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J287" s="5" t="n">
         <v>0</v>
@@ -23138,12 +23134,12 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Southam</t>
+          <t>Spennymoor</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D288" s="3" t="n">
@@ -23189,12 +23185,12 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Southend-on-sea</t>
+          <t>St. Austell</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D289" s="5" t="n">
@@ -23240,12 +23236,12 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Spennymoor</t>
+          <t>St. Ives</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D290" s="3" t="n">
@@ -23291,12 +23287,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>St. Austell</t>
+          <t>St. Neots</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D291" s="5" t="n">
@@ -23342,12 +23338,12 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>St. Ives</t>
+          <t>Stafford</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D292" s="3" t="n">
@@ -23393,12 +23389,12 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>St. Neots</t>
+          <t>Staines</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
@@ -23444,12 +23440,12 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>Street</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D294" s="3" t="n">
@@ -23495,12 +23491,12 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Staines</t>
+          <t>Stroud</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D295" s="5" t="n">
@@ -23546,7 +23542,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Taunton</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -23597,12 +23593,12 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Stroud</t>
+          <t>Tipton</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D297" s="5" t="n">
@@ -23648,12 +23644,12 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Taunton</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D298" s="3" t="n">
@@ -23664,13 +23660,13 @@
       </c>
       <c r="F298" s="2" t="inlineStr"/>
       <c r="G298" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H298" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I298" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J298" s="3" t="n">
         <v>0</v>
@@ -23699,12 +23695,12 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Tipton</t>
+          <t>Ulverston</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D299" s="5" t="n">
@@ -23715,10 +23711,10 @@
       </c>
       <c r="F299" s="4" t="inlineStr"/>
       <c r="G299" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H299" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I299" s="5" t="n">
         <v>0</v>
@@ -23750,12 +23746,12 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D300" s="3" t="n">
@@ -23766,13 +23762,13 @@
       </c>
       <c r="F300" s="2" t="inlineStr"/>
       <c r="G300" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H300" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I300" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J300" s="3" t="n">
         <v>0</v>
@@ -23801,12 +23797,12 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Ulverston</t>
+          <t>Waltham Cross</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D301" s="5" t="n">
@@ -23817,10 +23813,10 @@
       </c>
       <c r="F301" s="4" t="inlineStr"/>
       <c r="G301" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H301" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I301" s="5" t="n">
         <v>0</v>
@@ -23852,12 +23848,12 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Walton-on-thames</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D302" s="3" t="n">
@@ -23903,7 +23899,7 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Waltham Cross</t>
+          <t>Ware</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
@@ -23954,12 +23950,12 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Wednesbury</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D304" s="3" t="n">
@@ -24005,12 +24001,12 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Ware</t>
+          <t>Wellingborough</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D305" s="5" t="n">
@@ -24056,12 +24052,12 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Wednesbury</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D306" s="3" t="n">
@@ -24107,12 +24103,12 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Wellingborough</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D307" s="5" t="n">
@@ -24158,12 +24154,12 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D308" s="3" t="n">
@@ -24209,12 +24205,12 @@
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Whitstable</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D309" s="5" t="n">
@@ -24225,13 +24221,13 @@
       </c>
       <c r="F309" s="4" t="inlineStr"/>
       <c r="G309" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H309" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I309" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J309" s="5" t="n">
         <v>0</v>
@@ -24260,12 +24256,12 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Wilmslow</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D310" s="3" t="n">
@@ -24311,12 +24307,12 @@
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Whitstable</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D311" s="5" t="n">
@@ -24327,13 +24323,13 @@
       </c>
       <c r="F311" s="4" t="inlineStr"/>
       <c r="G311" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H311" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I311" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J311" s="5" t="n">
         <v>0</v>
@@ -24362,12 +24358,12 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Wilmslow</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D312" s="3" t="n">
@@ -24413,12 +24409,12 @@
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Witney</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D313" s="5" t="n">
@@ -24464,12 +24460,12 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Worksop</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D314" s="3" t="n">
@@ -24515,12 +24511,12 @@
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Witney</t>
+          <t>Wymondham</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D315" s="5" t="n">
@@ -24558,110 +24554,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316">
-      <c r="A316" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B316" s="2" t="inlineStr">
-        <is>
-          <t>Worksop</t>
-        </is>
-      </c>
-      <c r="C316" s="2" t="inlineStr">
-        <is>
-          <t>Nottinghamshire</t>
-        </is>
-      </c>
-      <c r="D316" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E316" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F316" s="2" t="inlineStr"/>
-      <c r="G316" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H316" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I316" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J316" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K316" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L316" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M316" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N316" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O316" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B317" s="4" t="inlineStr">
-        <is>
-          <t>Wymondham</t>
-        </is>
-      </c>
-      <c r="C317" s="4" t="inlineStr">
-        <is>
-          <t>Norfolk</t>
-        </is>
-      </c>
-      <c r="D317" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E317" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F317" s="4" t="inlineStr"/>
-      <c r="G317" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H317" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I317" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J317" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K317" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L317" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M317" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N317" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O317" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O317"/>
+  <autoFilter ref="A1:O315"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25023,7 +24917,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
@@ -25149,7 +25043,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>10</v>
@@ -25340,7 +25234,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>18</v>
@@ -25456,7 +25350,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -25789,7 +25683,7 @@
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
       <c r="D59" s="4" t="inlineStr"/>
@@ -25865,7 +25759,7 @@
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
@@ -25892,7 +25786,7 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>2</v>
@@ -26009,7 +25903,7 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>
@@ -26119,7 +26013,7 @@
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
       <c r="D77" s="4" t="inlineStr"/>
@@ -26163,7 +26057,7 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C79" s="5" t="n">
         <v>1</v>
@@ -26272,17 +26166,17 @@
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/14</t>
+          <t>3 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>6 / 3.6 / 2/14</t>
+          <t>5 / 3.7 / 2/14</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
@@ -26292,12 +26186,12 @@
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26310,13 +26204,13 @@
       <c r="B3" s="14" t="inlineStr"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>4 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr"/>
@@ -26328,7 +26222,7 @@
       <c r="H3" s="14" t="inlineStr"/>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26341,25 +26235,25 @@
       <c r="B4" s="13" t="inlineStr"/>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>10 / 5.4 / 7/14</t>
+          <t>10 / 5.8 / 8/14</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.3 / 0/14</t>
+          <t>3 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.3 / 0/14</t>
+          <t>2 / 3.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26377,23 +26271,23 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>5 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/14</t>
+          <t>3 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr"/>
@@ -26412,28 +26306,28 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>2 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>3 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26451,22 +26345,22 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.6 / 0/14</t>
+          <t>4 / 3.7 / 0/14</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>3 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
@@ -26476,7 +26370,7 @@
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.3 / 0/14</t>
+          <t>2 / 2.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26489,12 +26383,12 @@
       <c r="B8" s="13" t="inlineStr"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>2 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -26504,7 +26398,7 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.4 / 0/14</t>
+          <t>5 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
@@ -26533,7 +26427,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -26567,7 +26461,7 @@
       <c r="B10" s="13" t="inlineStr"/>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -26609,7 +26503,7 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -26662,7 +26556,7 @@
       <c r="C12" s="13" t="inlineStr"/>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -26752,17 +26646,17 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.6 / 0/14</t>
+          <t>3 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 0/14</t>
+          <t>2 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
@@ -26772,12 +26666,12 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.5 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26790,24 +26684,24 @@
       <c r="B15" s="14" t="inlineStr"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.2 / 0/14</t>
+          <t>2 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr"/>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/14</t>
+          <t>3 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>2 / 4.5 / 4/14</t>
+          <t>2 / 4.2 / 3/14</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
@@ -26830,22 +26724,22 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.3 / 0/14</t>
+          <t>2 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>6 / 1.9 / 1/14</t>
+          <t>6 / 2.3 / 2/14</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
@@ -26868,12 +26762,12 @@
       <c r="B17" s="14" t="inlineStr"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.8 / 1/14</t>
+          <t>2 / 3.6 / 1/14</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
@@ -26881,12 +26775,12 @@
       <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.4 / 5/14</t>
+          <t>5 / 3.7 / 5/14</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.9 / 0/14</t>
+          <t>2 / 2.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26904,12 +26798,12 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>1 / 3.4 / 3/14</t>
+          <t>1 / 3.2 / 3/14</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr"/>
@@ -26940,7 +26834,7 @@
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>17 / 9.5 / 10/14</t>
+          <t>17 / 10.4 / 11/14</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr"/>
@@ -26948,7 +26842,7 @@
       <c r="H19" s="14" t="inlineStr"/>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.5 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26960,12 +26854,12 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.4 / 0/14</t>
+          <t>4 / 3.5 / 0/14</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
@@ -26985,12 +26879,12 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
@@ -27029,12 +26923,12 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27057,7 +26951,7 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
@@ -27092,22 +26986,22 @@
       <c r="D23" s="14" t="inlineStr"/>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>7 / 7.3 / 14/14</t>
+          <t>7 / 7.1 / 14/14</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>5 / 2.9 / 0/14</t>
+          <t>4 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>7 / 5.8 / 7/14</t>
+          <t>7 / 6.0 / 8/14</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr"/>
@@ -27120,7 +27014,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -27168,7 +27062,7 @@
       <c r="B25" s="14" t="inlineStr"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr"/>
@@ -27180,7 +27074,7 @@
       <c r="F25" s="14" t="inlineStr"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/14</t>
+          <t>3 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
@@ -27190,7 +27084,7 @@
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27205,23 +27099,23 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>11 / 9.3 / 10/14</t>
+          <t>10 / 9.8 / 11/14</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/14</t>
+          <t>2 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27280,7 +27174,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -27300,12 +27194,12 @@
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -27315,7 +27209,7 @@
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27327,7 +27221,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 0/14</t>
+          <t>3 / 3.0 / 0/14</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -27337,7 +27231,7 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -27347,12 +27241,12 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/14</t>
+          <t>1 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/14</t>
+          <t>2 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
@@ -27374,7 +27268,7 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -27389,7 +27283,7 @@
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -27399,12 +27293,12 @@
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
@@ -27479,17 +27373,17 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 0/14</t>
+          <t>4 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.3 / 0/14</t>
+          <t>4 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/14</t>
+          <t>3 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -27499,7 +27393,7 @@
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27517,12 +27411,12 @@
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.6 / 0/14</t>
+          <t>0 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/14</t>
+          <t>3 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
@@ -27537,7 +27431,7 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
@@ -27570,17 +27464,17 @@
       <c r="B35" s="14" t="inlineStr"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>9 / 4.3 / 6/14</t>
+          <t>9 / 4.9 / 7/14</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr"/>
@@ -27596,7 +27490,7 @@
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27608,7 +27502,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>2 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -27655,7 +27549,7 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>5 / 1.4 / 0/14</t>
+          <t>5 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -27665,7 +27559,7 @@
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>2 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
@@ -27675,12 +27569,12 @@
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
@@ -27737,7 +27631,7 @@
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27755,28 +27649,28 @@
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.3 / 4/14</t>
+          <t>7 / 3.7 / 5/14</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27791,14 +27685,14 @@
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.5 / 0/14</t>
+          <t>4 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr"/>
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.4 / 0/14</t>
+          <t>2 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
@@ -27818,27 +27712,27 @@
       <c r="D41" s="14" t="inlineStr"/>
       <c r="E41" s="14" t="inlineStr">
         <is>
+          <t>1 / 1.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
           <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="H41" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>1 / 1.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27850,7 +27744,7 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.0 / 0/14</t>
+          <t>3 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -27870,7 +27764,7 @@
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
@@ -27897,7 +27791,7 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.0 / 0/14</t>
+          <t>2 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
@@ -27912,7 +27806,7 @@
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
@@ -27927,7 +27821,7 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
@@ -27945,12 +27839,12 @@
       <c r="B44" s="13" t="inlineStr"/>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>4 / 5.9 / 6/14</t>
+          <t>4 / 5.5 / 5/14</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -27960,22 +27854,22 @@
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.6 / 0/14</t>
+          <t>2 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.6 / 0/14</t>
+          <t>5 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.3 / 0/14</t>
+          <t>4 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27988,7 +27882,7 @@
       <c r="B45" s="14" t="inlineStr"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>2 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
@@ -27998,7 +27892,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>16 / 14.1 / 12/14</t>
+          <t>20 / 15.4 / 13/14</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr"/>
@@ -28006,7 +27900,7 @@
       <c r="H45" s="14" t="inlineStr"/>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28018,7 +27912,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>19 / 21.4 / 13/14</t>
+          <t>18 / 22.5 / 14/14</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -28028,22 +27922,22 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.3 / 0/14</t>
+          <t>1 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/14</t>
+          <t>3 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/14</t>
+          <t>3 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -28053,7 +27947,7 @@
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28066,7 +27960,7 @@
       <c r="B47" s="14" t="inlineStr"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
@@ -28076,12 +27970,12 @@
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>6 / 4.2 / 6/14</t>
+          <t>7 / 4.6 / 7/14</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.8 / 0/14</t>
+          <t>2 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -28106,12 +28000,12 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.9 / 0/14</t>
+          <t>3 / 3.8 / 0/14</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>5 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr"/>
@@ -28122,12 +28016,12 @@
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.3 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28186,7 +28080,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.6 / 0/14</t>
+          <t>5 / 3.8 / 0/14</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -28239,22 +28133,22 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.6 / 0/14</t>
+          <t>1 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">
@@ -28276,7 +28170,7 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>1 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -28301,17 +28195,17 @@
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="H52" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.1 / 0/14</t>
-        </is>
-      </c>
-      <c r="H52" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28323,7 +28217,7 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>9 / 2.4 / 2/14</t>
+          <t>9 / 2.9 / 3/14</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -28333,7 +28227,7 @@
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -28386,7 +28280,7 @@
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
@@ -28413,7 +28307,7 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
@@ -28467,7 +28361,7 @@
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
@@ -28477,7 +28371,7 @@
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -28487,7 +28381,7 @@
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28418,7 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="H57" s="14" t="inlineStr">
@@ -28599,12 +28493,12 @@
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>3 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr">
@@ -28620,7 +28514,7 @@
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28633,12 +28527,12 @@
       <c r="B60" s="13" t="inlineStr"/>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.9 / 0/14</t>
+          <t>2 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -28648,22 +28542,22 @@
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.7 / 0/14</t>
+          <t>5 / 3.8 / 0/14</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="H60" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
-      <c r="H60" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/14</t>
-        </is>
-      </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28686,17 +28580,17 @@
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>6 / 4.2 / 5/14</t>
+          <t>7 / 4.6 / 6/14</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>3 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="H61" s="14" t="inlineStr">
@@ -28726,12 +28620,12 @@
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/14</t>
+          <t>2 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
@@ -28741,7 +28635,7 @@
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28756,7 +28650,7 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>7 / 7.9 / 10/14</t>
+          <t>7 / 8.1 / 11/14</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
@@ -28767,7 +28661,7 @@
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
-          <t>5 / 4.1 / 0/14</t>
+          <t>4 / 4.1 / 0/14</t>
         </is>
       </c>
       <c r="I63" s="14" t="inlineStr"/>
@@ -28783,23 +28677,23 @@
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>5 / 4.0 / 0/14</t>
+          <t>5 / 4.1 / 0/14</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>8 / 4.7 / 4/14</t>
+          <t>8 / 5.0 / 5/14</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>7 / 3.5 / 1/14</t>
+          <t>8 / 3.9 / 2/14</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/14</t>
+          <t>1 / 2.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28858,12 +28752,12 @@
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.9 / 0/14</t>
+          <t>1 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>5 / 0.4 / 0/14</t>
+          <t>3 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
@@ -28873,7 +28767,7 @@
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
@@ -28888,7 +28782,7 @@
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
@@ -28911,12 +28805,12 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.6 / 0/14</t>
+          <t>1 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.4 / 0/14</t>
+          <t>3 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
@@ -28963,7 +28857,7 @@
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
@@ -28978,7 +28872,7 @@
       </c>
       <c r="H68" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I68" s="13" t="inlineStr">
@@ -28995,7 +28889,7 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>9 / 3.0 / 1/14</t>
+          <t>10 / 3.4 / 2/14</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
@@ -29005,7 +28899,7 @@
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
@@ -29043,7 +28937,7 @@
       <c r="B70" s="13" t="inlineStr"/>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
@@ -29053,7 +28947,7 @@
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.6 / 0/14</t>
+          <t>1 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
@@ -29073,7 +28967,7 @@
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29091,24 +28985,24 @@
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>3 / 5.9 / 6/14</t>
+          <t>2 / 5.3 / 5/14</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>12 / 6.2 / 7/14</t>
+          <t>12 / 6.7 / 8/14</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 0/14</t>
+          <t>2 / 3.0 / 0/14</t>
         </is>
       </c>
       <c r="H71" s="14" t="inlineStr"/>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.5 / 0/14</t>
+          <t>1 / 2.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29136,17 +29030,17 @@
       </c>
       <c r="F72" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I72" s="13" t="inlineStr">
@@ -29164,22 +29058,22 @@
       <c r="B73" s="14" t="inlineStr"/>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.7 / 0/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.6 / 6/14</t>
+          <t>2 / 3.3 / 5/14</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.7 / 0/14</t>
+          <t>3 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>5 / 5.2 / 5/14</t>
+          <t>5 / 5.3 / 5/14</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -29209,27 +29103,27 @@
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.2 / 0/14</t>
+          <t>5 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.7 / 0/14</t>
+          <t>4 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.6 / 0/14</t>
+          <t>4 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/14</t>
+          <t>3 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29247,22 +29141,22 @@
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>1 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.9 / 0/14</t>
+          <t>4 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="H75" s="14" t="inlineStr">
@@ -29295,17 +29189,17 @@
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>0 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.7 / 0/14</t>
+          <t>3 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
@@ -29315,7 +29209,7 @@
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29333,19 +29227,19 @@
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.5 / 0/14</t>
+          <t>2 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>8 / 4.4 / 6/14</t>
+          <t>8 / 5.0 / 7/14</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr"/>
       <c r="G77" s="14" t="inlineStr"/>
       <c r="H77" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.5 / 4/14</t>
+          <t>5 / 3.7 / 4/14</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
@@ -29364,7 +29258,7 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.3 / 0/14</t>
+          <t>2 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -29379,12 +29273,12 @@
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>3 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.1 / 0/14</t>
+          <t>3 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
@@ -29404,19 +29298,19 @@
       <c r="D79" s="14" t="inlineStr"/>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>8 / 6.6 / 7/14</t>
+          <t>8 / 6.8 / 8/14</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>11 / 13.9 / 14/14</t>
+          <t>11 / 13.5 / 14/14</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>
       <c r="H79" s="14" t="inlineStr"/>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.4 / 0/14</t>
+          <t>2 / 2.3 / 0/14</t>
         </is>
       </c>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$199</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$326</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$325</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1672</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1809</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="6">
@@ -8359,7 +8359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O326"/>
+  <dimension ref="A1:O325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>1</v>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0</v>
@@ -10101,12 +10101,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chelmsford</t>
+          <t>Milton Keynes</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>/chelmsford/service-administrator-jobs</t>
+          <t>/milton-keynes/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
@@ -10130,10 +10130,10 @@
         <v>0</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" s="5" t="n">
         <v>0</v>
@@ -10156,27 +10156,27 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Milton Keynes</t>
+          <t>Chelmsford</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>/milton-keynes/service-administrator-jobs</t>
+          <t>/chelmsford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0</v>
@@ -10185,10 +10185,10 @@
         <v>0</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0</v>
@@ -20430,12 +20430,12 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Ellesmere Port</t>
+          <t>Epsom</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
@@ -20446,7 +20446,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr"/>
       <c r="G232" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H232" s="3" t="n">
         <v>0</v>
@@ -20458,7 +20458,7 @@
         <v>0</v>
       </c>
       <c r="K232" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L232" s="3" t="n">
         <v>0</v>
@@ -20481,7 +20481,7 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Epsom</t>
+          <t>Esher</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -20503,13 +20503,13 @@
         <v>0</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J233" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K233" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L233" s="5" t="n">
         <v>0</v>
@@ -20532,12 +20532,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Esher</t>
+          <t>Farnborough</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
@@ -20548,13 +20548,13 @@
       </c>
       <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H234" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J234" s="3" t="n">
         <v>0</v>
@@ -20583,12 +20583,12 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Farnborough</t>
+          <t>Felixstowe</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
@@ -20634,12 +20634,12 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Felixstowe</t>
+          <t>Fetcham</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
         <v>0</v>
@@ -20671,7 +20671,7 @@
         <v>0</v>
       </c>
       <c r="N236" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O236" s="3" t="n">
         <v>0</v>
@@ -20685,12 +20685,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Fetcham</t>
+          <t>Folkestone</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
@@ -20713,7 +20713,7 @@
         <v>0</v>
       </c>
       <c r="K237" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L237" s="5" t="n">
         <v>0</v>
@@ -20722,7 +20722,7 @@
         <v>0</v>
       </c>
       <c r="N237" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O237" s="5" t="n">
         <v>0</v>
@@ -20736,12 +20736,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Folkestone</t>
+          <t>Freshwater</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
@@ -20755,7 +20755,7 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I238" s="3" t="n">
         <v>0</v>
@@ -20764,7 +20764,7 @@
         <v>0</v>
       </c>
       <c r="K238" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L238" s="3" t="n">
         <v>0</v>
@@ -20787,12 +20787,12 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Freshwater</t>
+          <t>Gainsborough</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
@@ -20803,10 +20803,10 @@
       </c>
       <c r="F239" s="4" t="inlineStr"/>
       <c r="G239" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H239" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I239" s="5" t="n">
         <v>0</v>
@@ -20838,12 +20838,12 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Gainsborough</t>
+          <t>Gerrards Cross</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
@@ -20889,12 +20889,12 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Gerrards Cross</t>
+          <t>Godalming</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D241" s="5" t="n">
@@ -20905,13 +20905,13 @@
       </c>
       <c r="F241" s="4" t="inlineStr"/>
       <c r="G241" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H241" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J241" s="5" t="n">
         <v>0</v>
@@ -20940,7 +20940,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Godalming</t>
+          <t>Godstone</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -20956,13 +20956,13 @@
       </c>
       <c r="F242" s="2" t="inlineStr"/>
       <c r="G242" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H242" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J242" s="3" t="n">
         <v>0</v>
@@ -20991,12 +20991,12 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Godstone</t>
+          <t>Goole</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
@@ -21042,12 +21042,12 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Goole</t>
+          <t>Gravesend</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
@@ -21058,10 +21058,10 @@
       </c>
       <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I244" s="3" t="n">
         <v>0</v>
@@ -21093,12 +21093,12 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Gravesend</t>
+          <t>Great Yarmouth</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
@@ -21109,10 +21109,10 @@
       </c>
       <c r="F245" s="4" t="inlineStr"/>
       <c r="G245" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H245" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I245" s="5" t="n">
         <v>0</v>
@@ -21144,12 +21144,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Great Yarmouth</t>
+          <t>Hailsham</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
@@ -21160,13 +21160,13 @@
       </c>
       <c r="F246" s="2" t="inlineStr"/>
       <c r="G246" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J246" s="3" t="n">
         <v>0</v>
@@ -21195,12 +21195,12 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Hailsham</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
@@ -21214,10 +21214,10 @@
         <v>0</v>
       </c>
       <c r="H247" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I247" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J247" s="5" t="n">
         <v>0</v>
@@ -21246,12 +21246,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Hastings</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
@@ -21265,10 +21265,10 @@
         <v>0</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I248" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J248" s="3" t="n">
         <v>0</v>
@@ -21297,12 +21297,12 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Hastings</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
@@ -21313,13 +21313,13 @@
       </c>
       <c r="F249" s="4" t="inlineStr"/>
       <c r="G249" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H249" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I249" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J249" s="5" t="n">
         <v>0</v>
@@ -21348,12 +21348,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>Heanor</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
@@ -21399,12 +21399,12 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Heanor</t>
+          <t>Hebburn</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="F251" s="4" t="inlineStr"/>
       <c r="G251" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H251" s="5" t="n">
         <v>0</v>
@@ -21436,7 +21436,7 @@
         <v>0</v>
       </c>
       <c r="N251" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O251" s="5" t="n">
         <v>0</v>
@@ -21450,12 +21450,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Hebburn</t>
+          <t>Hertford</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
@@ -21466,7 +21466,7 @@
       </c>
       <c r="F252" s="2" t="inlineStr"/>
       <c r="G252" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H252" s="3" t="n">
         <v>0</v>
@@ -21487,7 +21487,7 @@
         <v>0</v>
       </c>
       <c r="N252" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O252" s="3" t="n">
         <v>0</v>
@@ -21501,12 +21501,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Hertford</t>
+          <t>Huntingdon</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
@@ -21552,12 +21552,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Huntingdon</t>
+          <t>Ilminster</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
@@ -21603,12 +21603,12 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Ilminster</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
@@ -21654,12 +21654,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
@@ -21705,12 +21705,12 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Kidlington</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
@@ -21756,12 +21756,12 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Kidlington</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
@@ -21807,12 +21807,12 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Lewes</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
@@ -21858,12 +21858,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Lewes</t>
+          <t>Lichfield</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
@@ -21874,7 +21874,7 @@
       </c>
       <c r="F260" s="2" t="inlineStr"/>
       <c r="G260" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H260" s="3" t="n">
         <v>0</v>
@@ -21895,7 +21895,7 @@
         <v>0</v>
       </c>
       <c r="N260" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O260" s="3" t="n">
         <v>0</v>
@@ -21909,12 +21909,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Lichfield</t>
+          <t>Liskeard</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
@@ -21925,7 +21925,7 @@
       </c>
       <c r="F261" s="4" t="inlineStr"/>
       <c r="G261" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H261" s="5" t="n">
         <v>0</v>
@@ -21946,7 +21946,7 @@
         <v>0</v>
       </c>
       <c r="N261" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O261" s="5" t="n">
         <v>0</v>
@@ -21960,12 +21960,12 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Liskeard</t>
+          <t>Littlehampton</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D262" s="3" t="n">
@@ -22011,12 +22011,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Littlehampton</t>
+          <t>Loughborough</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
@@ -22062,12 +22062,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Loughborough</t>
+          <t>Marlborough</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D264" s="3" t="n">
@@ -22113,12 +22113,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Marlborough</t>
+          <t>Marlow</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
@@ -22164,12 +22164,12 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Marlow</t>
+          <t>Mirfield</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
@@ -22215,12 +22215,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Mirfield</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
@@ -22231,13 +22231,13 @@
       </c>
       <c r="F267" s="4" t="inlineStr"/>
       <c r="G267" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H267" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I267" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J267" s="5" t="n">
         <v>0</v>
@@ -22266,12 +22266,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D268" s="3" t="n">
@@ -22282,13 +22282,13 @@
       </c>
       <c r="F268" s="2" t="inlineStr"/>
       <c r="G268" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H268" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I268" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J268" s="3" t="n">
         <v>0</v>
@@ -22317,12 +22317,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D269" s="5" t="n">
@@ -22368,12 +22368,12 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Newmarket</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D270" s="3" t="n">
@@ -22419,12 +22419,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Newmarket</t>
+          <t>Newton Aycliffe</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D271" s="5" t="n">
@@ -22470,12 +22470,12 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Newton Aycliffe</t>
+          <t>North Shields</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D272" s="3" t="n">
@@ -22521,12 +22521,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>North Shields</t>
+          <t>Northfleet</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
@@ -22537,13 +22537,13 @@
       </c>
       <c r="F273" s="4" t="inlineStr"/>
       <c r="G273" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H273" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I273" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J273" s="5" t="n">
         <v>0</v>
@@ -22572,12 +22572,12 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Northfleet</t>
+          <t>Otley</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D274" s="3" t="n">
@@ -22588,13 +22588,13 @@
       </c>
       <c r="F274" s="2" t="inlineStr"/>
       <c r="G274" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H274" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I274" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J274" s="3" t="n">
         <v>0</v>
@@ -22623,12 +22623,12 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Otley</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
@@ -22639,13 +22639,13 @@
       </c>
       <c r="F275" s="4" t="inlineStr"/>
       <c r="G275" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H275" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I275" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J275" s="5" t="n">
         <v>0</v>
@@ -22674,12 +22674,12 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Pontefract</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D276" s="3" t="n">
@@ -22690,13 +22690,13 @@
       </c>
       <c r="F276" s="2" t="inlineStr"/>
       <c r="G276" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H276" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I276" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J276" s="3" t="n">
         <v>0</v>
@@ -22725,12 +22725,12 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Pontefract</t>
+          <t>Portishead</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
@@ -22776,12 +22776,12 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Portishead</t>
+          <t>Ramsgate</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D278" s="3" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Ramsgate</t>
+          <t>Redruth</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D279" s="5" t="n">
@@ -22878,12 +22878,12 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Redruth</t>
+          <t>Reigate</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D280" s="3" t="n">
@@ -22894,7 +22894,7 @@
       </c>
       <c r="F280" s="2" t="inlineStr"/>
       <c r="G280" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H280" s="3" t="n">
         <v>0</v>
@@ -22906,7 +22906,7 @@
         <v>0</v>
       </c>
       <c r="K280" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L280" s="3" t="n">
         <v>0</v>
@@ -22929,12 +22929,12 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Reigate</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D281" s="5" t="n">
@@ -22945,7 +22945,7 @@
       </c>
       <c r="F281" s="4" t="inlineStr"/>
       <c r="G281" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H281" s="5" t="n">
         <v>0</v>
@@ -22957,7 +22957,7 @@
         <v>0</v>
       </c>
       <c r="K281" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L281" s="5" t="n">
         <v>0</v>
@@ -22980,12 +22980,12 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D282" s="3" t="n">
@@ -23031,12 +23031,12 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Rochester</t>
+          <t>Rugby</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D283" s="5" t="n">
@@ -23082,12 +23082,12 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Rugby</t>
+          <t>Ryton</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D284" s="3" t="n">
@@ -23133,12 +23133,12 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Ryton</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D285" s="5" t="n">
@@ -23184,12 +23184,12 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D286" s="3" t="n">
@@ -23235,12 +23235,12 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Seaham</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D287" s="5" t="n">
@@ -23286,12 +23286,12 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Seaham</t>
+          <t>Sevenoaks</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D288" s="3" t="n">
@@ -23337,12 +23337,12 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Sevenoaks</t>
+          <t>Shirley</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D289" s="5" t="n">
@@ -23388,12 +23388,12 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Snodland</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D290" s="3" t="n">
@@ -23404,13 +23404,13 @@
       </c>
       <c r="F290" s="2" t="inlineStr"/>
       <c r="G290" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H290" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I290" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J290" s="3" t="n">
         <v>0</v>
@@ -23439,12 +23439,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Snodland</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D291" s="5" t="n">
@@ -23461,7 +23461,7 @@
         <v>0</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J291" s="5" t="n">
         <v>0</v>
@@ -23473,7 +23473,7 @@
         <v>0</v>
       </c>
       <c r="M291" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N291" s="5" t="n">
         <v>0</v>
@@ -23490,12 +23490,12 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Southam</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D292" s="3" t="n">
@@ -23506,7 +23506,7 @@
       </c>
       <c r="F292" s="2" t="inlineStr"/>
       <c r="G292" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H292" s="3" t="n">
         <v>0</v>
@@ -23524,7 +23524,7 @@
         <v>0</v>
       </c>
       <c r="M292" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N292" s="3" t="n">
         <v>0</v>
@@ -23541,12 +23541,12 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Southam</t>
+          <t>Southend-on-sea</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
@@ -23592,12 +23592,12 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Southend-on-sea</t>
+          <t>Spennymoor</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D294" s="3" t="n">
@@ -23643,12 +23643,12 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Spennymoor</t>
+          <t>St. Austell</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D295" s="5" t="n">
@@ -23694,12 +23694,12 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>St. Austell</t>
+          <t>St. Ives</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D296" s="3" t="n">
@@ -23745,12 +23745,12 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>St. Ives</t>
+          <t>Stafford</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D297" s="5" t="n">
@@ -23796,12 +23796,12 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>Staines</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D298" s="3" t="n">
@@ -23847,12 +23847,12 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Staines</t>
+          <t>Street</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D299" s="5" t="n">
@@ -23898,12 +23898,12 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Stretford</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D300" s="3" t="n">
@@ -23949,12 +23949,12 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Stretford</t>
+          <t>Stroud</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D301" s="5" t="n">
@@ -24000,12 +24000,12 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Stroud</t>
+          <t>Swindon</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D302" s="3" t="n">
@@ -24051,12 +24051,12 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Swindon</t>
+          <t>Tadley</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D303" s="5" t="n">
@@ -24067,10 +24067,10 @@
       </c>
       <c r="F303" s="4" t="inlineStr"/>
       <c r="G303" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H303" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I303" s="5" t="n">
         <v>0</v>
@@ -24102,12 +24102,12 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Tadley</t>
+          <t>Taunton</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D304" s="3" t="n">
@@ -24118,10 +24118,10 @@
       </c>
       <c r="F304" s="2" t="inlineStr"/>
       <c r="G304" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H304" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I304" s="3" t="n">
         <v>0</v>
@@ -24153,12 +24153,12 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Taunton</t>
+          <t>Tipton</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D305" s="5" t="n">
@@ -24204,12 +24204,12 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Tipton</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D306" s="3" t="n">
@@ -24220,13 +24220,13 @@
       </c>
       <c r="F306" s="2" t="inlineStr"/>
       <c r="G306" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H306" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I306" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J306" s="3" t="n">
         <v>0</v>
@@ -24255,12 +24255,12 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Ulverston</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D307" s="5" t="n">
@@ -24274,10 +24274,10 @@
         <v>0</v>
       </c>
       <c r="H307" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J307" s="5" t="n">
         <v>0</v>
@@ -24306,12 +24306,12 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Ulverston</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D308" s="3" t="n">
@@ -24322,10 +24322,10 @@
       </c>
       <c r="F308" s="2" t="inlineStr"/>
       <c r="G308" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H308" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I308" s="3" t="n">
         <v>0</v>
@@ -24357,12 +24357,12 @@
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Waltham Abbey</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D309" s="5" t="n">
@@ -24408,12 +24408,12 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Waltham Abbey</t>
+          <t>Waltham Cross</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D310" s="3" t="n">
@@ -24459,12 +24459,12 @@
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Waltham Cross</t>
+          <t>Walton-on-thames</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D311" s="5" t="n">
@@ -24510,12 +24510,12 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Ware</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D312" s="3" t="n">
@@ -24561,12 +24561,12 @@
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Ware</t>
+          <t>Wednesbury</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D313" s="5" t="n">
@@ -24612,12 +24612,12 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Wednesbury</t>
+          <t>Wellingborough</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D314" s="3" t="n">
@@ -24663,12 +24663,12 @@
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Wellingborough</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D315" s="5" t="n">
@@ -24714,12 +24714,12 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D316" s="3" t="n">
@@ -24765,12 +24765,12 @@
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D317" s="5" t="n">
@@ -24816,12 +24816,12 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Whitstable</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D318" s="3" t="n">
@@ -24832,13 +24832,13 @@
       </c>
       <c r="F318" s="2" t="inlineStr"/>
       <c r="G318" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H318" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I318" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J318" s="3" t="n">
         <v>0</v>
@@ -24867,12 +24867,12 @@
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Whitstable</t>
+          <t>Wigan</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D319" s="5" t="n">
@@ -24883,13 +24883,13 @@
       </c>
       <c r="F319" s="4" t="inlineStr"/>
       <c r="G319" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H319" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I319" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J319" s="5" t="n">
         <v>0</v>
@@ -24918,12 +24918,12 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Wigan</t>
+          <t>Wilmslow</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D320" s="3" t="n">
@@ -24969,12 +24969,12 @@
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Wilmslow</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D321" s="5" t="n">
@@ -25020,12 +25020,12 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D322" s="3" t="n">
@@ -25071,12 +25071,12 @@
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Witney</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D323" s="5" t="n">
@@ -25122,12 +25122,12 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Witney</t>
+          <t>Worksop</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D324" s="3" t="n">
@@ -25173,12 +25173,12 @@
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>Worksop</t>
+          <t>Wymondham</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D325" s="5" t="n">
@@ -25216,59 +25216,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B326" s="2" t="inlineStr">
-        <is>
-          <t>Wymondham</t>
-        </is>
-      </c>
-      <c r="C326" s="2" t="inlineStr">
-        <is>
-          <t>Norfolk</t>
-        </is>
-      </c>
-      <c r="D326" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E326" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F326" s="2" t="inlineStr"/>
-      <c r="G326" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H326" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I326" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J326" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K326" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L326" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M326" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N326" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O326" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O326"/>
+  <autoFilter ref="A1:O325"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25490,7 +25439,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
@@ -25630,7 +25579,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
@@ -25978,7 +25927,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$199</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$325</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$321</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1669</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>236</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1806</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="6">
@@ -641,14 +641,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1626</v>
+        <v>2160</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>269</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3">
@@ -658,114 +658,114 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1138</v>
+        <v>1432</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Sales &amp; Marketing</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>983</v>
+        <v>1074</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>518</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>HR / Recruitment</t>
+          <t>Healthcare &amp; Medical</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>882</v>
+        <v>1009</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>98</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>I.T. &amp; Communications</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Call Centre / CustomerService</t>
+          <t>HR / Recruitment</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>774</v>
+        <v>726</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>221</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>I.T. &amp; Communications</t>
+          <t>Real Estate &amp; Property</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>767</v>
+        <v>492</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Banking &amp; Financial Services</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>724</v>
+        <v>446</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>67</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Real Estate &amp; Property</t>
+          <t>Retail &amp; Consumer Products</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>635</v>
+        <v>429</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Banking &amp; Financial Services</t>
+          <t>Call Centre / CustomerService</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>19</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
@@ -775,72 +775,74 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer Products</t>
+          <t>Executive Positions</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Executive Positions</t>
+          <t>Consulting &amp; Corporate Strategy</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="C14" s="8" t="inlineStr"/>
+        <v>104</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Consulting &amp; Corporate Strategy</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>197</v>
+        <v>86</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Advert / Media / Entertainment</t>
+          <t>Science &amp; Technology</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>15</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="C16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
+          <t>Advert / Media / Entertainment</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="C17" s="8" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -863,7 +865,7 @@
         <v>10000</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>1433</v>
+        <v>894</v>
       </c>
     </row>
   </sheetData>
@@ -8359,7 +8361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O325"/>
+  <dimension ref="A1:O321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8872,23 +8874,23 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Widnes</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0</v>
@@ -8923,12 +8925,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Frodsham</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -8974,12 +8976,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Frodsham</t>
+          <t>Leigh</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -9025,12 +9027,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Leigh</t>
+          <t>Lymm</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -9076,12 +9078,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Lymm</t>
+          <t>Lyndhurst</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -9127,12 +9129,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Lyndhurst</t>
+          <t>Merthyr Tydfil</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -9178,12 +9180,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Merthyr Tydfil</t>
+          <t>Newport-on-tay</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -9229,7 +9231,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Newport-on-tay</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -9280,12 +9282,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Perth</t>
+          <t>Widnes</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -9450,7 +9452,7 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>1</v>
@@ -9461,7 +9463,7 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0</v>
@@ -10431,12 +10433,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Farnham</t>
+          <t>Sheffield</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -10447,7 +10449,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>/farnham/service-administrator-jobs</t>
+          <t>/sheffield/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
@@ -10486,30 +10488,30 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Farnham</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>/oxford/service-administrator-jobs</t>
+          <t>/farnham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0</v>
@@ -10518,7 +10520,7 @@
         <v>0</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>0</v>
@@ -10541,30 +10543,30 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Sheffield</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>/sheffield/service-administrator-jobs</t>
+          <t>/oxford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41" s="5" t="n">
         <v>0</v>
@@ -10573,7 +10575,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41" s="5" t="n">
         <v>0</v>
@@ -14259,7 +14261,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Ruislip</t>
+          <t>Wandsworth</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -14275,10 +14277,10 @@
       </c>
       <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" s="5" t="n">
         <v>0</v>
@@ -14310,7 +14312,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Wandsworth</t>
+          <t>Wembley</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -14361,7 +14363,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Wembley</t>
+          <t>Worcester Park</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -14377,10 +14379,10 @@
       </c>
       <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" s="5" t="n">
         <v>0</v>
@@ -14407,28 +14409,28 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Worcester Park</t>
+          <t>Cheadle</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114" s="3" t="n">
         <v>0</v>
@@ -14440,7 +14442,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L114" s="3" t="n">
         <v>0</v>
@@ -14463,35 +14465,35 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Cheadle</t>
+          <t>Cramlington</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E115" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H115" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J115" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L115" s="5" t="n">
         <v>0</v>
@@ -14514,16 +14516,16 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Cramlington</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -14536,7 +14538,7 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J116" s="3" t="n">
         <v>0</v>
@@ -14565,12 +14567,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Dartford</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14587,13 +14589,13 @@
         <v>0</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J117" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="5" t="n">
         <v>0</v>
@@ -14616,12 +14618,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Dartford</t>
+          <t>Gosport</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -14632,19 +14634,19 @@
       </c>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="3" t="n">
         <v>0</v>
@@ -14667,12 +14669,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Gosport</t>
+          <t>Lisburn</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -14683,22 +14685,22 @@
       </c>
       <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="H119" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I119" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="M119" s="5" t="n">
         <v>0</v>
@@ -14718,12 +14720,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Lisburn</t>
+          <t>Northwich</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
@@ -14734,7 +14736,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
@@ -14746,10 +14748,10 @@
         <v>0</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M120" s="3" t="n">
         <v>0</v>
@@ -14769,12 +14771,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Northwich</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -14785,7 +14787,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H121" s="5" t="n">
         <v>0</v>
@@ -14797,7 +14799,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L121" s="5" t="n">
         <v>0</v>
@@ -14820,16 +14822,16 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E122" s="3" t="n">
         <v>0</v>
@@ -14848,7 +14850,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L122" s="3" t="n">
         <v>0</v>
@@ -14871,12 +14873,12 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Burgess Hill</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -14887,7 +14889,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H123" s="5" t="n">
         <v>0</v>
@@ -14899,7 +14901,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L123" s="5" t="n">
         <v>0</v>
@@ -14922,12 +14924,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Burgess Hill</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -14938,13 +14940,13 @@
       </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J124" s="3" t="n">
         <v>0</v>
@@ -14973,12 +14975,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Fleet</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -14989,19 +14991,19 @@
       </c>
       <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H125" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J125" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" s="5" t="n">
         <v>0</v>
@@ -15024,12 +15026,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Hove</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -15046,13 +15048,13 @@
         <v>0</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L126" s="3" t="n">
         <v>0</v>
@@ -15075,12 +15077,12 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Hove</t>
+          <t>Inverness</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -15091,13 +15093,13 @@
       </c>
       <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H127" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J127" s="5" t="n">
         <v>0</v>
@@ -15126,12 +15128,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Inverness</t>
+          <t>Knaresborough</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -15142,7 +15144,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H128" s="3" t="n">
         <v>0</v>
@@ -15154,7 +15156,7 @@
         <v>0</v>
       </c>
       <c r="K128" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L128" s="3" t="n">
         <v>0</v>
@@ -15177,12 +15179,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Knaresborough</t>
+          <t>Leighton Buzzard</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15193,7 +15195,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H129" s="5" t="n">
         <v>0</v>
@@ -15205,7 +15207,7 @@
         <v>0</v>
       </c>
       <c r="K129" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L129" s="5" t="n">
         <v>0</v>
@@ -15228,12 +15230,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Leighton Buzzard</t>
+          <t>Maidenhead</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -15244,7 +15246,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H130" s="3" t="n">
         <v>0</v>
@@ -15256,7 +15258,7 @@
         <v>0</v>
       </c>
       <c r="K130" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="3" t="n">
         <v>0</v>
@@ -15279,12 +15281,12 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Maidenhead</t>
+          <t>Newry</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15295,7 +15297,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H131" s="5" t="n">
         <v>0</v>
@@ -15307,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="K131" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" s="5" t="n">
         <v>0</v>
@@ -15330,12 +15332,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Newry</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
@@ -15346,7 +15348,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H132" s="3" t="n">
         <v>0</v>
@@ -15358,10 +15360,10 @@
         <v>0</v>
       </c>
       <c r="K132" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="3" t="n">
         <v>0</v>
@@ -15381,12 +15383,12 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Stockport</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15397,7 +15399,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H133" s="5" t="n">
         <v>0</v>
@@ -15409,10 +15411,10 @@
         <v>0</v>
       </c>
       <c r="K133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M133" s="5" t="n">
         <v>0</v>
@@ -15432,12 +15434,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Stockport</t>
+          <t>Telford</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -15483,12 +15485,12 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Telford</t>
+          <t>Tunbridge Wells</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15499,13 +15501,13 @@
       </c>
       <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J135" s="5" t="n">
         <v>0</v>
@@ -15534,12 +15536,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Tunbridge Wells</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
@@ -15550,13 +15552,13 @@
       </c>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J136" s="3" t="n">
         <v>0</v>
@@ -15585,16 +15587,16 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Amersham</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E137" s="5" t="n">
         <v>0</v>
@@ -15607,7 +15609,7 @@
         <v>0</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J137" s="5" t="n">
         <v>0</v>
@@ -15636,12 +15638,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Amersham</t>
+          <t>Atherstone</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -15652,7 +15654,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H138" s="3" t="n">
         <v>0</v>
@@ -15670,7 +15672,7 @@
         <v>0</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N138" s="3" t="n">
         <v>0</v>
@@ -15687,12 +15689,12 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Atherstone</t>
+          <t>Ballyclare</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15703,7 +15705,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H139" s="5" t="n">
         <v>0</v>
@@ -15721,7 +15723,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N139" s="5" t="n">
         <v>0</v>
@@ -15738,7 +15740,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Ballyclare</t>
+          <t>Ballymena</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -15754,7 +15756,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H140" s="3" t="n">
         <v>0</v>
@@ -15769,7 +15771,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" s="3" t="n">
         <v>0</v>
@@ -15789,12 +15791,12 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Ballymena</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15805,7 +15807,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H141" s="5" t="n">
         <v>0</v>
@@ -15820,7 +15822,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M141" s="5" t="n">
         <v>0</v>
@@ -15840,12 +15842,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Beaminster</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -15891,12 +15893,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Beaminster</t>
+          <t>Berwick-upon-tweed</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15907,13 +15909,13 @@
       </c>
       <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H143" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="J143" s="5" t="n">
         <v>0</v>
@@ -15942,12 +15944,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Berwick-upon-tweed</t>
+          <t>Bicester</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -15958,13 +15960,13 @@
       </c>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H144" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J144" s="3" t="n">
         <v>0</v>
@@ -15993,12 +15995,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Bicester</t>
+          <t>Bridgwater</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -16044,12 +16046,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Bridgwater</t>
+          <t>Brinsworth</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -16095,12 +16097,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Brinsworth</t>
+          <t>Bromsgrove</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -16146,12 +16148,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Bromsgrove</t>
+          <t>Chatham</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -16197,12 +16199,12 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Chatham</t>
+          <t>Cirencester</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -16248,12 +16250,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Cirencester</t>
+          <t>Coalville</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
@@ -16299,12 +16301,12 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Coalville</t>
+          <t>Cottingham</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -16350,12 +16352,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Cottingham</t>
+          <t>Crawley</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -16401,12 +16403,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Crawley</t>
+          <t>Crewe</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -16452,12 +16454,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Crewe</t>
+          <t>Darlington</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -16468,7 +16470,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H154" s="3" t="n">
         <v>0</v>
@@ -16489,7 +16491,7 @@
         <v>0</v>
       </c>
       <c r="N154" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O154" s="3" t="n">
         <v>0</v>
@@ -16503,12 +16505,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Darlington</t>
+          <t>Didcot</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -16519,7 +16521,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H155" s="5" t="n">
         <v>0</v>
@@ -16540,7 +16542,7 @@
         <v>0</v>
       </c>
       <c r="N155" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O155" s="5" t="n">
         <v>0</v>
@@ -16554,12 +16556,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Didcot</t>
+          <t>East Grinstead</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -16570,10 +16572,10 @@
       </c>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I156" s="3" t="n">
         <v>0</v>
@@ -16605,12 +16607,12 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>East Grinstead</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -16656,7 +16658,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Fareham</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -16672,13 +16674,13 @@
       </c>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J158" s="3" t="n">
         <v>0</v>
@@ -16693,7 +16695,7 @@
         <v>0</v>
       </c>
       <c r="N158" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O158" s="3" t="n">
         <v>0</v>
@@ -16707,12 +16709,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Fareham</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -16723,13 +16725,13 @@
       </c>
       <c r="F159" s="4" t="inlineStr"/>
       <c r="G159" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H159" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J159" s="5" t="n">
         <v>0</v>
@@ -16744,7 +16746,7 @@
         <v>0</v>
       </c>
       <c r="N159" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O159" s="5" t="n">
         <v>0</v>
@@ -16758,12 +16760,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -16774,10 +16776,10 @@
       </c>
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I160" s="3" t="n">
         <v>0</v>
@@ -16809,12 +16811,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Haywards Heath</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -16825,10 +16827,10 @@
       </c>
       <c r="F161" s="4" t="inlineStr"/>
       <c r="G161" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I161" s="5" t="n">
         <v>0</v>
@@ -16860,7 +16862,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Haywards Heath</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -16911,12 +16913,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Keynsham</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -16962,12 +16964,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Keynsham</t>
+          <t>Kirriemuir</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
@@ -17013,12 +17015,12 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Kirriemuir</t>
+          <t>Knowle</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -17064,12 +17066,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Knowle</t>
+          <t>Lowestoft</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -17115,12 +17117,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Lowestoft</t>
+          <t>Maldon</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -17131,16 +17133,16 @@
       </c>
       <c r="F167" s="4" t="inlineStr"/>
       <c r="G167" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H167" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I167" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J167" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="K167" s="5" t="n">
         <v>0</v>
@@ -17166,12 +17168,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Maldon</t>
+          <t>Melksham</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -17182,7 +17184,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H168" s="3" t="n">
         <v>0</v>
@@ -17191,7 +17193,7 @@
         <v>0</v>
       </c>
       <c r="J168" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K168" s="3" t="n">
         <v>0</v>
@@ -17217,12 +17219,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Melksham</t>
+          <t>Newbury</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -17233,19 +17235,19 @@
       </c>
       <c r="F169" s="4" t="inlineStr"/>
       <c r="G169" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H169" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J169" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K169" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L169" s="5" t="n">
         <v>0</v>
@@ -17268,12 +17270,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Newbury</t>
+          <t>Newton Abbot</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
@@ -17284,7 +17286,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H170" s="3" t="n">
         <v>0</v>
@@ -17296,7 +17298,7 @@
         <v>0</v>
       </c>
       <c r="K170" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L170" s="3" t="n">
         <v>0</v>
@@ -17319,12 +17321,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Newton Abbot</t>
+          <t>Newtownards</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -17335,13 +17337,13 @@
       </c>
       <c r="F171" s="4" t="inlineStr"/>
       <c r="G171" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H171" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" s="5" t="n">
         <v>0</v>
@@ -17350,7 +17352,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M171" s="5" t="n">
         <v>0</v>
@@ -17370,12 +17372,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Newtownards</t>
+          <t>Redditch</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -17386,7 +17388,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H172" s="3" t="n">
         <v>0</v>
@@ -17401,7 +17403,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M172" s="3" t="n">
         <v>0</v>
@@ -17421,12 +17423,12 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Redditch</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -17472,12 +17474,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Ringwood</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -17488,10 +17490,10 @@
       </c>
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I174" s="3" t="n">
         <v>0</v>
@@ -17523,7 +17525,7 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Rickmansworth</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -17539,7 +17541,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr"/>
       <c r="G175" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H175" s="5" t="n">
         <v>0</v>
@@ -17551,7 +17553,7 @@
         <v>0</v>
       </c>
       <c r="K175" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L175" s="5" t="n">
         <v>0</v>
@@ -17574,12 +17576,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Ringwood</t>
+          <t>Stonehouse</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -17593,7 +17595,7 @@
         <v>1</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>0</v>
@@ -17602,7 +17604,7 @@
         <v>0</v>
       </c>
       <c r="K176" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L176" s="3" t="n">
         <v>0</v>
@@ -17625,12 +17627,12 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Thame</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -17641,7 +17643,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr"/>
       <c r="G177" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H177" s="5" t="n">
         <v>0</v>
@@ -17653,7 +17655,7 @@
         <v>0</v>
       </c>
       <c r="K177" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L177" s="5" t="n">
         <v>0</v>
@@ -17676,12 +17678,12 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Stonehouse</t>
+          <t>Torquay</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
@@ -17692,7 +17694,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H178" s="3" t="n">
         <v>0</v>
@@ -17704,7 +17706,7 @@
         <v>0</v>
       </c>
       <c r="K178" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L178" s="3" t="n">
         <v>0</v>
@@ -17727,12 +17729,12 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Thame</t>
+          <t>Trowbridge</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D179" s="5" t="n">
@@ -17778,12 +17780,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Truro</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -17829,12 +17831,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Trowbridge</t>
+          <t>Ventnor</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
@@ -17845,10 +17847,10 @@
       </c>
       <c r="F181" s="4" t="inlineStr"/>
       <c r="G181" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H181" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="I181" s="5" t="n">
         <v>0</v>
@@ -17880,12 +17882,12 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Truro</t>
+          <t>Waterlooville</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -17896,13 +17898,13 @@
       </c>
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H182" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J182" s="3" t="n">
         <v>0</v>
@@ -17931,12 +17933,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Ventnor</t>
+          <t>Welwyn Garden City</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -17947,10 +17949,10 @@
       </c>
       <c r="F183" s="4" t="inlineStr"/>
       <c r="G183" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H183" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I183" s="5" t="n">
         <v>0</v>
@@ -17959,7 +17961,7 @@
         <v>0</v>
       </c>
       <c r="K183" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L183" s="5" t="n">
         <v>0</v>
@@ -17982,12 +17984,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Waterlooville</t>
+          <t>Wokingham</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
@@ -17998,13 +18000,13 @@
       </c>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H184" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J184" s="3" t="n">
         <v>0</v>
@@ -18033,12 +18035,12 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Welwyn Garden City</t>
+          <t>Woodbridge</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
@@ -18049,7 +18051,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr"/>
       <c r="G185" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H185" s="5" t="n">
         <v>0</v>
@@ -18061,7 +18063,7 @@
         <v>0</v>
       </c>
       <c r="K185" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L185" s="5" t="n">
         <v>0</v>
@@ -18084,12 +18086,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Wokingham</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
@@ -18135,23 +18137,23 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Woodbridge</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E187" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F187" s="4" t="inlineStr"/>
       <c r="G187" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H187" s="5" t="n">
         <v>0</v>
@@ -18186,23 +18188,23 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Alderley Edge</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E188" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H188" s="3" t="n">
         <v>0</v>
@@ -18237,12 +18239,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Alresford</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
@@ -18288,12 +18290,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Alderley Edge</t>
+          <t>Alton</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -18339,12 +18341,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Alresford</t>
+          <t>Ashington</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
@@ -18390,12 +18392,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Alton</t>
+          <t>Aylesford</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -18441,12 +18443,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Ashington</t>
+          <t>Banbury</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
@@ -18492,12 +18494,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Aylesford</t>
+          <t>Banstead</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -18543,12 +18545,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Banbury</t>
+          <t>Barnstaple</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>devon</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
@@ -18594,12 +18596,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Banstead</t>
+          <t>Bexhill-on-sea</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -18645,12 +18647,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Barnstaple</t>
+          <t>Billericay</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>devon</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -18696,12 +18698,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Bexhill-on-sea</t>
+          <t>Bishop's Stortford</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -18747,12 +18749,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Billericay</t>
+          <t>Bognor Regis</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -18798,12 +18800,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Bishop's Stortford</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -18849,12 +18851,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Bognor Regis</t>
+          <t>Bracknell</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -18900,12 +18902,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Brighouse</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -18951,12 +18953,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Bracknell</t>
+          <t>Buckingham</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -18967,7 +18969,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr"/>
       <c r="G203" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H203" s="5" t="n">
         <v>0</v>
@@ -18988,7 +18990,7 @@
         <v>0</v>
       </c>
       <c r="N203" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O203" s="5" t="n">
         <v>0</v>
@@ -19002,12 +19004,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Brighouse</t>
+          <t>Bury St Edmunds</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -19053,12 +19055,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Buckingham</t>
+          <t>Caerphilly</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -19069,7 +19071,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr"/>
       <c r="G205" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H205" s="5" t="n">
         <v>0</v>
@@ -19090,7 +19092,7 @@
         <v>0</v>
       </c>
       <c r="N205" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O205" s="5" t="n">
         <v>0</v>
@@ -19104,12 +19106,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Bury St Edmunds</t>
+          <t>Camberley</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -19155,12 +19157,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Caerphilly</t>
+          <t>Canterbury</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -19206,12 +19208,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Camberley</t>
+          <t>Carrickfergus</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -19257,12 +19259,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>Caterham</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -19273,10 +19275,10 @@
       </c>
       <c r="F209" s="4" t="inlineStr"/>
       <c r="G209" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H209" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I209" s="5" t="n">
         <v>0</v>
@@ -19308,12 +19310,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Carrickfergus</t>
+          <t>Chelmsley Wood</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -19359,12 +19361,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Caterham</t>
+          <t>Cheltenham</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -19375,10 +19377,10 @@
       </c>
       <c r="F211" s="4" t="inlineStr"/>
       <c r="G211" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H211" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I211" s="5" t="n">
         <v>0</v>
@@ -19410,12 +19412,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Chelmsley Wood</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -19461,12 +19463,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Cheltenham</t>
+          <t>Chichester</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
@@ -19512,12 +19514,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Chigwell</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -19563,12 +19565,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Chichester</t>
+          <t>Christchurch</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
@@ -19614,12 +19616,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Chigwell</t>
+          <t>Cleethorpes</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -19665,12 +19667,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Christchurch</t>
+          <t>Cobham</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
@@ -19681,10 +19683,10 @@
       </c>
       <c r="F217" s="4" t="inlineStr"/>
       <c r="G217" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H217" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I217" s="5" t="n">
         <v>0</v>
@@ -19716,12 +19718,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Cleethorpes</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
@@ -19732,7 +19734,7 @@
       </c>
       <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
         <v>0</v>
@@ -19741,7 +19743,7 @@
         <v>0</v>
       </c>
       <c r="J218" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K218" s="3" t="n">
         <v>0</v>
@@ -19767,12 +19769,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Cobham</t>
+          <t>Colden Common</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
@@ -19786,7 +19788,7 @@
         <v>0</v>
       </c>
       <c r="H219" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I219" s="5" t="n">
         <v>0</v>
@@ -19804,7 +19806,7 @@
         <v>0</v>
       </c>
       <c r="N219" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O219" s="5" t="n">
         <v>0</v>
@@ -19818,12 +19820,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>Congleton</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
@@ -19834,7 +19836,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr"/>
       <c r="G220" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H220" s="3" t="n">
         <v>0</v>
@@ -19843,7 +19845,7 @@
         <v>0</v>
       </c>
       <c r="J220" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K220" s="3" t="n">
         <v>0</v>
@@ -19869,12 +19871,12 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Colden Common</t>
+          <t>Cullompton</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
@@ -19885,7 +19887,7 @@
       </c>
       <c r="F221" s="4" t="inlineStr"/>
       <c r="G221" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H221" s="5" t="n">
         <v>0</v>
@@ -19906,7 +19908,7 @@
         <v>0</v>
       </c>
       <c r="N221" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O221" s="5" t="n">
         <v>0</v>
@@ -19920,12 +19922,12 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Congleton</t>
+          <t>Devizes</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
@@ -19971,12 +19973,12 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Cullompton</t>
+          <t>Dewsbury</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
@@ -20022,12 +20024,12 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Devizes</t>
+          <t>Dorking</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D224" s="3" t="n">
@@ -20073,12 +20075,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Dewsbury</t>
+          <t>Dunmow</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D225" s="5" t="n">
@@ -20089,7 +20091,7 @@
       </c>
       <c r="F225" s="4" t="inlineStr"/>
       <c r="G225" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H225" s="5" t="n">
         <v>0</v>
@@ -20104,7 +20106,7 @@
         <v>0</v>
       </c>
       <c r="L225" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M225" s="5" t="n">
         <v>0</v>
@@ -20124,12 +20126,12 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Dorking</t>
+          <t>Dursley</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
@@ -20175,12 +20177,12 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Dunmow</t>
+          <t>Eastbourne</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D227" s="5" t="n">
@@ -20194,7 +20196,7 @@
         <v>0</v>
       </c>
       <c r="H227" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I227" s="5" t="n">
         <v>0</v>
@@ -20206,7 +20208,7 @@
         <v>0</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M227" s="5" t="n">
         <v>0</v>
@@ -20226,12 +20228,12 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Dursley</t>
+          <t>Eccles</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
@@ -20277,12 +20279,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Eastbourne</t>
+          <t>Ellesmere</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
@@ -20293,10 +20295,10 @@
       </c>
       <c r="F229" s="4" t="inlineStr"/>
       <c r="G229" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H229" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I229" s="5" t="n">
         <v>0</v>
@@ -20328,12 +20330,12 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Eccles</t>
+          <t>Epsom</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
@@ -20344,7 +20346,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr"/>
       <c r="G230" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
         <v>0</v>
@@ -20356,7 +20358,7 @@
         <v>0</v>
       </c>
       <c r="K230" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L230" s="3" t="n">
         <v>0</v>
@@ -20379,12 +20381,12 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Ellesmere</t>
+          <t>Esher</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
@@ -20395,13 +20397,13 @@
       </c>
       <c r="F231" s="4" t="inlineStr"/>
       <c r="G231" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H231" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J231" s="5" t="n">
         <v>0</v>
@@ -20430,12 +20432,12 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Epsom</t>
+          <t>Farnborough</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
@@ -20446,7 +20448,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr"/>
       <c r="G232" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H232" s="3" t="n">
         <v>0</v>
@@ -20458,7 +20460,7 @@
         <v>0</v>
       </c>
       <c r="K232" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L232" s="3" t="n">
         <v>0</v>
@@ -20481,7 +20483,7 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Esher</t>
+          <t>Fetcham</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -20503,7 +20505,7 @@
         <v>0</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J233" s="5" t="n">
         <v>0</v>
@@ -20518,7 +20520,7 @@
         <v>0</v>
       </c>
       <c r="N233" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O233" s="5" t="n">
         <v>0</v>
@@ -20532,12 +20534,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Farnborough</t>
+          <t>Folkestone</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
@@ -20548,7 +20550,7 @@
       </c>
       <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H234" s="3" t="n">
         <v>0</v>
@@ -20560,7 +20562,7 @@
         <v>0</v>
       </c>
       <c r="K234" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L234" s="3" t="n">
         <v>0</v>
@@ -20583,12 +20585,12 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Felixstowe</t>
+          <t>Freshwater</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
@@ -20599,10 +20601,10 @@
       </c>
       <c r="F235" s="4" t="inlineStr"/>
       <c r="G235" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H235" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I235" s="5" t="n">
         <v>0</v>
@@ -20634,12 +20636,12 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Fetcham</t>
+          <t>Gainsborough</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
@@ -20650,7 +20652,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H236" s="3" t="n">
         <v>0</v>
@@ -20671,7 +20673,7 @@
         <v>0</v>
       </c>
       <c r="N236" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O236" s="3" t="n">
         <v>0</v>
@@ -20685,12 +20687,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Folkestone</t>
+          <t>Gerrards Cross</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
@@ -20701,7 +20703,7 @@
       </c>
       <c r="F237" s="4" t="inlineStr"/>
       <c r="G237" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H237" s="5" t="n">
         <v>0</v>
@@ -20713,7 +20715,7 @@
         <v>0</v>
       </c>
       <c r="K237" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L237" s="5" t="n">
         <v>0</v>
@@ -20736,12 +20738,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Freshwater</t>
+          <t>Godalming</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
@@ -20755,10 +20757,10 @@
         <v>0</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J238" s="3" t="n">
         <v>0</v>
@@ -20787,12 +20789,12 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Gainsborough</t>
+          <t>Godstone</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
@@ -20838,12 +20840,12 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Gerrards Cross</t>
+          <t>Goole</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
@@ -20889,12 +20891,12 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Godalming</t>
+          <t>Gravesend</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D241" s="5" t="n">
@@ -20908,10 +20910,10 @@
         <v>0</v>
       </c>
       <c r="H241" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J241" s="5" t="n">
         <v>0</v>
@@ -20940,12 +20942,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Godstone</t>
+          <t>Great Yarmouth</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
@@ -20991,12 +20993,12 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Goole</t>
+          <t>Hailsham</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
@@ -21007,13 +21009,13 @@
       </c>
       <c r="F243" s="4" t="inlineStr"/>
       <c r="G243" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H243" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I243" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J243" s="5" t="n">
         <v>0</v>
@@ -21042,12 +21044,12 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Gravesend</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
@@ -21093,12 +21095,12 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Great Yarmouth</t>
+          <t>Hastings</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
@@ -21109,13 +21111,13 @@
       </c>
       <c r="F245" s="4" t="inlineStr"/>
       <c r="G245" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H245" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I245" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J245" s="5" t="n">
         <v>0</v>
@@ -21144,12 +21146,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Hailsham</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
@@ -21160,13 +21162,13 @@
       </c>
       <c r="F246" s="2" t="inlineStr"/>
       <c r="G246" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H246" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J246" s="3" t="n">
         <v>0</v>
@@ -21195,12 +21197,12 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Heanor</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
@@ -21211,10 +21213,10 @@
       </c>
       <c r="F247" s="4" t="inlineStr"/>
       <c r="G247" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H247" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I247" s="5" t="n">
         <v>0</v>
@@ -21246,12 +21248,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Hastings</t>
+          <t>Hebburn</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
@@ -21268,7 +21270,7 @@
         <v>0</v>
       </c>
       <c r="I248" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J248" s="3" t="n">
         <v>0</v>
@@ -21283,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="N248" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O248" s="3" t="n">
         <v>0</v>
@@ -21297,7 +21299,7 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>Hertford</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
@@ -21348,12 +21350,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Heanor</t>
+          <t>Huntingdon</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
@@ -21399,12 +21401,12 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Hebburn</t>
+          <t>Ilminster</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
@@ -21415,7 +21417,7 @@
       </c>
       <c r="F251" s="4" t="inlineStr"/>
       <c r="G251" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H251" s="5" t="n">
         <v>0</v>
@@ -21436,7 +21438,7 @@
         <v>0</v>
       </c>
       <c r="N251" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O251" s="5" t="n">
         <v>0</v>
@@ -21450,12 +21452,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Hertford</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
@@ -21501,12 +21503,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Huntingdon</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
@@ -21552,12 +21554,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Ilminster</t>
+          <t>Kidlington</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
@@ -21603,12 +21605,12 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
@@ -21654,12 +21656,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Lewes</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
@@ -21705,12 +21707,12 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Kidlington</t>
+          <t>Lichfield</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
@@ -21721,7 +21723,7 @@
       </c>
       <c r="F257" s="4" t="inlineStr"/>
       <c r="G257" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H257" s="5" t="n">
         <v>0</v>
@@ -21742,7 +21744,7 @@
         <v>0</v>
       </c>
       <c r="N257" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O257" s="5" t="n">
         <v>0</v>
@@ -21756,12 +21758,12 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Liskeard</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
@@ -21807,7 +21809,7 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Lewes</t>
+          <t>Littlehampton</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
@@ -21858,12 +21860,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Lichfield</t>
+          <t>Loughborough</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
@@ -21874,7 +21876,7 @@
       </c>
       <c r="F260" s="2" t="inlineStr"/>
       <c r="G260" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H260" s="3" t="n">
         <v>0</v>
@@ -21895,7 +21897,7 @@
         <v>0</v>
       </c>
       <c r="N260" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O260" s="3" t="n">
         <v>0</v>
@@ -21909,12 +21911,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Liskeard</t>
+          <t>Marlborough</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
@@ -21960,12 +21962,12 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Littlehampton</t>
+          <t>Marlow</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D262" s="3" t="n">
@@ -22011,12 +22013,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Loughborough</t>
+          <t>Mirfield</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
@@ -22062,12 +22064,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Marlborough</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D264" s="3" t="n">
@@ -22078,13 +22080,13 @@
       </c>
       <c r="F264" s="2" t="inlineStr"/>
       <c r="G264" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H264" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J264" s="3" t="n">
         <v>0</v>
@@ -22113,12 +22115,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Marlow</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
@@ -22164,12 +22166,12 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Mirfield</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
@@ -22215,12 +22217,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Newmarket</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
@@ -22231,13 +22233,13 @@
       </c>
       <c r="F267" s="4" t="inlineStr"/>
       <c r="G267" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H267" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I267" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J267" s="5" t="n">
         <v>0</v>
@@ -22266,12 +22268,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Newton Aycliffe</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D268" s="3" t="n">
@@ -22317,12 +22319,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>North Shields</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D269" s="5" t="n">
@@ -22368,12 +22370,12 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Newmarket</t>
+          <t>Northfleet</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D270" s="3" t="n">
@@ -22384,13 +22386,13 @@
       </c>
       <c r="F270" s="2" t="inlineStr"/>
       <c r="G270" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H270" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I270" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J270" s="3" t="n">
         <v>0</v>
@@ -22419,12 +22421,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Newton Aycliffe</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D271" s="5" t="n">
@@ -22435,13 +22437,13 @@
       </c>
       <c r="F271" s="4" t="inlineStr"/>
       <c r="G271" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H271" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I271" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J271" s="5" t="n">
         <v>0</v>
@@ -22470,12 +22472,12 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>North Shields</t>
+          <t>Pontefract</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D272" s="3" t="n">
@@ -22521,12 +22523,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Northfleet</t>
+          <t>Portishead</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
@@ -22537,13 +22539,13 @@
       </c>
       <c r="F273" s="4" t="inlineStr"/>
       <c r="G273" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H273" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I273" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J273" s="5" t="n">
         <v>0</v>
@@ -22572,12 +22574,12 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Otley</t>
+          <t>Ramsgate</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D274" s="3" t="n">
@@ -22623,12 +22625,12 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Redruth</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
@@ -22639,13 +22641,13 @@
       </c>
       <c r="F275" s="4" t="inlineStr"/>
       <c r="G275" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H275" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I275" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J275" s="5" t="n">
         <v>0</v>
@@ -22674,12 +22676,12 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Pontefract</t>
+          <t>Reigate</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D276" s="3" t="n">
@@ -22690,7 +22692,7 @@
       </c>
       <c r="F276" s="2" t="inlineStr"/>
       <c r="G276" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H276" s="3" t="n">
         <v>0</v>
@@ -22702,7 +22704,7 @@
         <v>0</v>
       </c>
       <c r="K276" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L276" s="3" t="n">
         <v>0</v>
@@ -22725,12 +22727,12 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Portishead</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
@@ -22776,12 +22778,12 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Ramsgate</t>
+          <t>Rickmansworth</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D278" s="3" t="n">
@@ -22827,12 +22829,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Redruth</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D279" s="5" t="n">
@@ -22878,12 +22880,12 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Reigate</t>
+          <t>Rugby</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D280" s="3" t="n">
@@ -22894,7 +22896,7 @@
       </c>
       <c r="F280" s="2" t="inlineStr"/>
       <c r="G280" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H280" s="3" t="n">
         <v>0</v>
@@ -22906,7 +22908,7 @@
         <v>0</v>
       </c>
       <c r="K280" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L280" s="3" t="n">
         <v>0</v>
@@ -22929,12 +22931,12 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Ryton</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D281" s="5" t="n">
@@ -22980,12 +22982,12 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Rochester</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D282" s="3" t="n">
@@ -23031,12 +23033,12 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Rugby</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D283" s="5" t="n">
@@ -23082,12 +23084,12 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Ryton</t>
+          <t>Seaham</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D284" s="3" t="n">
@@ -23133,12 +23135,12 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Sevenoaks</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D285" s="5" t="n">
@@ -23184,12 +23186,12 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Shirley</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D286" s="3" t="n">
@@ -23235,12 +23237,12 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Seaham</t>
+          <t>Snodland</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D287" s="5" t="n">
@@ -23251,13 +23253,13 @@
       </c>
       <c r="F287" s="4" t="inlineStr"/>
       <c r="G287" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H287" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I287" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J287" s="5" t="n">
         <v>0</v>
@@ -23286,12 +23288,12 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Sevenoaks</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D288" s="3" t="n">
@@ -23302,7 +23304,7 @@
       </c>
       <c r="F288" s="2" t="inlineStr"/>
       <c r="G288" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H288" s="3" t="n">
         <v>0</v>
@@ -23320,7 +23322,7 @@
         <v>0</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N288" s="3" t="n">
         <v>0</v>
@@ -23337,12 +23339,12 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Shirley</t>
+          <t>Southam</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D289" s="5" t="n">
@@ -23388,12 +23390,12 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Snodland</t>
+          <t>Southend-on-sea</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D290" s="3" t="n">
@@ -23404,13 +23406,13 @@
       </c>
       <c r="F290" s="2" t="inlineStr"/>
       <c r="G290" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H290" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I290" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J290" s="3" t="n">
         <v>0</v>
@@ -23439,12 +23441,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Spennymoor</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D291" s="5" t="n">
@@ -23455,7 +23457,7 @@
       </c>
       <c r="F291" s="4" t="inlineStr"/>
       <c r="G291" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H291" s="5" t="n">
         <v>0</v>
@@ -23473,7 +23475,7 @@
         <v>0</v>
       </c>
       <c r="M291" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N291" s="5" t="n">
         <v>0</v>
@@ -23490,12 +23492,12 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Southam</t>
+          <t>St. Austell</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D292" s="3" t="n">
@@ -23541,12 +23543,12 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Southend-on-sea</t>
+          <t>St. Ives</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
@@ -23592,12 +23594,12 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Spennymoor</t>
+          <t>Stafford</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D294" s="3" t="n">
@@ -23643,12 +23645,12 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>St. Austell</t>
+          <t>Staines</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D295" s="5" t="n">
@@ -23694,12 +23696,12 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>St. Ives</t>
+          <t>Street</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D296" s="3" t="n">
@@ -23745,12 +23747,12 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Stafford</t>
+          <t>Stretford</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D297" s="5" t="n">
@@ -23796,12 +23798,12 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Staines</t>
+          <t>Stroud</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D298" s="3" t="n">
@@ -23847,12 +23849,12 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Swindon</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D299" s="5" t="n">
@@ -23898,12 +23900,12 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Stretford</t>
+          <t>Tadley</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D300" s="3" t="n">
@@ -23914,10 +23916,10 @@
       </c>
       <c r="F300" s="2" t="inlineStr"/>
       <c r="G300" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H300" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I300" s="3" t="n">
         <v>0</v>
@@ -23949,12 +23951,12 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Stroud</t>
+          <t>Taunton</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D301" s="5" t="n">
@@ -24000,12 +24002,12 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Swindon</t>
+          <t>Tipton</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D302" s="3" t="n">
@@ -24051,12 +24053,12 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Tadley</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D303" s="5" t="n">
@@ -24070,10 +24072,10 @@
         <v>0</v>
       </c>
       <c r="H303" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I303" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J303" s="5" t="n">
         <v>0</v>
@@ -24102,12 +24104,12 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Taunton</t>
+          <t>Ulverston</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D304" s="3" t="n">
@@ -24118,10 +24120,10 @@
       </c>
       <c r="F304" s="2" t="inlineStr"/>
       <c r="G304" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H304" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I304" s="3" t="n">
         <v>0</v>
@@ -24153,7 +24155,7 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Tipton</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
@@ -24204,12 +24206,12 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Waltham Abbey</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D306" s="3" t="n">
@@ -24220,13 +24222,13 @@
       </c>
       <c r="F306" s="2" t="inlineStr"/>
       <c r="G306" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H306" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I306" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J306" s="3" t="n">
         <v>0</v>
@@ -24255,12 +24257,12 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Ulverston</t>
+          <t>Waltham Cross</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D307" s="5" t="n">
@@ -24271,10 +24273,10 @@
       </c>
       <c r="F307" s="4" t="inlineStr"/>
       <c r="G307" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H307" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I307" s="5" t="n">
         <v>0</v>
@@ -24306,12 +24308,12 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Walton-on-thames</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D308" s="3" t="n">
@@ -24357,12 +24359,12 @@
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Waltham Abbey</t>
+          <t>Ware</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D309" s="5" t="n">
@@ -24408,12 +24410,12 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Waltham Cross</t>
+          <t>Wednesbury</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D310" s="3" t="n">
@@ -24459,12 +24461,12 @@
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D311" s="5" t="n">
@@ -24510,12 +24512,12 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Ware</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D312" s="3" t="n">
@@ -24561,12 +24563,12 @@
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Wednesbury</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D313" s="5" t="n">
@@ -24612,12 +24614,12 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Wellingborough</t>
+          <t>Whitstable</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D314" s="3" t="n">
@@ -24628,13 +24630,13 @@
       </c>
       <c r="F314" s="2" t="inlineStr"/>
       <c r="G314" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H314" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I314" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J314" s="3" t="n">
         <v>0</v>
@@ -24663,12 +24665,12 @@
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Wigan</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D315" s="5" t="n">
@@ -24714,12 +24716,12 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Wilmslow</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D316" s="3" t="n">
@@ -24765,12 +24767,12 @@
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D317" s="5" t="n">
@@ -24816,12 +24818,12 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Whitstable</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D318" s="3" t="n">
@@ -24832,13 +24834,13 @@
       </c>
       <c r="F318" s="2" t="inlineStr"/>
       <c r="G318" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H318" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I318" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J318" s="3" t="n">
         <v>0</v>
@@ -24867,12 +24869,12 @@
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Wigan</t>
+          <t>Witney</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D319" s="5" t="n">
@@ -24918,12 +24920,12 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Wilmslow</t>
+          <t>Worksop</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D320" s="3" t="n">
@@ -24969,12 +24971,12 @@
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Wymondham</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D321" s="5" t="n">
@@ -25012,212 +25014,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B322" s="2" t="inlineStr">
-        <is>
-          <t>Windsor</t>
-        </is>
-      </c>
-      <c r="C322" s="2" t="inlineStr">
-        <is>
-          <t>Berkshire</t>
-        </is>
-      </c>
-      <c r="D322" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E322" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F322" s="2" t="inlineStr"/>
-      <c r="G322" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H322" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I322" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J322" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K322" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L322" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M322" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N322" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O322" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B323" s="4" t="inlineStr">
-        <is>
-          <t>Witney</t>
-        </is>
-      </c>
-      <c r="C323" s="4" t="inlineStr">
-        <is>
-          <t>Oxfordshire</t>
-        </is>
-      </c>
-      <c r="D323" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E323" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F323" s="4" t="inlineStr"/>
-      <c r="G323" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H323" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I323" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J323" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K323" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L323" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M323" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N323" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O323" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B324" s="2" t="inlineStr">
-        <is>
-          <t>Worksop</t>
-        </is>
-      </c>
-      <c r="C324" s="2" t="inlineStr">
-        <is>
-          <t>Nottinghamshire</t>
-        </is>
-      </c>
-      <c r="D324" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E324" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F324" s="2" t="inlineStr"/>
-      <c r="G324" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H324" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I324" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J324" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K324" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L324" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M324" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N324" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O324" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B325" s="4" t="inlineStr">
-        <is>
-          <t>Wymondham</t>
-        </is>
-      </c>
-      <c r="C325" s="4" t="inlineStr">
-        <is>
-          <t>Norfolk</t>
-        </is>
-      </c>
-      <c r="D325" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E325" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F325" s="4" t="inlineStr"/>
-      <c r="G325" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H325" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I325" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J325" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K325" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L325" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M325" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N325" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O325" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O325"/>
+  <autoFilter ref="A1:O321"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25336,7 +25134,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="3" t="n">
@@ -25418,7 +25216,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
@@ -25741,7 +25539,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="5" t="n">
@@ -25894,7 +25692,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>19</v>
@@ -26010,7 +25808,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -26090,7 +25888,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
@@ -26164,7 +25962,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>2</v>
@@ -26400,7 +26198,7 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
@@ -26419,7 +26217,7 @@
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>2</v>
@@ -26671,7 +26469,7 @@
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
       <c r="D77" s="4" t="inlineStr"/>
@@ -26820,32 +26618,32 @@
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.3 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.7 / 2/14</t>
+          <t>4 / 3.7 / 2/14</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>4 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26858,19 +26656,19 @@
       <c r="B3" s="14" t="inlineStr"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>4 / 1.5 / 0/14</t>
+          <t>4 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr"/>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>12 / 1.6 / 1/14</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr"/>
@@ -26889,25 +26687,25 @@
       <c r="B4" s="13" t="inlineStr"/>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>10 / 5.8 / 8/14</t>
+          <t>7 / 6.1 / 9/14</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.4 / 0/14</t>
+          <t>2 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.1 / 0/14</t>
+          <t>0 / 2.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26925,23 +26723,23 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>5 / 2.3 / 0/14</t>
+          <t>5 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/14</t>
+          <t>6 / 2.1 / 1/14</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr"/>
@@ -26960,23 +26758,23 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>15 / 2.9 / 1/14</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.3 / 0/14</t>
+          <t>3 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -26999,12 +26797,12 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.7 / 0/14</t>
+          <t>4 / 3.8 / 0/14</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>2 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
@@ -27014,7 +26812,7 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.3 / 0/14</t>
+          <t>8 / 0.9 / 1/14</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
@@ -27024,7 +26822,7 @@
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.2 / 0/14</t>
+          <t>1 / 2.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27042,17 +26840,17 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/14</t>
+          <t>3 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.6 / 0/14</t>
+          <t>4 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
@@ -27081,28 +26879,28 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.4 / 0/14</t>
+          <t>1 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>7 / 1.6 / 1/14</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27120,7 +26918,7 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -27157,12 +26955,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>0 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>3 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -27204,33 +27002,33 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
       <c r="D12" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.4 / 0/14</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>0 / 1.2 / 0/14</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.5 / 0/14</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>1 / 1.4 / 0/14</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/14</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
@@ -27300,7 +27098,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.6 / 0/14</t>
+          <t>0 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -27310,7 +27108,7 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
@@ -27320,12 +27118,12 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27338,7 +27136,7 @@
       <c r="B15" s="14" t="inlineStr"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/14</t>
+          <t>3 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr"/>
@@ -27349,7 +27147,7 @@
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>2 / 4.2 / 3/14</t>
+          <t>1 / 3.9 / 3/14</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
@@ -27373,37 +27171,37 @@
       <c r="B16" s="13" t="inlineStr"/>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.2 / 0/14</t>
+          <t>2 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>6 / 2.3 / 2/14</t>
+          <t>3 / 2.5 / 2/14</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>13 / 1.1 / 1/14</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27421,7 +27219,7 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.6 / 1/14</t>
+          <t>4 / 3.5 / 1/14</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
@@ -27429,12 +27227,12 @@
       <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.7 / 5/14</t>
+          <t>4 / 3.9 / 5/14</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.8 / 0/14</t>
+          <t>0 / 2.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27447,29 +27245,29 @@
       <c r="B18" s="13" t="inlineStr"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>1 / 3.2 / 3/14</t>
+          <t>2 / 3.1 / 3/14</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>2 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr"/>
       <c r="G18" s="13" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.3 / 0/14</t>
+          <t>0 / 3.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27482,13 +27280,13 @@
       <c r="B19" s="14" t="inlineStr"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>17 / 10.4 / 11/14</t>
+          <t>14 / 11.1 / 12/14</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr"/>
@@ -27496,7 +27294,7 @@
       <c r="H19" s="14" t="inlineStr"/>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27508,7 +27306,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.5 / 0/14</t>
+          <t>2 / 3.5 / 0/14</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -27533,7 +27331,7 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>4 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
@@ -27543,7 +27341,7 @@
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27566,13 +27364,13 @@
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>3 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
@@ -27582,7 +27380,7 @@
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27605,27 +27403,27 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>3 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>2 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27640,22 +27438,22 @@
       <c r="D23" s="14" t="inlineStr"/>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>4 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>7 / 7.1 / 14/14</t>
+          <t>4 / 6.6 / 13/14</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 0/14</t>
+          <t>8 / 3.6 / 1/14</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>7 / 6.0 / 8/14</t>
+          <t>4 / 6.0 / 8/14</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr"/>
@@ -27668,12 +27466,12 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>2 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
@@ -27693,7 +27491,7 @@
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>2 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
@@ -27716,29 +27514,29 @@
       <c r="B25" s="14" t="inlineStr"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/14</t>
+          <t>9 / 2.8 / 1/14</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27753,13 +27551,13 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>10 / 9.8 / 11/14</t>
+          <t>13 / 10.4 / 12/14</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>18 / 1.4 / 1/14</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
@@ -27769,7 +27567,7 @@
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27801,7 +27599,7 @@
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -27828,7 +27626,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>2 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -27838,7 +27636,7 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -27848,12 +27646,12 @@
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>2 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -27863,7 +27661,7 @@
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27875,7 +27673,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.0 / 0/14</t>
+          <t>4 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -27885,7 +27683,7 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -27895,12 +27693,12 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/14</t>
+          <t>0 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/14</t>
+          <t>6 / 1.1 / 1/14</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
@@ -27922,12 +27720,12 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>2 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
@@ -27952,7 +27750,7 @@
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
@@ -27994,7 +27792,7 @@
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
@@ -28022,32 +27820,32 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.2 / 0/14</t>
+          <t>3 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.4 / 0/14</t>
+          <t>4 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/14</t>
+          <t>6 / 2.9 / 1/14</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28060,22 +27858,22 @@
       <c r="B33" s="14" t="inlineStr"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.3 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/14</t>
+          <t>1 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/14</t>
+          <t>3 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -28085,12 +27883,12 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28123,28 +27921,28 @@
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>9 / 4.9 / 7/14</t>
+          <t>6 / 5.1 / 8/14</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/14</t>
+          <t>3 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28156,7 +27954,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -28171,7 +27969,7 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -28181,7 +27979,7 @@
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
@@ -28203,27 +28001,27 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>5 / 1.6 / 0/14</t>
+          <t>4 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
+          <t>1 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>1 / 1.2 / 0/14</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
-        <is>
-          <t>2 / 1.2 / 0/14</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -28260,7 +28058,7 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -28270,7 +28068,7 @@
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
@@ -28285,7 +28083,7 @@
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28298,33 +28096,33 @@
       <c r="B39" s="14" t="inlineStr"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>7 / 3.7 / 5/14</t>
+          <t>6 / 4.1 / 6/14</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>7 / 1.6 / 1/14</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>2 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28339,14 +28137,14 @@
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.7 / 0/14</t>
+          <t>2 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr"/>
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.5 / 0/14</t>
+          <t>2 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
@@ -28366,7 +28164,7 @@
       <c r="D41" s="14" t="inlineStr"/>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr">
@@ -28376,7 +28174,7 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
@@ -28386,7 +28184,7 @@
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28398,7 +28196,7 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.9 / 0/14</t>
+          <t>2 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -28418,12 +28216,12 @@
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>2 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
@@ -28433,7 +28231,7 @@
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28445,12 +28243,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.9 / 0/14</t>
+          <t>0 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
@@ -28460,7 +28258,7 @@
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
@@ -28475,12 +28273,12 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28493,12 +28291,12 @@
       <c r="B44" s="13" t="inlineStr"/>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>4 / 5.5 / 5/14</t>
+          <t>2 / 5.0 / 4/14</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -28513,12 +28311,12 @@
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.8 / 0/14</t>
+          <t>7 / 3.2 / 1/14</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.4 / 0/14</t>
+          <t>4 / 3.5 / 0/14</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
@@ -28536,17 +28334,17 @@
       <c r="B45" s="14" t="inlineStr"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>20 / 15.4 / 13/14</t>
+          <t>2 / 15.3 / 13/14</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr"/>
@@ -28554,7 +28352,7 @@
       <c r="H45" s="14" t="inlineStr"/>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28566,7 +28364,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>18 / 22.5 / 14/14</t>
+          <t>1 / 21.1 / 13/14</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -28576,22 +28374,22 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/14</t>
+          <t>1 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/14</t>
+          <t>0 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/14</t>
+          <t>0 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -28601,7 +28399,7 @@
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28614,33 +28412,33 @@
       <c r="B47" s="14" t="inlineStr"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.9 / 0/14</t>
+          <t>0 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>7 / 4.6 / 7/14</t>
+          <t>8 / 5.0 / 8/14</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.6 / 0/14</t>
+          <t>3 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>8 / 0.9 / 1/14</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr"/>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28654,18 +28452,18 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.8 / 0/14</t>
+          <t>3 / 3.7 / 0/14</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>5 / 1.8 / 0/14</t>
+          <t>5 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr"/>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>6 / 1.5 / 1/14</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
@@ -28675,7 +28473,7 @@
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28532,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.8 / 0/14</t>
+          <t>0 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -28744,7 +28542,7 @@
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -28764,7 +28562,7 @@
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I50" s="13" t="inlineStr">
@@ -28787,32 +28585,32 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.4 / 0/14</t>
+          <t>1 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
+          <t>3 / 1.5 / 0/14</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>3 / 1.2 / 0/14</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
           <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>2 / 1.1 / 0/14</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>1 / 1.3 / 0/14</t>
-        </is>
-      </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28824,7 +28622,7 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -28839,7 +28637,7 @@
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
@@ -28871,7 +28669,7 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>9 / 2.9 / 3/14</t>
+          <t>8 / 3.3 / 4/14</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -28929,7 +28727,7 @@
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
@@ -28949,7 +28747,7 @@
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28759,7 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
@@ -28976,7 +28774,7 @@
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
@@ -28996,7 +28794,7 @@
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29020,22 +28818,22 @@
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29047,7 +28845,7 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
@@ -29072,7 +28870,7 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="H57" s="14" t="inlineStr">
@@ -29094,7 +28892,7 @@
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
@@ -29104,7 +28902,7 @@
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -29142,33 +28940,33 @@
       <c r="B59" s="14" t="inlineStr"/>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>2 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.3 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/14</t>
+          <t>1 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr"/>
       <c r="H59" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>0 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29181,37 +28979,37 @@
       <c r="B60" s="13" t="inlineStr"/>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>3 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.8 / 0/14</t>
+          <t>2 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.8 / 0/14</t>
+          <t>3 / 3.7 / 0/14</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
+          <t>1 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="H60" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
-      <c r="H60" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/14</t>
-        </is>
-      </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29229,27 +29027,27 @@
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>4 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>7 / 4.6 / 6/14</t>
+          <t>5 / 4.8 / 6/14</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/14</t>
+          <t>4 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr"/>
@@ -29268,23 +29066,23 @@
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.9 / 0/14</t>
+          <t>3 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.2 / 0/14</t>
+          <t>9 / 2.8 / 1/14</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>3 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
@@ -29304,18 +29102,18 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>7 / 8.1 / 11/14</t>
+          <t>12 / 8.6 / 12/14</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>4 / 4.9 / 6/14</t>
+          <t>13 / 5.6 / 7/14</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
-          <t>4 / 4.1 / 0/14</t>
+          <t>3 / 4.1 / 0/14</t>
         </is>
       </c>
       <c r="I63" s="14" t="inlineStr"/>
@@ -29336,18 +29134,18 @@
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>8 / 5.0 / 5/14</t>
+          <t>6 / 5.1 / 6/14</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>8 / 3.9 / 2/14</t>
+          <t>18 / 5.0 / 3/14</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/14</t>
+          <t>0 / 1.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29406,12 +29204,12 @@
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.6 / 0/14</t>
+          <t>0 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.6 / 0/14</t>
+          <t>6 / 1.0 / 1/14</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
@@ -29421,7 +29219,7 @@
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
@@ -29459,12 +29257,12 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.5 / 0/14</t>
+          <t>0 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/14</t>
+          <t>1 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
@@ -29474,17 +29272,17 @@
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
+          <t>6 / 0.4 / 1/14</t>
+        </is>
+      </c>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="H67" s="14" t="inlineStr">
+      <c r="I67" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="I67" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29496,7 +29294,7 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>3 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -29511,17 +29309,17 @@
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.3 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>2 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -29543,7 +29341,7 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>10 / 3.4 / 2/14</t>
+          <t>10 / 3.8 / 3/14</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
@@ -29553,22 +29351,22 @@
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>2 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H69" s="14" t="inlineStr">
@@ -29591,7 +29389,7 @@
       <c r="B70" s="13" t="inlineStr"/>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
@@ -29601,7 +29399,7 @@
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.4 / 0/14</t>
+          <t>0 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
@@ -29621,7 +29419,7 @@
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29634,29 +29432,29 @@
       <c r="B71" s="14" t="inlineStr"/>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>2 / 5.3 / 5/14</t>
+          <t>2 / 4.7 / 4/14</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>12 / 6.7 / 8/14</t>
+          <t>11 / 7.2 / 9/14</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.0 / 0/14</t>
+          <t>7 / 3.3 / 1/14</t>
         </is>
       </c>
       <c r="H71" s="14" t="inlineStr"/>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29674,19 +29472,19 @@
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.3 / 0/14</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>2 / 3.8 / 0/14</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
-      <c r="E72" s="13" t="inlineStr">
-        <is>
-          <t>4 / 3.9 / 0/14</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.4 / 0/14</t>
-        </is>
-      </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
           <t>2 / 1.6 / 0/14</t>
@@ -29699,7 +29497,7 @@
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29712,33 +29510,33 @@
       <c r="B73" s="14" t="inlineStr"/>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/14</t>
+          <t>3 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.3 / 5/14</t>
+          <t>1 / 2.9 / 4/14</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/14</t>
+          <t>4 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>5 / 5.3 / 5/14</t>
+          <t>3 / 5.2 / 5/14</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.2 / 0/14</t>
+          <t>9 / 3.7 / 1/14</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr"/>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29752,32 +29550,32 @@
       <c r="C74" s="13" t="inlineStr"/>
       <c r="D74" s="13" t="inlineStr">
         <is>
+          <t>2 / 2.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>4 / 3.3 / 0/14</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="inlineStr">
+        <is>
+          <t>4 / 3.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="G74" s="13" t="inlineStr">
+        <is>
+          <t>11 / 2.6 / 1/14</t>
+        </is>
+      </c>
+      <c r="H74" s="13" t="inlineStr">
+        <is>
           <t>2 / 2.1 / 0/14</t>
         </is>
       </c>
-      <c r="E74" s="13" t="inlineStr">
-        <is>
-          <t>5 / 3.3 / 0/14</t>
-        </is>
-      </c>
-      <c r="F74" s="13" t="inlineStr">
-        <is>
-          <t>4 / 2.9 / 0/14</t>
-        </is>
-      </c>
-      <c r="G74" s="13" t="inlineStr">
-        <is>
-          <t>4 / 1.8 / 0/14</t>
-        </is>
-      </c>
-      <c r="H74" s="13" t="inlineStr">
-        <is>
-          <t>3 / 2.0 / 0/14</t>
-        </is>
-      </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29800,27 +29598,27 @@
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 0/14</t>
+          <t>4 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>0 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>5 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29843,27 +29641,27 @@
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/14</t>
+          <t>1 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.8 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 0/14</t>
+          <t>2 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -29886,14 +29684,14 @@
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>8 / 5.0 / 7/14</t>
+          <t>5 / 5.4 / 7/14</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr"/>
       <c r="G77" s="14" t="inlineStr"/>
       <c r="H77" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.7 / 4/14</t>
+          <t>2 / 3.7 / 4/14</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
@@ -29912,27 +29710,27 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.1 / 0/14</t>
+          <t>1 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.6 / 0/14</t>
+          <t>2 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>5 / 5.5 / 5/14</t>
+          <t>4 / 5.4 / 5/14</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/14</t>
+          <t>4 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.3 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
@@ -29952,19 +29750,19 @@
       <c r="D79" s="14" t="inlineStr"/>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>8 / 6.8 / 8/14</t>
+          <t>9 / 7.1 / 9/14</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>11 / 13.5 / 14/14</t>
+          <t>9 / 12.9 / 14/14</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>
       <c r="H79" s="14" t="inlineStr"/>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.3 / 0/14</t>
+          <t>0 / 2.1 / 0/14</t>
         </is>
       </c>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$194</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$220</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="6">
@@ -8171,7 +8171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O221"/>
+  <dimension ref="A1:O220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18417,12 +18417,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Rickmansworth</t>
+          <t>Ringwood</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -18433,10 +18433,10 @@
       </c>
       <c r="F197" s="4" t="inlineStr"/>
       <c r="G197" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H197" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I197" s="5" t="n">
         <v>0</v>
@@ -18468,12 +18468,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Ringwood</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -18484,10 +18484,10 @@
       </c>
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I198" s="3" t="n">
         <v>0</v>
@@ -18519,12 +18519,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Sevenoaks</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Sevenoaks</t>
+          <t>Sherborne</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -18621,12 +18621,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Sherborne</t>
+          <t>Smethwick</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -18672,12 +18672,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Smethwick</t>
+          <t>South Shields</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -18688,10 +18688,10 @@
       </c>
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I202" s="3" t="n">
         <v>0</v>
@@ -18723,12 +18723,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>South Shields</t>
+          <t>Spennymoor</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -18739,10 +18739,10 @@
       </c>
       <c r="F203" s="4" t="inlineStr"/>
       <c r="G203" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H203" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I203" s="5" t="n">
         <v>0</v>
@@ -18774,12 +18774,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Spennymoor</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -18790,13 +18790,13 @@
       </c>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H204" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J204" s="3" t="n">
         <v>0</v>
@@ -18825,12 +18825,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Torquay</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -18841,13 +18841,13 @@
       </c>
       <c r="F205" s="4" t="inlineStr"/>
       <c r="G205" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H205" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J205" s="5" t="n">
         <v>0</v>
@@ -18876,12 +18876,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Trowbridge</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -18927,12 +18927,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Trowbridge</t>
+          <t>Ulverston</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -18943,10 +18943,10 @@
       </c>
       <c r="F207" s="4" t="inlineStr"/>
       <c r="G207" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H207" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I207" s="5" t="n">
         <v>0</v>
@@ -18978,12 +18978,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Ulverston</t>
+          <t>Uttoxeter</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -18994,10 +18994,10 @@
       </c>
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I208" s="3" t="n">
         <v>0</v>
@@ -19029,12 +19029,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Uttoxeter</t>
+          <t>Ventnor</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -19045,10 +19045,10 @@
       </c>
       <c r="F209" s="4" t="inlineStr"/>
       <c r="G209" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H209" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I209" s="5" t="n">
         <v>0</v>
@@ -19080,12 +19080,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Ventnor</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -19096,10 +19096,10 @@
       </c>
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I210" s="3" t="n">
         <v>0</v>
@@ -19131,12 +19131,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Waltham Abbey</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -19182,12 +19182,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Waltham Abbey</t>
+          <t>Walton-on-thames</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -19233,12 +19233,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
@@ -19284,12 +19284,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -19335,12 +19335,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Wilmslow</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
@@ -19386,12 +19386,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Wilmslow</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -19437,12 +19437,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Winsford</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
@@ -19488,12 +19488,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Winsford</t>
+          <t>Worthing</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
@@ -19539,12 +19539,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Worthing</t>
+          <t>Wymondham</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
@@ -19590,12 +19590,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Wymondham</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
@@ -19633,59 +19633,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B221" s="4" t="inlineStr">
-        <is>
-          <t>Yeovil</t>
-        </is>
-      </c>
-      <c r="C221" s="4" t="inlineStr">
-        <is>
-          <t>Somerset</t>
-        </is>
-      </c>
-      <c r="D221" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E221" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F221" s="4" t="inlineStr"/>
-      <c r="G221" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H221" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I221" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J221" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L221" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M221" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N221" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O221" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O221"/>
+  <autoFilter ref="A1:O220"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20207,7 +20156,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="5" t="n">
@@ -20476,7 +20425,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>2</v>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2160</v>
+        <v>2172</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>215</v>
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1432</v>
+        <v>1418</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>726</v>
+        <v>707</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>8</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>32</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>2</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>3</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" s="8" t="inlineStr"/>
     </row>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -21314,7 +21314,7 @@
       <c r="B4" s="13" t="inlineStr"/>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>2 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>3 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -21385,7 +21385,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -21467,7 +21467,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>2 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -21545,7 +21545,7 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -21774,7 +21774,7 @@
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>1 / 3.9 / 3/14</t>
+          <t>0 / 3.9 / 3/14</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
@@ -21846,7 +21846,7 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.5 / 1/14</t>
+          <t>5 / 3.6 / 1/14</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
@@ -21913,7 +21913,7 @@
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>14 / 11.1 / 12/14</t>
+          <t>15 / 11.2 / 12/14</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr"/>
@@ -22147,7 +22147,7 @@
       <c r="D25" s="14" t="inlineStr"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr"/>
@@ -22216,7 +22216,7 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/14</t>
+          <t>1 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -22288,7 +22288,7 @@
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22300,7 +22300,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 0/14</t>
+          <t>5 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -22457,7 +22457,7 @@
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.7 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/14</t>
+          <t>4 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>6 / 5.1 / 8/14</t>
+          <t>7 / 5.2 / 8/14</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr"/>
@@ -22633,7 +22633,7 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
@@ -22833,7 +22833,7 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -22923,7 +22923,7 @@
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>2 / 5.0 / 4/14</t>
+          <t>3 / 5.1 / 4/14</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -22971,7 +22971,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>2 / 15.3 / 13/14</t>
+          <t>0 / 15.1 / 13/14</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr"/>
@@ -22991,7 +22991,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>1 / 21.1 / 13/14</t>
+          <t>2 / 21.2 / 13/14</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -23054,7 +23054,7 @@
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/14</t>
+          <t>2 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -23079,7 +23079,7 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.7 / 0/14</t>
+          <t>4 / 3.8 / 0/14</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -23222,7 +23222,7 @@
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -23364,7 +23364,7 @@
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
@@ -23445,7 +23445,7 @@
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
@@ -23567,7 +23567,7 @@
       <c r="B59" s="14" t="inlineStr"/>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.1 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
@@ -23659,7 +23659,7 @@
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>4 / 0.9 / 0/14</t>
+          <t>3 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="F61" s="14" t="inlineStr">
@@ -23761,7 +23761,7 @@
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>6 / 5.1 / 6/14</t>
+          <t>5 / 5.0 / 5/14</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
@@ -23894,7 +23894,7 @@
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -23921,7 +23921,7 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -23946,7 +23946,7 @@
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.1 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -23978,7 +23978,7 @@
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
@@ -24021,7 +24021,7 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -24069,7 +24069,7 @@
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>11 / 7.2 / 9/14</t>
+          <t>10 / 7.1 / 9/14</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
@@ -24152,7 +24152,7 @@
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>3 / 5.2 / 5/14</t>
+          <t>2 / 5.1 / 5/14</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -24192,7 +24192,7 @@
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>11 / 2.6 / 1/14</t>
+          <t>10 / 2.5 / 1/14</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>4 / 5.4 / 5/14</t>
+          <t>2 / 5.3 / 5/14</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$194</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$217</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1038</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1158</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2172</v>
+        <v>2271</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>215</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1418</v>
+        <v>1441</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1095</v>
+        <v>1042</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1021</v>
+        <v>1003</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>968</v>
+        <v>957</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>12</v>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -778,7 +778,7 @@
         <v>364</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>2</v>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -814,35 +814,35 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Science &amp; Technology</t>
+          <t>Advert / Media / Entertainment</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C16" s="8" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Advert / Media / Entertainment</t>
+          <t>Science &amp; Technology</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="C17" s="7" t="n">
-        <v>4</v>
-      </c>
+      <c r="C17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
         <v>10000</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>904</v>
+        <v>923</v>
       </c>
     </row>
   </sheetData>
@@ -8171,7 +8171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O220"/>
+  <dimension ref="A1:O217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8276,23 +8276,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Runcorn</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0</v>
@@ -8327,12 +8327,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Pontypridd</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Pontypridd</t>
+          <t>Runcorn</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>1</v>
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0</v>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Hounslow</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" s="5" t="n">
         <v>0</v>
@@ -13045,7 +13045,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N91" s="5" t="n">
         <v>0</v>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Hounslow</t>
+          <t>Ilford</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -13087,7 +13087,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
@@ -13096,7 +13096,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>0</v>
@@ -13113,7 +13113,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Ilford</t>
+          <t>Isleworth</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="5" t="n">
         <v>0</v>
@@ -13138,7 +13138,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93" s="5" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Isleworth</t>
+          <t>Purley</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Purley</t>
+          <t>Sutton</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Sutton</t>
+          <t>Twickenham</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3" t="n">
         <v>0</v>
@@ -13297,7 +13297,7 @@
         <v>0</v>
       </c>
       <c r="L96" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="3" t="n">
         <v>0</v>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Twickenham</t>
+          <t>Uxbridge</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -13333,7 +13333,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" s="5" t="n">
         <v>0</v>
@@ -13348,7 +13348,7 @@
         <v>0</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" s="5" t="n">
         <v>0</v>
@@ -13368,7 +13368,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Uxbridge</t>
+          <t>West Drayton</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>West Drayton</t>
+          <t>Worcester Park</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -13465,28 +13465,28 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Worcester Park</t>
+          <t>Cheadle</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
@@ -13498,7 +13498,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>0</v>
@@ -13521,35 +13521,35 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Cheadle</t>
+          <t>Slough</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E101" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H101" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L101" s="5" t="n">
         <v>0</v>
@@ -13572,12 +13572,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Slough</t>
+          <t>Tunbridge Wells</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
@@ -13588,10 +13588,10 @@
       </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I102" s="3" t="n">
         <v>1</v>
@@ -13600,7 +13600,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="n">
         <v>0</v>
@@ -13623,26 +13623,26 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Tunbridge Wells</t>
+          <t>Newbury</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E103" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I103" s="5" t="n">
         <v>1</v>
@@ -13651,7 +13651,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="5" t="n">
         <v>0</v>
@@ -13674,12 +13674,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Newbury</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
@@ -13690,25 +13690,25 @@
       </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H104" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K104" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M104" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N104" s="3" t="n">
         <v>0</v>
@@ -13725,12 +13725,12 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -13747,7 +13747,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" s="5" t="n">
         <v>0</v>
@@ -13759,7 +13759,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N105" s="5" t="n">
         <v>0</v>
@@ -13776,23 +13776,23 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Dartford</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="3" t="n">
         <v>0</v>
@@ -13827,12 +13827,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Dartford</t>
+          <t>Guildford</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -13878,12 +13878,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Guildford</t>
+          <t>Northwich</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
@@ -13894,13 +13894,13 @@
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108" s="3" t="n">
         <v>0</v>
@@ -13929,12 +13929,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Northwich</t>
+          <t>Sittingbourne</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -13948,7 +13948,7 @@
         <v>2</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" s="5" t="n">
         <v>0</v>
@@ -13957,7 +13957,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="5" t="n">
         <v>0</v>
@@ -13980,29 +13980,29 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Sittingbourne</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H110" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I110" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -14031,12 +14031,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Ballyclare</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -14047,13 +14047,13 @@
       </c>
       <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H111" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J111" s="5" t="n">
         <v>0</v>
@@ -14082,12 +14082,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Ballyclare</t>
+          <t>Berwick-upon-tweed</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
@@ -14098,13 +14098,13 @@
       </c>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H112" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -14133,12 +14133,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Berwick-upon-tweed</t>
+          <t>Camberley</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14149,13 +14149,13 @@
       </c>
       <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H113" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J113" s="5" t="n">
         <v>0</v>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Camberley</t>
+          <t>Caterham</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -14200,10 +14200,10 @@
       </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>0</v>
@@ -14235,12 +14235,12 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Caterham</t>
+          <t>Cramlington</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14251,13 +14251,13 @@
       </c>
       <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J115" s="5" t="n">
         <v>0</v>
@@ -14286,12 +14286,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Cramlington</t>
+          <t>Devizes</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
@@ -14302,13 +14302,13 @@
       </c>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J116" s="3" t="n">
         <v>0</v>
@@ -14337,12 +14337,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Devizes</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14353,10 +14353,10 @@
       </c>
       <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" s="5" t="n">
         <v>0</v>
@@ -14388,7 +14388,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Gosport</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Gosport</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -14458,10 +14458,10 @@
         <v>1</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119" s="5" t="n">
         <v>0</v>
@@ -14490,12 +14490,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
@@ -14512,13 +14512,13 @@
         <v>0</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="3" t="n">
         <v>0</v>
@@ -14541,12 +14541,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H121" s="5" t="n">
         <v>0</v>
@@ -14569,7 +14569,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" s="5" t="n">
         <v>0</v>
@@ -14592,12 +14592,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Knaresborough</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
@@ -14608,19 +14608,19 @@
       </c>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H122" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="L122" s="3" t="n">
         <v>0</v>
@@ -14643,12 +14643,12 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Knaresborough</t>
+          <t>Leatherhead</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -14659,10 +14659,10 @@
       </c>
       <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" s="5" t="n">
         <v>0</v>
@@ -14671,7 +14671,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L123" s="5" t="n">
         <v>0</v>
@@ -14694,12 +14694,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Leatherhead</t>
+          <t>Maidenhead</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -14710,10 +14710,10 @@
       </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>0</v>
@@ -14722,13 +14722,13 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -14745,12 +14745,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Maidenhead</t>
+          <t>Maldon</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -14770,16 +14770,16 @@
         <v>0</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K125" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M125" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N125" s="5" t="n">
         <v>0</v>
@@ -14796,12 +14796,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Maldon</t>
+          <t>Margate</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -14815,13 +14815,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I126" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K126" s="3" t="n">
         <v>0</v>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Margate</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -14863,10 +14863,10 @@
       </c>
       <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I127" s="5" t="n">
         <v>0</v>
@@ -14898,12 +14898,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Newton Abbot</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -14914,13 +14914,13 @@
       </c>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H128" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" s="3" t="n">
         <v>0</v>
@@ -14949,12 +14949,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Newton Abbot</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -14965,13 +14965,13 @@
       </c>
       <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H129" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" s="5" t="n">
         <v>0</v>
@@ -15000,12 +15000,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H130" s="3" t="n">
         <v>0</v>
@@ -15028,10 +15028,10 @@
         <v>0</v>
       </c>
       <c r="K130" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="3" t="n">
         <v>0</v>
@@ -15051,12 +15051,12 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H131" s="5" t="n">
         <v>0</v>
@@ -15079,10 +15079,10 @@
         <v>0</v>
       </c>
       <c r="K131" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M131" s="5" t="n">
         <v>0</v>
@@ -15102,12 +15102,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Tadley</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
@@ -15118,10 +15118,10 @@
       </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H132" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="I132" s="3" t="n">
         <v>0</v>
@@ -15153,12 +15153,12 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Tadley</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15204,12 +15204,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Verwood</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -15220,10 +15220,10 @@
       </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -15255,12 +15255,12 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Verwood</t>
+          <t>Welwyn Garden City</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H135" s="5" t="n">
         <v>0</v>
@@ -15283,7 +15283,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="5" t="n">
         <v>0</v>
@@ -15306,12 +15306,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Welwyn Garden City</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
@@ -15322,10 +15322,10 @@
       </c>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I136" s="3" t="n">
         <v>0</v>
@@ -15357,12 +15357,12 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Woodbridge</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -15373,10 +15373,10 @@
       </c>
       <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H137" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137" s="5" t="n">
         <v>0</v>
@@ -15385,7 +15385,7 @@
         <v>0</v>
       </c>
       <c r="K137" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" s="5" t="n">
         <v>0</v>
@@ -15408,23 +15408,23 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Woodbridge</t>
+          <t>Alresford</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H138" s="3" t="n">
         <v>0</v>
@@ -15459,12 +15459,12 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Alresford</t>
+          <t>Amersham</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15510,12 +15510,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Amersham</t>
+          <t>Atherstone</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H140" s="3" t="n">
         <v>0</v>
@@ -15544,7 +15544,7 @@
         <v>0</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N140" s="3" t="n">
         <v>0</v>
@@ -15561,12 +15561,12 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Atherstone</t>
+          <t>Barrow-in-furness</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15580,7 +15580,7 @@
         <v>0</v>
       </c>
       <c r="H141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I141" s="5" t="n">
         <v>0</v>
@@ -15595,7 +15595,7 @@
         <v>0</v>
       </c>
       <c r="M141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N141" s="5" t="n">
         <v>0</v>
@@ -15612,12 +15612,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Barrow-in-furness</t>
+          <t>Beaminster</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -15628,10 +15628,10 @@
       </c>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142" s="3" t="n">
         <v>0</v>
@@ -15663,12 +15663,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Beaminster</t>
+          <t>Bexhill-on-sea</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15714,12 +15714,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Bexhill-on-sea</t>
+          <t>Billericay</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -15765,12 +15765,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Billericay</t>
+          <t>Birchington</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15781,10 +15781,10 @@
       </c>
       <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I145" s="5" t="n">
         <v>0</v>
@@ -15816,12 +15816,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Birchington</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -15832,10 +15832,10 @@
       </c>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I146" s="3" t="n">
         <v>0</v>
@@ -15867,12 +15867,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -15918,12 +15918,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Bridgwater</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Bridgwater</t>
+          <t>Brighouse</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H149" s="5" t="n">
         <v>0</v>
@@ -16000,7 +16000,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M149" s="5" t="n">
         <v>0</v>
@@ -16020,12 +16020,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Brighouse</t>
+          <t>Bury St. Edmunds</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
         <v>0</v>
@@ -16051,7 +16051,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M150" s="3" t="n">
         <v>0</v>
@@ -16071,12 +16071,12 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Bury St. Edmunds</t>
+          <t>Canterbury</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -16122,7 +16122,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>Chatham</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Chatham</t>
+          <t>Chertsey</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -16189,10 +16189,10 @@
       </c>
       <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I153" s="5" t="n">
         <v>0</v>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Chertsey</t>
+          <t>Christchurch</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -16240,10 +16240,10 @@
       </c>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>0</v>
@@ -16275,12 +16275,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Christchurch</t>
+          <t>Cirencester</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155" s="5" t="n">
         <v>0</v>
@@ -16306,7 +16306,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" s="5" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Cirencester</t>
+          <t>Cleethorpes</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -16342,7 +16342,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156" s="3" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" s="3" t="n">
         <v>0</v>
@@ -16377,12 +16377,12 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Cleethorpes</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -16393,7 +16393,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H157" s="5" t="n">
         <v>0</v>
@@ -16402,7 +16402,7 @@
         <v>0</v>
       </c>
       <c r="J157" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K157" s="5" t="n">
         <v>0</v>
@@ -16428,12 +16428,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>Congleton</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" s="3" t="n">
         <v>0</v>
@@ -16453,7 +16453,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" s="3" t="n">
         <v>0</v>
@@ -16479,12 +16479,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Congleton</t>
+          <t>Crawley</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -16495,10 +16495,10 @@
       </c>
       <c r="F159" s="4" t="inlineStr"/>
       <c r="G159" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I159" s="5" t="n">
         <v>0</v>
@@ -16530,12 +16530,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Crawley</t>
+          <t>Dunmow</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -16549,7 +16549,7 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160" s="3" t="n">
         <v>0</v>
@@ -16561,7 +16561,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M160" s="3" t="n">
         <v>0</v>
@@ -16581,12 +16581,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Dunmow</t>
+          <t>Eastbourne</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -16600,7 +16600,7 @@
         <v>0</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I161" s="5" t="n">
         <v>0</v>
@@ -16612,7 +16612,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M161" s="5" t="n">
         <v>0</v>
@@ -16632,12 +16632,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Eastbourne</t>
+          <t>Eccles</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
@@ -16648,10 +16648,10 @@
       </c>
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" s="3" t="n">
         <v>0</v>
@@ -16683,12 +16683,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Eccles</t>
+          <t>Esher</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -16699,13 +16699,13 @@
       </c>
       <c r="F163" s="4" t="inlineStr"/>
       <c r="G163" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" s="5" t="n">
         <v>0</v>
@@ -16734,12 +16734,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Esher</t>
+          <t>Fareham</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
@@ -16753,10 +16753,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J164" s="3" t="n">
         <v>0</v>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Fareham</t>
+          <t>Farnborough</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -16801,10 +16801,10 @@
       </c>
       <c r="F165" s="4" t="inlineStr"/>
       <c r="G165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I165" s="5" t="n">
         <v>0</v>
@@ -16836,12 +16836,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Farnborough</t>
+          <t>Folkestone</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -16852,7 +16852,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
         <v>0</v>
@@ -16864,7 +16864,7 @@
         <v>0</v>
       </c>
       <c r="K166" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L166" s="3" t="n">
         <v>0</v>
@@ -16887,12 +16887,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Folkestone</t>
+          <t>Freshwater</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -16906,7 +16906,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167" s="5" t="n">
         <v>0</v>
@@ -16915,7 +16915,7 @@
         <v>0</v>
       </c>
       <c r="K167" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L167" s="5" t="n">
         <v>0</v>
@@ -16938,12 +16938,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Freshwater</t>
+          <t>Gainsborough</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -16954,10 +16954,10 @@
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I168" s="3" t="n">
         <v>0</v>
@@ -16989,12 +16989,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Gainsborough</t>
+          <t>Godalming</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -17005,13 +17005,13 @@
       </c>
       <c r="F169" s="4" t="inlineStr"/>
       <c r="G169" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H169" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J169" s="5" t="n">
         <v>0</v>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Godalming</t>
+          <t>Godstone</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -17056,13 +17056,13 @@
       </c>
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H170" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170" s="3" t="n">
         <v>0</v>
@@ -17091,12 +17091,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Godstone</t>
+          <t>Gravesend</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -17107,10 +17107,10 @@
       </c>
       <c r="F171" s="4" t="inlineStr"/>
       <c r="G171" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H171" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I171" s="5" t="n">
         <v>0</v>
@@ -17142,12 +17142,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Gravesend</t>
+          <t>Great Yarmouth</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -17158,10 +17158,10 @@
       </c>
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>0</v>
@@ -17193,12 +17193,12 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Great Yarmouth</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H174" s="3" t="n">
         <v>0</v>
@@ -17275,7 +17275,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M174" s="3" t="n">
         <v>0</v>
@@ -17295,12 +17295,12 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -17314,7 +17314,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I175" s="5" t="n">
         <v>0</v>
@@ -17326,7 +17326,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M175" s="5" t="n">
         <v>0</v>
@@ -17346,12 +17346,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Hertford</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -17362,10 +17362,10 @@
       </c>
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>0</v>
@@ -17397,12 +17397,12 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Hertford</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Hove</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -17499,12 +17499,12 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Hove</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D179" s="5" t="n">
@@ -17550,12 +17550,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Keighley</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -17566,7 +17566,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
         <v>0</v>
@@ -17581,7 +17581,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M180" s="3" t="n">
         <v>0</v>
@@ -17601,12 +17601,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Keighley</t>
+          <t>Kirriemuir</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
@@ -17617,7 +17617,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr"/>
       <c r="G181" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H181" s="5" t="n">
         <v>0</v>
@@ -17632,7 +17632,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M181" s="5" t="n">
         <v>0</v>
@@ -17652,12 +17652,12 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Kirriemuir</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -17703,12 +17703,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Knowle</t>
+          <t>Lewes</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -17754,12 +17754,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Lisburn</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
@@ -17805,12 +17805,12 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Lewes</t>
+          <t>Liss</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
@@ -17821,10 +17821,10 @@
       </c>
       <c r="F185" s="4" t="inlineStr"/>
       <c r="G185" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H185" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I185" s="5" t="n">
         <v>0</v>
@@ -17856,12 +17856,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Lisburn</t>
+          <t>Littlehampton</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
@@ -17907,12 +17907,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Liss</t>
+          <t>Luton</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
@@ -17923,10 +17923,10 @@
       </c>
       <c r="F187" s="4" t="inlineStr"/>
       <c r="G187" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H187" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I187" s="5" t="n">
         <v>0</v>
@@ -17958,12 +17958,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Littlehampton</t>
+          <t>Lyndhurst</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
@@ -18009,12 +18009,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Luton</t>
+          <t>North Shields</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
@@ -18060,12 +18060,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Lyndhurst</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -18076,13 +18076,13 @@
       </c>
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J190" s="3" t="n">
         <v>0</v>
@@ -18111,12 +18111,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Marlow</t>
+          <t>Pontefract</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
@@ -18162,12 +18162,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>North Shields</t>
+          <t>Reigate</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="K192" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L192" s="3" t="n">
         <v>0</v>
@@ -18213,12 +18213,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
@@ -18235,7 +18235,7 @@
         <v>0</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J193" s="5" t="n">
         <v>0</v>
@@ -18244,7 +18244,7 @@
         <v>0</v>
       </c>
       <c r="L193" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M193" s="5" t="n">
         <v>0</v>
@@ -18264,12 +18264,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Pontefract</t>
+          <t>Ringwood</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -18280,10 +18280,10 @@
       </c>
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I194" s="3" t="n">
         <v>0</v>
@@ -18315,12 +18315,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Reigate</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
@@ -18331,7 +18331,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr"/>
       <c r="G195" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H195" s="5" t="n">
         <v>0</v>
@@ -18343,7 +18343,7 @@
         <v>0</v>
       </c>
       <c r="K195" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L195" s="5" t="n">
         <v>0</v>
@@ -18366,12 +18366,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Sevenoaks</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H196" s="3" t="n">
         <v>0</v>
@@ -18397,7 +18397,7 @@
         <v>0</v>
       </c>
       <c r="L196" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M196" s="3" t="n">
         <v>0</v>
@@ -18417,12 +18417,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Ringwood</t>
+          <t>Sherborne</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -18433,10 +18433,10 @@
       </c>
       <c r="F197" s="4" t="inlineStr"/>
       <c r="G197" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H197" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I197" s="5" t="n">
         <v>0</v>
@@ -18468,12 +18468,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Smethwick</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -18519,12 +18519,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Sevenoaks</t>
+          <t>South Shields</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -18535,10 +18535,10 @@
       </c>
       <c r="F199" s="4" t="inlineStr"/>
       <c r="G199" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H199" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I199" s="5" t="n">
         <v>0</v>
@@ -18570,12 +18570,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Sherborne</t>
+          <t>Spennymoor</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -18621,12 +18621,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Smethwick</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -18637,13 +18637,13 @@
       </c>
       <c r="F201" s="4" t="inlineStr"/>
       <c r="G201" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H201" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J201" s="5" t="n">
         <v>0</v>
@@ -18672,12 +18672,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>South Shields</t>
+          <t>Torquay</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -18688,10 +18688,10 @@
       </c>
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I202" s="3" t="n">
         <v>0</v>
@@ -18723,12 +18723,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Spennymoor</t>
+          <t>Trowbridge</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -18774,12 +18774,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ulverston</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -18793,10 +18793,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J204" s="3" t="n">
         <v>0</v>
@@ -18825,12 +18825,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Uttoxeter</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -18876,12 +18876,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Trowbridge</t>
+          <t>Ventnor</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -18892,10 +18892,10 @@
       </c>
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I206" s="3" t="n">
         <v>0</v>
@@ -18927,12 +18927,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Ulverston</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -18943,10 +18943,10 @@
       </c>
       <c r="F207" s="4" t="inlineStr"/>
       <c r="G207" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H207" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I207" s="5" t="n">
         <v>0</v>
@@ -18978,12 +18978,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Uttoxeter</t>
+          <t>Waltham Abbey</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -19029,12 +19029,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Ventnor</t>
+          <t>Walton-on-thames</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -19045,10 +19045,10 @@
       </c>
       <c r="F209" s="4" t="inlineStr"/>
       <c r="G209" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H209" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I209" s="5" t="n">
         <v>0</v>
@@ -19080,12 +19080,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -19131,12 +19131,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Waltham Abbey</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -19182,12 +19182,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Wilmslow</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -19233,12 +19233,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
@@ -19284,12 +19284,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Winsford</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -19335,12 +19335,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Wilmslow</t>
+          <t>Worthing</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
@@ -19386,12 +19386,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Wymondham</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -19437,12 +19437,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Winsford</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
@@ -19480,161 +19480,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>Worthing</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>Sussex</t>
-        </is>
-      </c>
-      <c r="D218" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F218" s="2" t="inlineStr"/>
-      <c r="G218" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N218" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O218" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B219" s="4" t="inlineStr">
-        <is>
-          <t>Wymondham</t>
-        </is>
-      </c>
-      <c r="C219" s="4" t="inlineStr">
-        <is>
-          <t>Norfolk</t>
-        </is>
-      </c>
-      <c r="D219" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E219" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F219" s="4" t="inlineStr"/>
-      <c r="G219" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H219" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I219" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J219" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K219" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L219" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M219" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N219" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O219" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>Yeovil</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>Somerset</t>
-        </is>
-      </c>
-      <c r="D220" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E220" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F220" s="2" t="inlineStr"/>
-      <c r="G220" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H220" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I220" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J220" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K220" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L220" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M220" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N220" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O220" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O220"/>
+  <autoFilter ref="A1:O217"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19776,7 +19623,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
@@ -19835,7 +19682,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
@@ -20040,7 +19887,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="4" t="inlineStr">
@@ -20309,7 +20156,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>6</v>
@@ -20425,7 +20272,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>2</v>
@@ -20986,7 +20833,7 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>
@@ -21250,7 +21097,7 @@
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.7 / 2/14</t>
+          <t>5 / 3.9 / 2/14</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
@@ -21260,7 +21107,7 @@
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.2 / 0/14</t>
+          <t>4 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -21270,7 +21117,7 @@
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21283,25 +21130,25 @@
       <c r="B3" s="14" t="inlineStr"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>4 / 1.6 / 0/14</t>
+          <t>4 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr"/>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>12 / 1.6 / 1/14</t>
+          <t>13 / 2.4 / 2/14</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr"/>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21314,25 +21161,25 @@
       <c r="B4" s="13" t="inlineStr"/>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.3 / 0/14</t>
+          <t>2 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>7 / 6.1 / 9/14</t>
+          <t>7 / 6.5 / 10/14</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.3 / 0/14</t>
+          <t>2 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.7 / 0/14</t>
+          <t>0 / 2.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21350,23 +21197,23 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/14</t>
+          <t>2 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>5 / 2.6 / 0/14</t>
+          <t>5 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.1 / 1/14</t>
+          <t>8 / 2.5 / 2/14</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>3 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr"/>
@@ -21380,28 +21227,28 @@
       <c r="B6" s="13" t="inlineStr"/>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>2 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>3 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>15 / 2.9 / 1/14</t>
+          <t>15 / 3.8 / 2/14</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/14</t>
+          <t>3 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -21424,22 +21271,22 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.8 / 0/14</t>
+          <t>4 / 3.9 / 0/14</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.5 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>8 / 0.9 / 1/14</t>
+          <t>8 / 1.4 / 2/14</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
@@ -21462,22 +21309,22 @@
       <c r="B8" s="13" t="inlineStr"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/14</t>
+          <t>3 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.9 / 0/14</t>
+          <t>4 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
@@ -21511,23 +21358,23 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.4 / 0/14</t>
+          <t>1 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>7 / 1.6 / 1/14</t>
+          <t>7 / 2.0 / 2/14</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21582,12 +21429,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.8 / 0/14</t>
+          <t>0 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.3 / 0/14</t>
+          <t>3 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -21629,7 +21476,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
@@ -21645,7 +21492,7 @@
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
@@ -21655,7 +21502,7 @@
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
@@ -21677,7 +21524,7 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -21725,7 +21572,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>0 / 3.4 / 0/14</t>
+          <t>0 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -21745,12 +21592,12 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21763,24 +21610,24 @@
       <c r="B15" s="14" t="inlineStr"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/14</t>
+          <t>3 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr"/>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/14</t>
+          <t>3 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>0 / 3.9 / 3/14</t>
+          <t>0 / 3.5 / 3/14</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
@@ -21798,17 +21645,17 @@
       <c r="B16" s="13" t="inlineStr"/>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.1 / 0/14</t>
+          <t>2 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 2/14</t>
+          <t>3 / 2.7 / 2/14</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
@@ -21818,17 +21665,17 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>13 / 1.1 / 1/14</t>
+          <t>13 / 2.0 / 2/14</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21841,12 +21688,12 @@
       <c r="B17" s="14" t="inlineStr"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.6 / 1/14</t>
+          <t>6 / 3.6 / 1/14</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
@@ -21854,12 +21701,12 @@
       <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.9 / 5/14</t>
+          <t>4 / 4.1 / 5/14</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.4 / 0/14</t>
+          <t>0 / 2.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21872,29 +21719,29 @@
       <c r="B18" s="13" t="inlineStr"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>2 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.1 / 3/14</t>
+          <t>2 / 3.0 / 3/14</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/14</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr"/>
       <c r="G18" s="13" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>2 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>0 / 3.1 / 0/14</t>
+          <t>0 / 2.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21907,13 +21754,13 @@
       <c r="B19" s="14" t="inlineStr"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>15 / 11.2 / 12/14</t>
+          <t>15 / 11.9 / 12/14</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr"/>
@@ -21921,7 +21768,7 @@
       <c r="H19" s="14" t="inlineStr"/>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21933,12 +21780,12 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.5 / 0/14</t>
+          <t>2 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
@@ -21958,17 +21805,17 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.1 / 0/14</t>
+          <t>4 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21997,17 +21844,17 @@
       <c r="F21" s="14" t="inlineStr"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.2 / 0/14</t>
+          <t>4 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22030,7 +21877,7 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/14</t>
+          <t>3 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
@@ -22040,17 +21887,17 @@
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.2 / 0/14</t>
+          <t>2 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22065,17 +21912,17 @@
       <c r="D23" s="14" t="inlineStr"/>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>4 / 1.9 / 0/14</t>
+          <t>4 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>4 / 6.6 / 13/14</t>
+          <t>3 / 6.3 / 12/14</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>8 / 3.6 / 1/14</t>
+          <t>9 / 4.1 / 2/14</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -22093,7 +21940,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -22118,7 +21965,7 @@
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.1 / 0/14</t>
+          <t>2 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
@@ -22141,7 +21988,7 @@
       <c r="B25" s="14" t="inlineStr"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr"/>
@@ -22153,7 +22000,7 @@
       <c r="F25" s="14" t="inlineStr"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>9 / 2.8 / 1/14</t>
+          <t>10 / 3.4 / 2/14</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
@@ -22163,7 +22010,7 @@
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22178,13 +22025,13 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>13 / 10.4 / 12/14</t>
+          <t>14 / 11.0 / 13/14</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>18 / 1.4 / 1/14</t>
+          <t>18 / 2.6 / 2/14</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
@@ -22194,7 +22041,7 @@
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22226,7 +22073,7 @@
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>0 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -22253,7 +22100,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.7 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -22263,7 +22110,7 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -22273,12 +22120,12 @@
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.2 / 0/14</t>
+          <t>3 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -22300,7 +22147,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.1 / 0/14</t>
+          <t>5 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -22320,12 +22167,12 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.8 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>6 / 1.1 / 1/14</t>
+          <t>7 / 1.6 / 2/14</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
@@ -22347,12 +22194,12 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.2 / 0/14</t>
+          <t>2 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
@@ -22362,7 +22209,7 @@
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -22372,7 +22219,7 @@
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -22419,7 +22266,7 @@
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>2 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
@@ -22447,32 +22294,32 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.3 / 0/14</t>
+          <t>3 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>3 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>6 / 2.9 / 1/14</t>
+          <t>5 / 3.0 / 1/14</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22485,22 +22332,22 @@
       <c r="B33" s="14" t="inlineStr"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/14</t>
+          <t>1 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.1 / 0/14</t>
+          <t>3 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -22510,12 +22357,12 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22543,17 +22390,17 @@
       <c r="B35" s="14" t="inlineStr"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>7 / 5.2 / 8/14</t>
+          <t>8 / 5.7 / 9/14</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr"/>
@@ -22581,7 +22428,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -22596,7 +22443,7 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -22628,7 +22475,7 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>4 / 1.9 / 0/14</t>
+          <t>4 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -22653,7 +22500,7 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
@@ -22685,7 +22532,7 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -22710,7 +22557,7 @@
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22723,7 +22570,7 @@
       <c r="B39" s="14" t="inlineStr"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
@@ -22734,22 +22581,22 @@
       <c r="E39" s="14" t="inlineStr"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>6 / 4.1 / 6/14</t>
+          <t>6 / 4.5 / 7/14</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>7 / 1.6 / 1/14</t>
+          <t>11 / 2.3 / 2/14</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22611,7 @@
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.8 / 0/14</t>
+          <t>2 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr"/>
@@ -22791,7 +22638,7 @@
       <c r="D41" s="14" t="inlineStr"/>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>2 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr">
@@ -22823,7 +22670,7 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.7 / 0/14</t>
+          <t>2 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -22843,7 +22690,7 @@
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>0 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
@@ -22858,7 +22705,7 @@
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22870,7 +22717,7 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.7 / 0/14</t>
+          <t>0 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
@@ -22885,7 +22732,7 @@
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
@@ -22900,7 +22747,7 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
@@ -22918,12 +22765,12 @@
       <c r="B44" s="13" t="inlineStr"/>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>3 / 5.1 / 4/14</t>
+          <t>3 / 4.6 / 3/14</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -22933,22 +22780,22 @@
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.4 / 0/14</t>
+          <t>3 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>7 / 3.2 / 1/14</t>
+          <t>7 / 3.6 / 2/14</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.5 / 0/14</t>
+          <t>4 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22971,7 +22818,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>0 / 15.1 / 13/14</t>
+          <t>2 / 14.4 / 12/14</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr"/>
@@ -22979,7 +22826,7 @@
       <c r="H45" s="14" t="inlineStr"/>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22991,7 +22838,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>2 / 21.2 / 13/14</t>
+          <t>2 / 19.8 / 12/14</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -23001,7 +22848,7 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -23026,7 +22873,7 @@
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>0 / 1.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23039,33 +22886,33 @@
       <c r="B47" s="14" t="inlineStr"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.6 / 0/14</t>
+          <t>0 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>8 / 5.0 / 8/14</t>
+          <t>8 / 5.4 / 9/14</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.6 / 0/14</t>
+          <t>2 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>8 / 0.9 / 1/14</t>
+          <t>9 / 1.4 / 2/14</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr"/>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23079,28 +22926,28 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.8 / 0/14</t>
+          <t>3 / 3.7 / 0/14</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.0 / 0/14</t>
+          <t>5 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr"/>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>6 / 1.5 / 1/14</t>
+          <t>7 / 1.9 / 2/14</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23159,7 +23006,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>0 / 3.6 / 0/14</t>
+          <t>0 / 3.5 / 0/14</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -23169,7 +23016,7 @@
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -23212,32 +23059,32 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.3 / 0/14</t>
+          <t>1 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.2 / 0/14</t>
+          <t>4 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>3 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23296,7 +23143,7 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>8 / 3.3 / 4/14</t>
+          <t>8 / 3.7 / 5/14</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -23359,7 +23206,7 @@
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
@@ -23369,7 +23216,7 @@
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
@@ -23386,7 +23233,7 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
@@ -23440,7 +23287,7 @@
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
@@ -23450,7 +23297,7 @@
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>2 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -23529,7 +23376,7 @@
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -23582,13 +23429,13 @@
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr"/>
       <c r="H59" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.8 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
@@ -23606,12 +23453,12 @@
       <c r="B60" s="13" t="inlineStr"/>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.8 / 0/14</t>
+          <t>4 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.7 / 0/14</t>
+          <t>2 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -23621,12 +23468,12 @@
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.7 / 0/14</t>
+          <t>4 / 3.7 / 0/14</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>3 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -23636,7 +23483,7 @@
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23654,27 +23501,27 @@
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>0 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.8 / 0/14</t>
+          <t>3 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>5 / 4.8 / 6/14</t>
+          <t>5 / 4.9 / 6/14</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.0 / 0/14</t>
+          <t>5 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr"/>
@@ -23693,7 +23540,7 @@
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.9 / 0/14</t>
+          <t>3 / 3.0 / 0/14</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
@@ -23704,17 +23551,17 @@
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>9 / 2.8 / 1/14</t>
+          <t>9 / 3.4 / 2/14</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23729,13 +23576,13 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>12 / 8.6 / 12/14</t>
+          <t>12 / 9.1 / 13/14</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>13 / 5.6 / 7/14</t>
+          <t>12 / 6.2 / 8/14</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr">
@@ -23756,23 +23603,23 @@
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>5 / 4.1 / 0/14</t>
+          <t>5 / 4.2 / 0/14</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>5 / 5.0 / 5/14</t>
+          <t>5 / 5.1 / 5/14</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>18 / 5.0 / 3/14</t>
+          <t>20 / 6.3 / 4/14</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23831,12 +23678,12 @@
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.4 / 0/14</t>
+          <t>0 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>6 / 1.0 / 1/14</t>
+          <t>6 / 1.4 / 2/14</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
@@ -23861,7 +23708,7 @@
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
@@ -23884,22 +23731,22 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.3 / 0/14</t>
+          <t>0 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.4 / 0/14</t>
+          <t>1 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>6 / 0.4 / 1/14</t>
+          <t>6 / 0.9 / 2/14</t>
         </is>
       </c>
       <c r="H67" s="14" t="inlineStr">
@@ -23921,7 +23768,7 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>3 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -23936,22 +23783,22 @@
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
+          <t>1 / 0.8 / 0/14</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>2 / 0.2 / 0/14</t>
+        </is>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
           <t>1 / 0.7 / 0/14</t>
-        </is>
-      </c>
-      <c r="G68" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.1 / 0/14</t>
-        </is>
-      </c>
-      <c r="H68" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I68" s="13" t="inlineStr">
@@ -23968,7 +23815,7 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>10 / 3.8 / 3/14</t>
+          <t>11 / 4.4 / 4/14</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
@@ -23978,12 +23825,12 @@
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
@@ -23993,7 +23840,7 @@
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.1 / 0/14</t>
+          <t>2 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="H69" s="14" t="inlineStr">
@@ -24016,17 +23863,17 @@
       <c r="B70" s="13" t="inlineStr"/>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>3 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.1 / 0/14</t>
+          <t>0 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
@@ -24059,29 +23906,29 @@
       <c r="B71" s="14" t="inlineStr"/>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>2 / 4.7 / 4/14</t>
+          <t>2 / 4.1 / 3/14</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>10 / 7.1 / 9/14</t>
+          <t>9 / 7.5 / 10/14</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>7 / 3.3 / 1/14</t>
+          <t>6 / 3.5 / 2/14</t>
         </is>
       </c>
       <c r="H71" s="14" t="inlineStr"/>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24099,32 +23946,32 @@
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.2 / 0/14</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>2 / 3.6 / 0/14</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
-      <c r="E72" s="13" t="inlineStr">
-        <is>
-          <t>2 / 3.8 / 0/14</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.4 / 0/14</t>
-        </is>
-      </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>2 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24137,33 +23984,33 @@
       <c r="B73" s="14" t="inlineStr"/>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/14</t>
+          <t>3 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.9 / 4/14</t>
+          <t>1 / 2.6 / 3/14</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.1 / 0/14</t>
+          <t>4 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>2 / 5.1 / 5/14</t>
+          <t>2 / 5.0 / 5/14</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>9 / 3.7 / 1/14</t>
+          <t>9 / 4.1 / 2/14</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr"/>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24177,32 +24024,32 @@
       <c r="C74" s="13" t="inlineStr"/>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
+          <t>4 / 3.4 / 0/14</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="inlineStr">
+        <is>
           <t>4 / 3.3 / 0/14</t>
         </is>
       </c>
-      <c r="F74" s="13" t="inlineStr">
-        <is>
-          <t>4 / 3.1 / 0/14</t>
-        </is>
-      </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>10 / 2.5 / 1/14</t>
+          <t>10 / 3.2 / 2/14</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/14</t>
+          <t>2 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24220,27 +24067,27 @@
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.2 / 0/14</t>
+          <t>4 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.8 / 0/14</t>
+          <t>0 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>5 / 1.4 / 0/14</t>
+          <t>5 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="I75" s="14" t="inlineStr">
@@ -24268,12 +24115,12 @@
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.7 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
@@ -24288,7 +24135,7 @@
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24306,24 +24153,24 @@
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.4 / 0/14</t>
+          <t>2 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>5 / 5.4 / 7/14</t>
+          <t>5 / 5.7 / 7/14</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr"/>
       <c r="G77" s="14" t="inlineStr"/>
       <c r="H77" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.7 / 4/14</t>
+          <t>2 / 3.8 / 4/14</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>1 / 1.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24337,22 +24184,22 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.9 / 0/14</t>
+          <t>1 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.6 / 0/14</t>
+          <t>2 / 3.5 / 0/14</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>2 / 5.3 / 5/14</t>
+          <t>2 / 5.0 / 4/14</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.1 / 0/14</t>
+          <t>5 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
@@ -24377,19 +24224,19 @@
       <c r="D79" s="14" t="inlineStr"/>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>9 / 7.1 / 9/14</t>
+          <t>9 / 7.4 / 10/14</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>9 / 12.9 / 14/14</t>
+          <t>8 / 12.1 / 14/14</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>
       <c r="H79" s="14" t="inlineStr"/>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.1 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$194</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$216</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1031</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>904</v>
+        <v>927</v>
       </c>
     </row>
     <row r="4">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1151</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="6">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8">
@@ -648,7 +648,7 @@
         <v>2271</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
         <v>704</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
@@ -817,7 +817,7 @@
         <v>84</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -865,7 +865,7 @@
         <v>10000</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>923</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -880,7 +880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H194"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -954,7 +954,7 @@
       <c r="D2" s="11" t="inlineStr"/>
       <c r="E2" s="11" t="inlineStr"/>
       <c r="F2" s="12" t="n">
-        <v>1222</v>
+        <v>1236</v>
       </c>
       <c r="G2" s="11" t="inlineStr"/>
       <c r="H2" s="11" t="inlineStr">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="F3" s="12" t="n">
-        <v>1034</v>
+        <v>1046</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>1034</v>
+        <v>1046</v>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="F4" s="12" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G4" s="11" t="inlineStr"/>
       <c r="H4" s="11" t="inlineStr">
@@ -1531,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>1</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>1</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>1</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>1</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>1</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>1</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>1</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>1</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>1</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>1</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>1</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>1</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>1</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>1</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>1</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5740,24 +5740,24 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>North East</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Finance &amp; Accounts</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>/job-search/somerset/service-administrator-jobs</t>
+          <t>/job-search/north-east/finance-accounts-jobs</t>
         </is>
       </c>
       <c r="F131" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
@@ -5778,24 +5778,24 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/customer-sales-jobs</t>
+          <t>/job-search/somerset/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -5826,14 +5826,14 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>/job-search/west-yorkshire/customer-sales-jobs</t>
+          <t>/job-search/london/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F133" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
@@ -5854,24 +5854,24 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>/job-search/leicestershire/service-administrator-jobs</t>
+          <t>/job-search/west-yorkshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F134" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5892,24 +5892,24 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>/job-search/warrington-halton/service-administrator-jobs</t>
+          <t>/job-search/manchester-salford/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F135" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -5940,14 +5940,14 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>/job-search/suffolk/service-administrator-jobs</t>
+          <t>/job-search/leicestershire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F136" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -5978,14 +5978,14 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>/job-search/derbyshire/service-administrator-jobs</t>
+          <t>/job-search/warrington-halton/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F137" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -6016,14 +6016,14 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-east/service-administrator-jobs</t>
+          <t>/job-search/suffolk/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -6054,14 +6054,14 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>/job-search/lincolnshire/service-administrator-jobs</t>
+          <t>/job-search/derbyshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F139" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -6092,14 +6092,14 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>/job-search/merseyside-liverpool/service-administrator-jobs</t>
+          <t>/job-search/cheshire-east/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -6130,14 +6130,14 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>/job-search/shropshire/service-administrator-jobs</t>
+          <t>/job-search/lincolnshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F141" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -6168,14 +6168,14 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>/job-search/wigan-bolton/service-administrator-jobs</t>
+          <t>/job-search/merseyside-liverpool/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>/job-search/black-country/service-administrator-jobs</t>
+          <t>/job-search/shropshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F143" s="5" t="n">
@@ -6234,24 +6234,24 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Legal Assistant &amp; Paralegal</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/paralegal-jobs</t>
+          <t>/job-search/wigan-bolton/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6272,24 +6272,24 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Legal Assistant &amp; Paralegal</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>/job-search/suffolk/paralegal-jobs</t>
+          <t>/job-search/black-country/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F145" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -6320,14 +6320,14 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>/job-search/essex/paralegal-jobs</t>
+          <t>/job-search/london/paralegal-jobs</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -6358,14 +6358,14 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>/job-search/norfolk/paralegal-jobs</t>
+          <t>/job-search/suffolk/paralegal-jobs</t>
         </is>
       </c>
       <c r="F147" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -6386,24 +6386,24 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Legal Assistant &amp; Paralegal</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/marketing-jobs</t>
+          <t>/job-search/essex/paralegal-jobs</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6424,24 +6424,24 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Legal Assistant &amp; Paralegal</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>/job-search/surrey/marketing-jobs</t>
+          <t>/job-search/norfolk/paralegal-jobs</t>
         </is>
       </c>
       <c r="F149" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -6472,14 +6472,14 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/marketing-jobs</t>
+          <t>/job-search/london/marketing-jobs</t>
         </is>
       </c>
       <c r="F150" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -6510,14 +6510,14 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>/job-search/birmingham-solihull/marketing-jobs</t>
+          <t>/job-search/surrey/marketing-jobs</t>
         </is>
       </c>
       <c r="F151" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -6538,24 +6538,24 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/hr-recruitment-jobs</t>
+          <t>/job-search/manchester-salford/marketing-jobs</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6576,24 +6576,24 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/hr-recruitment-jobs</t>
+          <t>/job-search/birmingham-solihull/marketing-jobs</t>
         </is>
       </c>
       <c r="F153" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>/job-search/nottinghamshire/hr-recruitment-jobs</t>
+          <t>/job-search/berkshire/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F154" s="3" t="n">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -6662,14 +6662,14 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>/job-search/birmingham-solihull/hr-recruitment-jobs</t>
+          <t>/job-search/manchester-salford/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F155" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -6700,14 +6700,14 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>/job-search/sussex/hr-recruitment-jobs</t>
+          <t>/job-search/nottinghamshire/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6728,24 +6728,24 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-west/service-administrator-jobs</t>
+          <t>/job-search/birmingham-solihull/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F157" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -6766,24 +6766,24 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>/job-search/edinburgh-lothians/service-administrator-jobs</t>
+          <t>/job-search/sussex/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -6814,14 +6814,14 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>/job-search/worcestershire/service-administrator-jobs</t>
+          <t>/job-search/cheshire-west/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F159" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -6842,17 +6842,17 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/marketing-jobs</t>
+          <t>/job-search/edinburgh-lothians/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F160" s="3" t="n">
@@ -6880,24 +6880,24 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>/job-search/kent/support-worker</t>
+          <t>/job-search/worcestershire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F161" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -6918,24 +6918,24 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>North East</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>/job-search/north-east/customer-sales-jobs</t>
+          <t>/job-search/berkshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F162" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -6966,14 +6966,14 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>/job-search/oxfordshire/support-worker</t>
+          <t>/job-search/kent/support-worker</t>
         </is>
       </c>
       <c r="F163" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -6994,24 +6994,24 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>North East</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>/job-search/north-yorkshire/finance-accounts-jobs</t>
+          <t>/job-search/north-east/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F164" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7032,24 +7032,24 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>/job-search/bedfordshire/service-administrator-jobs</t>
+          <t>/job-search/oxfordshire/support-worker</t>
         </is>
       </c>
       <c r="F165" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -7070,24 +7070,24 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Finance &amp; Accounts</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/customer-sales-jobs</t>
+          <t>/job-search/north-yorkshire/finance-accounts-jobs</t>
         </is>
       </c>
       <c r="F166" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7108,24 +7108,24 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>/job-search/buckinghamshire/marketing-jobs</t>
+          <t>/job-search/bedfordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F167" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -7146,24 +7146,24 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cardiff-vale/service-administrator-jobs</t>
+          <t>/job-search/bristol-bath/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F168" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7184,24 +7184,24 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/customer-sales-jobs</t>
+          <t>/job-search/buckinghamshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F169" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -7222,24 +7222,24 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/customer-sales-jobs</t>
+          <t>/job-search/cardiff-vale/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F170" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>/job-search/kent/customer-sales-jobs</t>
+          <t>/job-search/berkshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F171" s="5" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -7308,14 +7308,14 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>/job-search/glasgow/customer-sales-jobs</t>
+          <t>/job-search/hertfordshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F172" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>/job-search/surrey/customer-sales-jobs</t>
+          <t>/job-search/kent/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F173" s="5" t="n">
@@ -7374,24 +7374,24 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/marketing-jobs</t>
+          <t>/job-search/glasgow/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F174" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7412,24 +7412,24 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>/job-search/gloucestershire/marketing-jobs</t>
+          <t>/job-search/surrey/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F175" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -7460,14 +7460,14 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/marketing-jobs</t>
+          <t>/job-search/bristol-bath/marketing-jobs</t>
         </is>
       </c>
       <c r="F176" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -7498,14 +7498,14 @@
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>/job-search/kent/marketing-jobs</t>
+          <t>/job-search/gloucestershire/marketing-jobs</t>
         </is>
       </c>
       <c r="F177" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -7536,14 +7536,14 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>/job-search/oxfordshire/marketing-jobs</t>
+          <t>/job-search/hertfordshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F178" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7564,24 +7564,24 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>/job-search/tayside/service-administrator-jobs</t>
+          <t>/job-search/kent/marketing-jobs</t>
         </is>
       </c>
       <c r="F179" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -7602,24 +7602,24 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>/job-search/south-wales-valleys/service-administrator-jobs</t>
+          <t>/job-search/oxfordshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F180" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7640,24 +7640,24 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>/job-search/cambridgeshire/marketing-jobs</t>
+          <t>/job-search/tayside/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F181" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -7678,24 +7678,24 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-west/marketing-jobs</t>
+          <t>/job-search/south-wales-valleys/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F182" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -7726,14 +7726,14 @@
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>/job-search/essex/marketing-jobs</t>
+          <t>/job-search/cambridgeshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F183" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -7764,14 +7764,14 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>/job-search/merseyside-liverpool/marketing-jobs</t>
+          <t>/job-search/cheshire-west/marketing-jobs</t>
         </is>
       </c>
       <c r="F184" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>North East</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -7802,14 +7802,14 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>/job-search/north-east/marketing-jobs</t>
+          <t>/job-search/essex/marketing-jobs</t>
         </is>
       </c>
       <c r="F185" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -7830,17 +7830,17 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>/job-search/devon/customer-sales-jobs</t>
+          <t>/job-search/merseyside-liverpool/marketing-jobs</t>
         </is>
       </c>
       <c r="F186" s="3" t="n">
@@ -7868,24 +7868,24 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North East</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>/job-search/hampshire/customer-sales-jobs</t>
+          <t>/job-search/north-east/marketing-jobs</t>
         </is>
       </c>
       <c r="F187" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G187" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -7916,14 +7916,14 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>/job-search/north-scotland/customer-sales-jobs</t>
+          <t>/job-search/devon/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F188" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -7944,24 +7944,24 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>/job-search/greater-manchester-south/marketing-jobs</t>
+          <t>/job-search/hampshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F189" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -7982,17 +7982,17 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>/job-search/northern-ireland-east/marketing-jobs</t>
+          <t>/job-search/north-scotland/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F190" s="3" t="n">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -8030,14 +8030,14 @@
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>/job-search/north-yorkshire/marketing-jobs</t>
+          <t>/job-search/greater-manchester-south/marketing-jobs</t>
         </is>
       </c>
       <c r="F191" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G191" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -8058,24 +8058,24 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>/job-search/essex/finance-accounts-jobs</t>
+          <t>/job-search/northern-ireland-east/marketing-jobs</t>
         </is>
       </c>
       <c r="F192" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8096,24 +8096,24 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/finance-accounts-jobs</t>
+          <t>/job-search/north-yorkshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F193" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G193" s="5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -8134,33 +8134,109 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
+          <t>Essex</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Finance &amp; Accounts</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/essex/finance-accounts-jobs</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>Finance &amp; Accounts</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t>/job-search/manchester-salford/finance-accounts-jobs</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H195" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
           <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>HR &amp; Recruitment</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>/job-search/coventry-warwickshire/hr-recruitment-jobs</t>
         </is>
       </c>
-      <c r="F194" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G194" s="3" t="n">
+      <c r="F196" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H194"/>
+  <autoFilter ref="A1:H196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8171,7 +8247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O217"/>
+  <dimension ref="A1:O216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8327,12 +8403,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Pontypridd</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -8378,12 +8454,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Runcorn</t>
+          <t>Pontypridd</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
@@ -8429,7 +8505,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Widnes</t>
+          <t>Runcorn</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -8480,16 +8556,16 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -8502,7 +8578,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>0</v>
@@ -8531,23 +8607,23 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Forfar</t>
+          <t>Widnes</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0</v>
@@ -8582,12 +8658,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Frodsham</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -8633,12 +8709,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Knutsford</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -8684,12 +8760,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Leigh</t>
+          <t>Frodsham</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -8735,12 +8811,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Lymm</t>
+          <t>Knutsford</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -8786,12 +8862,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Merthyr Tydfil</t>
+          <t>Leigh</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -8837,12 +8913,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Newport-on-tay</t>
+          <t>Lymm</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -8888,12 +8964,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Perth</t>
+          <t>Merthyr Tydfil</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -8934,32 +9010,28 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Newport-on-tay</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>/manchester/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0</v>
@@ -8971,10 +9043,10 @@
         <v>0</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>0</v>
@@ -8994,33 +9066,33 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Bristol</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>/bristol/service-administrator-jobs</t>
+          <t>/manchester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>0</v>
@@ -9029,7 +9101,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>0</v>
@@ -9049,39 +9121,39 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Bristol</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>/birmingham/service-administrator-jobs</t>
+          <t>/bristol/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>0</v>
@@ -9104,12 +9176,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Warrington</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -9120,11 +9192,11 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>/warrington/service-administrator-jobs</t>
+          <t>/birmingham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0</v>
@@ -9136,7 +9208,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>0</v>
@@ -9159,27 +9231,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Warrington</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>/cardiff/service-administrator-jobs</t>
+          <t>/warrington/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
@@ -9214,23 +9286,23 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>/edinburgh/service-administrator-jobs</t>
+          <t>/leeds/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
@@ -9249,7 +9321,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>0</v>
@@ -9269,12 +9341,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -9285,11 +9357,11 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>/leeds/service-administrator-jobs</t>
+          <t>/cardiff/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0</v>
@@ -9304,7 +9376,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>0</v>
@@ -9333,7 +9405,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>1</v>
@@ -9344,7 +9416,7 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
@@ -9379,33 +9451,33 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Exeter</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>/exeter/service-administrator-jobs</t>
+          <t>/edinburgh/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" s="5" t="n">
         <v>0</v>
@@ -9414,7 +9486,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>0</v>
@@ -9434,33 +9506,33 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Bolton</t>
+          <t>Exeter</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>/bolton/jobs</t>
+          <t>/exeter/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>0</v>
@@ -9469,7 +9541,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>0</v>
@@ -9489,33 +9561,33 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>/cambridge/service-administrator-jobs</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="I25" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="5" t="n">
         <v>0</v>
@@ -9544,12 +9616,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Bolton</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -9560,11 +9632,11 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>/coventry/service-administrator-jobs</t>
+          <t>/bolton/jobs</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0</v>
@@ -9582,7 +9654,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>0</v>
@@ -9599,12 +9671,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -9615,7 +9687,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>/glasgow/service-administrator-jobs</t>
+          <t>/cambridge/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
@@ -9654,12 +9726,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -9670,29 +9742,29 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>/liverpool/service-administrator-jobs</t>
+          <t>/coventry/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3" t="n">
         <v>4</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0</v>
@@ -9709,12 +9781,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -9725,11 +9797,11 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>/nottingham/jobs</t>
+          <t>/norwich/jobs</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>0</v>
@@ -9738,7 +9810,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K29" s="5" t="n">
         <v>0</v>
@@ -9747,7 +9819,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="5" t="n">
         <v>0</v>
@@ -9764,12 +9836,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Peterborough</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
@@ -9780,11 +9852,11 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/peterborough/service-administrator-jobs</t>
+          <t>/nottingham/jobs</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0</v>
@@ -9802,7 +9874,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>0</v>
@@ -9819,39 +9891,39 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>/oxford/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="H31" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="L31" s="5" t="n">
         <v>0</v>
@@ -9929,12 +10001,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -9945,11 +10017,11 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>/norwich/jobs</t>
+          <t>/glasgow/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H33" s="5" t="n">
         <v>0</v>
@@ -9958,7 +10030,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K33" s="5" t="n">
         <v>0</v>
@@ -9984,12 +10056,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Peterborough</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
@@ -10000,14 +10072,14 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>/oxford/service-administrator-jobs</t>
+          <t>/peterborough/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0</v>
@@ -10016,7 +10088,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0</v>
@@ -10039,12 +10111,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
@@ -10055,17 +10127,17 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>/leicester/service-administrator-jobs</t>
+          <t>/bradford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="5" t="n">
         <v>0</v>
@@ -10074,7 +10146,7 @@
         <v>0</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="5" t="n">
         <v>0</v>
@@ -10094,23 +10166,23 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Belfast</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>/belfast/service-administrator-jobs</t>
+          <t>/liverpool/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
@@ -10126,7 +10198,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0</v>
@@ -10149,12 +10221,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Gloucester</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -10165,11 +10237,11 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>/bournemouth/service-administrator-jobs</t>
+          <t>/gloucester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37" s="5" t="n">
         <v>0</v>
@@ -10184,7 +10256,7 @@
         <v>0</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" s="5" t="n">
         <v>0</v>
@@ -10204,27 +10276,27 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>/chester/jobs</t>
+          <t>/barnsley/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0</v>
@@ -10259,23 +10331,23 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Gloucester</t>
+          <t>Belfast</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>/gloucester/service-administrator-jobs</t>
+          <t>/belfast/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
@@ -10291,10 +10363,10 @@
         <v>0</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" s="5" t="n">
         <v>0</v>
@@ -10314,12 +10386,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
@@ -10330,7 +10402,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>/barnsley/service-administrator-jobs</t>
+          <t>/bournemouth/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
@@ -10369,12 +10441,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Bradford</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
@@ -10385,17 +10457,17 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>/bradford/service-administrator-jobs</t>
+          <t>/chester/jobs</t>
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="5" t="n">
         <v>0</v>
@@ -10404,7 +10476,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="5" t="n">
         <v>0</v>
@@ -10534,12 +10606,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Hemel Hempstead</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -10550,23 +10622,23 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>/hemel-hempstead/service-administrator-jobs</t>
+          <t>/hull/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>0</v>
@@ -10589,12 +10661,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Huddersfield</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
@@ -10605,11 +10677,11 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>/huddersfield/service-administrator-jobs</t>
+          <t>/leicester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="5" t="n">
         <v>0</v>
@@ -10624,7 +10696,7 @@
         <v>0</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="5" t="n">
         <v>0</v>
@@ -10644,12 +10716,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Milton Keynes</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
@@ -10660,11 +10732,11 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>/hull/service-administrator-jobs</t>
+          <t>/milton-keynes/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0</v>
@@ -10676,7 +10748,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>0</v>
@@ -10699,12 +10771,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Milton Keynes</t>
+          <t>Northampton</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
@@ -10715,11 +10787,11 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>/milton-keynes/service-administrator-jobs</t>
+          <t>/northampton/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" s="5" t="n">
         <v>0</v>
@@ -10731,7 +10803,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="5" t="n">
         <v>0</v>
@@ -10754,12 +10826,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Northampton</t>
+          <t>Salford</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
@@ -10770,11 +10842,11 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>/northampton/service-administrator-jobs</t>
+          <t>/salford/jobs</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -10789,7 +10861,7 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
@@ -10809,12 +10881,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Salford</t>
+          <t>Sheffield</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
@@ -10825,14 +10897,14 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>/salford/jobs</t>
+          <t>/sheffield/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G49" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="5" t="n">
         <v>0</v>
@@ -10844,7 +10916,7 @@
         <v>0</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="5" t="n">
         <v>0</v>
@@ -10864,12 +10936,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Sheffield</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
@@ -10880,14 +10952,14 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>/sheffield/service-administrator-jobs</t>
+          <t>/sunderland/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>0</v>
@@ -10919,12 +10991,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Warwick</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
@@ -10935,11 +11007,11 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>/sunderland/service-administrator-jobs</t>
+          <t>/warwick/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51" s="5" t="n">
         <v>0</v>
@@ -10957,7 +11029,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="5" t="n">
         <v>0</v>
@@ -10974,27 +11046,27 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Wakefield</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>/wakefield/jobs</t>
+          <t>/altrincham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>0</v>
@@ -11029,23 +11101,23 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Warwick</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>/warwick/service-administrator-jobs</t>
+          <t>/bedford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G53" s="5" t="n">
@@ -11067,7 +11139,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" s="5" t="n">
         <v>0</v>
@@ -11084,12 +11156,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Brighton &amp; Hove</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
@@ -11100,7 +11172,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>/altrincham/service-administrator-jobs</t>
+          <t>/brighton-hove/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
@@ -11139,12 +11211,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
@@ -11155,14 +11227,14 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>/bedford/service-administrator-jobs</t>
+          <t>/durham/jobs</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="5" t="n">
         <v>0</v>
@@ -11194,12 +11266,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove</t>
+          <t>Hemel Hempstead</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
@@ -11210,11 +11282,11 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>/brighton-hove/service-administrator-jobs</t>
+          <t>/hemel-hempstead/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0</v>
@@ -11226,7 +11298,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="3" t="n">
         <v>0</v>
@@ -11249,12 +11321,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Huddersfield</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
@@ -11265,14 +11337,14 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>/durham/jobs</t>
+          <t>/huddersfield/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="5" t="n">
         <v>0</v>
@@ -11284,7 +11356,7 @@
         <v>0</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="5" t="n">
         <v>0</v>
@@ -11304,12 +11376,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Maidstone</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
@@ -11320,14 +11392,14 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>/newcastle/service-administrator-jobs</t>
+          <t>/maidstone/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>0</v>
@@ -11524,12 +11596,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Wakefield</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
@@ -11540,7 +11612,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>/rotherham/service-administrator-jobs</t>
+          <t>/wakefield/jobs</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
@@ -11889,7 +11961,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Maidstone</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -11901,7 +11973,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>/maidstone/service-administrator-jobs</t>
+          <t>/newcastle/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
@@ -12093,7 +12165,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
@@ -12105,7 +12177,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>/scarborough/service-administrator-jobs</t>
+          <t>/rotherham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
@@ -12144,7 +12216,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
@@ -12156,7 +12228,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>/shrewsbury/service-administrator-jobs</t>
+          <t>/scarborough/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
@@ -12195,7 +12267,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Stoke-On-Trent</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -12207,7 +12279,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>/stoke-on-trent/service-administrator-jobs</t>
+          <t>/shrewsbury/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G75" s="5" t="n">
@@ -12246,7 +12318,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Wigston</t>
+          <t>Stoke-On-Trent</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
@@ -12258,7 +12330,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>/wigston/service-administrator-jobs</t>
+          <t>/stoke-on-trent/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
@@ -12297,7 +12369,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Worcester</t>
+          <t>Wigston</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
@@ -12309,7 +12381,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>/worcester/service-administrator-jobs</t>
+          <t>/wigston/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G77" s="5" t="n">
@@ -12343,28 +12415,28 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Barnet</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
+          <t>Worcester</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>/worcester/service-administrator-jobs</t>
+        </is>
+      </c>
       <c r="G78" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>0</v>
@@ -12373,7 +12445,7 @@
         <v>0</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" s="3" t="n">
         <v>0</v>
@@ -12399,7 +12471,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Southwark</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -12408,29 +12480,29 @@
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E79" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="5" t="n">
         <v>0</v>
@@ -12450,7 +12522,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Southwark</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -12459,7 +12531,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>0</v>
@@ -12481,7 +12553,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="3" t="n">
         <v>0</v>
@@ -12501,7 +12573,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Chessington</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -12517,10 +12589,10 @@
       </c>
       <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" s="5" t="n">
         <v>0</v>
@@ -12529,7 +12601,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81" s="5" t="n">
         <v>0</v>
@@ -12552,7 +12624,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Romford</t>
+          <t>Chessington</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12568,10 +12640,10 @@
       </c>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>0</v>
@@ -12580,7 +12652,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="3" t="n">
         <v>0</v>
@@ -12603,7 +12675,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Beckenham</t>
+          <t>Romford</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -12612,7 +12684,7 @@
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" s="5" t="n">
         <v>0</v>
@@ -12622,7 +12694,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" s="5" t="n">
         <v>0</v>
@@ -12654,7 +12726,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Bexley</t>
+          <t>Beckenham</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12807,7 +12879,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Bushey</t>
+          <t>Croydon</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -12823,7 +12895,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="5" t="n">
         <v>0</v>
@@ -12838,7 +12910,7 @@
         <v>0</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="5" t="n">
         <v>0</v>
@@ -12858,7 +12930,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Croydon</t>
+          <t>Enfield</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -12909,7 +12981,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Enfield</t>
+          <t>Harrow</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -12940,10 +13012,10 @@
         <v>0</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N89" s="5" t="n">
         <v>0</v>
@@ -12960,7 +13032,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Harrow</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -12976,7 +13048,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="3" t="n">
         <v>0</v>
@@ -12994,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>0</v>
@@ -13266,7 +13338,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Twickenham</t>
+          <t>Teddington</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13282,7 +13354,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" s="3" t="n">
         <v>0</v>
@@ -13297,7 +13369,7 @@
         <v>0</v>
       </c>
       <c r="L96" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="3" t="n">
         <v>0</v>
@@ -13479,7 +13551,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -13498,7 +13570,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>0</v>
@@ -13521,12 +13593,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Slough</t>
+          <t>Guildford</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -13537,10 +13609,10 @@
       </c>
       <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" s="5" t="n">
         <v>1</v>
@@ -13572,12 +13644,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Tunbridge Wells</t>
+          <t>Slough</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
@@ -13588,10 +13660,10 @@
       </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3" t="n">
         <v>1</v>
@@ -13600,7 +13672,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="3" t="n">
         <v>0</v>
@@ -13623,12 +13695,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Newbury</t>
+          <t>Dartford</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -13639,13 +13711,13 @@
       </c>
       <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H103" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="J103" s="5" t="n">
         <v>0</v>
@@ -13674,12 +13746,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Newbury</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
@@ -13690,25 +13762,25 @@
       </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H104" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K104" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M104" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N104" s="3" t="n">
         <v>0</v>
@@ -13725,12 +13797,12 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -13747,7 +13819,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" s="5" t="n">
         <v>0</v>
@@ -13759,7 +13831,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N105" s="5" t="n">
         <v>0</v>
@@ -13776,7 +13848,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Dartford</t>
+          <t>Tunbridge Wells</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -13785,17 +13857,17 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>1</v>
@@ -13804,7 +13876,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="3" t="n">
         <v>0</v>
@@ -13827,12 +13899,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Guildford</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -13843,13 +13915,13 @@
       </c>
       <c r="F107" s="4" t="inlineStr"/>
       <c r="G107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H107" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J107" s="5" t="n">
         <v>0</v>
@@ -13878,12 +13950,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Northwich</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
@@ -13894,7 +13966,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
         <v>0</v>
@@ -13906,7 +13978,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="3" t="n">
         <v>0</v>
@@ -13929,12 +14001,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Sittingbourne</t>
+          <t>Northwich</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -13948,7 +14020,7 @@
         <v>2</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" s="5" t="n">
         <v>0</v>
@@ -13957,7 +14029,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="5" t="n">
         <v>0</v>
@@ -13980,29 +14052,29 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Sittingbourne</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -14031,12 +14103,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Ballyclare</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -14047,13 +14119,13 @@
       </c>
       <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H111" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="J111" s="5" t="n">
         <v>0</v>
@@ -14082,12 +14154,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Berwick-upon-tweed</t>
+          <t>Ballyclare</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
@@ -14098,13 +14170,13 @@
       </c>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -14133,12 +14205,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Camberley</t>
+          <t>Barrow-in-furness</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14149,10 +14221,10 @@
       </c>
       <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H113" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="I113" s="5" t="n">
         <v>0</v>
@@ -14184,7 +14256,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Caterham</t>
+          <t>Camberley</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -14200,10 +14272,10 @@
       </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>0</v>
@@ -14235,12 +14307,12 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Cramlington</t>
+          <t>Caterham</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14251,13 +14323,13 @@
       </c>
       <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J115" s="5" t="n">
         <v>0</v>
@@ -14286,12 +14358,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Devizes</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
@@ -14302,16 +14374,16 @@
       </c>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="K116" s="3" t="n">
         <v>0</v>
@@ -14337,12 +14409,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Cramlington</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14353,13 +14425,13 @@
       </c>
       <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J117" s="5" t="n">
         <v>0</v>
@@ -14388,12 +14460,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Gosport</t>
+          <t>Devizes</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -14404,10 +14476,10 @@
       </c>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
@@ -14439,12 +14511,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -14458,10 +14530,10 @@
         <v>1</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119" s="5" t="n">
         <v>0</v>
@@ -14490,12 +14562,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Knaresborough</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
@@ -14506,7 +14578,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
@@ -14518,7 +14590,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L120" s="3" t="n">
         <v>0</v>
@@ -14541,12 +14613,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Leatherhead</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -14557,10 +14629,10 @@
       </c>
       <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121" s="5" t="n">
         <v>0</v>
@@ -14592,12 +14664,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Knaresborough</t>
+          <t>Maidenhead</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
@@ -14620,13 +14692,13 @@
         <v>0</v>
       </c>
       <c r="K122" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L122" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N122" s="3" t="n">
         <v>0</v>
@@ -14643,12 +14715,12 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Leatherhead</t>
+          <t>Maldon</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -14659,16 +14731,16 @@
       </c>
       <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I123" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K123" s="5" t="n">
         <v>0</v>
@@ -14694,12 +14766,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Maidenhead</t>
+          <t>Margate</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -14713,7 +14785,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>0</v>
@@ -14722,13 +14794,13 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -14745,12 +14817,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Maldon</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -14761,7 +14833,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H125" s="5" t="n">
         <v>0</v>
@@ -14770,7 +14842,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K125" s="5" t="n">
         <v>0</v>
@@ -14796,12 +14868,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Margate</t>
+          <t>Newton Abbot</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -14812,13 +14884,13 @@
       </c>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" s="3" t="n">
         <v>0</v>
@@ -14847,12 +14919,12 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -14898,12 +14970,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Newton Abbot</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -14914,22 +14986,22 @@
       </c>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H128" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J128" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K128" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" s="3" t="n">
         <v>0</v>
@@ -14949,12 +15021,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15000,12 +15072,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Tadley</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -15019,7 +15091,7 @@
         <v>0</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I130" s="3" t="n">
         <v>0</v>
@@ -15028,10 +15100,10 @@
         <v>0</v>
       </c>
       <c r="K130" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="3" t="n">
         <v>0</v>
@@ -15051,12 +15123,12 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15067,10 +15139,10 @@
       </c>
       <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="I131" s="5" t="n">
         <v>0</v>
@@ -15102,12 +15174,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Tadley</t>
+          <t>Verwood</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
@@ -15118,10 +15190,10 @@
       </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I132" s="3" t="n">
         <v>0</v>
@@ -15153,12 +15225,12 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15172,7 +15244,7 @@
         <v>0</v>
       </c>
       <c r="H133" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I133" s="5" t="n">
         <v>0</v>
@@ -15181,7 +15253,7 @@
         <v>0</v>
       </c>
       <c r="K133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="5" t="n">
         <v>0</v>
@@ -15204,12 +15276,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Verwood</t>
+          <t>Woodbridge</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -15255,16 +15327,16 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Welwyn Garden City</t>
+          <t>Alresford</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135" s="5" t="n">
         <v>0</v>
@@ -15283,7 +15355,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L135" s="5" t="n">
         <v>0</v>
@@ -15306,26 +15378,26 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Amersham</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136" s="3" t="n">
         <v>0</v>
@@ -15334,7 +15406,7 @@
         <v>0</v>
       </c>
       <c r="K136" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" s="3" t="n">
         <v>0</v>
@@ -15357,23 +15429,23 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Woodbridge</t>
+          <t>Atherstone</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H137" s="5" t="n">
         <v>0</v>
@@ -15391,7 +15463,7 @@
         <v>0</v>
       </c>
       <c r="M137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N137" s="5" t="n">
         <v>0</v>
@@ -15408,12 +15480,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Alresford</t>
+          <t>Basildon</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -15424,7 +15496,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H138" s="3" t="n">
         <v>0</v>
@@ -15439,7 +15511,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="3" t="n">
         <v>0</v>
@@ -15459,12 +15531,12 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Amersham</t>
+          <t>Beaminster</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15510,12 +15582,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Atherstone</t>
+          <t>Berwick-upon-tweed</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
@@ -15532,7 +15604,7 @@
         <v>0</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140" s="3" t="n">
         <v>0</v>
@@ -15544,7 +15616,7 @@
         <v>0</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N140" s="3" t="n">
         <v>0</v>
@@ -15561,12 +15633,12 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Barrow-in-furness</t>
+          <t>Bexhill-on-sea</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15577,10 +15649,10 @@
       </c>
       <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141" s="5" t="n">
         <v>0</v>
@@ -15612,12 +15684,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Beaminster</t>
+          <t>Billericay</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -15663,12 +15735,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Bexhill-on-sea</t>
+          <t>Birchington</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15679,10 +15751,10 @@
       </c>
       <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143" s="5" t="n">
         <v>0</v>
@@ -15714,12 +15786,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Billericay</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -15765,12 +15837,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Birchington</t>
+          <t>Bridgwater</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15781,10 +15853,10 @@
       </c>
       <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I145" s="5" t="n">
         <v>0</v>
@@ -15816,12 +15888,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Brighouse</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -15832,7 +15904,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" s="3" t="n">
         <v>0</v>
@@ -15847,7 +15919,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M146" s="3" t="n">
         <v>0</v>
@@ -15867,12 +15939,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Buckingham</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -15918,12 +15990,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Bridgwater</t>
+          <t>Bury St. Edmunds</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -15969,12 +16041,12 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Brighouse</t>
+          <t>Chatham</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -15985,7 +16057,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149" s="5" t="n">
         <v>0</v>
@@ -16000,7 +16072,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M149" s="5" t="n">
         <v>0</v>
@@ -16020,12 +16092,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Bury St. Edmunds</t>
+          <t>Chertsey</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
@@ -16036,10 +16108,10 @@
       </c>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>0</v>
@@ -16071,12 +16143,12 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>Chichester</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -16122,12 +16194,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Chatham</t>
+          <t>Christchurch</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -16173,12 +16245,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Chertsey</t>
+          <t>Cirencester</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -16192,7 +16264,7 @@
         <v>0</v>
       </c>
       <c r="H153" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I153" s="5" t="n">
         <v>0</v>
@@ -16204,7 +16276,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M153" s="5" t="n">
         <v>0</v>
@@ -16224,12 +16296,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Christchurch</t>
+          <t>Cleethorpes</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -16275,12 +16347,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Cirencester</t>
+          <t>Congleton</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -16291,7 +16363,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H155" s="5" t="n">
         <v>0</v>
@@ -16306,7 +16378,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" s="5" t="n">
         <v>0</v>
@@ -16326,12 +16398,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Cleethorpes</t>
+          <t>Crawley</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -16342,10 +16414,10 @@
       </c>
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I156" s="3" t="n">
         <v>0</v>
@@ -16377,7 +16449,7 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>Dunmow</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -16402,13 +16474,13 @@
         <v>0</v>
       </c>
       <c r="J157" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M157" s="5" t="n">
         <v>0</v>
@@ -16428,12 +16500,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Congleton</t>
+          <t>Eastbourne</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
@@ -16444,10 +16516,10 @@
       </c>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I158" s="3" t="n">
         <v>0</v>
@@ -16479,12 +16551,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Crawley</t>
+          <t>Esher</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -16498,10 +16570,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J159" s="5" t="n">
         <v>0</v>
@@ -16530,12 +16602,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Dunmow</t>
+          <t>Fareham</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -16549,7 +16621,7 @@
         <v>0</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I160" s="3" t="n">
         <v>0</v>
@@ -16561,7 +16633,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" s="3" t="n">
         <v>0</v>
@@ -16581,12 +16653,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Eastbourne</t>
+          <t>Farnborough</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -16597,10 +16669,10 @@
       </c>
       <c r="F161" s="4" t="inlineStr"/>
       <c r="G161" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I161" s="5" t="n">
         <v>0</v>
@@ -16632,12 +16704,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Eccles</t>
+          <t>Folkestone</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
@@ -16648,7 +16720,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162" s="3" t="n">
         <v>0</v>
@@ -16660,7 +16732,7 @@
         <v>0</v>
       </c>
       <c r="K162" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" s="3" t="n">
         <v>0</v>
@@ -16683,12 +16755,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Esher</t>
+          <t>Freshwater</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -16702,10 +16774,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J163" s="5" t="n">
         <v>0</v>
@@ -16734,12 +16806,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Fareham</t>
+          <t>Gainsborough</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
@@ -16750,10 +16822,10 @@
       </c>
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I164" s="3" t="n">
         <v>0</v>
@@ -16785,12 +16857,12 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Farnborough</t>
+          <t>Godalming</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -16801,13 +16873,13 @@
       </c>
       <c r="F165" s="4" t="inlineStr"/>
       <c r="G165" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J165" s="5" t="n">
         <v>0</v>
@@ -16836,12 +16908,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Folkestone</t>
+          <t>Gosport</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -16855,7 +16927,7 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I166" s="3" t="n">
         <v>0</v>
@@ -16864,7 +16936,7 @@
         <v>0</v>
       </c>
       <c r="K166" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L166" s="3" t="n">
         <v>0</v>
@@ -16887,12 +16959,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Freshwater</t>
+          <t>Gravesend</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -16938,12 +17010,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Gainsborough</t>
+          <t>Great Yarmouth</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -16989,12 +17061,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Godalming</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -17005,13 +17077,13 @@
       </c>
       <c r="F169" s="4" t="inlineStr"/>
       <c r="G169" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H169" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J169" s="5" t="n">
         <v>0</v>
@@ -17040,12 +17112,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Godstone</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
@@ -17056,7 +17128,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H170" s="3" t="n">
         <v>0</v>
@@ -17071,7 +17143,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M170" s="3" t="n">
         <v>0</v>
@@ -17091,12 +17163,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Gravesend</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -17110,10 +17182,10 @@
         <v>0</v>
       </c>
       <c r="H171" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171" s="5" t="n">
         <v>0</v>
@@ -17142,12 +17214,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Great Yarmouth</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -17158,10 +17230,10 @@
       </c>
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>0</v>
@@ -17193,12 +17265,12 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Hertford</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -17244,12 +17316,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -17260,7 +17332,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H174" s="3" t="n">
         <v>0</v>
@@ -17275,7 +17347,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M174" s="3" t="n">
         <v>0</v>
@@ -17295,12 +17367,12 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -17311,10 +17383,10 @@
       </c>
       <c r="F175" s="4" t="inlineStr"/>
       <c r="G175" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H175" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I175" s="5" t="n">
         <v>0</v>
@@ -17346,12 +17418,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Hertford</t>
+          <t>Keighley</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -17362,7 +17434,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
         <v>0</v>
@@ -17377,7 +17449,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M176" s="3" t="n">
         <v>0</v>
@@ -17397,12 +17469,12 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Kirriemuir</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -17448,12 +17520,12 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Hove</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
@@ -17499,12 +17571,12 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Lisburn</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D179" s="5" t="n">
@@ -17550,12 +17622,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Keighley</t>
+          <t>Liss</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -17569,7 +17641,7 @@
         <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I180" s="3" t="n">
         <v>0</v>
@@ -17581,7 +17653,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M180" s="3" t="n">
         <v>0</v>
@@ -17601,12 +17673,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Kirriemuir</t>
+          <t>Littlehampton</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
@@ -17652,12 +17724,12 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Luton</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -17703,12 +17775,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Lewes</t>
+          <t>Lyndhurst</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -17754,12 +17826,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Lisburn</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
@@ -17770,13 +17842,13 @@
       </c>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J184" s="3" t="n">
         <v>0</v>
@@ -17805,12 +17877,12 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Liss</t>
+          <t>Pontefract</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
@@ -17821,10 +17893,10 @@
       </c>
       <c r="F185" s="4" t="inlineStr"/>
       <c r="G185" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H185" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I185" s="5" t="n">
         <v>0</v>
@@ -17856,12 +17928,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Littlehampton</t>
+          <t>Reigate</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
@@ -17872,7 +17944,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
         <v>0</v>
@@ -17884,7 +17956,7 @@
         <v>0</v>
       </c>
       <c r="K186" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L186" s="3" t="n">
         <v>0</v>
@@ -17907,12 +17979,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Luton</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
@@ -17923,7 +17995,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr"/>
       <c r="G187" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H187" s="5" t="n">
         <v>0</v>
@@ -17938,7 +18010,7 @@
         <v>0</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M187" s="5" t="n">
         <v>0</v>
@@ -17958,7 +18030,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Lyndhurst</t>
+          <t>Ringwood</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -17974,10 +18046,10 @@
       </c>
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I188" s="3" t="n">
         <v>0</v>
@@ -18009,12 +18081,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>North Shields</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
@@ -18060,12 +18132,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Seaford</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -18076,13 +18148,13 @@
       </c>
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H190" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J190" s="3" t="n">
         <v>0</v>
@@ -18111,12 +18183,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Pontefract</t>
+          <t>Sevenoaks</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
@@ -18162,12 +18234,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Reigate</t>
+          <t>Sherborne</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -18178,7 +18250,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H192" s="3" t="n">
         <v>0</v>
@@ -18190,7 +18262,7 @@
         <v>0</v>
       </c>
       <c r="K192" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L192" s="3" t="n">
         <v>0</v>
@@ -18213,12 +18285,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Smethwick</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
@@ -18229,7 +18301,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr"/>
       <c r="G193" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H193" s="5" t="n">
         <v>0</v>
@@ -18244,7 +18316,7 @@
         <v>0</v>
       </c>
       <c r="L193" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M193" s="5" t="n">
         <v>0</v>
@@ -18264,12 +18336,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Ringwood</t>
+          <t>South Shields</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -18315,12 +18387,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Southend-on-sea</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
@@ -18366,12 +18438,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Sevenoaks</t>
+          <t>Spennymoor</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -18417,12 +18489,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Sherborne</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -18433,13 +18505,13 @@
       </c>
       <c r="F197" s="4" t="inlineStr"/>
       <c r="G197" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H197" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J197" s="5" t="n">
         <v>0</v>
@@ -18468,12 +18540,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Smethwick</t>
+          <t>Stockport</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -18519,12 +18591,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>South Shields</t>
+          <t>Taunton</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -18535,10 +18607,10 @@
       </c>
       <c r="F199" s="4" t="inlineStr"/>
       <c r="G199" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H199" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I199" s="5" t="n">
         <v>0</v>
@@ -18570,12 +18642,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Spennymoor</t>
+          <t>Torquay</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -18621,12 +18693,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Tranent</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -18637,13 +18709,13 @@
       </c>
       <c r="F201" s="4" t="inlineStr"/>
       <c r="G201" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H201" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J201" s="5" t="n">
         <v>0</v>
@@ -18672,12 +18744,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Trowbridge</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -18723,12 +18795,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Trowbridge</t>
+          <t>Ulverston</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -18739,10 +18811,10 @@
       </c>
       <c r="F203" s="4" t="inlineStr"/>
       <c r="G203" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H203" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I203" s="5" t="n">
         <v>0</v>
@@ -18774,12 +18846,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Ulverston</t>
+          <t>Uttoxeter</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -18790,10 +18862,10 @@
       </c>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I204" s="3" t="n">
         <v>0</v>
@@ -18825,12 +18897,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Uttoxeter</t>
+          <t>Ventnor</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -18841,10 +18913,10 @@
       </c>
       <c r="F205" s="4" t="inlineStr"/>
       <c r="G205" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H205" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I205" s="5" t="n">
         <v>0</v>
@@ -18876,12 +18948,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Ventnor</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -18892,10 +18964,10 @@
       </c>
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H206" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I206" s="3" t="n">
         <v>0</v>
@@ -18927,12 +18999,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Waltham Abbey</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -18978,12 +19050,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Waltham Abbey</t>
+          <t>Walton-on-thames</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -19029,12 +19101,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Welwyn Garden City</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -19045,7 +19117,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr"/>
       <c r="G209" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H209" s="5" t="n">
         <v>0</v>
@@ -19057,7 +19129,7 @@
         <v>0</v>
       </c>
       <c r="K209" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L209" s="5" t="n">
         <v>0</v>
@@ -19182,12 +19254,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Wilmslow</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -19233,12 +19305,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Winsford</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
@@ -19284,12 +19356,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Winsford</t>
+          <t>Worthing</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -19335,12 +19407,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Worthing</t>
+          <t>Wymondham</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
@@ -19386,12 +19458,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Wymondham</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -19429,59 +19501,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B217" s="4" t="inlineStr">
-        <is>
-          <t>Yeovil</t>
-        </is>
-      </c>
-      <c r="C217" s="4" t="inlineStr">
-        <is>
-          <t>Somerset</t>
-        </is>
-      </c>
-      <c r="D217" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E217" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F217" s="4" t="inlineStr"/>
-      <c r="G217" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H217" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I217" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J217" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K217" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L217" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M217" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N217" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O217" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O217"/>
+  <autoFilter ref="A1:O216"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19604,14 +19625,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
@@ -19623,7 +19644,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
@@ -19646,7 +19667,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
@@ -19665,7 +19686,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr"/>
@@ -19703,7 +19724,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
@@ -19757,7 +19778,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
@@ -19788,7 +19809,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
@@ -19805,7 +19826,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="5" t="n">
@@ -19814,7 +19835,7 @@
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr"/>
@@ -19826,7 +19847,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
@@ -19843,18 +19864,18 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>6</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr"/>
@@ -19872,7 +19893,7 @@
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>9</v>
@@ -19887,13 +19908,11 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="5" t="n">
@@ -19903,7 +19922,7 @@
         <v>13</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" s="4" t="inlineStr"/>
     </row>
@@ -19929,13 +19948,13 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr"/>
@@ -19965,10 +19984,10 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C23" s="5" t="n">
         <v>16</v>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>14</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>6</v>
@@ -20003,15 +20022,15 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
@@ -20030,11 +20049,11 @@
         <v>11</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
@@ -20122,7 +20141,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
@@ -20156,22 +20175,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>9</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>78</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>23</v>
@@ -20189,13 +20208,13 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr"/>
@@ -20253,7 +20272,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
@@ -20272,22 +20291,20 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
@@ -20354,7 +20371,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
@@ -20371,13 +20388,13 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
@@ -20483,7 +20500,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
       <c r="D51" s="4" t="inlineStr"/>
@@ -20530,7 +20547,7 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr"/>
@@ -20562,7 +20579,7 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="3" t="n">
@@ -20632,7 +20649,7 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
@@ -20649,7 +20666,7 @@
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
       <c r="D61" s="4" t="inlineStr"/>
@@ -20670,7 +20687,7 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
@@ -20689,17 +20706,17 @@
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D63" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr"/>
@@ -20890,7 +20907,7 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
@@ -20951,7 +20968,7 @@
       <c r="D77" s="4" t="inlineStr"/>
       <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G77" s="5" t="n">
         <v>11</v>
@@ -20966,7 +20983,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>1</v>
@@ -20985,7 +21002,7 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1051</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1173</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="6">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Warrington</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -9192,11 +9192,11 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>/birmingham/service-administrator-jobs</t>
+          <t>/warrington/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>0</v>
@@ -9231,27 +9231,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Warrington</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>/warrington/service-administrator-jobs</t>
+          <t>/birmingham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
@@ -9263,7 +9263,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" s="5" t="n">
         <v>0</v>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
@@ -9852,14 +9852,14 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/nottingham/jobs</t>
+          <t>/oxford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0</v>
@@ -9868,13 +9868,13 @@
         <v>0</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>0</v>
@@ -9891,39 +9891,39 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Basingstoke</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>/oxford/service-administrator-jobs</t>
+          <t>/basingstoke/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" s="5" t="n">
         <v>0</v>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Basingstoke</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
@@ -9962,17 +9962,17 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>/basingstoke/service-administrator-jobs</t>
+          <t>/glasgow/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>0</v>
@@ -10001,12 +10001,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -10017,11 +10017,11 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>/glasgow/service-administrator-jobs</t>
+          <t>/nottingham/jobs</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H33" s="5" t="n">
         <v>0</v>
@@ -10039,7 +10039,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" s="5" t="n">
         <v>0</v>
@@ -20175,7 +20175,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>5</v>
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>2</v>
@@ -20430,7 +20430,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr"/>
@@ -20850,7 +20850,7 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$196</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$216</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2271</v>
+        <v>2282</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1042</v>
+        <v>1080</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1003</v>
+        <v>1020</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -710,36 +710,36 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Real Estate &amp; Property</t>
+          <t>Banking &amp; Financial Services</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Banking &amp; Financial Services</t>
+          <t>Real Estate &amp; Property</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>456</v>
+        <v>412</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>12</v>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>2</v>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -840,36 +840,25 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Ventes et Commercialisation</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="8" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Total Ontap JobG8 jobs published today</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B18" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="C19" s="10" t="n">
-        <v>927</v>
+      <c r="C18" s="10" t="n">
+        <v>922</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C19"/>
+  <autoFilter ref="A1:C18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21191,7 +21180,7 @@
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.2 / 0/14</t>
+          <t>3 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -21214,7 +21203,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -21225,7 +21214,7 @@
       <c r="F5" s="14" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>8 / 2.5 / 2/14</t>
+          <t>7 / 2.4 / 2/14</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
@@ -21249,7 +21238,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -21288,7 +21277,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.9 / 0/14</t>
+          <t>3 / 3.8 / 0/14</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -21409,7 +21398,7 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -21456,7 +21445,7 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -21677,7 +21666,7 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -21705,12 +21694,12 @@
       <c r="B17" s="14" t="inlineStr"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>2 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.6 / 1/14</t>
+          <t>7 / 3.6 / 1/14</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
@@ -22042,7 +22031,7 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>14 / 11.0 / 13/14</t>
+          <t>13 / 10.9 / 13/14</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
@@ -22070,37 +22059,37 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
+          <t>1 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.7 / 0/14</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>1 / 0.1 / 0/14</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/14</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 1.7 / 0/14</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
@@ -22417,7 +22406,7 @@
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>8 / 5.7 / 9/14</t>
+          <t>7 / 5.6 / 9/14</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr"/>
@@ -23304,7 +23293,7 @@
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
@@ -23470,7 +23459,7 @@
       <c r="B60" s="13" t="inlineStr"/>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.1 / 0/14</t>
+          <t>3 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
@@ -23557,7 +23546,7 @@
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.0 / 0/14</t>
+          <t>4 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
@@ -23593,13 +23582,13 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>12 / 9.1 / 13/14</t>
+          <t>8 / 8.9 / 13/14</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>12 / 6.2 / 8/14</t>
+          <t>11 / 6.1 / 8/14</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr">
@@ -23753,7 +23742,7 @@
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.3 / 0/14</t>
+          <t>0 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
@@ -23785,7 +23774,7 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -23810,7 +23799,7 @@
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.2 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -24021,7 +24010,7 @@
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>9 / 4.1 / 2/14</t>
+          <t>10 / 4.2 / 2/14</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr"/>
@@ -24246,7 +24235,7 @@
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>8 / 12.1 / 14/14</t>
+          <t>7 / 12.1 / 14/14</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$212</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1046</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1168</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2282</v>
+        <v>2096</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>232</v>
@@ -658,36 +658,36 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1441</v>
+        <v>1231</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing</t>
+          <t>Healthcare &amp; Medical</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1080</v>
+        <v>1129</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>191</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Medical</t>
+          <t>Sales &amp; Marketing</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1020</v>
+        <v>1053</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>54</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>961</v>
+        <v>945</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>707</v>
+        <v>725</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8">
@@ -723,36 +723,36 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>449</v>
+        <v>513</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Real Estate &amp; Property</t>
+          <t>Retail &amp; Consumer Products</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>412</v>
+        <v>499</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer Products</t>
+          <t>Real Estate &amp; Property</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>411</v>
+        <v>491</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12">
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>275</v>
+        <v>352</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>2</v>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
@@ -854,7 +854,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>922</v>
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -8236,7 +8236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O216"/>
+  <dimension ref="A1:O212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9770,12 +9770,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -9786,23 +9786,23 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>/norwich/jobs</t>
+          <t>/oxford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="5" t="n">
         <v>0</v>
@@ -9825,39 +9825,39 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Basingstoke</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/oxford/service-administrator-jobs</t>
+          <t>/basingstoke/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>0</v>
@@ -9880,12 +9880,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Basingstoke</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
@@ -9896,17 +9896,17 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>/basingstoke/service-administrator-jobs</t>
+          <t>/glasgow/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31" s="5" t="n">
         <v>0</v>
@@ -9935,12 +9935,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
@@ -9951,11 +9951,11 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>/glasgow/service-administrator-jobs</t>
+          <t>/norwich/jobs</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0</v>
@@ -9964,7 +9964,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>0</v>
@@ -13475,28 +13475,28 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Worcester Park</t>
+          <t>Cheadle</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E99" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" s="5" t="n">
         <v>0</v>
@@ -13508,7 +13508,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L99" s="5" t="n">
         <v>0</v>
@@ -13531,35 +13531,35 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Cheadle</t>
+          <t>Guildford</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>0</v>
@@ -13582,12 +13582,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Guildford</t>
+          <t>Slough</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -13598,10 +13598,10 @@
       </c>
       <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" s="5" t="n">
         <v>1</v>
@@ -13633,29 +13633,29 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Slough</t>
+          <t>Dartford</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E102" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H102" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J102" s="3" t="n">
         <v>0</v>
@@ -13684,12 +13684,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Dartford</t>
+          <t>Newbury</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
@@ -13700,13 +13700,13 @@
       </c>
       <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H103" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J103" s="5" t="n">
         <v>0</v>
@@ -13735,12 +13735,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Newbury</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
@@ -13751,25 +13751,25 @@
       </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H104" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K104" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M104" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N104" s="3" t="n">
         <v>0</v>
@@ -13786,12 +13786,12 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Tunbridge Wells</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
@@ -13802,13 +13802,13 @@
       </c>
       <c r="F105" s="4" t="inlineStr"/>
       <c r="G105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H105" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="I105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" s="5" t="n">
         <v>0</v>
@@ -13820,7 +13820,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N105" s="5" t="n">
         <v>0</v>
@@ -13837,35 +13837,35 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Tunbridge Wells</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="3" t="n">
         <v>0</v>
@@ -13888,12 +13888,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -13904,7 +13904,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr"/>
       <c r="G107" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H107" s="5" t="n">
         <v>0</v>
@@ -13916,7 +13916,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="5" t="n">
         <v>0</v>
@@ -13939,12 +13939,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Northwich</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H108" s="3" t="n">
         <v>0</v>
@@ -13967,7 +13967,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="3" t="n">
         <v>0</v>
@@ -13990,12 +13990,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Northwich</t>
+          <t>Sittingbourne</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -14009,7 +14009,7 @@
         <v>2</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" s="5" t="n">
         <v>0</v>
@@ -14018,7 +14018,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="5" t="n">
         <v>0</v>
@@ -14041,29 +14041,29 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Sittingbourne</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H110" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I110" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -14092,12 +14092,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Ballyclare</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -14108,13 +14108,13 @@
       </c>
       <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H111" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J111" s="5" t="n">
         <v>0</v>
@@ -14143,12 +14143,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Ballyclare</t>
+          <t>Barrow-in-furness</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
@@ -14159,10 +14159,10 @@
       </c>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H112" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -14194,12 +14194,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Barrow-in-furness</t>
+          <t>Camberley</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14210,10 +14210,10 @@
       </c>
       <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I113" s="5" t="n">
         <v>0</v>
@@ -14245,7 +14245,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Camberley</t>
+          <t>Caterham</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -14261,10 +14261,10 @@
       </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>0</v>
@@ -14296,12 +14296,12 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Caterham</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14312,16 +14312,16 @@
       </c>
       <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K115" s="5" t="n">
         <v>0</v>
@@ -14347,12 +14347,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>Cramlington</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
@@ -14369,10 +14369,10 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K116" s="3" t="n">
         <v>0</v>
@@ -14398,12 +14398,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Cramlington</t>
+          <t>Devizes</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14414,13 +14414,13 @@
       </c>
       <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H117" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J117" s="5" t="n">
         <v>0</v>
@@ -14449,12 +14449,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Devizes</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -14465,10 +14465,10 @@
       </c>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Knaresborough</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -14516,10 +14516,10 @@
       </c>
       <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" s="5" t="n">
         <v>0</v>
@@ -14528,7 +14528,7 @@
         <v>0</v>
       </c>
       <c r="K119" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L119" s="5" t="n">
         <v>0</v>
@@ -14551,12 +14551,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Knaresborough</t>
+          <t>Leatherhead</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
@@ -14567,10 +14567,10 @@
       </c>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>0</v>
@@ -14579,7 +14579,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L120" s="3" t="n">
         <v>0</v>
@@ -14602,12 +14602,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Leatherhead</t>
+          <t>Maidenhead</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -14618,10 +14618,10 @@
       </c>
       <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I121" s="5" t="n">
         <v>0</v>
@@ -14630,13 +14630,13 @@
         <v>0</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N121" s="5" t="n">
         <v>0</v>
@@ -14653,12 +14653,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Maidenhead</t>
+          <t>Maldon</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
@@ -14678,16 +14678,16 @@
         <v>0</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K122" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N122" s="3" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Maldon</t>
+          <t>Margate</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -14723,13 +14723,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I123" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K123" s="5" t="n">
         <v>0</v>
@@ -14755,12 +14755,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Margate</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -14771,10 +14771,10 @@
       </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>0</v>
@@ -14806,12 +14806,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Newton Abbot</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -14822,13 +14822,13 @@
       </c>
       <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H125" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J125" s="5" t="n">
         <v>0</v>
@@ -14857,12 +14857,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Newton Abbot</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -14873,13 +14873,13 @@
       </c>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H126" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126" s="3" t="n">
         <v>0</v>
@@ -14908,12 +14908,12 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H127" s="5" t="n">
         <v>0</v>
@@ -14936,10 +14936,10 @@
         <v>0</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" s="5" t="n">
         <v>0</v>
@@ -14959,12 +14959,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H128" s="3" t="n">
         <v>0</v>
@@ -14987,10 +14987,10 @@
         <v>0</v>
       </c>
       <c r="K128" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L128" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="3" t="n">
         <v>0</v>
@@ -15010,12 +15010,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Tadley</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15026,10 +15026,10 @@
       </c>
       <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H129" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="I129" s="5" t="n">
         <v>0</v>
@@ -15061,12 +15061,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Tadley</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -15112,12 +15112,12 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Verwood</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15128,10 +15128,10 @@
       </c>
       <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H131" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I131" s="5" t="n">
         <v>0</v>
@@ -15163,12 +15163,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Verwood</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
@@ -15179,10 +15179,10 @@
       </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132" s="3" t="n">
         <v>0</v>
@@ -15191,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="K132" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="3" t="n">
         <v>0</v>
@@ -15214,26 +15214,26 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Alresford</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" s="5" t="n">
         <v>0</v>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="K133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L133" s="5" t="n">
         <v>0</v>
@@ -15265,23 +15265,23 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Woodbridge</t>
+          <t>Atherstone</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -15299,7 +15299,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
@@ -15316,12 +15316,12 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Alresford</t>
+          <t>Basildon</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H135" s="5" t="n">
         <v>0</v>
@@ -15347,7 +15347,7 @@
         <v>0</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" s="5" t="n">
         <v>0</v>
@@ -15367,12 +15367,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Amersham</t>
+          <t>Beaminster</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
@@ -15418,12 +15418,12 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Atherstone</t>
+          <t>Berwick-upon-tweed</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -15440,7 +15440,7 @@
         <v>0</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J137" s="5" t="n">
         <v>0</v>
@@ -15452,7 +15452,7 @@
         <v>0</v>
       </c>
       <c r="M137" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N137" s="5" t="n">
         <v>0</v>
@@ -15469,12 +15469,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Basildon</t>
+          <t>Bexhill-on-sea</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -15485,7 +15485,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138" s="3" t="n">
         <v>0</v>
@@ -15500,7 +15500,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M138" s="3" t="n">
         <v>0</v>
@@ -15520,12 +15520,12 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Beaminster</t>
+          <t>Billericay</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15571,12 +15571,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Berwick-upon-tweed</t>
+          <t>Birchington</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
@@ -15590,10 +15590,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J140" s="3" t="n">
         <v>0</v>
@@ -15622,12 +15622,12 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Bexhill-on-sea</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15673,12 +15673,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Billericay</t>
+          <t>Bridgwater</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Birchington</t>
+          <t>Brighouse</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15743,7 +15743,7 @@
         <v>0</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I143" s="5" t="n">
         <v>0</v>
@@ -15755,7 +15755,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143" s="5" t="n">
         <v>0</v>
@@ -15775,12 +15775,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Buckingham</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -15826,12 +15826,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Bridgwater</t>
+          <t>Bury St. Edmunds</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15877,12 +15877,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Brighouse</t>
+          <t>Chertsey</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -15896,7 +15896,7 @@
         <v>0</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I146" s="3" t="n">
         <v>0</v>
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M146" s="3" t="n">
         <v>0</v>
@@ -15928,12 +15928,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Buckingham</t>
+          <t>Chichester</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Bury St. Edmunds</t>
+          <t>Christchurch</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -16030,12 +16030,12 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Chatham</t>
+          <t>Cirencester</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
@@ -16046,7 +16046,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H149" s="5" t="n">
         <v>0</v>
@@ -16061,7 +16061,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M149" s="5" t="n">
         <v>0</v>
@@ -16081,12 +16081,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Chertsey</t>
+          <t>Cleethorpes</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
@@ -16097,10 +16097,10 @@
       </c>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" s="3" t="n">
         <v>0</v>
@@ -16132,12 +16132,12 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Chichester</t>
+          <t>Congleton</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -16183,12 +16183,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Christchurch</t>
+          <t>Crawley</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -16199,10 +16199,10 @@
       </c>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I152" s="3" t="n">
         <v>0</v>
@@ -16234,12 +16234,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Cirencester</t>
+          <t>Dunmow</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -16285,12 +16285,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Cleethorpes</t>
+          <t>Eastbourne</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -16301,10 +16301,10 @@
       </c>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>0</v>
@@ -16336,12 +16336,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Congleton</t>
+          <t>Esher</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -16352,13 +16352,13 @@
       </c>
       <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J155" s="5" t="n">
         <v>0</v>
@@ -16387,12 +16387,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Crawley</t>
+          <t>Fareham</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -16438,12 +16438,12 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Dunmow</t>
+          <t>Farnborough</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157" s="5" t="n">
         <v>0</v>
@@ -16469,7 +16469,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M157" s="5" t="n">
         <v>0</v>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Eastbourne</t>
+          <t>Folkestone</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
@@ -16508,7 +16508,7 @@
         <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I158" s="3" t="n">
         <v>0</v>
@@ -16517,7 +16517,7 @@
         <v>0</v>
       </c>
       <c r="K158" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L158" s="3" t="n">
         <v>0</v>
@@ -16540,12 +16540,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Esher</t>
+          <t>Freshwater</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -16559,10 +16559,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J159" s="5" t="n">
         <v>0</v>
@@ -16591,12 +16591,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Fareham</t>
+          <t>Gainsborough</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -16607,10 +16607,10 @@
       </c>
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160" s="3" t="n">
         <v>0</v>
@@ -16642,12 +16642,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Farnborough</t>
+          <t>Godalming</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -16658,13 +16658,13 @@
       </c>
       <c r="F161" s="4" t="inlineStr"/>
       <c r="G161" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H161" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J161" s="5" t="n">
         <v>0</v>
@@ -16693,12 +16693,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Folkestone</t>
+          <t>Gosport</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
@@ -16712,7 +16712,7 @@
         <v>0</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" s="3" t="n">
         <v>0</v>
@@ -16721,7 +16721,7 @@
         <v>0</v>
       </c>
       <c r="K162" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L162" s="3" t="n">
         <v>0</v>
@@ -16744,12 +16744,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Freshwater</t>
+          <t>Gravesend</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -16795,12 +16795,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Gainsborough</t>
+          <t>Great Yarmouth</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
@@ -16846,12 +16846,12 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Godalming</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -16862,13 +16862,13 @@
       </c>
       <c r="F165" s="4" t="inlineStr"/>
       <c r="G165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J165" s="5" t="n">
         <v>0</v>
@@ -16897,12 +16897,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Gosport</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -16916,7 +16916,7 @@
         <v>0</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" s="3" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M166" s="3" t="n">
         <v>0</v>
@@ -16948,12 +16948,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Gravesend</t>
+          <t>Hatfield</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -16967,10 +16967,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J167" s="5" t="n">
         <v>0</v>
@@ -16999,12 +16999,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Great Yarmouth</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -17015,10 +17015,10 @@
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I168" s="3" t="n">
         <v>0</v>
@@ -17050,12 +17050,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Hertford</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -17101,12 +17101,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H170" s="3" t="n">
         <v>0</v>
@@ -17132,7 +17132,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M170" s="3" t="n">
         <v>0</v>
@@ -17152,12 +17152,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -17168,13 +17168,13 @@
       </c>
       <c r="F171" s="4" t="inlineStr"/>
       <c r="G171" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H171" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" s="5" t="n">
         <v>0</v>
@@ -17203,12 +17203,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Keighley</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -17222,7 +17222,7 @@
         <v>0</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172" s="3" t="n">
         <v>0</v>
@@ -17234,7 +17234,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M172" s="3" t="n">
         <v>0</v>
@@ -17254,12 +17254,12 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Hertford</t>
+          <t>Kirriemuir</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -17305,12 +17305,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -17356,12 +17356,12 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Lisburn</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -17407,12 +17407,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Keighley</t>
+          <t>Liss</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -17426,7 +17426,7 @@
         <v>0</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>0</v>
@@ -17438,7 +17438,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M176" s="3" t="n">
         <v>0</v>
@@ -17458,12 +17458,12 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Kirriemuir</t>
+          <t>Littlehampton</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -17509,12 +17509,12 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Luton</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
@@ -17560,12 +17560,12 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Lisburn</t>
+          <t>Lyndhurst</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D179" s="5" t="n">
@@ -17611,12 +17611,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Liss</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -17630,10 +17630,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J180" s="3" t="n">
         <v>0</v>
@@ -17662,12 +17662,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Littlehampton</t>
+          <t>Pontefract</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
@@ -17713,12 +17713,12 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Luton</t>
+          <t>Reigate</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -17729,7 +17729,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H182" s="3" t="n">
         <v>0</v>
@@ -17741,7 +17741,7 @@
         <v>0</v>
       </c>
       <c r="K182" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L182" s="3" t="n">
         <v>0</v>
@@ -17764,12 +17764,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Lyndhurst</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -17780,7 +17780,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr"/>
       <c r="G183" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H183" s="5" t="n">
         <v>0</v>
@@ -17795,7 +17795,7 @@
         <v>0</v>
       </c>
       <c r="L183" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M183" s="5" t="n">
         <v>0</v>
@@ -17815,12 +17815,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Ringwood</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
@@ -17834,10 +17834,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J184" s="3" t="n">
         <v>0</v>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Pontefract</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
@@ -17917,12 +17917,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Reigate</t>
+          <t>Seaford</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H186" s="3" t="n">
         <v>0</v>
@@ -17945,7 +17945,7 @@
         <v>0</v>
       </c>
       <c r="K186" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L186" s="3" t="n">
         <v>0</v>
@@ -17968,12 +17968,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Sevenoaks</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
@@ -17984,7 +17984,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr"/>
       <c r="G187" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H187" s="5" t="n">
         <v>0</v>
@@ -17999,7 +17999,7 @@
         <v>0</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M187" s="5" t="n">
         <v>0</v>
@@ -18019,12 +18019,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Ringwood</t>
+          <t>Sherborne</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
@@ -18035,10 +18035,10 @@
       </c>
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I188" s="3" t="n">
         <v>0</v>
@@ -18070,12 +18070,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Smethwick</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
@@ -18121,12 +18121,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Seaford</t>
+          <t>South Shields</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -18137,10 +18137,10 @@
       </c>
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I190" s="3" t="n">
         <v>0</v>
@@ -18172,12 +18172,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Sevenoaks</t>
+          <t>Southend-on-sea</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
@@ -18223,12 +18223,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Sherborne</t>
+          <t>Spennymoor</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -18274,12 +18274,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Smethwick</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
@@ -18290,13 +18290,13 @@
       </c>
       <c r="F193" s="4" t="inlineStr"/>
       <c r="G193" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H193" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J193" s="5" t="n">
         <v>0</v>
@@ -18325,12 +18325,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>South Shields</t>
+          <t>Stockport</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -18341,10 +18341,10 @@
       </c>
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I194" s="3" t="n">
         <v>0</v>
@@ -18376,12 +18376,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Southend-on-sea</t>
+          <t>Taunton</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
@@ -18427,12 +18427,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Spennymoor</t>
+          <t>Torquay</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -18478,12 +18478,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Tranent</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -18494,13 +18494,13 @@
       </c>
       <c r="F197" s="4" t="inlineStr"/>
       <c r="G197" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H197" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J197" s="5" t="n">
         <v>0</v>
@@ -18529,12 +18529,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Stockport</t>
+          <t>Trowbridge</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -18580,12 +18580,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Taunton</t>
+          <t>Ulverston</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -18596,10 +18596,10 @@
       </c>
       <c r="F199" s="4" t="inlineStr"/>
       <c r="G199" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H199" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I199" s="5" t="n">
         <v>0</v>
@@ -18631,12 +18631,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Uttoxeter</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -18682,12 +18682,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Tranent</t>
+          <t>Ventnor</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -18698,10 +18698,10 @@
       </c>
       <c r="F201" s="4" t="inlineStr"/>
       <c r="G201" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H201" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I201" s="5" t="n">
         <v>0</v>
@@ -18733,12 +18733,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Trowbridge</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -18784,12 +18784,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Ulverston</t>
+          <t>Waltham Abbey</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -18800,10 +18800,10 @@
       </c>
       <c r="F203" s="4" t="inlineStr"/>
       <c r="G203" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H203" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I203" s="5" t="n">
         <v>0</v>
@@ -18835,12 +18835,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Uttoxeter</t>
+          <t>Welwyn Garden City</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -18851,7 +18851,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H204" s="3" t="n">
         <v>0</v>
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="K204" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L204" s="3" t="n">
         <v>0</v>
@@ -18886,12 +18886,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Ventnor</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -18902,10 +18902,10 @@
       </c>
       <c r="F205" s="4" t="inlineStr"/>
       <c r="G205" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H205" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I205" s="5" t="n">
         <v>0</v>
@@ -18937,12 +18937,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -18988,12 +18988,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Waltham Abbey</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -19039,12 +19039,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Walton-on-thames</t>
+          <t>Winsford</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Welwyn Garden City</t>
+          <t>Woodbridge</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr"/>
       <c r="G209" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H209" s="5" t="n">
         <v>0</v>
@@ -19118,7 +19118,7 @@
         <v>0</v>
       </c>
       <c r="K209" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L209" s="5" t="n">
         <v>0</v>
@@ -19141,12 +19141,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Worthing</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -19192,12 +19192,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Wymondham</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -19243,12 +19243,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -19286,212 +19286,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B213" s="4" t="inlineStr">
-        <is>
-          <t>Winsford</t>
-        </is>
-      </c>
-      <c r="C213" s="4" t="inlineStr">
-        <is>
-          <t>Cheshire - West</t>
-        </is>
-      </c>
-      <c r="D213" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E213" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F213" s="4" t="inlineStr"/>
-      <c r="G213" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H213" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I213" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J213" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K213" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L213" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M213" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N213" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O213" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>Worthing</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>Sussex</t>
-        </is>
-      </c>
-      <c r="D214" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E214" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F214" s="2" t="inlineStr"/>
-      <c r="G214" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H214" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I214" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J214" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K214" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L214" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M214" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N214" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O214" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B215" s="4" t="inlineStr">
-        <is>
-          <t>Wymondham</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr">
-        <is>
-          <t>Norfolk</t>
-        </is>
-      </c>
-      <c r="D215" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E215" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F215" s="4" t="inlineStr"/>
-      <c r="G215" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H215" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I215" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J215" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K215" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L215" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M215" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N215" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O215" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>Yeovil</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>Somerset</t>
-        </is>
-      </c>
-      <c r="D216" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F216" s="2" t="inlineStr"/>
-      <c r="G216" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O216" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O216"/>
+  <autoFilter ref="A1:O212"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19633,7 +19429,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
@@ -20032,7 +19828,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>11</v>
@@ -20164,7 +19960,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>5</v>
@@ -20261,7 +20057,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
@@ -20676,7 +20472,7 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
@@ -20695,7 +20491,7 @@
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>5</v>
@@ -21098,27 +20894,27 @@
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.9 / 2/14</t>
+          <t>2 / 3.8 / 2/14</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>0 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.4 / 0/14</t>
+          <t>2 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>0 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
@@ -21136,25 +20932,25 @@
       <c r="B3" s="14" t="inlineStr"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>4 / 1.8 / 0/14</t>
+          <t>14 / 2.6 / 1/14</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr"/>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>13 / 2.4 / 2/14</t>
+          <t>9 / 3.0 / 3/14</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr"/>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21167,25 +20963,25 @@
       <c r="B4" s="13" t="inlineStr"/>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/14</t>
+          <t>2 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>7 / 6.5 / 10/14</t>
+          <t>5 / 6.6 / 10/14</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.3 / 0/14</t>
+          <t>5 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.4 / 0/14</t>
+          <t>0 / 2.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21208,18 +21004,18 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>5 / 2.9 / 0/14</t>
+          <t>6 / 3.2 / 1/14</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>7 / 2.4 / 2/14</t>
+          <t>8 / 2.9 / 3/14</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr"/>
@@ -21233,28 +21029,28 @@
       <c r="B6" s="13" t="inlineStr"/>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.7 / 0/14</t>
+          <t>5 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>15 / 3.8 / 2/14</t>
+          <t>13 / 4.6 / 3/14</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.7 / 0/14</t>
+          <t>4 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -21277,32 +21073,32 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.8 / 0/14</t>
+          <t>3 / 3.7 / 0/14</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>8 / 1.4 / 2/14</t>
+          <t>6 / 1.9 / 3/14</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21315,7 +21111,7 @@
       <c r="B8" s="13" t="inlineStr"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -21325,18 +21121,18 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.3 / 0/14</t>
+          <t>1 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.2 / 0/14</t>
+          <t>5 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
@@ -21364,23 +21160,23 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.3 / 0/14</t>
+          <t>1 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>7 / 2.0 / 2/14</t>
+          <t>6 / 2.4 / 3/14</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21393,7 +21189,7 @@
       <c r="B10" s="13" t="inlineStr"/>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>3 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -21413,7 +21209,7 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>3 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -21423,7 +21219,7 @@
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21435,12 +21231,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.5 / 0/14</t>
+          <t>8 / 1.1 / 1/14</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -21482,38 +21278,38 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
       <c r="D12" s="13" t="inlineStr">
         <is>
+          <t>1 / 0.4 / 0/14</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.9 / 0/14</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>0 / 1.1 / 0/14</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/14</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.4 / 0/14</t>
-        </is>
-      </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21578,7 +21374,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>0 / 3.2 / 0/14</t>
+          <t>0 / 3.0 / 0/14</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -21598,12 +21394,12 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21616,24 +21412,24 @@
       <c r="B15" s="14" t="inlineStr"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/14</t>
+          <t>3 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr"/>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/14</t>
+          <t>3 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>0 / 3.5 / 3/14</t>
+          <t>2 / 3.2 / 2/14</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
@@ -21651,37 +21447,37 @@
       <c r="B16" s="13" t="inlineStr"/>
       <c r="C16" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.7 / 0/14</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>2 / 2.8 / 0/14</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>2 / 2.9 / 2/14</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>1 / 0.4 / 0/14</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>10 / 2.7 / 3/14</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>2 / 0.9 / 0/14</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.8 / 0/14</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>2 / 2.9 / 0/14</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>3 / 2.7 / 2/14</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.4 / 0/14</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>13 / 2.0 / 2/14</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.8 / 0/14</t>
-        </is>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21694,12 +21490,12 @@
       <c r="B17" s="14" t="inlineStr"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>7 / 3.6 / 1/14</t>
+          <t>7 / 3.8 / 2/14</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
@@ -21707,12 +21503,12 @@
       <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>4 / 4.1 / 5/14</t>
+          <t>3 / 4.3 / 5/14</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.1 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21725,29 +21521,29 @@
       <c r="B18" s="13" t="inlineStr"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.1 / 0/14</t>
+          <t>2 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.0 / 3/14</t>
+          <t>1 / 2.6 / 2/14</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/14</t>
+          <t>2 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr"/>
       <c r="G18" s="13" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/14</t>
+          <t>3 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.8 / 0/14</t>
+          <t>0 / 2.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21760,13 +21556,13 @@
       <c r="B19" s="14" t="inlineStr"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.3 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>15 / 11.9 / 12/14</t>
+          <t>12 / 12.4 / 13/14</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr"/>
@@ -21774,7 +21570,7 @@
       <c r="H19" s="14" t="inlineStr"/>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21791,7 +21587,7 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
@@ -21811,17 +21607,17 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>4 / 1.4 / 0/14</t>
+          <t>7 / 1.9 / 1/14</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21850,17 +21646,17 @@
       <c r="F21" s="14" t="inlineStr"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>4 / 0.5 / 0/14</t>
+          <t>4 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>3 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21883,27 +21679,27 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.0 / 0/14</t>
+          <t>1 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>2 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/14</t>
+          <t>3 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21918,22 +21714,22 @@
       <c r="D23" s="14" t="inlineStr"/>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.1 / 0/14</t>
+          <t>6 / 2.5 / 1/14</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>3 / 6.3 / 12/14</t>
+          <t>2 / 6.0 / 11/14</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>9 / 4.1 / 2/14</t>
+          <t>5 / 4.4 / 2/14</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>4 / 6.0 / 8/14</t>
+          <t>5 / 6.0 / 8/14</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr"/>
@@ -21946,7 +21742,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -21971,7 +21767,7 @@
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
@@ -21994,29 +21790,29 @@
       <c r="B25" s="14" t="inlineStr"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>10 / 3.4 / 2/14</t>
+          <t>14 / 4.4 / 3/14</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>3 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22031,23 +21827,23 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>13 / 10.9 / 13/14</t>
+          <t>7 / 11.1 / 14/14</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>18 / 2.6 / 2/14</t>
+          <t>16 / 3.8 / 3/14</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.6 / 0/14</t>
+          <t>1 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.3 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22059,7 +21855,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
@@ -22069,7 +21865,7 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -22079,7 +21875,7 @@
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -22089,7 +21885,7 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
@@ -22106,7 +21902,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -22116,7 +21912,7 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -22126,12 +21922,12 @@
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.4 / 0/14</t>
+          <t>5 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -22153,12 +21949,12 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.3 / 0/14</t>
+          <t>4 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
@@ -22168,17 +21964,17 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>2 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>7 / 1.6 / 2/14</t>
+          <t>6 / 2.1 / 3/14</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
@@ -22200,12 +21996,12 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/14</t>
+          <t>3 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
@@ -22215,7 +22011,7 @@
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -22225,7 +22021,7 @@
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -22272,7 +22068,7 @@
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.2 / 0/14</t>
+          <t>3 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
@@ -22300,22 +22096,22 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.4 / 0/14</t>
+          <t>4 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.7 / 0/14</t>
+          <t>4 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.0 / 1/14</t>
+          <t>6 / 3.2 / 2/14</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -22325,7 +22121,7 @@
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22338,37 +22134,37 @@
       <c r="B33" s="14" t="inlineStr"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/14</t>
+          <t>3 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.5 / 0/14</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.6 / 0/14</t>
-        </is>
-      </c>
-      <c r="I33" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22396,7 +22192,7 @@
       <c r="B35" s="14" t="inlineStr"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -22406,18 +22202,18 @@
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>7 / 5.6 / 9/14</t>
+          <t>6 / 5.9 / 10/14</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/14</t>
+          <t>4 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
@@ -22449,7 +22245,7 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -22459,7 +22255,7 @@
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
@@ -22481,7 +22277,7 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.1 / 0/14</t>
+          <t>4 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -22528,7 +22324,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -22538,7 +22334,7 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -22553,7 +22349,7 @@
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
@@ -22576,28 +22372,28 @@
       <c r="B39" s="14" t="inlineStr"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>4 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>6 / 4.5 / 7/14</t>
+          <t>7 / 5.0 / 8/14</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>11 / 2.3 / 2/14</t>
+          <t>14 / 3.2 / 3/14</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>3 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
@@ -22617,14 +22413,14 @@
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.9 / 0/14</t>
+          <t>1 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr"/>
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.6 / 0/14</t>
+          <t>3 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
@@ -22644,7 +22440,7 @@
       <c r="D41" s="14" t="inlineStr"/>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr">
@@ -22654,7 +22450,7 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
@@ -22676,42 +22472,42 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.6 / 0/14</t>
+          <t>1 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
+          <t>1 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>1 / 1.8 / 0/14</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>1 / 1.8 / 0/14</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>0 / 1.6 / 0/14</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>2 / 1.5 / 0/14</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="F42" s="13" t="inlineStr">
-        <is>
-          <t>0 / 1.8 / 0/14</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>2 / 1.5 / 0/14</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.3 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22723,7 +22519,7 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.4 / 0/14</t>
+          <t>1 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
@@ -22738,7 +22534,7 @@
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
@@ -22758,7 +22554,7 @@
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22771,17 +22567,17 @@
       <c r="B44" s="13" t="inlineStr"/>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>3 / 4.6 / 3/14</t>
+          <t>2 / 4.1 / 2/14</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>3 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
@@ -22791,17 +22587,17 @@
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>7 / 3.6 / 2/14</t>
+          <t>8 / 4.1 / 3/14</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.6 / 0/14</t>
+          <t>4 / 3.8 / 0/14</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22824,7 +22620,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>2 / 14.4 / 12/14</t>
+          <t>3 / 13.6 / 11/14</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr"/>
@@ -22832,7 +22628,7 @@
       <c r="H45" s="14" t="inlineStr"/>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22844,7 +22640,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>2 / 19.8 / 12/14</t>
+          <t>2 / 18.1 / 11/14</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -22854,32 +22650,32 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>1 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
+          <t>0 / 2.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
           <t>0 / 2.1 / 0/14</t>
         </is>
       </c>
-      <c r="G46" s="13" t="inlineStr">
-        <is>
-          <t>0 / 2.1 / 0/14</t>
-        </is>
-      </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22892,33 +22688,33 @@
       <c r="B47" s="14" t="inlineStr"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.4 / 0/14</t>
+          <t>0 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>8 / 5.4 / 9/14</t>
+          <t>3 / 5.5 / 9/14</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.5 / 0/14</t>
+          <t>2 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>9 / 1.4 / 2/14</t>
+          <t>11 / 2.1 / 3/14</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr"/>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22932,18 +22728,18 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.7 / 0/14</t>
+          <t>3 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.3 / 0/14</t>
+          <t>7 / 2.7 / 1/14</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr"/>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>7 / 1.9 / 2/14</t>
+          <t>4 / 2.1 / 2/14</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
@@ -22953,7 +22749,7 @@
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23012,7 +22808,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>0 / 3.5 / 0/14</t>
+          <t>0 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -23022,7 +22818,7 @@
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -23065,32 +22861,32 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/14</t>
+          <t>2 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>3 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>4 / 1.4 / 0/14</t>
+          <t>5 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.5 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23102,7 +22898,7 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>0 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -23117,12 +22913,12 @@
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="inlineStr">
+        <is>
           <t>1 / 0.1 / 0/14</t>
-        </is>
-      </c>
-      <c r="F52" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
@@ -23149,7 +22945,7 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>8 / 3.7 / 5/14</t>
+          <t>8 / 4.1 / 6/14</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -23159,7 +22955,7 @@
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -23207,17 +23003,17 @@
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
@@ -23254,7 +23050,7 @@
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
@@ -23274,7 +23070,7 @@
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23293,22 +23089,22 @@
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>2 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="I56" s="13" t="inlineStr">
@@ -23325,7 +23121,7 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
@@ -23372,7 +23168,7 @@
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
@@ -23382,7 +23178,7 @@
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -23420,7 +23216,7 @@
       <c r="B59" s="14" t="inlineStr"/>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
@@ -23435,13 +23231,13 @@
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr"/>
       <c r="H59" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
@@ -23459,17 +23255,17 @@
       <c r="B60" s="13" t="inlineStr"/>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.0 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.6 / 0/14</t>
+          <t>2 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
@@ -23479,17 +23275,17 @@
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.3 / 0/14</t>
+          <t>3 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23507,27 +23303,27 @@
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>5 / 4.9 / 6/14</t>
+          <t>9 / 5.4 / 7/14</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>5 / 2.1 / 0/14</t>
+          <t>6 / 2.4 / 1/14</t>
         </is>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr"/>
@@ -23552,22 +23348,22 @@
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>2 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>9 / 3.4 / 2/14</t>
+          <t>9 / 3.9 / 3/14</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>2 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23582,13 +23378,13 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>8 / 8.9 / 13/14</t>
+          <t>10 / 9.1 / 13/14</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>11 / 6.1 / 8/14</t>
+          <t>9 / 6.5 / 9/14</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr">
@@ -23609,23 +23405,23 @@
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>5 / 4.2 / 0/14</t>
+          <t>2 / 4.1 / 0/14</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>5 / 5.1 / 5/14</t>
+          <t>5 / 5.3 / 5/14</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>20 / 6.3 / 4/14</t>
+          <t>12 / 7.0 / 5/14</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23662,7 +23458,7 @@
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="H65" s="14" t="inlineStr">
@@ -23684,12 +23480,12 @@
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.2 / 0/14</t>
+          <t>0 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>6 / 1.4 / 2/14</t>
+          <t>1 / 1.5 / 2/14</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
@@ -23714,7 +23510,7 @@
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
@@ -23737,22 +23533,22 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.0 / 0/14</t>
+          <t>0 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.2 / 0/14</t>
+          <t>0 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>6 / 0.9 / 2/14</t>
+          <t>6 / 1.3 / 3/14</t>
         </is>
       </c>
       <c r="H67" s="14" t="inlineStr">
@@ -23789,22 +23585,22 @@
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="I68" s="13" t="inlineStr">
@@ -23821,7 +23617,7 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>11 / 4.4 / 4/14</t>
+          <t>11 / 5.1 / 5/14</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
@@ -23831,22 +23627,22 @@
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.3 / 0/14</t>
+          <t>3 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="H69" s="14" t="inlineStr">
@@ -23869,17 +23665,17 @@
       <c r="B70" s="13" t="inlineStr"/>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/14</t>
+          <t>3 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.8 / 0/14</t>
+          <t>0 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
@@ -23917,24 +23713,24 @@
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>2 / 4.1 / 3/14</t>
+          <t>3 / 3.7 / 2/14</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>9 / 7.5 / 10/14</t>
+          <t>8 / 7.9 / 11/14</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.5 / 2/14</t>
+          <t>7 / 3.8 / 3/14</t>
         </is>
       </c>
       <c r="H71" s="14" t="inlineStr"/>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23947,37 +23743,37 @@
       <c r="B72" s="13" t="inlineStr"/>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>1 / 3.4 / 0/14</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
-      <c r="E72" s="13" t="inlineStr">
-        <is>
-          <t>2 / 3.6 / 0/14</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.3 / 0/14</t>
-        </is>
-      </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/14</t>
+          <t>2 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23990,33 +23786,33 @@
       <c r="B73" s="14" t="inlineStr"/>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/14</t>
+          <t>3 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.6 / 3/14</t>
+          <t>1 / 2.1 / 2/14</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.3 / 0/14</t>
+          <t>3 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>2 / 5.0 / 5/14</t>
+          <t>4 / 4.9 / 4/14</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>10 / 4.2 / 2/14</t>
+          <t>8 / 4.6 / 3/14</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr"/>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24035,27 +23831,27 @@
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.4 / 0/14</t>
+          <t>8 / 3.6 / 1/14</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.3 / 0/14</t>
+          <t>0 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>10 / 3.2 / 2/14</t>
+          <t>9 / 3.9 / 3/14</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.2 / 0/14</t>
+          <t>1 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24078,27 +23874,27 @@
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.4 / 0/14</t>
+          <t>3 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>5 / 1.6 / 0/14</t>
+          <t>6 / 2.0 / 1/14</t>
         </is>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24111,14 +23907,14 @@
       <c r="B76" s="13" t="inlineStr"/>
       <c r="C76" s="13" t="inlineStr">
         <is>
+          <t>1 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="D76" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
           <t>1 / 1.6 / 0/14</t>
@@ -24126,7 +23922,7 @@
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.5 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
@@ -24136,12 +23932,12 @@
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24154,29 +23950,29 @@
       <c r="B77" s="14" t="inlineStr"/>
       <c r="C77" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>2 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.2 / 0/14</t>
+          <t>2 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>5 / 5.7 / 7/14</t>
+          <t>8 / 6.3 / 8/14</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr"/>
       <c r="G77" s="14" t="inlineStr"/>
       <c r="H77" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.8 / 4/14</t>
+          <t>2 / 3.9 / 4/14</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.3 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24190,27 +23986,27 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.7 / 0/14</t>
+          <t>0 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.5 / 0/14</t>
+          <t>1 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>2 / 5.0 / 4/14</t>
+          <t>3 / 4.9 / 4/14</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.5 / 0/14</t>
+          <t>4 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
@@ -24230,19 +24026,19 @@
       <c r="D79" s="14" t="inlineStr"/>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>9 / 7.4 / 10/14</t>
+          <t>8 / 7.7 / 11/14</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>7 / 12.1 / 14/14</t>
+          <t>6 / 11.2 / 14/14</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>
       <c r="H79" s="14" t="inlineStr"/>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$216</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1038</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>927</v>
+        <v>954</v>
       </c>
     </row>
     <row r="4">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1160</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="6">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8">
@@ -648,7 +648,7 @@
         <v>2096</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3">
@@ -674,7 +674,7 @@
         <v>1129</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -713,7 +713,7 @@
         <v>725</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
@@ -726,7 +726,7 @@
         <v>513</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -817,7 +817,7 @@
         <v>94</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
@@ -854,7 +854,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>939</v>
+        <v>954</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H196"/>
+  <dimension ref="A1:H199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -943,7 +943,7 @@
       <c r="D2" s="11" t="inlineStr"/>
       <c r="E2" s="11" t="inlineStr"/>
       <c r="F2" s="12" t="n">
-        <v>1236</v>
+        <v>1259</v>
       </c>
       <c r="G2" s="11" t="inlineStr"/>
       <c r="H2" s="11" t="inlineStr">
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="F3" s="12" t="n">
-        <v>1046</v>
+        <v>1066</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>1046</v>
+        <v>1066</v>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="F4" s="12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G4" s="11" t="inlineStr"/>
       <c r="H4" s="11" t="inlineStr">
@@ -1520,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>1</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>1</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>1</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>1</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>1</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>1</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>1</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>1</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>1</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>1</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>1</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -4632,19 +4632,19 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/hr-recruitment-jobs</t>
+          <t>/job-search/london/customer-service-jobs</t>
         </is>
       </c>
       <c r="F102" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4665,24 +4665,24 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/service-administrator-jobs</t>
+          <t>/job-search/london/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F103" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -4703,24 +4703,24 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/finance-accounts-jobs</t>
+          <t>/job-search/manchester-salford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4741,24 +4741,24 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Finance &amp; Accounts</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>/job-search/oxfordshire/service-administrator-jobs</t>
+          <t>/job-search/london/finance-accounts-jobs</t>
         </is>
       </c>
       <c r="F105" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4789,14 +4789,14 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/service-administrator-jobs</t>
+          <t>/job-search/oxfordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -4827,14 +4827,14 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>/job-search/essex/service-administrator-jobs</t>
+          <t>/job-search/bristol-bath/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F107" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -4855,24 +4855,24 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>/job-search/hampshire/customer-service-jobs</t>
+          <t>/job-search/essex/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4893,24 +4893,24 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>/job-search/cambridgeshire/service-administrator-jobs</t>
+          <t>/job-search/hampshire/customer-service-jobs</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4941,14 +4941,14 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>/job-search/gloucestershire/service-administrator-jobs</t>
+          <t>/job-search/cambridgeshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -4969,24 +4969,24 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>/job-search/london/support-worker</t>
+          <t>/job-search/gloucestershire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -5007,17 +5007,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>/job-search/devon/finance-accounts-jobs</t>
+          <t>/job-search/london/support-worker</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
@@ -5045,24 +5045,24 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Finance &amp; Accounts</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>/job-search/dorset/service-administrator-jobs</t>
+          <t>/job-search/devon/finance-accounts-jobs</t>
         </is>
       </c>
       <c r="F113" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -5093,14 +5093,14 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>/job-search/devon/service-administrator-jobs</t>
+          <t>/job-search/dorset/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5121,24 +5121,24 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Customer Service &amp; Contact Centre</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>/job-search/surrey/customer-service-jobs</t>
+          <t>/job-search/devon/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>1</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>1</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>1</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>1</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>1</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>1</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>1</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>1</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>1</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>1</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>1</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>1</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
@@ -5767,24 +5767,24 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>/job-search/somerset/service-administrator-jobs</t>
+          <t>/job-search/wiltshire/support-worker</t>
         </is>
       </c>
       <c r="F132" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5805,24 +5805,24 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>/job-search/london/customer-sales-jobs</t>
+          <t>/job-search/somerset/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F133" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5853,14 +5853,14 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>/job-search/west-yorkshire/customer-sales-jobs</t>
+          <t>/job-search/london/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F134" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>1</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>1</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -6005,14 +6005,14 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>/job-search/suffolk/service-administrator-jobs</t>
+          <t>/job-search/cornwall/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Derbyshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -6043,14 +6043,14 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>/job-search/derbyshire/service-administrator-jobs</t>
+          <t>/job-search/suffolk/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F139" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Derbyshire</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -6081,14 +6081,14 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-east/service-administrator-jobs</t>
+          <t>/job-search/derbyshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -6119,14 +6119,14 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>/job-search/lincolnshire/service-administrator-jobs</t>
+          <t>/job-search/cheshire-east/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F141" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -6157,14 +6157,14 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>/job-search/merseyside-liverpool/service-administrator-jobs</t>
+          <t>/job-search/lincolnshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F142" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -6195,14 +6195,14 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>/job-search/shropshire/service-administrator-jobs</t>
+          <t>/job-search/merseyside-liverpool/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F143" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -6233,14 +6233,14 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>/job-search/wigan-bolton/service-administrator-jobs</t>
+          <t>/job-search/shropshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -6271,14 +6271,14 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>/job-search/black-country/service-administrator-jobs</t>
+          <t>/job-search/wigan-bolton/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F145" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -6299,24 +6299,24 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Legal Assistant &amp; Paralegal</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/paralegal-jobs</t>
+          <t>/job-search/black-country/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -6347,14 +6347,14 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>/job-search/suffolk/paralegal-jobs</t>
+          <t>/job-search/london/paralegal-jobs</t>
         </is>
       </c>
       <c r="F147" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -6385,14 +6385,14 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>/job-search/essex/paralegal-jobs</t>
+          <t>/job-search/suffolk/paralegal-jobs</t>
         </is>
       </c>
       <c r="F148" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G148" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -6423,14 +6423,14 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>/job-search/norfolk/paralegal-jobs</t>
+          <t>/job-search/essex/paralegal-jobs</t>
         </is>
       </c>
       <c r="F149" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -6451,24 +6451,24 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Legal Assistant &amp; Paralegal</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>/job-search/london/marketing-jobs</t>
+          <t>/job-search/norfolk/paralegal-jobs</t>
         </is>
       </c>
       <c r="F150" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>78</v>
+        <v>11</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -6499,14 +6499,14 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>/job-search/surrey/marketing-jobs</t>
+          <t>/job-search/london/marketing-jobs</t>
         </is>
       </c>
       <c r="F151" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6537,14 +6537,14 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/marketing-jobs</t>
+          <t>/job-search/surrey/marketing-jobs</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -6575,14 +6575,14 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>/job-search/birmingham-solihull/marketing-jobs</t>
+          <t>/job-search/manchester-salford/marketing-jobs</t>
         </is>
       </c>
       <c r="F153" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -6603,24 +6603,24 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/hr-recruitment-jobs</t>
+          <t>/job-search/birmingham-solihull/marketing-jobs</t>
         </is>
       </c>
       <c r="F154" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -6651,14 +6651,14 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/hr-recruitment-jobs</t>
+          <t>/job-search/berkshire/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F155" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -6689,14 +6689,14 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>/job-search/nottinghamshire/hr-recruitment-jobs</t>
+          <t>/job-search/manchester-salford/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F156" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G156" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>/job-search/birmingham-solihull/hr-recruitment-jobs</t>
+          <t>/job-search/nottinghamshire/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F157" s="5" t="n">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -6765,14 +6765,14 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>/job-search/sussex/hr-recruitment-jobs</t>
+          <t>/job-search/birmingham-solihull/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F158" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6793,24 +6793,24 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>HR &amp; Recruitment</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-west/service-administrator-jobs</t>
+          <t>/job-search/sussex/hr-recruitment-jobs</t>
         </is>
       </c>
       <c r="F159" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -6841,14 +6841,14 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>/job-search/edinburgh-lothians/service-administrator-jobs</t>
+          <t>/job-search/cheshire-west/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F160" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -6879,14 +6879,14 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>/job-search/worcestershire/service-administrator-jobs</t>
+          <t>/job-search/edinburgh-lothians/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F161" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -6907,24 +6907,24 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/marketing-jobs</t>
+          <t>/job-search/worcestershire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F162" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -6945,24 +6945,24 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>/job-search/kent/support-worker</t>
+          <t>/job-search/berkshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F163" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -6983,24 +6983,24 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>North East</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>/job-search/north-east/customer-sales-jobs</t>
+          <t>/job-search/kent/support-worker</t>
         </is>
       </c>
       <c r="F164" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7021,24 +7021,24 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>North East</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>/job-search/oxfordshire/support-worker</t>
+          <t>/job-search/north-east/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F165" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -7059,24 +7059,24 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>/job-search/north-yorkshire/finance-accounts-jobs</t>
+          <t>/job-search/oxfordshire/support-worker</t>
         </is>
       </c>
       <c r="F166" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7097,24 +7097,24 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Finance &amp; Accounts</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>/job-search/bedfordshire/service-administrator-jobs</t>
+          <t>/job-search/north-yorkshire/finance-accounts-jobs</t>
         </is>
       </c>
       <c r="F167" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -7135,17 +7135,17 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/customer-sales-jobs</t>
+          <t>/job-search/bedfordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F168" s="3" t="n">
@@ -7173,24 +7173,24 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>/job-search/buckinghamshire/marketing-jobs</t>
+          <t>/job-search/bristol-bath/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F169" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -7211,24 +7211,24 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cardiff-vale/service-administrator-jobs</t>
+          <t>/job-search/buckinghamshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F170" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7249,24 +7249,24 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/customer-sales-jobs</t>
+          <t>/job-search/cardiff-vale/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F171" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -7297,14 +7297,14 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/customer-sales-jobs</t>
+          <t>/job-search/berkshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F172" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -7335,14 +7335,14 @@
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>/job-search/kent/customer-sales-jobs</t>
+          <t>/job-search/hertfordshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F173" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -7373,14 +7373,14 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>/job-search/glasgow/customer-sales-jobs</t>
+          <t>/job-search/kent/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F174" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -7411,14 +7411,14 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>/job-search/surrey/customer-sales-jobs</t>
+          <t>/job-search/glasgow/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F175" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -7439,24 +7439,24 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>/job-search/bristol-bath/marketing-jobs</t>
+          <t>/job-search/surrey/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F176" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G176" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7477,24 +7477,24 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>/job-search/gloucestershire/marketing-jobs</t>
+          <t>/job-search/sussex/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F177" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/marketing-jobs</t>
+          <t>/job-search/bristol-bath/marketing-jobs</t>
         </is>
       </c>
       <c r="F178" s="3" t="n">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -7563,14 +7563,14 @@
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>/job-search/kent/marketing-jobs</t>
+          <t>/job-search/gloucestershire/marketing-jobs</t>
         </is>
       </c>
       <c r="F179" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -7601,14 +7601,14 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>/job-search/oxfordshire/marketing-jobs</t>
+          <t>/job-search/hertfordshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F180" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7629,24 +7629,24 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>/job-search/tayside/service-administrator-jobs</t>
+          <t>/job-search/kent/marketing-jobs</t>
         </is>
       </c>
       <c r="F181" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -7667,24 +7667,24 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>/job-search/south-wales-valleys/service-administrator-jobs</t>
+          <t>/job-search/oxfordshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F182" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7705,24 +7705,24 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>/job-search/cambridgeshire/marketing-jobs</t>
+          <t>/job-search/tayside/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F183" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -7743,24 +7743,24 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>/job-search/cheshire-west/marketing-jobs</t>
+          <t>/job-search/south-wales-valleys/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F184" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -7791,14 +7791,14 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>/job-search/essex/marketing-jobs</t>
+          <t>/job-search/cambridgeshire/marketing-jobs</t>
         </is>
       </c>
       <c r="F185" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -7829,14 +7829,14 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>/job-search/merseyside-liverpool/marketing-jobs</t>
+          <t>/job-search/cheshire-west/marketing-jobs</t>
         </is>
       </c>
       <c r="F186" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>North East</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -7867,14 +7867,14 @@
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>/job-search/north-east/marketing-jobs</t>
+          <t>/job-search/essex/marketing-jobs</t>
         </is>
       </c>
       <c r="F187" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G187" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -7895,24 +7895,24 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>/job-search/devon/customer-sales-jobs</t>
+          <t>/job-search/merseyside-liverpool/marketing-jobs</t>
         </is>
       </c>
       <c r="F188" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -7933,24 +7933,24 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North East</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>/job-search/hampshire/customer-sales-jobs</t>
+          <t>/job-search/north-east/marketing-jobs</t>
         </is>
       </c>
       <c r="F189" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -7971,24 +7971,24 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Customer Sales &amp; Sales Advisor</t>
+          <t>Finance &amp; Accounts</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>/job-search/north-scotland/customer-sales-jobs</t>
+          <t>/job-search/warrington-halton/finance-accounts-jobs</t>
         </is>
       </c>
       <c r="F190" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8009,24 +8009,24 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>/job-search/greater-manchester-south/marketing-jobs</t>
+          <t>/job-search/devon/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F191" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G191" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -8047,24 +8047,24 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>/job-search/northern-ireland-east/marketing-jobs</t>
+          <t>/job-search/hampshire/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F192" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8085,24 +8085,24 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Customer Sales &amp; Sales Advisor</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>/job-search/north-yorkshire/marketing-jobs</t>
+          <t>/job-search/north-scotland/customer-sales-jobs</t>
         </is>
       </c>
       <c r="F193" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G193" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -8123,24 +8123,24 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>/job-search/essex/finance-accounts-jobs</t>
+          <t>/job-search/greater-manchester-south/marketing-jobs</t>
         </is>
       </c>
       <c r="F194" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8161,24 +8161,24 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>/job-search/manchester-salford/finance-accounts-jobs</t>
+          <t>/job-search/northern-ireland-east/marketing-jobs</t>
         </is>
       </c>
       <c r="F195" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G195" s="5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
@@ -8199,33 +8199,147 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
+          <t>Yorkshire - North</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/north-yorkshire/marketing-jobs</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>Essex</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>Finance &amp; Accounts</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>/job-search/essex/finance-accounts-jobs</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Finance &amp; Accounts</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>/job-search/manchester-salford/finance-accounts-jobs</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>Regional/category</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
           <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D199" s="4" t="inlineStr">
         <is>
           <t>HR &amp; Recruitment</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E199" s="4" t="inlineStr">
         <is>
           <t>/job-search/coventry-warwickshire/hr-recruitment-jobs</t>
         </is>
       </c>
-      <c r="F196" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G196" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="F199" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H199" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H196"/>
+  <autoFilter ref="A1:H199"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8236,7 +8350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O212"/>
+  <dimension ref="A1:O216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8494,12 +8608,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Runcorn</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
@@ -8545,12 +8659,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Widnes</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -8561,13 +8675,13 @@
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>0</v>
@@ -8596,23 +8710,23 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Widnes</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0</v>
@@ -8647,7 +8761,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -8698,12 +8812,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Forfar</t>
+          <t>Frodsham</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -8749,12 +8863,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Frodsham</t>
+          <t>Knutsford</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -8800,12 +8914,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Knutsford</t>
+          <t>Leigh</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -8851,12 +8965,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Leigh</t>
+          <t>Lymm</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -8902,12 +9016,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Lymm</t>
+          <t>Merthyr Tydfil</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Wales South - Valleys</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -8953,12 +9067,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Merthyr Tydfil</t>
+          <t>Newport-on-tay</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Valleys</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -9004,12 +9118,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Newport-on-tay</t>
+          <t>Runcorn</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
@@ -9050,47 +9164,43 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Stockport</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>/manchester/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>0</v>
@@ -9110,33 +9220,33 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Bristol</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>/manchester/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="E17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>/bristol/service-administrator-jobs</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="H17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>0</v>
@@ -9145,7 +9255,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>0</v>
@@ -9165,33 +9275,33 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Warrington</t>
+          <t>Bristol</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>/warrington/service-administrator-jobs</t>
+          <t>/bristol/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>0</v>
@@ -9229,19 +9339,19 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>/birmingham/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>/birmingham/service-administrator-jobs</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
       </c>
@@ -9252,7 +9362,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L19" s="5" t="n">
         <v>0</v>
@@ -9275,27 +9385,27 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Warrington</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>/leeds/service-administrator-jobs</t>
+          <t>/warrington/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0</v>
@@ -9310,7 +9420,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>0</v>
@@ -9440,12 +9550,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -9456,17 +9566,17 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>/edinburgh/service-administrator-jobs</t>
+          <t>/glasgow/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="5" t="n">
         <v>0</v>
@@ -9495,33 +9605,33 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Exeter</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>/exeter/service-administrator-jobs</t>
+          <t>/leeds/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>0</v>
@@ -9530,7 +9640,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>0</v>
@@ -9605,33 +9715,33 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Bolton</t>
+          <t>Exeter</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>/bolton/jobs</t>
+          <t>/exeter/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>0</v>
@@ -9640,7 +9750,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>0</v>
@@ -9660,27 +9770,27 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>/cambridge/service-administrator-jobs</t>
+          <t>/nottingham/jobs</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>0</v>
@@ -9698,7 +9808,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27" s="5" t="n">
         <v>0</v>
@@ -9715,12 +9825,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -9731,11 +9841,11 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>/coventry/service-administrator-jobs</t>
+          <t>/cambridge/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0</v>
@@ -9753,7 +9863,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0</v>
@@ -9770,12 +9880,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -9786,14 +9896,14 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>/oxford/service-administrator-jobs</t>
+          <t>/edinburgh/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>0</v>
@@ -9802,7 +9912,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="5" t="n">
         <v>0</v>
@@ -9825,23 +9935,23 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Basingstoke</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/basingstoke/service-administrator-jobs</t>
+          <t>/liverpool/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
@@ -9851,13 +9961,13 @@
         <v>0</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>0</v>
@@ -9880,12 +9990,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
@@ -9896,11 +10006,11 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>/glasgow/service-administrator-jobs</t>
+          <t>/coventry/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>0</v>
@@ -9918,7 +10028,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N31" s="5" t="n">
         <v>0</v>
@@ -9935,12 +10045,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>Peterborough</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
@@ -9951,11 +10061,11 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>/norwich/jobs</t>
+          <t>/peterborough/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0</v>
@@ -9964,7 +10074,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>0</v>
@@ -9990,23 +10100,23 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>/nottingham/jobs</t>
+          <t>/leicester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
@@ -10028,7 +10138,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" s="5" t="n">
         <v>0</v>
@@ -10045,30 +10155,30 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Peterborough</t>
+          <t>Maidstone</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>/peterborough/service-administrator-jobs</t>
+          <t>/maidstone/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0</v>
@@ -10100,12 +10210,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Bradford</t>
+          <t>Milton Keynes</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
@@ -10116,26 +10226,26 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>/bradford/service-administrator-jobs</t>
+          <t>/milton-keynes/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="5" t="n">
         <v>0</v>
@@ -10155,12 +10265,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
@@ -10171,11 +10281,11 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>/liverpool/service-administrator-jobs</t>
+          <t>/norwich/jobs</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0</v>
@@ -10184,10 +10294,10 @@
         <v>0</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0</v>
@@ -10210,30 +10320,30 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Gloucester</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>/gloucester/service-administrator-jobs</t>
+          <t>/oxford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>0</v>
@@ -10245,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" s="5" t="n">
         <v>0</v>
@@ -10274,7 +10384,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>1</v>
@@ -10285,7 +10395,7 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0</v>
@@ -10320,39 +10430,39 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Belfast</t>
+          <t>Basingstoke</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>/basingstoke/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>/belfast/service-administrator-jobs</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="5" t="n">
         <v>0</v>
@@ -10375,27 +10485,27 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>/bournemouth/service-administrator-jobs</t>
+          <t>/bedford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0</v>
@@ -10430,39 +10540,39 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Belfast</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>/belfast/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>/chester/jobs</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="L41" s="5" t="n">
         <v>0</v>
@@ -10485,42 +10595,42 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>Gloucester</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>/gloucester/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>/doncaster/service-administrator-jobs</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>0</v>
@@ -10540,7 +10650,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -10549,24 +10659,24 @@
         </is>
       </c>
       <c r="D43" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>/newcastle/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>/gateshead/jobs</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="J43" s="5" t="n">
         <v>0</v>
@@ -10595,42 +10705,42 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>/plymouth/service-administrator-jobs</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>/hull/service-administrator-jobs</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>0</v>
@@ -10650,30 +10760,30 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>Sheffield</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>/leicester/service-administrator-jobs</t>
+          <t>/sheffield/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>0</v>
@@ -10705,12 +10815,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Milton Keynes</t>
+          <t>Bolton</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
@@ -10721,11 +10831,11 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>/milton-keynes/service-administrator-jobs</t>
+          <t>/bolton/jobs</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0</v>
@@ -10737,7 +10847,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>0</v>
@@ -10760,12 +10870,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Northampton</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
@@ -10776,7 +10886,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>/northampton/service-administrator-jobs</t>
+          <t>/bournemouth/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
@@ -10815,12 +10925,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Salford</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
@@ -10831,7 +10941,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>/salford/jobs</t>
+          <t>/bradford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
@@ -10870,7 +10980,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Sheffield</t>
+          <t>Doncaster</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -10886,14 +10996,14 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>/sheffield/service-administrator-jobs</t>
+          <t>/doncaster/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" s="5" t="n">
         <v>0</v>
@@ -10925,7 +11035,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -10941,7 +11051,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>/sunderland/service-administrator-jobs</t>
+          <t>/gateshead/jobs</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
@@ -10980,12 +11090,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Warwick</t>
+          <t>Huddersfield</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
@@ -10996,7 +11106,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>/warwick/service-administrator-jobs</t>
+          <t>/huddersfield/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G51" s="5" t="n">
@@ -11015,10 +11125,10 @@
         <v>0</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" s="5" t="n">
         <v>0</v>
@@ -11035,23 +11145,23 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>/altrincham/service-administrator-jobs</t>
+          <t>/reading/jobs</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
@@ -11061,7 +11171,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="3" t="n">
         <v>0</v>
@@ -11090,23 +11200,23 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Salford</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>/bedford/service-administrator-jobs</t>
+          <t>/salford/jobs</t>
         </is>
       </c>
       <c r="G53" s="5" t="n">
@@ -11125,7 +11235,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="5" t="n">
         <v>0</v>
@@ -11145,27 +11255,27 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>/brighton-hove/service-administrator-jobs</t>
+          <t>/sunderland/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0</v>
@@ -11200,12 +11310,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
@@ -11216,14 +11326,14 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>/durham/jobs</t>
+          <t>/altrincham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" s="5" t="n">
         <v>0</v>
@@ -11255,12 +11365,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Hemel Hempstead</t>
+          <t>Ashford</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
@@ -11271,7 +11381,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>/hemel-hempstead/service-administrator-jobs</t>
+          <t>/ashford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
@@ -11281,13 +11391,13 @@
         <v>0</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="3" t="n">
         <v>0</v>
@@ -11310,12 +11420,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Huddersfield</t>
+          <t>Brighton &amp; Hove</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
@@ -11326,11 +11436,11 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>/huddersfield/service-administrator-jobs</t>
+          <t>/brighton-hove/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="5" t="n">
         <v>0</v>
@@ -11345,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" s="5" t="n">
         <v>0</v>
@@ -11365,12 +11475,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Maidstone</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
@@ -11381,14 +11491,14 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>/maidstone/service-administrator-jobs</t>
+          <t>/chester/jobs</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>0</v>
@@ -11420,12 +11530,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
@@ -11436,14 +11546,14 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>/plymouth/service-administrator-jobs</t>
+          <t>/durham/jobs</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="5" t="n">
         <v>0</v>
@@ -11475,12 +11585,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Poole</t>
+          <t>Hemel Hempstead</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
@@ -11491,11 +11601,11 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>/poole/service-administrator-jobs</t>
+          <t>/hemel-hempstead/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0</v>
@@ -11507,7 +11617,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="3" t="n">
         <v>0</v>
@@ -11530,12 +11640,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
@@ -11546,7 +11656,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>/reading/jobs</t>
+          <t>/hull/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
@@ -11585,12 +11695,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Wakefield</t>
+          <t>Northampton</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
@@ -11601,7 +11711,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>/wakefield/jobs</t>
+          <t>/northampton/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
@@ -11640,12 +11750,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
@@ -11656,11 +11766,11 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>/york/service-administrator-jobs</t>
+          <t>/portsmouth/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" s="5" t="n">
         <v>0</v>
@@ -11675,7 +11785,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="5" t="n">
         <v>0</v>
@@ -11695,23 +11805,27 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Ashford</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr"/>
+          <t>Stoke-on-trent</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Staffordshire</t>
+        </is>
+      </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>/ashford/service-administrator-jobs</t>
+          <t>/stoke-on-trent/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0</v>
@@ -11746,23 +11860,27 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Aylesbury</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr"/>
+          <t>Wakefield</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Yorkshire - West</t>
+        </is>
+      </c>
       <c r="D65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>/aylesbury/service-administrator-jobs</t>
+          <t>/wakefield/jobs</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="5" t="n">
         <v>0</v>
@@ -11797,19 +11915,23 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Chester Le Street</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
+          <t>Warwick</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
+        </is>
+      </c>
       <c r="D66" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>/chester-le-street/service-administrator-jobs</t>
+          <t>/warwick/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
@@ -11831,7 +11953,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N66" s="3" t="n">
         <v>0</v>
@@ -11848,7 +11970,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Farnham</t>
+          <t>Aylesbury</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
@@ -11860,7 +11982,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>/farnham/service-administrator-jobs</t>
+          <t>/aylesbury/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
@@ -11899,7 +12021,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Macclesfield</t>
+          <t>Chester Le Street</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr"/>
@@ -11911,7 +12033,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>/macclesfield/service-administrator-jobs</t>
+          <t>/chester-le-street/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
@@ -11950,7 +12072,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Farnham</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -11962,7 +12084,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>/newcastle/service-administrator-jobs</t>
+          <t>/farnham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
@@ -12001,7 +12123,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Newtownabbey</t>
+          <t>Macclesfield</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
@@ -12013,7 +12135,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>/newtownabbey/service-administrator-jobs</t>
+          <t>/macclesfield/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
@@ -12052,7 +12174,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Northallerton</t>
+          <t>Newtownabbey</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
@@ -12064,7 +12186,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>/northallerton/jobs</t>
+          <t>/newtownabbey/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
@@ -12103,7 +12225,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Northallerton</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
@@ -12115,7 +12237,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>/portsmouth/service-administrator-jobs</t>
+          <t>/northallerton/jobs</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
@@ -12154,7 +12276,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Poole</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
@@ -12166,7 +12288,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>/rotherham/service-administrator-jobs</t>
+          <t>/poole/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
@@ -12205,7 +12327,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
@@ -12217,7 +12339,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>/scarborough/service-administrator-jobs</t>
+          <t>/rotherham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
@@ -12256,7 +12378,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -12268,7 +12390,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>/shrewsbury/service-administrator-jobs</t>
+          <t>/scarborough/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G75" s="5" t="n">
@@ -12307,7 +12429,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Stoke-On-Trent</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
@@ -12319,7 +12441,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>/stoke-on-trent/service-administrator-jobs</t>
+          <t>/shrewsbury/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
@@ -12455,28 +12577,28 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Barnet</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr"/>
       <c r="D79" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>/york/service-administrator-jobs</t>
+        </is>
+      </c>
       <c r="G79" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H79" s="5" t="n">
         <v>0</v>
@@ -12485,7 +12607,7 @@
         <v>0</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" s="5" t="n">
         <v>0</v>
@@ -12511,7 +12633,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Southwark</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -12520,29 +12642,29 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="3" t="n">
         <v>0</v>
@@ -12562,7 +12684,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barking</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -12571,17 +12693,17 @@
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I81" s="5" t="n">
         <v>0</v>
@@ -12596,7 +12718,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" s="5" t="n">
         <v>0</v>
@@ -12613,7 +12735,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Chessington</t>
+          <t>Croydon</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12622,7 +12744,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82" s="3" t="n">
         <v>0</v>
@@ -12641,13 +12763,13 @@
         <v>0</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" s="3" t="n">
         <v>0</v>
@@ -12673,14 +12795,14 @@
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H83" s="5" t="n">
         <v>1</v>
@@ -12715,7 +12837,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Beckenham</t>
+          <t>Uxbridge</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12724,14 +12846,14 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H84" s="3" t="n">
         <v>0</v>
@@ -12766,7 +12888,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Bexleyheath</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -12775,20 +12897,20 @@
         </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" s="5" t="n">
         <v>0</v>
@@ -12817,7 +12939,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Borehamwood</t>
+          <t>Harrow</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12826,20 +12948,20 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" s="3" t="n">
         <v>0</v>
@@ -12851,7 +12973,7 @@
         <v>0</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" s="3" t="n">
         <v>0</v>
@@ -12868,7 +12990,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Croydon</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -12877,14 +12999,14 @@
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H87" s="5" t="n">
         <v>0</v>
@@ -12899,7 +13021,7 @@
         <v>0</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" s="5" t="n">
         <v>0</v>
@@ -12919,7 +13041,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Enfield</t>
+          <t>Kingston Upon Thames</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -12928,7 +13050,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" s="3" t="n">
         <v>0</v>
@@ -12938,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" s="3" t="n">
         <v>0</v>
@@ -12950,7 +13072,7 @@
         <v>0</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="3" t="n">
         <v>0</v>
@@ -12970,7 +13092,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Harrow</t>
+          <t>Southwark</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -12979,14 +13101,14 @@
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" s="5" t="n">
         <v>0</v>
@@ -13001,10 +13123,10 @@
         <v>0</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N89" s="5" t="n">
         <v>0</v>
@@ -13021,7 +13143,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Chessington</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -13037,10 +13159,10 @@
       </c>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" s="3" t="n">
         <v>0</v>
@@ -13072,7 +13194,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Hounslow</t>
+          <t>Enfield</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -13103,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N91" s="5" t="n">
         <v>0</v>
@@ -13123,7 +13245,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Ilford</t>
+          <t>Hounslow</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -13148,7 +13270,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
@@ -13157,7 +13279,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>0</v>
@@ -13174,7 +13296,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Isleworth</t>
+          <t>Ilford</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -13190,7 +13312,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" s="5" t="n">
         <v>0</v>
@@ -13199,7 +13321,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" s="5" t="n">
         <v>0</v>
@@ -13225,7 +13347,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Purley</t>
+          <t>Isleworth</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -13276,7 +13398,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Sutton</t>
+          <t>Orpington</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -13292,7 +13414,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" s="5" t="n">
         <v>0</v>
@@ -13301,7 +13423,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" s="5" t="n">
         <v>0</v>
@@ -13327,7 +13449,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Teddington</t>
+          <t>Purley</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13378,7 +13500,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Uxbridge</t>
+          <t>Sutton</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -13429,7 +13551,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>West Drayton</t>
+          <t>Wembley</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13445,10 +13567,10 @@
       </c>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" s="3" t="n">
         <v>0</v>
@@ -13475,28 +13597,28 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Cheadle</t>
+          <t>West Drayton</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E99" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" s="5" t="n">
         <v>0</v>
@@ -13508,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L99" s="5" t="n">
         <v>0</v>
@@ -13540,7 +13662,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -13550,7 +13672,7 @@
         <v>2</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>1</v>
@@ -13559,7 +13681,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>0</v>
@@ -13582,12 +13704,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Slough</t>
+          <t>Tunbridge Wells</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
@@ -13598,10 +13720,10 @@
       </c>
       <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="H101" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="I101" s="5" t="n">
         <v>1</v>
@@ -13633,12 +13755,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Dartford</t>
+          <t>Northwich</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
@@ -13649,13 +13771,13 @@
       </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H102" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3" t="n">
         <v>0</v>
@@ -13684,7 +13806,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Newbury</t>
+          <t>Slough</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -13700,7 +13822,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H103" s="5" t="n">
         <v>0</v>
@@ -13712,7 +13834,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="5" t="n">
         <v>0</v>
@@ -13735,16 +13857,16 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Bury St Edmunds</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E104" s="3" t="n">
         <v>0</v>
@@ -13769,7 +13891,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N104" s="3" t="n">
         <v>0</v>
@@ -13786,29 +13908,29 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Tunbridge Wells</t>
+          <t>Cheltenham</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E105" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F105" s="4" t="inlineStr"/>
       <c r="G105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" s="5" t="n">
         <v>0</v>
@@ -13817,7 +13939,7 @@
         <v>0</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" s="5" t="n">
         <v>0</v>
@@ -13837,12 +13959,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Dartford</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
@@ -13853,19 +13975,19 @@
       </c>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J106" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="3" t="n">
         <v>0</v>
@@ -13888,12 +14010,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -13904,7 +14026,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr"/>
       <c r="G107" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H107" s="5" t="n">
         <v>0</v>
@@ -13916,7 +14038,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="5" t="n">
         <v>0</v>
@@ -13939,12 +14061,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Northwich</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
@@ -13955,7 +14077,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
         <v>0</v>
@@ -13967,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="3" t="n">
         <v>0</v>
@@ -13990,12 +14112,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Sittingbourne</t>
+          <t>Newton Abbot</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -14009,10 +14131,10 @@
         <v>2</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" s="5" t="n">
         <v>0</v>
@@ -14041,29 +14163,29 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -14092,16 +14214,16 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Ballyclare</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E111" s="5" t="n">
         <v>0</v>
@@ -14114,7 +14236,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" s="5" t="n">
         <v>0</v>
@@ -14143,12 +14265,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Barrow-in-furness</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
@@ -14162,10 +14284,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="I112" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -14194,12 +14316,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Camberley</t>
+          <t>Ballyclare</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14245,7 +14367,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Caterham</t>
+          <t>Camberley</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -14261,10 +14383,10 @@
       </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>0</v>
@@ -14296,12 +14418,12 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>Caterham</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14312,16 +14434,16 @@
       </c>
       <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K115" s="5" t="n">
         <v>0</v>
@@ -14347,12 +14469,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Cramlington</t>
+          <t>Chertsey</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
@@ -14366,10 +14488,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J116" s="3" t="n">
         <v>0</v>
@@ -14398,12 +14520,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Devizes</t>
+          <t>Chichester</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14414,13 +14536,13 @@
       </c>
       <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H117" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117" s="5" t="n">
         <v>0</v>
@@ -14449,12 +14571,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Cramlington</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -14465,13 +14587,13 @@
       </c>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
@@ -14500,12 +14622,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Knaresborough</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -14516,10 +14638,10 @@
       </c>
       <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" s="5" t="n">
         <v>0</v>
@@ -14528,7 +14650,7 @@
         <v>0</v>
       </c>
       <c r="K119" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L119" s="5" t="n">
         <v>0</v>
@@ -14551,12 +14673,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Leatherhead</t>
+          <t>Farnborough</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
@@ -14567,10 +14689,10 @@
       </c>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>0</v>
@@ -14602,12 +14724,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Maidenhead</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -14618,25 +14740,25 @@
       </c>
       <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M121" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N121" s="5" t="n">
         <v>0</v>
@@ -14653,12 +14775,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Maldon</t>
+          <t>Knaresborough</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
@@ -14678,10 +14800,10 @@
         <v>0</v>
       </c>
       <c r="J122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="K122" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="L122" s="3" t="n">
         <v>0</v>
@@ -14704,12 +14826,12 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Margate</t>
+          <t>Lisburn</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
@@ -14720,10 +14842,10 @@
       </c>
       <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I123" s="5" t="n">
         <v>0</v>
@@ -14755,12 +14877,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Maidenhead</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -14771,13 +14893,13 @@
       </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" s="3" t="n">
         <v>0</v>
@@ -14789,7 +14911,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -14806,12 +14928,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Newton Abbot</t>
+          <t>Margate</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -14822,13 +14944,13 @@
       </c>
       <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H125" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J125" s="5" t="n">
         <v>0</v>
@@ -14857,12 +14979,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Redhill</t>
+          <t>Newbury</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -14873,13 +14995,13 @@
       </c>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H126" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" s="3" t="n">
         <v>0</v>
@@ -14908,12 +15030,12 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Redhill</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -14924,7 +15046,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H127" s="5" t="n">
         <v>0</v>
@@ -14936,10 +15058,10 @@
         <v>0</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M127" s="5" t="n">
         <v>0</v>
@@ -14959,12 +15081,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Ringwood</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -14975,10 +15097,10 @@
       </c>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>0</v>
@@ -15010,12 +15132,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Tadley</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15026,10 +15148,10 @@
       </c>
       <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I129" s="5" t="n">
         <v>0</v>
@@ -15061,12 +15183,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -15077,10 +15199,10 @@
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I130" s="3" t="n">
         <v>0</v>
@@ -15112,12 +15234,12 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Verwood</t>
+          <t>Swindon</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15163,12 +15285,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Tadley</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
@@ -15182,7 +15304,7 @@
         <v>0</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I132" s="3" t="n">
         <v>0</v>
@@ -15191,7 +15313,7 @@
         <v>0</v>
       </c>
       <c r="K132" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L132" s="3" t="n">
         <v>0</v>
@@ -15214,26 +15336,26 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Alresford</t>
+          <t>Ulverston</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Cumbria - South</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I133" s="5" t="n">
         <v>0</v>
@@ -15265,23 +15387,23 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Atherstone</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -15299,7 +15421,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
@@ -15316,23 +15438,23 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Basildon</t>
+          <t>Welwyn Garden City</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135" s="5" t="n">
         <v>0</v>
@@ -15344,10 +15466,10 @@
         <v>0</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M135" s="5" t="n">
         <v>0</v>
@@ -15367,12 +15489,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Beaminster</t>
+          <t>Alresford</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
@@ -15418,12 +15540,12 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Berwick-upon-tweed</t>
+          <t>Basildon</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
@@ -15440,7 +15562,7 @@
         <v>0</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J137" s="5" t="n">
         <v>0</v>
@@ -15449,7 +15571,7 @@
         <v>0</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" s="5" t="n">
         <v>0</v>
@@ -15469,12 +15591,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Bexhill-on-sea</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -15520,12 +15642,12 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Billericay</t>
+          <t>Beaminster</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
@@ -15571,12 +15693,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Birchington</t>
+          <t>Bexhill-on-sea</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
@@ -15587,10 +15709,10 @@
       </c>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140" s="3" t="n">
         <v>0</v>
@@ -15622,12 +15744,12 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Billericay</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
@@ -15673,12 +15795,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Bridgwater</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
@@ -15724,12 +15846,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Brighouse</t>
+          <t>Bridgwater</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
@@ -15740,7 +15862,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" s="5" t="n">
         <v>0</v>
@@ -15755,7 +15877,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M143" s="5" t="n">
         <v>0</v>
@@ -15775,12 +15897,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Buckingham</t>
+          <t>Brighouse</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
@@ -15791,7 +15913,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144" s="3" t="n">
         <v>0</v>
@@ -15806,7 +15928,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" s="3" t="n">
         <v>0</v>
@@ -15826,12 +15948,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Bury St. Edmunds</t>
+          <t>Buckingham</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
@@ -15877,12 +15999,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Chertsey</t>
+          <t>Bury St. Edmunds</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
@@ -15893,10 +16015,10 @@
       </c>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I146" s="3" t="n">
         <v>0</v>
@@ -15928,12 +16050,12 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Chichester</t>
+          <t>Cheadle</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
@@ -15944,7 +16066,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" s="5" t="n">
         <v>0</v>
@@ -15956,7 +16078,7 @@
         <v>0</v>
       </c>
       <c r="K147" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L147" s="5" t="n">
         <v>0</v>
@@ -16046,7 +16168,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149" s="5" t="n">
         <v>0</v>
@@ -16061,7 +16183,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M149" s="5" t="n">
         <v>0</v>
@@ -16132,12 +16254,12 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Congleton</t>
+          <t>Clydebank</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
@@ -16183,12 +16305,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Crawley</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
@@ -16202,13 +16324,13 @@
         <v>0</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I152" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J152" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K152" s="3" t="n">
         <v>0</v>
@@ -16234,12 +16356,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Dunmow</t>
+          <t>Congleton</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
@@ -16250,7 +16372,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H153" s="5" t="n">
         <v>0</v>
@@ -16265,7 +16387,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M153" s="5" t="n">
         <v>0</v>
@@ -16285,12 +16407,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Eastbourne</t>
+          <t>Crewe</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
@@ -16301,10 +16423,10 @@
       </c>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>0</v>
@@ -16336,12 +16458,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Esher</t>
+          <t>Dunmow</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
@@ -16358,7 +16480,7 @@
         <v>0</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J155" s="5" t="n">
         <v>0</v>
@@ -16367,7 +16489,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" s="5" t="n">
         <v>0</v>
@@ -16387,12 +16509,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Fareham</t>
+          <t>Eastbourne</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
@@ -16438,12 +16560,12 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Farnborough</t>
+          <t>Eccles</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
@@ -16489,12 +16611,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Folkestone</t>
+          <t>Esher</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
@@ -16511,13 +16633,13 @@
         <v>0</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J158" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K158" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L158" s="3" t="n">
         <v>0</v>
@@ -16540,12 +16662,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Freshwater</t>
+          <t>Faversham</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -16591,12 +16713,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Gainsborough</t>
+          <t>Ferndown</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -16642,12 +16764,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Godalming</t>
+          <t>Folkestone</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
@@ -16664,13 +16786,13 @@
         <v>0</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J161" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K161" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L161" s="5" t="n">
         <v>0</v>
@@ -16693,7 +16815,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Gosport</t>
+          <t>Freshwater</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -16744,12 +16866,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Gravesend</t>
+          <t>Gainsborough</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
@@ -16760,10 +16882,10 @@
       </c>
       <c r="F163" s="4" t="inlineStr"/>
       <c r="G163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I163" s="5" t="n">
         <v>0</v>
@@ -16795,12 +16917,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Great Yarmouth</t>
+          <t>Gosport</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
@@ -16811,10 +16933,10 @@
       </c>
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164" s="3" t="n">
         <v>0</v>
@@ -16846,12 +16968,12 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Halifax</t>
+          <t>Gravesend</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
@@ -16862,10 +16984,10 @@
       </c>
       <c r="F165" s="4" t="inlineStr"/>
       <c r="G165" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165" s="5" t="n">
         <v>0</v>
@@ -16897,12 +17019,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Great Yarmouth</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
@@ -16913,7 +17035,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" s="3" t="n">
         <v>0</v>
@@ -16928,7 +17050,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M166" s="3" t="n">
         <v>0</v>
@@ -16948,12 +17070,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>Halifax</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
@@ -16964,13 +17086,13 @@
       </c>
       <c r="F167" s="4" t="inlineStr"/>
       <c r="G167" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J167" s="5" t="n">
         <v>0</v>
@@ -16999,12 +17121,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
@@ -17018,7 +17140,7 @@
         <v>0</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I168" s="3" t="n">
         <v>0</v>
@@ -17027,7 +17149,7 @@
         <v>0</v>
       </c>
       <c r="K168" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L168" s="3" t="n">
         <v>0</v>
@@ -17050,12 +17172,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Hertford</t>
+          <t>Hastings</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
@@ -17066,13 +17188,13 @@
       </c>
       <c r="F169" s="4" t="inlineStr"/>
       <c r="G169" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H169" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J169" s="5" t="n">
         <v>0</v>
@@ -17101,12 +17223,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
@@ -17117,10 +17239,10 @@
       </c>
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I170" s="3" t="n">
         <v>0</v>
@@ -17152,12 +17274,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Hertford</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
@@ -17203,12 +17325,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Keighley</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
@@ -17219,7 +17341,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172" s="3" t="n">
         <v>0</v>
@@ -17234,7 +17356,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M172" s="3" t="n">
         <v>0</v>
@@ -17254,12 +17376,12 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Kirriemuir</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
@@ -17270,7 +17392,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr"/>
       <c r="G173" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H173" s="5" t="n">
         <v>0</v>
@@ -17279,7 +17401,7 @@
         <v>0</v>
       </c>
       <c r="J173" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K173" s="5" t="n">
         <v>0</v>
@@ -17305,12 +17427,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Keynsham</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
@@ -17356,12 +17478,12 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Lisburn</t>
+          <t>Kirriemuir</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
@@ -17407,12 +17529,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Liss</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
@@ -17423,10 +17545,10 @@
       </c>
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I176" s="3" t="n">
         <v>0</v>
@@ -17458,12 +17580,12 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Littlehampton</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
@@ -17509,12 +17631,12 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Luton</t>
+          <t>Leigh-on-sea</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
@@ -17525,7 +17647,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H178" s="3" t="n">
         <v>0</v>
@@ -17537,7 +17659,7 @@
         <v>0</v>
       </c>
       <c r="K178" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L178" s="3" t="n">
         <v>0</v>
@@ -17560,7 +17682,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Lyndhurst</t>
+          <t>Liss</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -17576,10 +17698,10 @@
       </c>
       <c r="F179" s="4" t="inlineStr"/>
       <c r="G179" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H179" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I179" s="5" t="n">
         <v>0</v>
@@ -17611,12 +17733,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Littlehampton</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
@@ -17627,13 +17749,13 @@
       </c>
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H180" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J180" s="3" t="n">
         <v>0</v>
@@ -17662,12 +17784,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Pontefract</t>
+          <t>Lyndhurst</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
@@ -17713,12 +17835,12 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Reigate</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -17729,7 +17851,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182" s="3" t="n">
         <v>0</v>
@@ -17741,7 +17863,7 @@
         <v>0</v>
       </c>
       <c r="K182" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L182" s="3" t="n">
         <v>0</v>
@@ -17764,12 +17886,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -17786,7 +17908,7 @@
         <v>0</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J183" s="5" t="n">
         <v>0</v>
@@ -17795,7 +17917,7 @@
         <v>0</v>
       </c>
       <c r="L183" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M183" s="5" t="n">
         <v>0</v>
@@ -17815,12 +17937,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Ringwood</t>
+          <t>Pontefract</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
@@ -17831,10 +17953,10 @@
       </c>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I184" s="3" t="n">
         <v>0</v>
@@ -17866,12 +17988,12 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Redditch</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
@@ -17917,12 +18039,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Seaford</t>
+          <t>Reigate</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
@@ -17933,7 +18055,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H186" s="3" t="n">
         <v>0</v>
@@ -17945,7 +18067,7 @@
         <v>0</v>
       </c>
       <c r="K186" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L186" s="3" t="n">
         <v>0</v>
@@ -17968,12 +18090,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Sevenoaks</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
@@ -17984,7 +18106,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr"/>
       <c r="G187" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H187" s="5" t="n">
         <v>0</v>
@@ -17999,7 +18121,7 @@
         <v>0</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M187" s="5" t="n">
         <v>0</v>
@@ -18019,12 +18141,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Sherborne</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
@@ -18035,7 +18157,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H188" s="3" t="n">
         <v>0</v>
@@ -18050,7 +18172,7 @@
         <v>0</v>
       </c>
       <c r="L188" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M188" s="3" t="n">
         <v>0</v>
@@ -18070,12 +18192,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Smethwick</t>
+          <t>Seaford</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
@@ -18121,12 +18243,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>South Shields</t>
+          <t>Sittingbourne</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -18172,12 +18294,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Southend-on-sea</t>
+          <t>Smethwick</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
@@ -18223,12 +18345,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Spennymoor</t>
+          <t>South Shields</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -18239,10 +18361,10 @@
       </c>
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I192" s="3" t="n">
         <v>0</v>
@@ -18274,12 +18396,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Spennymoor</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
@@ -18290,13 +18412,13 @@
       </c>
       <c r="F193" s="4" t="inlineStr"/>
       <c r="G193" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H193" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J193" s="5" t="n">
         <v>0</v>
@@ -18325,12 +18447,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Stockport</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -18341,13 +18463,13 @@
       </c>
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H194" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J194" s="3" t="n">
         <v>0</v>
@@ -18427,12 +18549,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -18443,10 +18565,10 @@
       </c>
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I196" s="3" t="n">
         <v>0</v>
@@ -18478,12 +18600,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Tranent</t>
+          <t>Torquay</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -18529,12 +18651,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Trowbridge</t>
+          <t>Tranent</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -18580,12 +18702,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Ulverston</t>
+          <t>Trowbridge</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Cumbria - South</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -18596,10 +18718,10 @@
       </c>
       <c r="F199" s="4" t="inlineStr"/>
       <c r="G199" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H199" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I199" s="5" t="n">
         <v>0</v>
@@ -18631,12 +18753,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Uttoxeter</t>
+          <t>Truro</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -18682,12 +18804,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Ventnor</t>
+          <t>Uttoxeter</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -18698,10 +18820,10 @@
       </c>
       <c r="F201" s="4" t="inlineStr"/>
       <c r="G201" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H201" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I201" s="5" t="n">
         <v>0</v>
@@ -18733,12 +18855,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Ventnor</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -18749,10 +18871,10 @@
       </c>
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I202" s="3" t="n">
         <v>0</v>
@@ -18784,12 +18906,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Waltham Abbey</t>
+          <t>Verwood</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -18835,12 +18957,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Welwyn Garden City</t>
+          <t>Waltham Abbey</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -18851,7 +18973,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H204" s="3" t="n">
         <v>0</v>
@@ -18863,7 +18985,7 @@
         <v>0</v>
       </c>
       <c r="K204" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L204" s="3" t="n">
         <v>0</v>
@@ -18886,12 +19008,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Warminster</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -18902,10 +19024,10 @@
       </c>
       <c r="F205" s="4" t="inlineStr"/>
       <c r="G205" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H205" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I205" s="5" t="n">
         <v>0</v>
@@ -18937,12 +19059,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -18988,12 +19110,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Weybridge</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -19004,13 +19126,13 @@
       </c>
       <c r="F207" s="4" t="inlineStr"/>
       <c r="G207" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H207" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J207" s="5" t="n">
         <v>0</v>
@@ -19039,12 +19161,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Winsford</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -19090,12 +19212,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Woodbridge</t>
+          <t>Wigan</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -19141,12 +19263,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Worthing</t>
+          <t>Windsor</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -19192,12 +19314,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Wymondham</t>
+          <t>Winsford</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -19243,12 +19365,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -19259,10 +19381,10 @@
       </c>
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I212" s="3" t="n">
         <v>0</v>
@@ -19286,8 +19408,212 @@
         <v>0</v>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>Woodbridge</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>Suffolk</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" s="4" t="inlineStr"/>
+      <c r="G213" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Worthing</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Sussex</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" s="2" t="inlineStr"/>
+      <c r="G214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>Wymondham</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>Norfolk</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" s="4" t="inlineStr"/>
+      <c r="G215" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H215" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Yeovil</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Somerset</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" s="2" t="inlineStr"/>
+      <c r="G216" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O212"/>
+  <autoFilter ref="A1:O216"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19366,7 +19692,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
@@ -19383,15 +19709,15 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="5" t="n">
@@ -19406,18 +19732,18 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
@@ -19435,7 +19761,7 @@
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
@@ -19452,13 +19778,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
@@ -19488,16 +19814,14 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="G8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
@@ -19527,10 +19851,8 @@
           <t>Cornwall</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
@@ -19563,7 +19885,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
@@ -19611,7 +19933,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="5" t="n">
@@ -19620,7 +19942,7 @@
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr"/>
@@ -19632,7 +19954,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
@@ -19649,18 +19971,18 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr"/>
@@ -19672,13 +19994,13 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>9</v>
@@ -19693,18 +20015,18 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>4</v>
@@ -19733,13 +20055,13 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr"/>
@@ -19752,7 +20074,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr"/>
@@ -19769,13 +20091,13 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr"/>
@@ -19811,11 +20133,11 @@
       </c>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
@@ -19828,17 +20150,17 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
@@ -19926,7 +20248,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
@@ -19943,7 +20265,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
       <c r="D33" s="4" t="inlineStr"/>
@@ -19960,30 +20282,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -19993,13 +20313,13 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr"/>
@@ -20057,7 +20377,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
@@ -20076,20 +20396,20 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
@@ -20156,7 +20476,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
@@ -20173,13 +20493,13 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
@@ -20215,7 +20535,7 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr"/>
@@ -20223,7 +20543,7 @@
       <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47" s="4" t="inlineStr"/>
     </row>
@@ -20234,7 +20554,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>2</v>
@@ -20242,7 +20562,7 @@
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
@@ -20285,7 +20605,7 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
       <c r="D51" s="4" t="inlineStr"/>
@@ -20364,11 +20684,11 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
@@ -20413,7 +20733,7 @@
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
       <c r="D59" s="4" t="inlineStr"/>
@@ -20451,7 +20771,7 @@
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
       <c r="D61" s="4" t="inlineStr"/>
@@ -20472,12 +20792,12 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr"/>
@@ -20491,22 +20811,24 @@
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D63" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr"/>
-      <c r="I63" s="5" t="n">
-        <v>1</v>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -20516,21 +20838,19 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+      <c r="D64" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
     </row>
@@ -20635,17 +20955,17 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I71" s="4" t="inlineStr"/>
     </row>
@@ -20656,7 +20976,7 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="inlineStr"/>
@@ -20673,7 +20993,7 @@
         </is>
       </c>
       <c r="B73" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
       <c r="D73" s="4" t="inlineStr"/>
@@ -20681,7 +21001,7 @@
       <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="inlineStr"/>
       <c r="H73" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I73" s="4" t="inlineStr"/>
     </row>
@@ -20692,12 +21012,10 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr"/>
@@ -20713,7 +21031,7 @@
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
       <c r="D75" s="4" t="inlineStr"/>
@@ -20730,7 +21048,7 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="inlineStr"/>
@@ -20747,16 +21065,16 @@
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
       <c r="D77" s="4" t="inlineStr"/>
       <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
       <c r="I77" s="4" t="inlineStr"/>
@@ -20768,7 +21086,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>1</v>
@@ -20787,23 +21105,25 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
           <t>CHECK</t>
         </is>
       </c>
-      <c r="D79" s="5" t="n">
-        <v>1</v>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
       </c>
       <c r="E79" s="4" t="inlineStr"/>
       <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I79" s="4" t="inlineStr"/>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2096</v>
+        <v>2102</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1231</v>
+        <v>1240</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>118</v>
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1053</v>
+        <v>1076</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>186</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>945</v>
+        <v>909</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>24</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>725</v>
+        <v>738</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>10</v>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>35</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>2</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>3</v>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>3</v>
@@ -854,7 +854,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
   </sheetData>
@@ -21264,7 +21264,7 @@
       <c r="F3" s="14" t="inlineStr"/>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>9 / 3.0 / 3/14</t>
+          <t>10 / 3.1 / 3/14</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr"/>
@@ -21319,7 +21319,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -21330,7 +21330,7 @@
       <c r="F5" s="14" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>8 / 2.9 / 3/14</t>
+          <t>9 / 2.9 / 3/14</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
@@ -21431,7 +21431,7 @@
       <c r="B8" s="13" t="inlineStr"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -21556,7 +21556,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>8 / 1.1 / 1/14</t>
+          <t>7 / 1.0 / 1/14</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -21743,7 +21743,7 @@
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.2 / 2/14</t>
+          <t>1 / 3.1 / 2/14</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
@@ -21754,7 +21754,7 @@
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.0 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21810,7 +21810,7 @@
       <c r="B17" s="14" t="inlineStr"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>3 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
@@ -22044,7 +22044,7 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>5 / 4.4 / 2/14</t>
+          <t>6 / 4.5 / 3/14</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -22269,7 +22269,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>4 / 3.4 / 0/14</t>
+          <t>3 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -22426,7 +22426,7 @@
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.0 / 0/14</t>
+          <t>3 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
@@ -22692,7 +22692,7 @@
       <c r="B39" s="14" t="inlineStr"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>4 / 0.6 / 0/14</t>
+          <t>2 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
@@ -22708,7 +22708,7 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>14 / 3.2 / 3/14</t>
+          <t>13 / 3.1 / 3/14</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
@@ -22797,12 +22797,12 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -22902,7 +22902,7 @@
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/14</t>
+          <t>2 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
@@ -23023,7 +23023,7 @@
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.4 / 0/14</t>
+          <t>1 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -23181,7 +23181,7 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/14</t>
+          <t>1 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
@@ -23191,7 +23191,7 @@
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/14</t>
+          <t>2 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -23275,7 +23275,7 @@
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>2 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -23414,7 +23414,7 @@
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
@@ -23657,12 +23657,12 @@
       <c r="B62" s="13" t="inlineStr"/>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.1 / 0/14</t>
+          <t>3 / 3.0 / 0/14</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
@@ -23730,7 +23730,7 @@
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>5 / 5.3 / 5/14</t>
+          <t>4 / 5.2 / 5/14</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -24106,7 +24106,7 @@
       <c r="B73" s="14" t="inlineStr"/>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/14</t>
+          <t>2 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
@@ -24121,7 +24121,7 @@
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>4 / 4.9 / 4/14</t>
+          <t>3 / 4.8 / 4/14</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -24227,7 +24227,7 @@
       <c r="B76" s="13" t="inlineStr"/>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
@@ -24287,7 +24287,7 @@
       <c r="G77" s="14" t="inlineStr"/>
       <c r="H77" s="14" t="inlineStr">
         <is>
-          <t>2 / 3.9 / 4/14</t>
+          <t>1 / 3.8 / 4/14</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
@@ -24306,7 +24306,7 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.4 / 0/14</t>
+          <t>1 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -24316,12 +24316,12 @@
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>3 / 4.9 / 4/14</t>
+          <t>2 / 4.8 / 4/14</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.7 / 0/14</t>
+          <t>5 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$199</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$215</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1209</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2102</v>
+        <v>2138</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3">
@@ -661,7 +661,7 @@
         <v>1240</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4">
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1076</v>
+        <v>1057</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>24</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>10</v>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>2</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>3</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
@@ -8350,7 +8350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O216"/>
+  <dimension ref="A1:O215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14010,12 +14010,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr"/>
       <c r="G107" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H107" s="5" t="n">
         <v>0</v>
@@ -14038,7 +14038,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="5" t="n">
         <v>0</v>
@@ -14061,12 +14061,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Newton Abbot</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
@@ -14077,13 +14077,13 @@
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" s="3" t="n">
         <v>0</v>
@@ -14112,12 +14112,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Newton Abbot</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -14128,13 +14128,13 @@
       </c>
       <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H109" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109" s="5" t="n">
         <v>0</v>
@@ -14163,12 +14163,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
@@ -14179,13 +14179,13 @@
       </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -14223,20 +14223,20 @@
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E111" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H111" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="J111" s="5" t="n">
         <v>0</v>
@@ -14265,12 +14265,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Ballyclare</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
@@ -14281,13 +14281,13 @@
       </c>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -14316,12 +14316,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Ballyclare</t>
+          <t>Camberley</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Camberley</t>
+          <t>Caterham</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -14383,10 +14383,10 @@
       </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" s="3" t="n">
         <v>0</v>
@@ -14418,7 +14418,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Caterham</t>
+          <t>Chertsey</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -14434,10 +14434,10 @@
       </c>
       <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I115" s="5" t="n">
         <v>0</v>
@@ -14469,12 +14469,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Chertsey</t>
+          <t>Chichester</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
@@ -14485,13 +14485,13 @@
       </c>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" s="3" t="n">
         <v>0</v>
@@ -14520,12 +14520,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Chichester</t>
+          <t>Cramlington</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14536,13 +14536,13 @@
       </c>
       <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J117" s="5" t="n">
         <v>0</v>
@@ -14571,12 +14571,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Cramlington</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -14587,13 +14587,13 @@
       </c>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Farnborough</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -14638,10 +14638,10 @@
       </c>
       <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" s="5" t="n">
         <v>0</v>
@@ -14673,12 +14673,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Farnborough</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
@@ -14689,13 +14689,13 @@
       </c>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" s="3" t="n">
         <v>0</v>
@@ -14724,12 +14724,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -14746,13 +14746,13 @@
         <v>0</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="5" t="n">
         <v>0</v>
@@ -19263,12 +19263,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Windsor</t>
+          <t>Winsford</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -19314,12 +19314,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Winsford</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -19330,10 +19330,10 @@
       </c>
       <c r="F211" s="4" t="inlineStr"/>
       <c r="G211" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H211" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I211" s="5" t="n">
         <v>0</v>
@@ -19365,12 +19365,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Woodbridge</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -19381,10 +19381,10 @@
       </c>
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I212" s="3" t="n">
         <v>0</v>
@@ -19416,12 +19416,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Woodbridge</t>
+          <t>Worthing</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
@@ -19432,10 +19432,10 @@
       </c>
       <c r="F213" s="4" t="inlineStr"/>
       <c r="G213" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H213" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I213" s="5" t="n">
         <v>0</v>
@@ -19467,12 +19467,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Worthing</t>
+          <t>Wymondham</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -19483,10 +19483,10 @@
       </c>
       <c r="F214" s="2" t="inlineStr"/>
       <c r="G214" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I214" s="3" t="n">
         <v>0</v>
@@ -19518,12 +19518,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Wymondham</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
@@ -19561,59 +19561,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>Yeovil</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>Somerset</t>
-        </is>
-      </c>
-      <c r="D216" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F216" s="2" t="inlineStr"/>
-      <c r="G216" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N216" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O216" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O216"/>
+  <autoFilter ref="A1:O215"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19709,7 +19658,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="5" t="n">
@@ -19755,7 +19704,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr"/>
@@ -21219,27 +21168,27 @@
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.8 / 2/14</t>
+          <t>2 / 3.7 / 2/14</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.5 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/14</t>
+          <t>2 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21252,25 +21201,25 @@
       <c r="B3" s="14" t="inlineStr"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>14 / 2.6 / 1/14</t>
+          <t>14 / 3.5 / 2/14</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr"/>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>10 / 3.1 / 3/14</t>
+          <t>10 / 3.7 / 4/14</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr"/>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21283,25 +21232,25 @@
       <c r="B4" s="13" t="inlineStr"/>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.5 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>5 / 6.6 / 10/14</t>
+          <t>5 / 6.7 / 10/14</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.6 / 0/14</t>
+          <t>5 / 3.8 / 0/14</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.0 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21324,13 +21273,13 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.2 / 1/14</t>
+          <t>6 / 3.6 / 2/14</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>9 / 2.9 / 3/14</t>
+          <t>9 / 3.4 / 4/14</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
@@ -21349,28 +21298,28 @@
       <c r="B6" s="13" t="inlineStr"/>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.0 / 0/14</t>
+          <t>5 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>13 / 4.6 / 3/14</t>
+          <t>13 / 5.4 / 4/14</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.0 / 0/14</t>
+          <t>4 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -21388,17 +21337,17 @@
       <c r="B7" s="14" t="inlineStr"/>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.0 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.7 / 0/14</t>
+          <t>3 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
@@ -21408,7 +21357,7 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>6 / 1.9 / 3/14</t>
+          <t>6 / 2.3 / 4/14</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
@@ -21418,7 +21367,7 @@
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21431,7 +21380,7 @@
       <c r="B8" s="13" t="inlineStr"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -21441,12 +21390,12 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/14</t>
+          <t>1 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.6 / 0/14</t>
+          <t>5 / 3.9 / 0/14</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
@@ -21480,13 +21429,13 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/14</t>
+          <t>1 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.4 / 3/14</t>
+          <t>6 / 2.7 / 4/14</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -21509,7 +21458,7 @@
       <c r="B10" s="13" t="inlineStr"/>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.0 / 0/14</t>
+          <t>3 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -21529,7 +21478,7 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.3 / 0/14</t>
+          <t>3 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -21551,12 +21500,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>7 / 1.0 / 1/14</t>
+          <t>7 / 1.5 / 2/14</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -21598,7 +21547,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
@@ -21614,7 +21563,7 @@
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
@@ -21694,7 +21643,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>0 / 3.0 / 0/14</t>
+          <t>0 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -21732,24 +21681,24 @@
       <c r="B15" s="14" t="inlineStr"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/14</t>
+          <t>3 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr"/>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/14</t>
+          <t>3 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>1 / 3.1 / 2/14</t>
+          <t>1 / 2.8 / 1/14</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>1 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
@@ -21772,12 +21721,12 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.8 / 0/14</t>
+          <t>2 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.9 / 2/14</t>
+          <t>2 / 3.0 / 2/14</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
@@ -21787,17 +21736,17 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>10 / 2.7 / 3/14</t>
+          <t>10 / 3.4 / 4/14</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.9 / 0/14</t>
+          <t>2 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21810,12 +21759,12 @@
       <c r="B17" s="14" t="inlineStr"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.5 / 0/14</t>
+          <t>4 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>7 / 3.8 / 2/14</t>
+          <t>6 / 3.9 / 3/14</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
@@ -21823,12 +21772,12 @@
       <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>3 / 4.3 / 5/14</t>
+          <t>3 / 4.4 / 5/14</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21841,29 +21790,29 @@
       <c r="B18" s="13" t="inlineStr"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.3 / 0/14</t>
+          <t>2 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.6 / 2/14</t>
+          <t>1 / 2.2 / 1/14</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr"/>
       <c r="G18" s="13" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.5 / 0/14</t>
+          <t>0 / 2.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21876,13 +21825,13 @@
       <c r="B19" s="14" t="inlineStr"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>12 / 12.4 / 13/14</t>
+          <t>11 / 12.8 / 14/14</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr"/>
@@ -21890,7 +21839,7 @@
       <c r="H19" s="14" t="inlineStr"/>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -21902,12 +21851,12 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.4 / 0/14</t>
+          <t>2 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
@@ -21927,7 +21876,7 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>7 / 1.9 / 1/14</t>
+          <t>7 / 2.4 / 2/14</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
@@ -21966,17 +21915,17 @@
       <c r="F21" s="14" t="inlineStr"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>4 / 0.8 / 0/14</t>
+          <t>4 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.3 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22004,12 +21953,12 @@
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.3 / 0/14</t>
+          <t>2 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.6 / 0/14</t>
+          <t>3 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
@@ -22034,17 +21983,17 @@
       <c r="D23" s="14" t="inlineStr"/>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.5 / 1/14</t>
+          <t>6 / 2.9 / 2/14</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>2 / 6.0 / 11/14</t>
+          <t>2 / 5.6 / 10/14</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>6 / 4.5 / 3/14</t>
+          <t>6 / 4.8 / 4/14</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -22062,7 +22011,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -22116,23 +22065,23 @@
       <c r="D25" s="14" t="inlineStr"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>14 / 4.4 / 3/14</t>
+          <t>14 / 5.2 / 4/14</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.3 / 0/14</t>
+          <t>3 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22153,7 +22102,7 @@
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>16 / 3.8 / 3/14</t>
+          <t>16 / 4.9 / 4/14</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
@@ -22163,7 +22112,7 @@
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22185,7 +22134,7 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -22195,7 +22144,7 @@
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -22222,7 +22171,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.6 / 0/14</t>
+          <t>2 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -22247,7 +22196,7 @@
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>5 / 0.7 / 0/14</t>
+          <t>5 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -22279,22 +22228,22 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.1 / 0/14</t>
+          <t>2 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.1 / 3/14</t>
+          <t>6 / 2.5 / 4/14</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
@@ -22321,7 +22270,7 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.6 / 0/14</t>
+          <t>3 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
@@ -22331,7 +22280,7 @@
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -22388,7 +22337,7 @@
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.4 / 0/14</t>
+          <t>3 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
@@ -22421,17 +22370,17 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.6 / 0/14</t>
+          <t>4 / 3.9 / 0/14</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/14</t>
+          <t>3 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>6 / 3.2 / 2/14</t>
+          <t>6 / 3.4 / 3/14</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -22459,7 +22408,7 @@
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
@@ -22469,17 +22418,17 @@
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.2 / 0/14</t>
+          <t>3 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>2 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
@@ -22512,28 +22461,28 @@
       <c r="B35" s="14" t="inlineStr"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>6 / 5.9 / 10/14</t>
+          <t>6 / 6.2 / 11/14</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.3 / 0/14</t>
+          <t>5 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
@@ -22550,32 +22499,32 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
+          <t>1 / 1.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
           <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.8 / 0/14</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
@@ -22597,7 +22546,7 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.3 / 0/14</t>
+          <t>4 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -22644,7 +22593,7 @@
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -22664,7 +22613,7 @@
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
@@ -22679,7 +22628,7 @@
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22692,33 +22641,33 @@
       <c r="B39" s="14" t="inlineStr"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>7 / 5.0 / 8/14</t>
+          <t>7 / 5.5 / 9/14</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>13 / 3.1 / 3/14</t>
+          <t>13 / 4.0 / 4/14</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/14</t>
+          <t>3 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22740,7 +22689,7 @@
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.8 / 0/14</t>
+          <t>3 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
@@ -22792,7 +22741,7 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.5 / 0/14</t>
+          <t>1 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -22812,7 +22761,7 @@
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
@@ -22827,7 +22776,7 @@
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22839,7 +22788,7 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 0/14</t>
+          <t>1 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
@@ -22869,12 +22818,12 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22892,32 +22841,32 @@
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>2 / 4.1 / 2/14</t>
+          <t>2 / 3.6 / 1/14</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.1 / 0/14</t>
+          <t>3 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.3 / 0/14</t>
+          <t>2 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>8 / 4.1 / 3/14</t>
+          <t>8 / 4.6 / 4/14</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.8 / 0/14</t>
+          <t>4 / 3.9 / 0/14</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22940,7 +22889,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>3 / 13.6 / 11/14</t>
+          <t>3 / 12.6 / 10/14</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr"/>
@@ -22948,7 +22897,7 @@
       <c r="H45" s="14" t="inlineStr"/>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -22960,7 +22909,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>2 / 18.1 / 11/14</t>
+          <t>2 / 16.5 / 10/14</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -22970,24 +22919,24 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.7 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
+          <t>0 / 1.9 / 0/14</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
           <t>0 / 2.0 / 0/14</t>
         </is>
       </c>
-      <c r="G46" s="13" t="inlineStr">
-        <is>
-          <t>0 / 2.1 / 0/14</t>
-        </is>
-      </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
           <t>0 / 0.1 / 0/14</t>
@@ -22995,7 +22944,7 @@
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23008,27 +22957,27 @@
       <c r="B47" s="14" t="inlineStr"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.2 / 0/14</t>
+          <t>0 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>3 / 5.5 / 9/14</t>
+          <t>3 / 5.6 / 9/14</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.3 / 0/14</t>
+          <t>1 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>11 / 2.1 / 3/14</t>
+          <t>12 / 2.9 / 4/14</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr"/>
@@ -23048,28 +22997,28 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.6 / 0/14</t>
+          <t>3 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>7 / 2.7 / 1/14</t>
+          <t>7 / 3.1 / 2/14</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr"/>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.1 / 2/14</t>
+          <t>5 / 2.5 / 2/14</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23077,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>0 / 3.4 / 0/14</t>
+          <t>0 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -23181,27 +23130,27 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>5 / 1.7 / 0/14</t>
+          <t>6 / 2.1 / 1/14</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>3 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
@@ -23218,7 +23167,7 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.7 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -23265,7 +23214,7 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>8 / 4.1 / 6/14</t>
+          <t>8 / 4.6 / 7/14</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -23275,7 +23224,7 @@
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/14</t>
+          <t>2 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -23323,22 +23272,22 @@
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>2 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
+          <t>1 / 0.3 / 0/14</t>
+        </is>
+      </c>
+      <c r="H54" s="13" t="inlineStr">
+        <is>
           <t>1 / 0.2 / 0/14</t>
-        </is>
-      </c>
-      <c r="H54" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
@@ -23355,7 +23304,7 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
@@ -23370,7 +23319,7 @@
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
@@ -23390,7 +23339,7 @@
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23409,7 +23358,7 @@
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>0 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
@@ -23424,7 +23373,7 @@
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.3 / 0/14</t>
+          <t>2 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="I56" s="13" t="inlineStr">
@@ -23441,7 +23390,7 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
@@ -23536,7 +23485,7 @@
       <c r="B59" s="14" t="inlineStr"/>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
@@ -23551,13 +23500,13 @@
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr"/>
       <c r="H59" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.5 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
@@ -23575,27 +23524,27 @@
       <c r="B60" s="13" t="inlineStr"/>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>2 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.4 / 0/14</t>
+          <t>2 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.7 / 0/14</t>
+          <t>4 / 3.8 / 0/14</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.5 / 0/14</t>
+          <t>3 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -23605,7 +23554,7 @@
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23623,7 +23572,7 @@
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
@@ -23633,12 +23582,12 @@
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>9 / 5.4 / 7/14</t>
+          <t>9 / 5.9 / 8/14</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.4 / 1/14</t>
+          <t>6 / 2.6 / 2/14</t>
         </is>
       </c>
       <c r="H61" s="14" t="inlineStr">
@@ -23662,28 +23611,28 @@
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.0 / 0/14</t>
+          <t>3 / 2.9 / 0/14</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/14</t>
+          <t>2 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>9 / 3.9 / 3/14</t>
+          <t>9 / 4.4 / 4/14</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.7 / 0/14</t>
+          <t>2 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23698,13 +23647,13 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>10 / 9.1 / 13/14</t>
+          <t>9 / 9.4 / 13/14</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>9 / 6.5 / 9/14</t>
+          <t>9 / 6.9 / 10/14</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr">
@@ -23725,23 +23674,23 @@
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>2 / 4.1 / 0/14</t>
+          <t>2 / 3.9 / 0/14</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>4 / 5.2 / 5/14</t>
+          <t>4 / 5.3 / 5/14</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>12 / 7.0 / 5/14</t>
+          <t>12 / 7.7 / 6/14</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -23800,12 +23749,12 @@
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.0 / 0/14</t>
+          <t>0 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 2/14</t>
+          <t>1 / 1.6 / 2/14</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
@@ -23830,7 +23779,7 @@
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
@@ -23853,12 +23802,12 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.1 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
@@ -23868,7 +23817,7 @@
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>6 / 1.3 / 3/14</t>
+          <t>6 / 1.7 / 4/14</t>
         </is>
       </c>
       <c r="H67" s="14" t="inlineStr">
@@ -23915,7 +23864,7 @@
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.2 / 0/14</t>
+          <t>1 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -23937,7 +23886,7 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>11 / 5.1 / 5/14</t>
+          <t>11 / 5.7 / 6/14</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
@@ -23947,7 +23896,7 @@
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
@@ -23957,12 +23906,12 @@
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.5 / 0/14</t>
+          <t>3 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="H69" s="14" t="inlineStr">
@@ -23990,12 +23939,12 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.9 / 0/14</t>
+          <t>3 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.5 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
@@ -24028,29 +23977,29 @@
       <c r="B71" s="14" t="inlineStr"/>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.7 / 2/14</t>
+          <t>3 / 3.3 / 1/14</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>8 / 7.9 / 11/14</t>
+          <t>8 / 8.4 / 12/14</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>7 / 3.8 / 3/14</t>
+          <t>8 / 4.1 / 4/14</t>
         </is>
       </c>
       <c r="H71" s="14" t="inlineStr"/>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24063,7 +24012,7 @@
       <c r="B72" s="13" t="inlineStr"/>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
@@ -24073,17 +24022,17 @@
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>1 / 3.4 / 0/14</t>
+          <t>1 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="F72" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
@@ -24093,7 +24042,7 @@
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24106,27 +24055,27 @@
       <c r="B73" s="14" t="inlineStr"/>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/14</t>
+          <t>1 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 2/14</t>
+          <t>1 / 1.8 / 1/14</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/14</t>
+          <t>3 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>3 / 4.8 / 4/14</t>
+          <t>3 / 4.6 / 3/14</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>8 / 4.6 / 3/14</t>
+          <t>8 / 4.9 / 4/14</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr"/>
@@ -24151,17 +24100,17 @@
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>8 / 3.6 / 1/14</t>
+          <t>8 / 3.9 / 2/14</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>0 / 3.2 / 0/14</t>
+          <t>0 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>9 / 3.9 / 3/14</t>
+          <t>9 / 4.5 / 4/14</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
@@ -24171,7 +24120,7 @@
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24189,32 +24138,32 @@
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>2 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.4 / 0/14</t>
+          <t>3 / 3.5 / 0/14</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.0 / 1/14</t>
+          <t>6 / 2.4 / 2/14</t>
         </is>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>2 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24237,12 +24186,12 @@
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
@@ -24252,12 +24201,12 @@
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24270,7 +24219,7 @@
       <c r="B77" s="14" t="inlineStr"/>
       <c r="C77" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.7 / 0/14</t>
+          <t>2 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
@@ -24280,7 +24229,7 @@
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>8 / 6.3 / 8/14</t>
+          <t>8 / 6.9 / 9/14</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr"/>
@@ -24292,7 +24241,7 @@
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.2 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24306,27 +24255,27 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.5 / 0/14</t>
+          <t>1 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>1 / 3.4 / 0/14</t>
+          <t>1 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>2 / 4.8 / 4/14</t>
+          <t>2 / 4.6 / 4/14</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.8 / 0/14</t>
+          <t>5 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
@@ -24346,19 +24295,19 @@
       <c r="D79" s="14" t="inlineStr"/>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>8 / 7.7 / 11/14</t>
+          <t>8 / 8.0 / 12/14</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>6 / 11.2 / 14/14</t>
+          <t>7 / 10.4 / 14/14</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>
       <c r="H79" s="14" t="inlineStr"/>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>117</v>
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1128</v>
+        <v>1112</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1057</v>
+        <v>1037</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>24</v>
@@ -710,49 +710,49 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>731</v>
+        <v>751</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Banking &amp; Financial Services</t>
+          <t>Retail &amp; Consumer Products</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>513</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer Products</t>
+          <t>Real Estate &amp; Property</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Real Estate &amp; Property</t>
+          <t>Banking &amp; Financial Services</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>34</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>2</v>
@@ -797,27 +797,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Consulting &amp; Corporate Strategy</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Consulting &amp; Corporate Strategy</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
         <v>87</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>3</v>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
@@ -854,7 +854,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>950</v>
+        <v>953</v>
       </c>
     </row>
   </sheetData>
@@ -24786,7 +24786,7 @@
       <c r="F5" s="14" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>9 / 3.4 / 4/14</t>
+          <t>8 / 3.4 / 4/14</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
@@ -24810,7 +24810,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -25012,7 +25012,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>7 / 1.5 / 2/14</t>
+          <t>6 / 1.4 / 2/14</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -25266,12 +25266,12 @@
       <c r="B17" s="14" t="inlineStr"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>4 / 0.8 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.9 / 3/14</t>
+          <t>5 / 3.8 / 2/14</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
@@ -25631,37 +25631,37 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
+          <t>1 / 0.1 / 0/14</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>1 / 0.3 / 0/14</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>0 / 1.4 / 0/14</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>1 / 0.3 / 0/14</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/14</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 1.4 / 0/14</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>1 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
@@ -26731,7 +26731,7 @@
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -26992,7 +26992,7 @@
       <c r="B59" s="14" t="inlineStr"/>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
@@ -27046,7 +27046,7 @@
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.8 / 0/14</t>
+          <t>3 / 3.7 / 0/14</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
@@ -27113,7 +27113,7 @@
       <c r="B62" s="13" t="inlineStr"/>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>2 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
@@ -27627,7 +27627,7 @@
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27762,7 +27762,7 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.3 / 0/14</t>
+          <t>0 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$198</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$284</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$279</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1314</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>364</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1449</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="6">
@@ -648,7 +648,7 @@
         <v>2140</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>117</v>
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1112</v>
+        <v>1089</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -710,36 +710,36 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Retail &amp; Consumer Products</t>
+          <t>Real Estate &amp; Property</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Real Estate &amp; Property</t>
+          <t>Retail &amp; Consumer Products</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>87</v>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>34</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>2</v>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>3</v>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>3</v>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" s="8" t="inlineStr"/>
     </row>
@@ -854,7 +854,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>953</v>
+        <v>957</v>
       </c>
     </row>
   </sheetData>
@@ -8312,7 +8312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O284"/>
+  <dimension ref="A1:O279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8426,14 +8426,14 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>0</v>
@@ -9228,43 +9228,47 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>LIVE PAGE</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Weston-super-mare</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>/manchester/service-administrator-jobs</t>
+        </is>
+      </c>
       <c r="G18" s="3" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>0</v>
@@ -9284,42 +9288,42 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>/manchester/service-administrator-jobs</t>
+          <t>/birmingham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0</v>
@@ -9339,39 +9343,39 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Bristol</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>/birmingham/service-administrator-jobs</t>
+          <t>/bristol/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>0</v>
@@ -9394,33 +9398,33 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Bristol</t>
+          <t>Warrington</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Cheshire - Warrington &amp; Halton</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>/bristol/service-administrator-jobs</t>
+          <t>/warrington/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J21" s="5" t="n">
         <v>0</v>
@@ -9429,7 +9433,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>0</v>
@@ -9458,7 +9462,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>1</v>
@@ -9469,7 +9473,7 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
@@ -9504,27 +9508,27 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Warrington</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - Warrington &amp; Halton</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>/warrington/service-administrator-jobs</t>
+          <t>/nottingham/jobs</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0</v>
@@ -9539,10 +9543,10 @@
         <v>0</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N23" s="5" t="n">
         <v>0</v>
@@ -9568,7 +9572,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>1</v>
@@ -9579,7 +9583,7 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0</v>
@@ -9614,27 +9618,27 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Chelmsford</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>/nottingham/jobs</t>
+          <t>/chelmsford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>0</v>
@@ -9643,16 +9647,16 @@
         <v>0</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N25" s="5" t="n">
         <v>0</v>
@@ -9669,27 +9673,27 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Chelmsford</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Wales South - Cardiff &amp; Vale</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>/chelmsford/service-administrator-jobs</t>
+          <t>/cardiff/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0</v>
@@ -9698,10 +9702,10 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>0</v>
@@ -9724,12 +9728,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Bradford</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -9740,7 +9744,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>/bradford/service-administrator-jobs</t>
+          <t>/glasgow/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
@@ -9750,7 +9754,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
         <v>0</v>
@@ -9759,7 +9763,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="5" t="n">
         <v>0</v>
@@ -9779,12 +9783,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Wales South - Cardiff &amp; Vale</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -9795,14 +9799,14 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>/cardiff/service-administrator-jobs</t>
+          <t>/oxford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0</v>
@@ -9834,12 +9838,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -9850,17 +9854,17 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>/glasgow/service-administrator-jobs</t>
+          <t>/plymouth/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="5" t="n">
         <v>0</v>
@@ -9869,7 +9873,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" s="5" t="n">
         <v>0</v>
@@ -9889,30 +9893,30 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>/oxford/service-administrator-jobs</t>
+          <t>/bradford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0</v>
@@ -9924,7 +9928,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>0</v>
@@ -9944,27 +9948,27 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Leicestershire</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>/plymouth/service-administrator-jobs</t>
+          <t>/leicester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>0</v>
@@ -9979,7 +9983,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M31" s="5" t="n">
         <v>0</v>
@@ -9999,12 +10003,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Leicestershire</t>
+          <t>Merseyside - Liverpool</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
@@ -10015,11 +10019,11 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>/leicester/service-administrator-jobs</t>
+          <t>/liverpool/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0</v>
@@ -10031,7 +10035,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>0</v>
@@ -10054,12 +10058,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Milton Keynes</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Merseyside - Liverpool</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -10070,7 +10074,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>/liverpool/service-administrator-jobs</t>
+          <t>/milton-keynes/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
@@ -10109,39 +10113,39 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Milton Keynes</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
         <v>8</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>/milton-keynes/service-administrator-jobs</t>
+          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0</v>
@@ -10164,33 +10168,33 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>/southampton/service-administrator-jobs, /southampton/support-worker</t>
+          <t>/cambridge/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" s="5" t="n">
         <v>0</v>
@@ -10219,7 +10223,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Peterborough</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -10235,7 +10239,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>/cambridge/service-administrator-jobs</t>
+          <t>/peterborough/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
@@ -10274,27 +10278,27 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Peterborough</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>/peterborough/service-administrator-jobs</t>
+          <t>/edinburgh/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H37" s="5" t="n">
         <v>0</v>
@@ -10329,12 +10333,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Maidstone</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
@@ -10345,14 +10349,14 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>/edinburgh/service-administrator-jobs</t>
+          <t>/maidstone/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>0</v>
@@ -10384,12 +10388,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Huddersfield</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -10400,11 +10404,11 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>/huddersfield/service-administrator-jobs</t>
+          <t>/shrewsbury/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H39" s="5" t="n">
         <v>0</v>
@@ -10419,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="5" t="n">
         <v>0</v>
@@ -10439,30 +10443,30 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Maidstone</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>/maidstone/service-administrator-jobs</t>
+          <t>/coventry/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0</v>
@@ -10477,7 +10481,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>0</v>
@@ -10494,30 +10498,30 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Sheffield</t>
+          <t>Huddersfield</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>/sheffield/service-administrator-jobs</t>
+          <t>/huddersfield/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="5" t="n">
         <v>0</v>
@@ -10529,7 +10533,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="5" t="n">
         <v>0</v>
@@ -10549,27 +10553,27 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>/shrewsbury/service-administrator-jobs</t>
+          <t>/norwich/jobs</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0</v>
@@ -10578,7 +10582,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
@@ -10604,33 +10608,33 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Basingstoke</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>/coventry/service-administrator-jobs</t>
+          <t>/basingstoke/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J43" s="5" t="n">
         <v>0</v>
@@ -10642,7 +10646,7 @@
         <v>0</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N43" s="5" t="n">
         <v>0</v>
@@ -10659,23 +10663,23 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>/norwich/jobs</t>
+          <t>/bedford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
@@ -10688,7 +10692,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
@@ -10714,12 +10718,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Basingstoke</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Yorkshire - East</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
@@ -10730,17 +10734,17 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>/basingstoke/service-administrator-jobs</t>
+          <t>/hull/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H45" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J45" s="5" t="n">
         <v>0</v>
@@ -10769,12 +10773,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Sheffield</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
@@ -10785,14 +10789,14 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>/bedford/service-administrator-jobs</t>
+          <t>/sheffield/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>0</v>
@@ -10824,27 +10828,27 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - East</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>/hull/service-administrator-jobs</t>
+          <t>/barnsley/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H47" s="5" t="n">
         <v>0</v>
@@ -10879,39 +10883,39 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Belfast</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>/reading/jobs</t>
+          <t>/belfast/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -10934,12 +10938,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
@@ -10950,7 +10954,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>/barnsley/service-administrator-jobs</t>
+          <t>/bournemouth/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G49" s="5" t="n">
@@ -10989,12 +10993,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Belfast</t>
+          <t>Gloucester</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
@@ -11005,7 +11009,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>/belfast/service-administrator-jobs</t>
+          <t>/gloucester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
@@ -11021,10 +11025,10 @@
         <v>0</v>
       </c>
       <c r="K50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="M50" s="3" t="n">
         <v>0</v>
@@ -11044,12 +11048,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
@@ -11060,17 +11064,17 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>/bournemouth/service-administrator-jobs</t>
+          <t>/newcastle/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J51" s="5" t="n">
         <v>0</v>
@@ -11099,12 +11103,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Gloucester</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
@@ -11115,17 +11119,17 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>/gloucester/service-administrator-jobs</t>
+          <t>/reading/jobs</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="3" t="n">
         <v>0</v>
@@ -11134,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M52" s="3" t="n">
         <v>0</v>
@@ -11154,12 +11158,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
@@ -11170,17 +11174,17 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>/newcastle/service-administrator-jobs</t>
+          <t>/rotherham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H53" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J53" s="5" t="n">
         <v>0</v>
@@ -11209,27 +11213,27 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Aylesbury</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>/rotherham/service-administrator-jobs</t>
+          <t>/aylesbury/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0</v>
@@ -11264,27 +11268,27 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Bolton</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>/sunderland/service-administrator-jobs</t>
+          <t>/bolton/jobs</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H55" s="5" t="n">
         <v>0</v>
@@ -11319,12 +11323,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Aylesbury</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
@@ -11335,7 +11339,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>/aylesbury/service-administrator-jobs</t>
+          <t>/chester/jobs</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
@@ -11374,12 +11378,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Bolton</t>
+          <t>Doncaster</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Yorkshire - South</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
@@ -11390,7 +11394,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>/bolton/jobs</t>
+          <t>/doncaster/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
@@ -11429,12 +11433,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
@@ -11445,7 +11449,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>/chester/jobs</t>
+          <t>/gateshead/jobs</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
@@ -11484,12 +11488,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>Hemel Hempstead</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - South</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
@@ -11500,11 +11504,11 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>/doncaster/service-administrator-jobs</t>
+          <t>/hemel-hempstead/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" s="5" t="n">
         <v>0</v>
@@ -11516,7 +11520,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="5" t="n">
         <v>0</v>
@@ -11539,12 +11543,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
@@ -11555,7 +11559,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>/gateshead/jobs</t>
+          <t>/portsmouth/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
@@ -11594,12 +11598,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Hemel Hempstead</t>
+          <t>Salford</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
@@ -11610,7 +11614,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>/hemel-hempstead/service-administrator-jobs</t>
+          <t>/salford/jobs</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
@@ -11626,10 +11630,10 @@
         <v>0</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="5" t="n">
         <v>0</v>
@@ -11649,12 +11653,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Stoke-on-trent</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
@@ -11665,7 +11669,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>/portsmouth/service-administrator-jobs</t>
+          <t>/stoke-on-trent/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
@@ -11704,12 +11708,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Salford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
@@ -11720,11 +11724,11 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>/salford/jobs</t>
+          <t>/sunderland/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" s="5" t="n">
         <v>0</v>
@@ -11739,7 +11743,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="5" t="n">
         <v>0</v>
@@ -11759,12 +11763,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Stoke-on-trent</t>
+          <t>Wakefield</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
@@ -11775,7 +11779,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>/stoke-on-trent/service-administrator-jobs</t>
+          <t>/wakefield/jobs</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
@@ -11814,12 +11818,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Wakefield</t>
+          <t>Warwick</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
@@ -11830,11 +11834,11 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>/wakefield/jobs</t>
+          <t>/warwick/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H65" s="5" t="n">
         <v>0</v>
@@ -11852,7 +11856,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" s="5" t="n">
         <v>0</v>
@@ -11869,12 +11873,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Warwick</t>
+          <t>York</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
@@ -11885,11 +11889,11 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>/warwick/service-administrator-jobs</t>
+          <t>/york/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0</v>
@@ -11907,7 +11911,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N66" s="3" t="n">
         <v>0</v>
@@ -11924,27 +11928,27 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Greater Manchester - South</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>/york/service-administrator-jobs</t>
+          <t>/altrincham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" s="5" t="n">
         <v>0</v>
@@ -11979,12 +11983,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Ashford</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - South</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
@@ -11995,17 +11999,17 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>/altrincham/service-administrator-jobs</t>
+          <t>/ashford/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="3" t="n">
         <v>0</v>
@@ -12034,12 +12038,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Ashford</t>
+          <t>Brighton &amp; Hove</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
@@ -12050,17 +12054,17 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>/ashford/service-administrator-jobs</t>
+          <t>/brighton-hove/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="5" t="n">
         <v>0</v>
@@ -12089,12 +12093,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
@@ -12105,14 +12109,14 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>/brighton-hove/service-administrator-jobs</t>
+          <t>/durham/jobs</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>0</v>
@@ -12144,12 +12148,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Northampton</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
@@ -12160,14 +12164,14 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>/durham/jobs</t>
+          <t>/northampton/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" s="5" t="n">
         <v>0</v>
@@ -12199,12 +12203,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Northampton</t>
+          <t>Worcester</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
@@ -12215,7 +12219,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>/northampton/service-administrator-jobs</t>
+          <t>/worcester/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
@@ -12254,27 +12258,23 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Scarborough</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>Yorkshire - North</t>
-        </is>
-      </c>
+          <t>Chester Le Street</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr"/>
       <c r="D73" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>/scarborough/service-administrator-jobs</t>
+          <t>/chester-le-street/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" s="5" t="n">
         <v>0</v>
@@ -12309,27 +12309,23 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Worcester</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Worcestershire</t>
-        </is>
-      </c>
+          <t>Farnham</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>/worcester/service-administrator-jobs</t>
+          <t>/farnham/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" s="3" t="n">
         <v>0</v>
@@ -12364,7 +12360,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Chester Le Street</t>
+          <t>Macclesfield</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -12376,7 +12372,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>/chester-le-street/service-administrator-jobs</t>
+          <t>/macclesfield/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G75" s="5" t="n">
@@ -12415,7 +12411,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Farnham</t>
+          <t>Newtownabbey</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
@@ -12427,7 +12423,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>/farnham/service-administrator-jobs</t>
+          <t>/newtownabbey/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
@@ -12466,7 +12462,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Macclesfield</t>
+          <t>Northallerton</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
@@ -12478,7 +12474,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>/macclesfield/service-administrator-jobs</t>
+          <t>/northallerton/jobs</t>
         </is>
       </c>
       <c r="G77" s="5" t="n">
@@ -12517,7 +12513,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Newtownabbey</t>
+          <t>Poole</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr"/>
@@ -12529,7 +12525,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>/newtownabbey/service-administrator-jobs</t>
+          <t>/poole/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
@@ -12568,7 +12564,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Northallerton</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -12580,7 +12576,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>/northallerton/jobs</t>
+          <t>/scarborough/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G79" s="5" t="n">
@@ -12619,7 +12615,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Poole</t>
+          <t>Wigston</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr"/>
@@ -12631,7 +12627,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>/poole/service-administrator-jobs</t>
+          <t>/wigston/service-administrator-jobs</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
@@ -12665,28 +12661,28 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>LIVE PAGE</t>
+          <t>HOLD – LONDON</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Wigston</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr"/>
+          <t>Barnet</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="D81" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>/wigston/service-administrator-jobs</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H81" s="5" t="n">
         <v>0</v>
@@ -12695,7 +12691,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K81" s="5" t="n">
         <v>0</v>
@@ -12721,7 +12717,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Croydon</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12730,14 +12726,14 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H82" s="3" t="n">
         <v>0</v>
@@ -12746,16 +12742,16 @@
         <v>0</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" s="3" t="n">
         <v>0</v>
@@ -12772,7 +12768,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Croydon</t>
+          <t>Barking</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -12781,17 +12777,17 @@
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E83" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I83" s="5" t="n">
         <v>0</v>
@@ -12800,10 +12796,10 @@
         <v>0</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="5" t="n">
         <v>1</v>
@@ -12823,7 +12819,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Barking</t>
+          <t>Dagenham</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12839,10 +12835,10 @@
       </c>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>0</v>
@@ -12857,7 +12853,7 @@
         <v>0</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>0</v>
@@ -12874,7 +12870,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Dagenham</t>
+          <t>Orpington</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -12890,7 +12886,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H85" s="5" t="n">
         <v>0</v>
@@ -12899,7 +12895,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" s="5" t="n">
         <v>0</v>
@@ -12925,7 +12921,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Orpington</t>
+          <t>Romford</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12944,13 +12940,13 @@
         <v>2</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" s="3" t="n">
         <v>0</v>
@@ -12976,7 +12972,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Romford</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -12985,14 +12981,14 @@
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E87" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H87" s="5" t="n">
         <v>1</v>
@@ -13027,7 +13023,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Carshalton</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -13043,10 +13039,10 @@
       </c>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>0</v>
@@ -13078,7 +13074,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Carshalton</t>
+          <t>Harrow</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -13094,13 +13090,13 @@
       </c>
       <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H89" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" s="5" t="n">
         <v>0</v>
@@ -13112,7 +13108,7 @@
         <v>0</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N89" s="5" t="n">
         <v>0</v>
@@ -13129,7 +13125,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Harrow</t>
+          <t>Kingston Upon Thames</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -13148,7 +13144,7 @@
         <v>0</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" s="3" t="n">
         <v>1</v>
@@ -13163,7 +13159,7 @@
         <v>0</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>0</v>
@@ -13180,7 +13176,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Kingston Upon Thames</t>
+          <t>Southall</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -13196,13 +13192,13 @@
       </c>
       <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" s="5" t="n">
         <v>0</v>
@@ -13231,7 +13227,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Southall</t>
+          <t>Southwark</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -13247,7 +13243,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0</v>
@@ -13262,7 +13258,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>0</v>
@@ -13282,7 +13278,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Southwark</t>
+          <t>Sutton</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -13298,7 +13294,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H93" s="5" t="n">
         <v>0</v>
@@ -13313,7 +13309,7 @@
         <v>0</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="5" t="n">
         <v>0</v>
@@ -13333,7 +13329,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Sutton</t>
+          <t>Uxbridge</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -13384,7 +13380,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Uxbridge</t>
+          <t>Beckenham</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -13393,14 +13389,14 @@
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" s="5" t="n">
         <v>0</v>
@@ -13435,7 +13431,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Beckenham</t>
+          <t>Bushey</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13486,7 +13482,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Bushey</t>
+          <t>Chessington</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -13502,10 +13498,10 @@
       </c>
       <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" s="5" t="n">
         <v>0</v>
@@ -13537,7 +13533,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Chessington</t>
+          <t>Enfield</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13556,7 +13552,7 @@
         <v>0</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I98" s="3" t="n">
         <v>0</v>
@@ -13568,7 +13564,7 @@
         <v>0</v>
       </c>
       <c r="L98" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="3" t="n">
         <v>0</v>
@@ -13588,7 +13584,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Enfield</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -13604,7 +13600,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" s="5" t="n">
         <v>0</v>
@@ -13619,7 +13615,7 @@
         <v>0</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" s="5" t="n">
         <v>0</v>
@@ -13639,7 +13635,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Hounslow</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13655,7 +13651,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
@@ -13673,7 +13669,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>0</v>
@@ -13690,7 +13686,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Hounslow</t>
+          <t>Ilford</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -13715,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" s="5" t="n">
         <v>0</v>
@@ -13724,7 +13720,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N101" s="5" t="n">
         <v>0</v>
@@ -13741,7 +13737,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Ilford</t>
+          <t>Isleworth</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -13757,7 +13753,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" s="3" t="n">
         <v>0</v>
@@ -13766,7 +13762,7 @@
         <v>0</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="n">
         <v>0</v>
@@ -13792,7 +13788,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Isleworth</t>
+          <t>Purley</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -13843,7 +13839,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Purley</t>
+          <t>Wembley</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -13859,10 +13855,10 @@
       </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" s="3" t="n">
         <v>0</v>
@@ -13894,7 +13890,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Wembley</t>
+          <t>West Drayton</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -13910,10 +13906,10 @@
       </c>
       <c r="F105" s="4" t="inlineStr"/>
       <c r="G105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" s="5" t="n">
         <v>0</v>
@@ -13940,40 +13936,40 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>HOLD – LONDON</t>
+          <t>MONITOR</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>West Drayton</t>
+          <t>Guildford</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="3" t="n">
         <v>0</v>
@@ -13996,26 +13992,26 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Guildford</t>
+          <t>Tunbridge Wells</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E107" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F107" s="4" t="inlineStr"/>
       <c r="G107" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I107" s="5" t="n">
         <v>1</v>
@@ -14024,7 +14020,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L107" s="5" t="n">
         <v>0</v>
@@ -14047,35 +14043,35 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Tunbridge Wells</t>
+          <t>Bury St Edmunds</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="3" t="n">
         <v>0</v>
@@ -14098,23 +14094,23 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Northwich</t>
+          <t>Cheltenham</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E109" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H109" s="5" t="n">
         <v>0</v>
@@ -14126,10 +14122,10 @@
         <v>0</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" s="5" t="n">
         <v>0</v>
@@ -14149,23 +14145,23 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Slough</t>
+          <t>Chichester</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H110" s="3" t="n">
         <v>0</v>
@@ -14200,12 +14196,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Bury St Edmunds</t>
+          <t>Dartford</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
@@ -14216,13 +14212,13 @@
       </c>
       <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H111" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J111" s="5" t="n">
         <v>0</v>
@@ -14251,12 +14247,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Cheltenham</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
@@ -14273,7 +14269,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -14282,7 +14278,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -14302,12 +14298,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Chichester</t>
+          <t>High Wycombe</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
@@ -14324,13 +14320,13 @@
         <v>0</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="5" t="n">
         <v>0</v>
@@ -14353,12 +14349,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Dartford</t>
+          <t>Kettering</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
@@ -14369,13 +14365,13 @@
       </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H114" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J114" s="3" t="n">
         <v>0</v>
@@ -14404,12 +14400,12 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Newton Abbot</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
@@ -14455,12 +14451,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Great Yarmouth</t>
+          <t>Northwich</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
@@ -14471,7 +14467,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H116" s="3" t="n">
         <v>0</v>
@@ -14483,7 +14479,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="3" t="n">
         <v>0</v>
@@ -14506,12 +14502,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>High Wycombe</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
@@ -14522,7 +14518,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H117" s="5" t="n">
         <v>0</v>
@@ -14534,7 +14530,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="5" t="n">
         <v>0</v>
@@ -14557,12 +14553,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Kettering</t>
+          <t>Slough</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
@@ -14573,13 +14569,13 @@
       </c>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
@@ -14608,12 +14604,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Newton Abbot</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
@@ -14624,13 +14620,13 @@
       </c>
       <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H119" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119" s="5" t="n">
         <v>0</v>
@@ -14659,12 +14655,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Weston-super-mare</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
@@ -14710,12 +14706,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
@@ -14726,13 +14722,13 @@
       </c>
       <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H121" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" s="5" t="n">
         <v>0</v>
@@ -14761,7 +14757,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Alresford</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -14770,7 +14766,7 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E122" s="3" t="n">
         <v>0</v>
@@ -14783,7 +14779,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" s="3" t="n">
         <v>0</v>
@@ -14812,7 +14808,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Alresford</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -14828,13 +14824,13 @@
       </c>
       <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="J123" s="5" t="n">
         <v>0</v>
@@ -14863,12 +14859,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Atherstone</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
@@ -14879,13 +14875,13 @@
       </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
         <v>0</v>
@@ -14897,7 +14893,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -14914,12 +14910,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Atherstone</t>
+          <t>Ballyclare</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
@@ -14930,7 +14926,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H125" s="5" t="n">
         <v>0</v>
@@ -14948,7 +14944,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N125" s="5" t="n">
         <v>0</v>
@@ -14965,12 +14961,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Ballyclare</t>
+          <t>Basildon</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
@@ -14981,7 +14977,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H126" s="3" t="n">
         <v>0</v>
@@ -14996,7 +14992,7 @@
         <v>0</v>
       </c>
       <c r="L126" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" s="3" t="n">
         <v>0</v>
@@ -15016,12 +15012,12 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Basildon</t>
+          <t>Blyth</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
@@ -15032,7 +15028,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H127" s="5" t="n">
         <v>0</v>
@@ -15047,7 +15043,7 @@
         <v>0</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M127" s="5" t="n">
         <v>0</v>
@@ -15067,12 +15063,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Blyth</t>
+          <t>Bungay</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
@@ -15118,12 +15114,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Bungay</t>
+          <t>Camberley</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
@@ -15169,12 +15165,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Camberley</t>
+          <t>Castleford</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -15220,12 +15216,12 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Castleford</t>
+          <t>Caterham</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
@@ -15236,10 +15232,10 @@
       </c>
       <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131" s="5" t="n">
         <v>0</v>
@@ -15271,7 +15267,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Caterham</t>
+          <t>Chertsey</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -15287,10 +15283,10 @@
       </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I132" s="3" t="n">
         <v>0</v>
@@ -15322,12 +15318,12 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Chertsey</t>
+          <t>Cramlington</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
@@ -15341,10 +15337,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="I133" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="J133" s="5" t="n">
         <v>0</v>
@@ -15373,12 +15369,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Cramlington</t>
+          <t>Eastbourne</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -15389,13 +15385,13 @@
       </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -15424,12 +15420,12 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Eastbourne</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
@@ -15475,7 +15471,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Farnborough</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -15491,10 +15487,10 @@
       </c>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136" s="3" t="n">
         <v>0</v>
@@ -15526,7 +15522,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Farnborough</t>
+          <t>Gosport</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -15542,10 +15538,10 @@
       </c>
       <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" s="5" t="n">
         <v>0</v>
@@ -15577,12 +15573,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Gosport</t>
+          <t>Great Yarmouth</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
@@ -15593,10 +15589,10 @@
       </c>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I138" s="3" t="n">
         <v>0</v>
@@ -17770,12 +17766,12 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Cheddar</t>
+          <t>Christchurch</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
@@ -17821,12 +17817,12 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Christchurch</t>
+          <t>Cleethorpes</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
@@ -17872,12 +17868,12 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Cirencester</t>
+          <t>Clydebank</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Scotland West - Glasgow</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
@@ -17923,12 +17919,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Cleethorpes</t>
+          <t>Colchester</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
@@ -17939,7 +17935,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H184" s="3" t="n">
         <v>0</v>
@@ -17948,7 +17944,7 @@
         <v>0</v>
       </c>
       <c r="J184" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K184" s="3" t="n">
         <v>0</v>
@@ -17974,12 +17970,12 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Clydebank</t>
+          <t>Congleton</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Scotland West - Glasgow</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
@@ -18025,12 +18021,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Colchester</t>
+          <t>Crewe</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
@@ -18041,7 +18037,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H186" s="3" t="n">
         <v>0</v>
@@ -18050,7 +18046,7 @@
         <v>0</v>
       </c>
       <c r="J186" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K186" s="3" t="n">
         <v>0</v>
@@ -18076,12 +18072,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Congleton</t>
+          <t>Devizes</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
@@ -18127,12 +18123,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Corby</t>
+          <t>Diss</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
@@ -18178,12 +18174,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Crewe</t>
+          <t>Droitwich</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
@@ -18229,12 +18225,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Devizes</t>
+          <t>Dunmow</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
@@ -18245,7 +18241,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H190" s="3" t="n">
         <v>0</v>
@@ -18260,7 +18256,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M190" s="3" t="n">
         <v>0</v>
@@ -18280,12 +18276,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Diss</t>
+          <t>Eccles</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Greater Manchester - Manchester &amp; Salford</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
@@ -18331,12 +18327,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Droitwich</t>
+          <t>Ellesmere</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
@@ -18382,12 +18378,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Dunmow</t>
+          <t>Esher</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
@@ -18404,7 +18400,7 @@
         <v>0</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J193" s="5" t="n">
         <v>0</v>
@@ -18413,7 +18409,7 @@
         <v>0</v>
       </c>
       <c r="L193" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M193" s="5" t="n">
         <v>0</v>
@@ -18433,12 +18429,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Eccles</t>
+          <t>Falmouth</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Manchester &amp; Salford</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
@@ -18484,12 +18480,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Ellesmere</t>
+          <t>Ferndown</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
@@ -18535,12 +18531,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Esher</t>
+          <t>Folkestone</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
@@ -18557,13 +18553,13 @@
         <v>0</v>
       </c>
       <c r="I196" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K196" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L196" s="3" t="n">
         <v>0</v>
@@ -18586,12 +18582,12 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Falmouth</t>
+          <t>Gainsborough</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
@@ -18637,12 +18633,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Ferndown</t>
+          <t>Glastonbury</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
@@ -18688,12 +18684,12 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Folkestone</t>
+          <t>Grantham</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
@@ -18704,7 +18700,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr"/>
       <c r="G199" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H199" s="5" t="n">
         <v>0</v>
@@ -18716,7 +18712,7 @@
         <v>0</v>
       </c>
       <c r="K199" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L199" s="5" t="n">
         <v>0</v>
@@ -18739,7 +18735,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Gainsborough</t>
+          <t>Grimsby</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -18790,12 +18786,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Glastonbury</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
@@ -18806,7 +18802,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr"/>
       <c r="G201" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H201" s="5" t="n">
         <v>0</v>
@@ -18818,7 +18814,7 @@
         <v>0</v>
       </c>
       <c r="K201" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L201" s="5" t="n">
         <v>0</v>
@@ -18841,12 +18837,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Grantham</t>
+          <t>Harrogate</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -18857,7 +18853,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H202" s="3" t="n">
         <v>0</v>
@@ -18872,7 +18868,7 @@
         <v>0</v>
       </c>
       <c r="L202" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M202" s="3" t="n">
         <v>0</v>
@@ -18892,12 +18888,12 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Grimsby</t>
+          <t>Hastings</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D203" s="5" t="n">
@@ -18908,13 +18904,13 @@
       </c>
       <c r="F203" s="4" t="inlineStr"/>
       <c r="G203" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H203" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J203" s="5" t="n">
         <v>0</v>
@@ -18943,12 +18939,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Havant</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -18962,7 +18958,7 @@
         <v>0</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I204" s="3" t="n">
         <v>0</v>
@@ -18971,7 +18967,7 @@
         <v>0</v>
       </c>
       <c r="K204" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L204" s="3" t="n">
         <v>0</v>
@@ -18994,12 +18990,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Harrogate</t>
+          <t>Haywards Heath</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
@@ -19010,7 +19006,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr"/>
       <c r="G205" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H205" s="5" t="n">
         <v>0</v>
@@ -19025,7 +19021,7 @@
         <v>0</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M205" s="5" t="n">
         <v>0</v>
@@ -19045,7 +19041,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Hastings</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -19061,13 +19057,13 @@
       </c>
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H206" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J206" s="3" t="n">
         <v>0</v>
@@ -19096,12 +19092,12 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Havant</t>
+          <t>Hove</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
@@ -19112,10 +19108,10 @@
       </c>
       <c r="F207" s="4" t="inlineStr"/>
       <c r="G207" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H207" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I207" s="5" t="n">
         <v>0</v>
@@ -19147,12 +19143,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Haywards Heath</t>
+          <t>Huntingdon</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -19198,12 +19194,12 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Keynsham</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Bristol &amp; Bath</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
@@ -19249,12 +19245,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Hove</t>
+          <t>Kidlington</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -19300,12 +19296,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Huntingdon</t>
+          <t>Kirriemuir</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Scotland Central - Tayside</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
@@ -19351,12 +19347,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Ivybridge</t>
+          <t>Knowle</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>West Midlands - Birmingham &amp; Solihull</t>
         </is>
       </c>
       <c r="D212" s="3" t="n">
@@ -19402,12 +19398,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Keynsham</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Bristol &amp; Bath</t>
+          <t>Northern Ireland - East</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
@@ -19453,12 +19449,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Kidlington</t>
+          <t>Leamington Spa</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D214" s="3" t="n">
@@ -19504,12 +19500,12 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Kirriemuir</t>
+          <t>Leatherhead</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Scotland Central - Tayside</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
@@ -19555,12 +19551,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Knowle</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Birmingham &amp; Solihull</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D216" s="3" t="n">
@@ -19606,12 +19602,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Liskeard</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Northern Ireland - East</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
@@ -19657,12 +19653,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Leamington Spa</t>
+          <t>Liss</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D218" s="3" t="n">
@@ -19673,10 +19669,10 @@
       </c>
       <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I218" s="3" t="n">
         <v>0</v>
@@ -19708,12 +19704,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Leatherhead</t>
+          <t>Littlehampton</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
@@ -19759,12 +19755,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Lowestoft</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
@@ -19810,12 +19806,12 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Liskeard</t>
+          <t>Luton</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
@@ -19861,7 +19857,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Liss</t>
+          <t>Lyndhurst</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -19877,10 +19873,10 @@
       </c>
       <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I222" s="3" t="n">
         <v>0</v>
@@ -19912,12 +19908,12 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Littlehampton</t>
+          <t>Maldon</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
@@ -19963,12 +19959,12 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Lowestoft</t>
+          <t>Margate</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Suffolk</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D224" s="3" t="n">
@@ -19979,10 +19975,10 @@
       </c>
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I224" s="3" t="n">
         <v>0</v>
@@ -20014,12 +20010,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Luton</t>
+          <t>Minehead</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D225" s="5" t="n">
@@ -20065,12 +20061,12 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Lyndhurst</t>
+          <t>Nantwich</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Cheshire - East</t>
         </is>
       </c>
       <c r="D226" s="3" t="n">
@@ -20116,12 +20112,12 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Maldon</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D227" s="5" t="n">
@@ -20167,12 +20163,12 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Margate</t>
+          <t>Oldbury</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D228" s="3" t="n">
@@ -20183,10 +20179,10 @@
       </c>
       <c r="F228" s="2" t="inlineStr"/>
       <c r="G228" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I228" s="3" t="n">
         <v>0</v>
@@ -20218,12 +20214,12 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Minehead</t>
+          <t>Paignton</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
@@ -20269,12 +20265,12 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Nantwich</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Cheshire - East</t>
+          <t>North Scotland</t>
         </is>
       </c>
       <c r="D230" s="3" t="n">
@@ -20285,13 +20281,13 @@
       </c>
       <c r="F230" s="2" t="inlineStr"/>
       <c r="G230" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H230" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J230" s="3" t="n">
         <v>0</v>
@@ -20320,12 +20316,12 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Potton</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Bedfordshire</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
@@ -20371,12 +20367,12 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Oldbury</t>
+          <t>Radstock</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D232" s="3" t="n">
@@ -20422,12 +20418,12 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Paignton</t>
+          <t>Reigate</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D233" s="5" t="n">
@@ -20438,7 +20434,7 @@
       </c>
       <c r="F233" s="4" t="inlineStr"/>
       <c r="G233" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H233" s="5" t="n">
         <v>0</v>
@@ -20450,7 +20446,7 @@
         <v>0</v>
       </c>
       <c r="K233" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L233" s="5" t="n">
         <v>0</v>
@@ -20473,12 +20469,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>North Scotland</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D234" s="3" t="n">
@@ -20495,7 +20491,7 @@
         <v>0</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J234" s="3" t="n">
         <v>0</v>
@@ -20504,7 +20500,7 @@
         <v>0</v>
       </c>
       <c r="L234" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M234" s="3" t="n">
         <v>0</v>
@@ -20524,12 +20520,12 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Pontefract</t>
+          <t>Rickmansworth</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
@@ -20575,12 +20571,12 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Potton</t>
+          <t>Ripon</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Bedfordshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D236" s="3" t="n">
@@ -20591,7 +20587,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H236" s="3" t="n">
         <v>0</v>
@@ -20606,7 +20602,7 @@
         <v>0</v>
       </c>
       <c r="L236" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M236" s="3" t="n">
         <v>0</v>
@@ -20626,12 +20622,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Radstock</t>
+          <t>Royston</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
@@ -20677,12 +20673,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Reigate</t>
+          <t>Salisbury</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D238" s="3" t="n">
@@ -20693,7 +20689,7 @@
       </c>
       <c r="F238" s="2" t="inlineStr"/>
       <c r="G238" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H238" s="3" t="n">
         <v>0</v>
@@ -20705,7 +20701,7 @@
         <v>0</v>
       </c>
       <c r="K238" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L238" s="3" t="n">
         <v>0</v>
@@ -20728,12 +20724,12 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Seaford</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
@@ -20744,7 +20740,7 @@
       </c>
       <c r="F239" s="4" t="inlineStr"/>
       <c r="G239" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H239" s="5" t="n">
         <v>0</v>
@@ -20759,7 +20755,7 @@
         <v>0</v>
       </c>
       <c r="L239" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M239" s="5" t="n">
         <v>0</v>
@@ -20779,12 +20775,12 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Rickmansworth</t>
+          <t>Seaham</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D240" s="3" t="n">
@@ -20830,12 +20826,12 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Ripon</t>
+          <t>Sevenoaks</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D241" s="5" t="n">
@@ -20846,7 +20842,7 @@
       </c>
       <c r="F241" s="4" t="inlineStr"/>
       <c r="G241" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H241" s="5" t="n">
         <v>0</v>
@@ -20861,7 +20857,7 @@
         <v>0</v>
       </c>
       <c r="L241" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M241" s="5" t="n">
         <v>0</v>
@@ -20881,12 +20877,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Royston</t>
+          <t>Shipley</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Yorkshire - West</t>
         </is>
       </c>
       <c r="D242" s="3" t="n">
@@ -20932,12 +20928,12 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Salisbury</t>
+          <t>Skegness</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
@@ -20983,12 +20979,12 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Seaford</t>
+          <t>Sleaford</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Lincolnshire</t>
         </is>
       </c>
       <c r="D244" s="3" t="n">
@@ -21034,12 +21030,12 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Seaham</t>
+          <t>Smethwick</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>West Midlands - Black Country</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
@@ -21085,12 +21081,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Sevenoaks</t>
+          <t>South Shields</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D246" s="3" t="n">
@@ -21101,10 +21097,10 @@
       </c>
       <c r="F246" s="2" t="inlineStr"/>
       <c r="G246" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I246" s="3" t="n">
         <v>0</v>
@@ -21136,12 +21132,12 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Shipley</t>
+          <t>Southend-on-sea</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
@@ -21187,12 +21183,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Skegness</t>
+          <t>Spennymoor</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
         </is>
       </c>
       <c r="D248" s="3" t="n">
@@ -21238,12 +21234,12 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Sleaford</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Lincolnshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
@@ -21254,13 +21250,13 @@
       </c>
       <c r="F249" s="4" t="inlineStr"/>
       <c r="G249" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H249" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I249" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J249" s="5" t="n">
         <v>0</v>
@@ -21289,12 +21285,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Smethwick</t>
+          <t>Street</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Black Country</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D250" s="3" t="n">
@@ -21340,12 +21336,12 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>South Shields</t>
+          <t>Studley</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>West Midlands - Coventry &amp; Warwickshire</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
@@ -21356,10 +21352,10 @@
       </c>
       <c r="F251" s="4" t="inlineStr"/>
       <c r="G251" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H251" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I251" s="5" t="n">
         <v>0</v>
@@ -21391,12 +21387,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Southend-on-sea</t>
+          <t>Tadley</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D252" s="3" t="n">
@@ -21407,10 +21403,10 @@
       </c>
       <c r="F252" s="2" t="inlineStr"/>
       <c r="G252" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H252" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I252" s="3" t="n">
         <v>0</v>
@@ -21442,12 +21438,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Spennymoor</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>North East - County Durham &amp; Darlington/Hartlepool</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
@@ -21493,12 +21489,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Taunton</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Somerset</t>
         </is>
       </c>
       <c r="D254" s="3" t="n">
@@ -21509,13 +21505,13 @@
       </c>
       <c r="F254" s="2" t="inlineStr"/>
       <c r="G254" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H254" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I254" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J254" s="3" t="n">
         <v>0</v>
@@ -21544,12 +21540,12 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Teignmouth</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
@@ -21595,12 +21591,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Studley</t>
+          <t>Telford</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>West Midlands - Coventry &amp; Warwickshire</t>
+          <t>Shropshire</t>
         </is>
       </c>
       <c r="D256" s="3" t="n">
@@ -21646,12 +21642,12 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Tadley</t>
+          <t>Tenbury Wells</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Hampshire</t>
+          <t>Worcestershire</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
@@ -21662,10 +21658,10 @@
       </c>
       <c r="F257" s="4" t="inlineStr"/>
       <c r="G257" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H257" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I257" s="5" t="n">
         <v>0</v>
@@ -21697,12 +21693,12 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Tonbridge</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
@@ -21748,12 +21744,12 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Taunton</t>
+          <t>Tranent</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Somerset</t>
+          <t>Scotland Central - Edinburgh &amp; Lothians</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
@@ -21799,12 +21795,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Teignmouth</t>
+          <t>Trowbridge</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D260" s="3" t="n">
@@ -21850,12 +21846,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Telford</t>
+          <t>Truro</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Shropshire</t>
+          <t>Cornwall</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
@@ -21901,12 +21897,12 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Tenbury Wells</t>
+          <t>Uttoxeter</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Worcestershire</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D262" s="3" t="n">
@@ -21952,12 +21948,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Tonbridge</t>
+          <t>Verwood</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
@@ -22003,12 +21999,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Tranent</t>
+          <t>Wallingford</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Scotland Central - Edinburgh &amp; Lothians</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D264" s="3" t="n">
@@ -22054,12 +22050,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Trowbridge</t>
+          <t>Wallsend</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
@@ -22105,12 +22101,12 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Truro</t>
+          <t>Waltham Abbey</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Cornwall</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D266" s="3" t="n">
@@ -22156,12 +22152,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Uttoxeter</t>
+          <t>Waltham Cross</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
@@ -22207,12 +22203,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Verwood</t>
+          <t>Wantage</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Oxfordshire</t>
         </is>
       </c>
       <c r="D268" s="3" t="n">
@@ -22258,12 +22254,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Wallingford</t>
+          <t>Warminster</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D269" s="5" t="n">
@@ -22274,10 +22270,10 @@
       </c>
       <c r="F269" s="4" t="inlineStr"/>
       <c r="G269" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H269" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I269" s="5" t="n">
         <v>0</v>
@@ -22309,12 +22305,12 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Wallsend</t>
+          <t>Westcliff-on-sea</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>North East - Tyneside, Wearside &amp; Northumberland</t>
+          <t>Essex</t>
         </is>
       </c>
       <c r="D270" s="3" t="n">
@@ -22360,12 +22356,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Waltham Abbey</t>
+          <t>Westerham</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="D271" s="5" t="n">
@@ -22411,12 +22407,12 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Waltham Cross</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Yorkshire - North</t>
         </is>
       </c>
       <c r="D272" s="3" t="n">
@@ -22462,12 +22458,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Wantage</t>
+          <t>Wigan</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Greater Manchester - Wigan &amp; Bolton</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
@@ -22513,12 +22509,12 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Warminster</t>
+          <t>Winsford</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Cheshire - West</t>
         </is>
       </c>
       <c r="D274" s="3" t="n">
@@ -22529,10 +22525,10 @@
       </c>
       <c r="F274" s="2" t="inlineStr"/>
       <c r="G274" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H274" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I274" s="3" t="n">
         <v>0</v>
@@ -22564,12 +22560,12 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Westcliff-on-sea</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Essex</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
@@ -22580,10 +22576,10 @@
       </c>
       <c r="F275" s="4" t="inlineStr"/>
       <c r="G275" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H275" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I275" s="5" t="n">
         <v>0</v>
@@ -22615,12 +22611,12 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Westerham</t>
+          <t>Wokingham</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D276" s="3" t="n">
@@ -22666,12 +22662,12 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Woodbridge</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Yorkshire - North</t>
+          <t>Suffolk</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
@@ -22717,12 +22713,12 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Wigan</t>
+          <t>Worthing</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Greater Manchester - Wigan &amp; Bolton</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="D278" s="3" t="n">
@@ -22733,10 +22729,10 @@
       </c>
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H278" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I278" s="3" t="n">
         <v>0</v>
@@ -22768,12 +22764,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Winsford</t>
+          <t>Wymondham</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Cheshire - West</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D279" s="5" t="n">
@@ -22811,263 +22807,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B280" s="2" t="inlineStr">
-        <is>
-          <t>Woking</t>
-        </is>
-      </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>Surrey</t>
-        </is>
-      </c>
-      <c r="D280" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E280" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F280" s="2" t="inlineStr"/>
-      <c r="G280" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H280" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I280" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J280" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K280" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L280" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M280" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N280" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O280" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B281" s="4" t="inlineStr">
-        <is>
-          <t>Wokingham</t>
-        </is>
-      </c>
-      <c r="C281" s="4" t="inlineStr">
-        <is>
-          <t>Berkshire</t>
-        </is>
-      </c>
-      <c r="D281" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E281" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" s="4" t="inlineStr"/>
-      <c r="G281" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H281" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I281" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J281" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K281" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L281" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M281" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N281" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O281" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B282" s="2" t="inlineStr">
-        <is>
-          <t>Woodbridge</t>
-        </is>
-      </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>Suffolk</t>
-        </is>
-      </c>
-      <c r="D282" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E282" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F282" s="2" t="inlineStr"/>
-      <c r="G282" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H282" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I282" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J282" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K282" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L282" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M282" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N282" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O282" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="4" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B283" s="4" t="inlineStr">
-        <is>
-          <t>Worthing</t>
-        </is>
-      </c>
-      <c r="C283" s="4" t="inlineStr">
-        <is>
-          <t>Sussex</t>
-        </is>
-      </c>
-      <c r="D283" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E283" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F283" s="4" t="inlineStr"/>
-      <c r="G283" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H283" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I283" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J283" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K283" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L283" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M283" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N283" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O283" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="2" t="inlineStr">
-        <is>
-          <t>MONITOR</t>
-        </is>
-      </c>
-      <c r="B284" s="2" t="inlineStr">
-        <is>
-          <t>Wymondham</t>
-        </is>
-      </c>
-      <c r="C284" s="2" t="inlineStr">
-        <is>
-          <t>Norfolk</t>
-        </is>
-      </c>
-      <c r="D284" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E284" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F284" s="2" t="inlineStr"/>
-      <c r="G284" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H284" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I284" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J284" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K284" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L284" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M284" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N284" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O284" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O284"/>
+  <autoFilter ref="A1:O279"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23163,7 +22904,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="5" t="n">
@@ -23287,7 +23028,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
@@ -23387,7 +23128,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="5" t="n">
@@ -23448,7 +23189,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr"/>
@@ -23738,7 +23479,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>9</v>
@@ -23833,7 +23574,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
@@ -23852,7 +23593,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>2</v>
@@ -23932,7 +23673,7 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
@@ -24210,7 +23951,7 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
@@ -24411,7 +24152,7 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>
@@ -24521,7 +24262,7 @@
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
       <c r="D77" s="4" t="inlineStr"/>
@@ -24542,7 +24283,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>1</v>
@@ -24561,7 +24302,7 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
@@ -24670,12 +24411,12 @@
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.7 / 2/14</t>
+          <t>2 / 3.6 / 2/14</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
@@ -24690,12 +24431,12 @@
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24708,25 +24449,25 @@
       <c r="B3" s="14" t="inlineStr"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>14 / 3.5 / 2/14</t>
+          <t>14 / 4.4 / 3/14</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr"/>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>10 / 3.7 / 4/14</t>
+          <t>10 / 4.4 / 5/14</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr"/>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24739,25 +24480,25 @@
       <c r="B4" s="13" t="inlineStr"/>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>2 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>5 / 6.7 / 10/14</t>
+          <t>5 / 6.8 / 10/14</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.8 / 0/14</t>
+          <t>5 / 4.0 / 0/14</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24780,18 +24521,18 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>6 / 3.6 / 2/14</t>
+          <t>6 / 3.9 / 3/14</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>8 / 3.4 / 4/14</t>
+          <t>8 / 3.8 / 5/14</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>1 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr"/>
@@ -24810,23 +24551,23 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.3 / 0/14</t>
+          <t>5 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>13 / 5.4 / 4/14</t>
+          <t>13 / 6.1 / 5/14</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>4 / 2.3 / 0/14</t>
+          <t>4 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -24849,32 +24590,32 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.6 / 0/14</t>
+          <t>3 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.8 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.3 / 4/14</t>
+          <t>6 / 2.7 / 5/14</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24902,7 +24643,7 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.9 / 0/14</t>
+          <t>5 / 4.3 / 0/14</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr"/>
@@ -24942,17 +24683,17 @@
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.7 / 4/14</t>
+          <t>6 / 3.1 / 5/14</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -24965,7 +24706,7 @@
       <c r="B10" s="13" t="inlineStr"/>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.1 / 0/14</t>
+          <t>3 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -24985,7 +24726,7 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.5 / 0/14</t>
+          <t>3 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -25007,12 +24748,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>6 / 1.4 / 2/14</t>
+          <t>5 / 1.8 / 2/14</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
@@ -25070,7 +24811,7 @@
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
@@ -25085,7 +24826,7 @@
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25150,7 +24891,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.7 / 0/14</t>
+          <t>0 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -25170,12 +24911,12 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25188,29 +24929,29 @@
       <c r="B15" s="14" t="inlineStr"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.5 / 0/14</t>
+          <t>3 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr"/>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.4 / 0/14</t>
+          <t>3 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.8 / 1/14</t>
+          <t>1 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr"/>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.7 / 0/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.9 / 0/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25228,12 +24969,12 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.6 / 0/14</t>
+          <t>2 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.0 / 2/14</t>
+          <t>2 / 3.1 / 2/14</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
@@ -25243,17 +24984,17 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>10 / 3.4 / 4/14</t>
+          <t>10 / 4.0 / 5/14</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.1 / 0/14</t>
+          <t>2 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25266,12 +25007,12 @@
       <c r="B17" s="14" t="inlineStr"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>1 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>5 / 3.8 / 2/14</t>
+          <t>4 / 3.7 / 2/14</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr"/>
@@ -25279,12 +25020,12 @@
       <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>3 / 4.4 / 5/14</t>
+          <t>3 / 4.6 / 5/14</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25297,12 +25038,12 @@
       <c r="B18" s="13" t="inlineStr"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.2 / 1/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -25314,12 +25055,12 @@
       <c r="G18" s="13" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.6 / 0/14</t>
+          <t>3 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.2 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25332,13 +25073,13 @@
       <c r="B19" s="14" t="inlineStr"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.0 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>11 / 12.8 / 14/14</t>
+          <t>11 / 13.1 / 14/14</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr"/>
@@ -25346,7 +25087,7 @@
       <c r="H19" s="14" t="inlineStr"/>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25358,7 +25099,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.3 / 0/14</t>
+          <t>2 / 3.2 / 0/14</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -25383,7 +25124,7 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>7 / 2.4 / 2/14</t>
+          <t>7 / 2.9 / 3/14</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
@@ -25393,7 +25134,7 @@
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25422,17 +25163,17 @@
       <c r="F21" s="14" t="inlineStr"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>4 / 1.1 / 0/14</t>
+          <t>4 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25455,27 +25196,27 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/14</t>
+          <t>1 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.8 / 0/14</t>
+          <t>3 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25490,17 +25231,17 @@
       <c r="D23" s="14" t="inlineStr"/>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.9 / 2/14</t>
+          <t>6 / 3.2 / 3/14</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>2 / 5.6 / 10/14</t>
+          <t>2 / 5.3 / 9/14</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>6 / 4.8 / 4/14</t>
+          <t>6 / 5.1 / 5/14</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -25518,7 +25259,7 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.7 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -25543,7 +25284,7 @@
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>1 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
@@ -25578,17 +25319,17 @@
       <c r="F25" s="14" t="inlineStr"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>14 / 5.2 / 4/14</t>
+          <t>14 / 6.1 / 5/14</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.4 / 0/14</t>
+          <t>3 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25603,13 +25344,13 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>7 / 11.1 / 14/14</t>
+          <t>7 / 11.2 / 14/14</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>16 / 4.9 / 4/14</t>
+          <t>16 / 6.1 / 5/14</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
@@ -25619,7 +25360,7 @@
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25631,7 +25372,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
@@ -25641,7 +25382,7 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -25651,7 +25392,7 @@
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -25661,7 +25402,7 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
@@ -25678,7 +25419,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.5 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -25688,7 +25429,7 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -25698,12 +25439,12 @@
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>5 / 1.1 / 0/14</t>
+          <t>5 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -25725,32 +25466,32 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.3 / 0/14</t>
+          <t>3 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.3 / 0/14</t>
+          <t>2 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.5 / 4/14</t>
+          <t>6 / 2.9 / 5/14</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
@@ -25772,12 +25513,12 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.8 / 0/14</t>
+          <t>3 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
@@ -25797,7 +25538,7 @@
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -25844,7 +25585,7 @@
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.6 / 0/14</t>
+          <t>3 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
@@ -25872,22 +25613,22 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.9 / 0/14</t>
+          <t>4 / 4.1 / 0/14</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/14</t>
+          <t>3 / 2.3 / 0/14</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>6 / 3.4 / 3/14</t>
+          <t>7 / 3.7 / 4/14</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -25897,7 +25638,7 @@
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25915,7 +25656,7 @@
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
@@ -25925,22 +25666,22 @@
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.3 / 0/14</t>
+          <t>3 / 2.4 / 0/14</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/14</t>
+          <t>2 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -25978,13 +25719,13 @@
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>6 / 6.2 / 11/14</t>
+          <t>6 / 6.4 / 12/14</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>5 / 2.4 / 0/14</t>
+          <t>5 / 2.6 / 0/14</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
@@ -26006,7 +25747,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -26031,7 +25772,7 @@
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
@@ -26053,7 +25794,7 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>4 / 2.5 / 0/14</t>
+          <t>4 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -26110,7 +25851,7 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -26120,12 +25861,12 @@
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
@@ -26135,7 +25876,7 @@
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.5 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26148,28 +25889,28 @@
       <c r="B39" s="14" t="inlineStr"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.6 / 0/14</t>
+          <t>2 / 0.7 / 0/14</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>7 / 5.5 / 9/14</t>
+          <t>7 / 6.0 / 10/14</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>13 / 4.0 / 4/14</t>
+          <t>13 / 4.9 / 5/14</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.3 / 0/14</t>
+          <t>3 / 2.5 / 0/14</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
@@ -26196,7 +25937,7 @@
       <c r="G40" s="13" t="inlineStr"/>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.9 / 0/14</t>
+          <t>3 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
@@ -26216,7 +25957,7 @@
       <c r="D41" s="14" t="inlineStr"/>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr">
@@ -26248,7 +25989,7 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>1 / 2.4 / 0/14</t>
+          <t>1 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -26258,7 +25999,7 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>1 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -26268,7 +26009,7 @@
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
@@ -26295,7 +26036,7 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.0 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
@@ -26310,27 +26051,27 @@
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
+          <t>0 / 0.5 / 0/14</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.2 / 0/14</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
           <t>0 / 0.6 / 0/14</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.2 / 0/14</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.0 / 0/14</t>
-        </is>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
-        <is>
-          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26343,37 +26084,37 @@
       <c r="B44" s="13" t="inlineStr"/>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.6 / 1/14</t>
+          <t>2 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>3 / 1.2 / 0/14</t>
+          <t>3 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.2 / 0/14</t>
+          <t>2 / 2.1 / 0/14</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>8 / 4.6 / 4/14</t>
+          <t>8 / 5.1 / 5/14</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>4 / 3.9 / 0/14</t>
+          <t>4 / 4.1 / 0/14</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26396,7 +26137,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>3 / 12.6 / 10/14</t>
+          <t>3 / 11.5 / 9/14</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr"/>
@@ -26404,7 +26145,7 @@
       <c r="H45" s="14" t="inlineStr"/>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.8 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26416,7 +26157,7 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>2 / 16.5 / 10/14</t>
+          <t>2 / 14.9 / 9/14</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -26426,12 +26167,12 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.5 / 0/14</t>
+          <t>1 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
@@ -26441,17 +26182,17 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.0 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26464,12 +26205,12 @@
       <c r="B47" s="14" t="inlineStr"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>0 / 2.1 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
@@ -26479,18 +26220,18 @@
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>1 / 2.1 / 0/14</t>
+          <t>1 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>12 / 2.9 / 4/14</t>
+          <t>12 / 3.7 / 5/14</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr"/>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26504,28 +26245,28 @@
       <c r="C48" s="13" t="inlineStr"/>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>3 / 3.4 / 0/14</t>
+          <t>3 / 3.3 / 0/14</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>7 / 3.1 / 2/14</t>
+          <t>7 / 3.6 / 3/14</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr"/>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>5 / 2.5 / 2/14</t>
+          <t>5 / 2.9 / 2/14</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.2 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26584,7 +26325,7 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>0 / 3.2 / 0/14</t>
+          <t>0 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -26594,7 +26335,7 @@
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.4 / 0/14</t>
+          <t>0 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -26637,32 +26378,32 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.1 / 1/14</t>
+          <t>6 / 2.4 / 2/14</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>3 / 1.8 / 0/14</t>
+          <t>3 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26674,7 +26415,7 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.6 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -26694,7 +26435,7 @@
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
@@ -26721,7 +26462,7 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>8 / 4.6 / 7/14</t>
+          <t>8 / 5.0 / 8/14</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -26779,22 +26520,22 @@
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/14</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
+          <t>1 / 0.4 / 0/14</t>
+        </is>
+      </c>
+      <c r="H54" s="13" t="inlineStr">
+        <is>
           <t>1 / 0.3 / 0/14</t>
-        </is>
-      </c>
-      <c r="H54" s="13" t="inlineStr">
-        <is>
-          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
@@ -26826,7 +26567,7 @@
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
@@ -26846,7 +26587,7 @@
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -26865,7 +26606,7 @@
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.8 / 0/14</t>
+          <t>0 / 1.7 / 0/14</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
@@ -26880,7 +26621,7 @@
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.4 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="I56" s="13" t="inlineStr">
@@ -26954,7 +26695,7 @@
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -27013,7 +26754,7 @@
       <c r="G59" s="14" t="inlineStr"/>
       <c r="H59" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
@@ -27031,17 +26772,17 @@
       <c r="B60" s="13" t="inlineStr"/>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.3 / 0/14</t>
+          <t>2 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>2 / 2.2 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
@@ -27051,17 +26792,17 @@
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>3 / 0.7 / 0/14</t>
+          <t>3 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27079,27 +26820,27 @@
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.2 / 0/14</t>
         </is>
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>9 / 5.9 / 8/14</t>
+          <t>9 / 6.4 / 9/14</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.6 / 2/14</t>
+          <t>6 / 2.8 / 3/14</t>
         </is>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.4 / 0/14</t>
+          <t>2 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr"/>
@@ -27113,7 +26854,7 @@
       <c r="B62" s="13" t="inlineStr"/>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.2 / 0/14</t>
+          <t>2 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
@@ -27124,22 +26865,22 @@
       <c r="E62" s="13" t="inlineStr"/>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>2 / 0.5 / 0/14</t>
+          <t>2 / 0.6 / 0/14</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>9 / 4.4 / 4/14</t>
+          <t>9 / 4.9 / 5/14</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27154,13 +26895,13 @@
       <c r="D63" s="14" t="inlineStr"/>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>9 / 9.4 / 13/14</t>
+          <t>9 / 9.6 / 14/14</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>9 / 6.9 / 10/14</t>
+          <t>9 / 7.2 / 11/14</t>
         </is>
       </c>
       <c r="H63" s="14" t="inlineStr">
@@ -27181,23 +26922,23 @@
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>2 / 3.9 / 0/14</t>
+          <t>2 / 3.8 / 0/14</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>4 / 5.3 / 5/14</t>
+          <t>3 / 5.2 / 5/14</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>12 / 7.7 / 6/14</t>
+          <t>12 / 8.4 / 7/14</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr"/>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27234,7 +26975,7 @@
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.1 / 0/14</t>
+          <t>1 / 0.2 / 0/14</t>
         </is>
       </c>
       <c r="H65" s="14" t="inlineStr">
@@ -27256,7 +26997,7 @@
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.8 / 0/14</t>
+          <t>0 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
@@ -27309,22 +27050,22 @@
       </c>
       <c r="D67" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.6 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.9 / 0/14</t>
+          <t>0 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>6 / 1.7 / 4/14</t>
+          <t>6 / 2.1 / 5/14</t>
         </is>
       </c>
       <c r="H67" s="14" t="inlineStr">
@@ -27346,7 +27087,7 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>2 / 1.9 / 0/14</t>
+          <t>2 / 1.8 / 0/14</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -27361,17 +27102,17 @@
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 0.8 / 0/14</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>1 / 0.3 / 0/14</t>
+          <t>1 / 0.4 / 0/14</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -27393,7 +27134,7 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>11 / 5.7 / 6/14</t>
+          <t>11 / 6.2 / 7/14</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
@@ -27408,7 +27149,7 @@
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.4 / 0/14</t>
+          <t>0 / 0.3 / 0/14</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
@@ -27418,12 +27159,12 @@
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>3 / 0.7 / 0/14</t>
+          <t>3 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.1 / 0/14</t>
+          <t>0 / 0.0 / 0/14</t>
         </is>
       </c>
       <c r="I69" s="14" t="inlineStr">
@@ -27441,17 +27182,17 @@
       <c r="B70" s="13" t="inlineStr"/>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.4 / 0/14</t>
+          <t>1 / 1.5 / 0/14</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>3 / 2.1 / 0/14</t>
+          <t>3 / 2.2 / 0/14</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
@@ -27489,24 +27230,24 @@
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.3 / 1/14</t>
+          <t>3 / 2.8 / 0/14</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>8 / 8.4 / 12/14</t>
+          <t>8 / 8.7 / 13/14</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr"/>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>8 / 4.1 / 4/14</t>
+          <t>8 / 4.5 / 5/14</t>
         </is>
       </c>
       <c r="H71" s="14" t="inlineStr"/>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.1 / 0/14</t>
+          <t>0 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27524,19 +27265,19 @@
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
+          <t>0 / 0.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>1 / 3.0 / 0/14</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="inlineStr">
+        <is>
           <t>0 / 0.1 / 0/14</t>
         </is>
       </c>
-      <c r="E72" s="13" t="inlineStr">
-        <is>
-          <t>1 / 3.2 / 0/14</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="inlineStr">
-        <is>
-          <t>0 / 0.1 / 0/14</t>
-        </is>
-      </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
           <t>1 / 1.8 / 0/14</t>
@@ -27549,7 +27290,7 @@
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.6 / 0/14</t>
+          <t>0 / 0.5 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27567,28 +27308,28 @@
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>1 / 1.8 / 1/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>3 / 2.6 / 0/14</t>
+          <t>3 / 2.7 / 0/14</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>3 / 4.6 / 3/14</t>
+          <t>3 / 4.4 / 2/14</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>8 / 4.9 / 4/14</t>
+          <t>8 / 5.3 / 5/14</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr"/>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>1 / 0.9 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27607,17 +27348,17 @@
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>8 / 3.9 / 2/14</t>
+          <t>8 / 4.2 / 3/14</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
         <is>
-          <t>0 / 3.1 / 0/14</t>
+          <t>0 / 3.0 / 0/14</t>
         </is>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>9 / 4.5 / 4/14</t>
+          <t>9 / 5.1 / 5/14</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
@@ -27627,7 +27368,7 @@
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.0 / 0/14</t>
+          <t>1 / 0.9 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27645,32 +27386,32 @@
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.8 / 0/14</t>
+          <t>1 / 1.6 / 0/14</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>3 / 3.5 / 0/14</t>
+          <t>3 / 3.6 / 0/14</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.5 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>6 / 2.4 / 2/14</t>
+          <t>6 / 2.7 / 3/14</t>
         </is>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
-          <t>2 / 1.2 / 0/14</t>
+          <t>2 / 1.3 / 0/14</t>
         </is>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
-          <t>0 / 0.7 / 0/14</t>
+          <t>0 / 0.6 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27693,12 +27434,12 @@
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.5 / 0/14</t>
+          <t>1 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.2 / 0/14</t>
+          <t>0 / 1.1 / 0/14</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
@@ -27708,12 +27449,12 @@
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>0 / 1.5 / 0/14</t>
+          <t>0 / 1.4 / 0/14</t>
         </is>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>0 / 0.9 / 0/14</t>
+          <t>0 / 0.7 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27726,24 +27467,24 @@
       <c r="B77" s="14" t="inlineStr"/>
       <c r="C77" s="14" t="inlineStr">
         <is>
-          <t>2 / 0.8 / 0/14</t>
+          <t>2 / 0.9 / 0/14</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>2 / 2.1 / 0/14</t>
+          <t>2 / 2.0 / 0/14</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>8 / 6.9 / 9/14</t>
+          <t>8 / 7.4 / 10/14</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr"/>
       <c r="G77" s="14" t="inlineStr"/>
       <c r="H77" s="14" t="inlineStr">
         <is>
-          <t>1 / 3.8 / 4/14</t>
+          <t>1 / 3.7 / 4/14</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
@@ -27762,22 +27503,22 @@
       <c r="C78" s="13" t="inlineStr"/>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>0 / 2.2 / 0/14</t>
+          <t>0 / 1.9 / 0/14</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>1 / 3.2 / 0/14</t>
+          <t>1 / 3.1 / 0/14</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>2 / 4.6 / 4/14</t>
+          <t>2 / 4.4 / 4/14</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>5 / 3.1 / 0/14</t>
+          <t>5 / 3.4 / 0/14</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
@@ -27787,7 +27528,7 @@
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
-          <t>1 / 1.1 / 0/14</t>
+          <t>1 / 1.0 / 0/14</t>
         </is>
       </c>
     </row>
@@ -27802,19 +27543,19 @@
       <c r="D79" s="14" t="inlineStr"/>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>8 / 8.0 / 12/14</t>
+          <t>8 / 8.3 / 13/14</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>7 / 10.4 / 14/14</t>
+          <t>7 / 9.7 / 14/14</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr"/>
       <c r="H79" s="14" t="inlineStr"/>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>0 / 1.4 / 0/14</t>
+          <t>0 / 1.3 / 0/14</t>
         </is>
       </c>
     </row>

--- a/pipeline/reports-daily/daily-region-overview.xlsx
+++ b/pipeline/reports-daily/daily-region-overview.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sitewide'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'JobG8 categories'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAGES'!$A$1:$H$198</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$279</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CITY OPPORTUNITIES'!$A$1:$O$268</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LIVE'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NOT LIVE'!$A$1:$I$79</definedName>
   </definedNames>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1289</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>950</v>
+        <v>959</v>
       </c>
     </row>
     <row r="4">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>339</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1424</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="6">
@@ -648,7 +648,7 @@
         <v>2140</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3">
@@ -739,7 +739,7 @@
         <v>517</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -854,7 +854,7 @@
         <v>10000</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>957</v>
+        <v>959</v>
       </c>
     </row>
   </sheetData>
@@ -943,7 +943,7 @@
       <c r="D2" s="11" t="inlineStr"/>
       <c r="E2" s="11" t="inlineStr"/>
       <c r="F2" s="12" t="n">
-        <v>1497</v>
+        <v>1465</v>
       </c>
       <c r="G2" s="11" t="inlineStr"/>
       <c r="H2" s="11" t="inlineStr">
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="F3" s="12" t="n">
-        <v>1305</v>
+        <v>1273</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>1305</v>
+        <v>1273</v>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>1</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>1</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>1</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>1</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>1</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>1</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>1</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>1</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4893,24 +4893,24 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Cambridgeshire</t>
+          <t>Hampshire</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Customer Service &amp; Contact Centre</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>/job-search/cambridgeshire/service-administrator-jobs</t>
+          <t>/job-search/hampshire/customer-service-jobs</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+          <t>Cambridgeshire</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4941,14 +4941,14 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>/job-search/gloucestershire/service-administrator-jobs</t>
+          <t>/job-search/cambridgeshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -4969,24 +4969,24 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Gloucestershire</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>/job-search/london/support-worker</t>
+          <t>/job-search/gloucestershire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -5007,24 +5007,24 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>/job-search/devon/finance-accounts-jobs</t>
+          <t>/job-search/london/support-worker</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5045,24 +5045,24 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Dorset</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Finance &amp; Accounts</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>/job-search/dorset/service-administrator-jobs</t>
+          <t>/job-search/devon/finance-accounts-jobs</t>
         </is>
       </c>
       <c r="F113" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Dorset</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -5093,14 +5093,14 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>/job-search/devon/service-administrator-jobs</t>
+          <t>/job-search/dorset/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Wiltshire</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -5131,14 +5131,14 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>/job-search/wiltshire/service-administrator-jobs</t>
+          <t>/job-search/devon/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Northamptonshire</t>
+          <t>Wiltshire</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -5169,14 +5169,14 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>/job-search/northamptonshire/service-administrator-jobs</t>
+          <t>/job-search/wiltshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Northamptonshire</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -5207,14 +5207,14 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>/job-search/berkshire/service-administrator-jobs</t>
+          <t>/job-search/northamptonshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F117" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Nottinghamshire</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5245,14 +5245,14 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>/job-search/nottinghamshire/service-administrator-jobs</t>
+          <t>/job-search/berkshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Buckinghamshire</t>
+          <t>Nottinghamshire</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -5283,14 +5283,14 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>/job-search/buckinghamshire/service-administrator-jobs</t>
+          <t>/job-search/nottinghamshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F119" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -5311,24 +5311,24 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Surrey</t>
+          <t>Buckinghamshire</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Support Worker</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>/job-search/surrey/support-worker</t>
+          <t>/job-search/buckinghamshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F120" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5349,24 +5349,24 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Hertfordshire</t>
+          <t>Surrey</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Admin &amp; Customer Service</t>
+          <t>Support Worker</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>/job-search/hertfordshire/service-administrator-jobs</t>
+          <t>/job-search/surrey/support-worker</t>
         </is>
       </c>
       <c r="F121" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Staffordshire</t>
+          <t>Hertfordshire</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -5397,14 +5397,14 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>/job-search/staffordshire/service-administrator-jobs</t>
+          <t>/job-search/hertfordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Norfolk</t>
+          <t>Staffordshire</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -5435,14 +5435,14 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>/job-search/norfolk/service-administrator-jobs</t>
+          <t>/job-search/staffordshire/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F123" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -5463,24 +5463,24 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Yorkshire - West</t>
+          <t>Norfolk</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts</t>
+          <t>Admin &amp; Customer Service</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>/job-search/west-yorkshire/finance-accounts-jobs</t>
+          <t>/job-search/norfolk/service-administrator-jobs</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Gloucestershire</t>
+    